--- a/src/main/resources/templates/summaryReportForm4.xlsx
+++ b/src/main/resources/templates/summaryReportForm4.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21231"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E186E322-90CC-4CBB-8A12-02D8631F2C55}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69D59011-A357-4054-8AF7-98032E1C488B}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2270,297 +2270,6 @@
   </si>
   <si>
     <t>$prod_value388</t>
-  </si>
-  <si>
-    <t>$dist_prd1000_value5_value2</t>
-  </si>
-  <si>
-    <t>$dist_prd_value9_value8</t>
-  </si>
-  <si>
-    <t>$dist_prd_value12_value11</t>
-  </si>
-  <si>
-    <t>$dist_prd_value15_value14</t>
-  </si>
-  <si>
-    <t>$dist_prd_value18_value17</t>
-  </si>
-  <si>
-    <t>$dist_prd_value21_value20</t>
-  </si>
-  <si>
-    <t>$dist_prd_value24_value23</t>
-  </si>
-  <si>
-    <t>$dist_prd_value27_value26</t>
-  </si>
-  <si>
-    <t>$dist_prd_value30_value29</t>
-  </si>
-  <si>
-    <t>$dist_prd_value33_value32</t>
-  </si>
-  <si>
-    <t>$dist_prd_value36_value35</t>
-  </si>
-  <si>
-    <t>$dist_prd_value39_value38</t>
-  </si>
-  <si>
-    <t>$dist_prd_value42_value41</t>
-  </si>
-  <si>
-    <t>$dist_prd_value45_value44</t>
-  </si>
-  <si>
-    <t>$dist_prd_value48_value47</t>
-  </si>
-  <si>
-    <t>$dist_prd_value51_value50</t>
-  </si>
-  <si>
-    <t>$dist_prd_value54_value53</t>
-  </si>
-  <si>
-    <t>$dist_prd_value57_value56</t>
-  </si>
-  <si>
-    <t>$dist_prd_value60_value59</t>
-  </si>
-  <si>
-    <t>$dist_prd_value63_value62</t>
-  </si>
-  <si>
-    <t>$dist_prd_value66_value65</t>
-  </si>
-  <si>
-    <t>$dist_prd_value69_value68</t>
-  </si>
-  <si>
-    <t>$dist_prd_value72_value71</t>
-  </si>
-  <si>
-    <t>$dist_prd_value75_value74</t>
-  </si>
-  <si>
-    <t>$dist_prd_value78_value77</t>
-  </si>
-  <si>
-    <t>$dist_prd_value81_value80</t>
-  </si>
-  <si>
-    <t>$dist_prd_value84_value83</t>
-  </si>
-  <si>
-    <t>$dist_prd_value87_value86</t>
-  </si>
-  <si>
-    <t>$dist_prd_value90_value89</t>
-  </si>
-  <si>
-    <t>$dist_prd_value93_value92</t>
-  </si>
-  <si>
-    <t>$dist_prd_value96_value95</t>
-  </si>
-  <si>
-    <t>$dist_prd_value99_value98</t>
-  </si>
-  <si>
-    <t>$dist_prd_value102_value101</t>
-  </si>
-  <si>
-    <t>$dist_prd_value105_value104</t>
-  </si>
-  <si>
-    <t>$dist_prd_value108_value107</t>
-  </si>
-  <si>
-    <t>$dist_prd_value111_value110</t>
-  </si>
-  <si>
-    <t>$dist_prd_value114_value113</t>
-  </si>
-  <si>
-    <t>$dist_prd_value117_value116</t>
-  </si>
-  <si>
-    <t>$dist_prd_value120_value119</t>
-  </si>
-  <si>
-    <t>$dist_prd_value123_value122</t>
-  </si>
-  <si>
-    <t>$dist_prd_value126_value125</t>
-  </si>
-  <si>
-    <t>$dist_prd_value129_value128</t>
-  </si>
-  <si>
-    <t>$dist_prd_value132_value131</t>
-  </si>
-  <si>
-    <t>$dist_prd_value135_value134</t>
-  </si>
-  <si>
-    <t>$dist_prd_value138_value137</t>
-  </si>
-  <si>
-    <t>$dist_prd_value141_value140</t>
-  </si>
-  <si>
-    <t>$dist_prd_value144_value143</t>
-  </si>
-  <si>
-    <t>$dist_prd_value147_value146</t>
-  </si>
-  <si>
-    <t>$dist_prd_value150_value149</t>
-  </si>
-  <si>
-    <t>$dist_prd_value153_value152</t>
-  </si>
-  <si>
-    <t>$dist_prd_value156_value155</t>
-  </si>
-  <si>
-    <t>$dist_prd_value159_value158</t>
-  </si>
-  <si>
-    <t>$dist_prd_value162_value161</t>
-  </si>
-  <si>
-    <t>$dist_prd_value165_value164</t>
-  </si>
-  <si>
-    <t>$dist_prd_value168_value167</t>
-  </si>
-  <si>
-    <t>$dist_prd_value171_value170</t>
-  </si>
-  <si>
-    <t>$dist_prd_value174_value173</t>
-  </si>
-  <si>
-    <t>$dist_prd_value177_value176</t>
-  </si>
-  <si>
-    <t>$dist_prd_value180_value179</t>
-  </si>
-  <si>
-    <t>$dist_prd_value183_value182</t>
-  </si>
-  <si>
-    <t>$dist_prd_value186_value185</t>
-  </si>
-  <si>
-    <t>$dist_prd_value189_value188</t>
-  </si>
-  <si>
-    <t>$dist_prd_value192_value191</t>
-  </si>
-  <si>
-    <t>$dist_prd_value195_value194</t>
-  </si>
-  <si>
-    <t>$dist_prd_value198_value197</t>
-  </si>
-  <si>
-    <t>$dist_prd_value201_value200</t>
-  </si>
-  <si>
-    <t>$dist_prd_value204_value203</t>
-  </si>
-  <si>
-    <t>$dist_prd_value207_value206</t>
-  </si>
-  <si>
-    <t>$dist_prd_value210_value209</t>
-  </si>
-  <si>
-    <t>$dist_prd_value213_value212</t>
-  </si>
-  <si>
-    <t>$dist_prd_value216_value215</t>
-  </si>
-  <si>
-    <t>$dist_prd_value219_value218</t>
-  </si>
-  <si>
-    <t>$dist_prd_value222_value221</t>
-  </si>
-  <si>
-    <t>$dist_prd_value225_value224</t>
-  </si>
-  <si>
-    <t>$dist_prd_value231_value230</t>
-  </si>
-  <si>
-    <t>$dist_prd_value234_value233</t>
-  </si>
-  <si>
-    <t>$dist_prd_value237_value236</t>
-  </si>
-  <si>
-    <t>$dist_prd_value240_value239</t>
-  </si>
-  <si>
-    <t>$dist_prd_value243_value242</t>
-  </si>
-  <si>
-    <t>$dist_prd_value246_value245</t>
-  </si>
-  <si>
-    <t>$dist_prd_value249_value248</t>
-  </si>
-  <si>
-    <t>$dist_prd_value252_value251</t>
-  </si>
-  <si>
-    <t>$dist_prd_value255_value254</t>
-  </si>
-  <si>
-    <t>$dist_prd_value258_value257</t>
-  </si>
-  <si>
-    <t>$dist_prd_value261_value260</t>
-  </si>
-  <si>
-    <t>$dist_prd_value264_value263</t>
-  </si>
-  <si>
-    <t>$dist_prd_value267_value266</t>
-  </si>
-  <si>
-    <t>$dist_prd_value270_value269</t>
-  </si>
-  <si>
-    <t>$dist_prd_value273_value272</t>
-  </si>
-  <si>
-    <t>$dist_prd_value276_value275</t>
-  </si>
-  <si>
-    <t>$dist_prd_value279_value278</t>
-  </si>
-  <si>
-    <t>$dist_prd_value282_value281</t>
-  </si>
-  <si>
-    <t>$dist_prd_value285_value284</t>
-  </si>
-  <si>
-    <t>$dist_prd_value288_value287</t>
-  </si>
-  <si>
-    <t>$dist_prd_value291_value290</t>
-  </si>
-  <si>
-    <t>$dist_prd_value294_value293</t>
-  </si>
-  <si>
-    <t>$dist_prd_value297_value296</t>
   </si>
   <si>
     <r>
@@ -2736,7 +2445,298 @@
     <t>Внесение минеральных удобрений на</t>
   </si>
   <si>
-    <t>$header_reportDate</t>
+    <t>$dist_pml_value5_value2</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value9_value8</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value12_value11</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value15_value14</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value18_value17</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value21_value20</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value24_value23</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value27_value26</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value30_value29</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value33_value32</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value36_value35</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value39_value38</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value42_value41</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value45_value44</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value48_value47</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value51_value50</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value54_value53</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value57_value56</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value60_value59</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value63_value62</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value66_value65</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value69_value68</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value72_value71</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value75_value74</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value78_value77</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value81_value80</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value84_value83</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value87_value86</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value90_value89</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value93_value92</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value96_value95</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value99_value98</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value102_value101</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value105_value104</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value108_value107</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value111_value110</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value114_value113</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value117_value116</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value120_value119</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value123_value122</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value126_value125</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value129_value128</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value132_value131</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value135_value134</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value138_value137</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value141_value140</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value144_value143</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value147_value146</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value150_value149</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value153_value152</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value156_value155</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value159_value158</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value162_value161</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value165_value164</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value168_value167</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value171_value170</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value174_value173</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value177_value176</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value180_value179</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value183_value182</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value186_value185</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value189_value188</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value192_value191</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value195_value194</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value198_value197</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value201_value200</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value204_value203</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value207_value206</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value210_value209</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value213_value212</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value216_value215</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value219_value218</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value222_value221</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value225_value224</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value231_value230</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value234_value233</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value237_value236</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value240_value239</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value243_value242</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value246_value245</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value249_value248</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value252_value251</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value255_value254</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value258_value257</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value261_value260</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value264_value263</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value267_value266</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value270_value269</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value273_value272</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value276_value275</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value279_value278</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value282_value281</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value285_value284</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value288_value287</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value291_value290</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value294_value293</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value297_value296</t>
+  </si>
+  <si>
+    <t>$cell_reportDate</t>
   </si>
 </sst>
 </file>
@@ -3462,117 +3462,253 @@
     <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3580,6 +3716,9 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -3590,177 +3729,38 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4045,21 +4045,21 @@
   <dimension ref="A1:OF11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" customWidth="1"/>
     <col min="2" max="3" width="30.7109375" customWidth="1"/>
     <col min="4" max="7" width="16.7109375" customWidth="1"/>
-    <col min="8" max="396" width="10.7109375" customWidth="1"/>
+    <col min="8" max="396" width="11.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:396" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="142" t="s">
-        <v>854</v>
-      </c>
-      <c r="B1" s="142"/>
-      <c r="C1" s="142"/>
-      <c r="D1" s="142"/>
-      <c r="E1" s="142"/>
-      <c r="F1" s="142"/>
+      <c r="A1" s="45" t="s">
+        <v>757</v>
+      </c>
+      <c r="B1" s="45"/>
+      <c r="C1" s="45"/>
+      <c r="D1" s="45"/>
+      <c r="E1" s="45"/>
+      <c r="F1" s="45"/>
       <c r="G1" s="44" t="s">
         <v>855</v>
       </c>
@@ -4069,3389 +4069,3390 @@
       <c r="K1" s="43"/>
       <c r="L1" s="41"/>
     </row>
+    <row r="2" spans="1:396" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:396" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="56" t="s">
+      <c r="A3" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="56" t="s">
+      <c r="B3" s="63" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="56" t="s">
+      <c r="C3" s="63" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="56" t="s">
-        <v>847</v>
+      <c r="D3" s="63" t="s">
+        <v>750</v>
       </c>
       <c r="E3" s="4"/>
-      <c r="F3" s="56" t="s">
-        <v>848</v>
+      <c r="F3" s="63" t="s">
+        <v>751</v>
       </c>
       <c r="G3" s="5"/>
-      <c r="H3" s="58" t="s">
-        <v>849</v>
-      </c>
-      <c r="I3" s="59"/>
-      <c r="J3" s="59"/>
-      <c r="K3" s="59"/>
-      <c r="L3" s="60"/>
-      <c r="M3" s="67" t="s">
+      <c r="H3" s="132" t="s">
+        <v>752</v>
+      </c>
+      <c r="I3" s="133"/>
+      <c r="J3" s="133"/>
+      <c r="K3" s="133"/>
+      <c r="L3" s="134"/>
+      <c r="M3" s="125" t="s">
         <v>3</v>
       </c>
-      <c r="N3" s="67"/>
-      <c r="O3" s="67"/>
-      <c r="P3" s="67"/>
-      <c r="Q3" s="67"/>
-      <c r="R3" s="67"/>
-      <c r="S3" s="67"/>
-      <c r="T3" s="67"/>
-      <c r="U3" s="67"/>
-      <c r="V3" s="67"/>
-      <c r="W3" s="67"/>
-      <c r="X3" s="67"/>
-      <c r="Y3" s="67"/>
-      <c r="Z3" s="67"/>
-      <c r="AA3" s="67"/>
-      <c r="AB3" s="67"/>
-      <c r="AC3" s="67"/>
-      <c r="AD3" s="68"/>
-      <c r="AE3" s="68"/>
-      <c r="AF3" s="68"/>
-      <c r="AG3" s="68"/>
-      <c r="AH3" s="68"/>
-      <c r="AI3" s="68"/>
-      <c r="AJ3" s="68"/>
-      <c r="AK3" s="68"/>
-      <c r="AL3" s="68"/>
-      <c r="AM3" s="68"/>
-      <c r="AN3" s="67"/>
-      <c r="AO3" s="67"/>
-      <c r="AP3" s="67"/>
-      <c r="AQ3" s="67"/>
-      <c r="AR3" s="67"/>
+      <c r="N3" s="125"/>
+      <c r="O3" s="125"/>
+      <c r="P3" s="125"/>
+      <c r="Q3" s="125"/>
+      <c r="R3" s="125"/>
+      <c r="S3" s="125"/>
+      <c r="T3" s="125"/>
+      <c r="U3" s="125"/>
+      <c r="V3" s="125"/>
+      <c r="W3" s="125"/>
+      <c r="X3" s="125"/>
+      <c r="Y3" s="125"/>
+      <c r="Z3" s="125"/>
+      <c r="AA3" s="125"/>
+      <c r="AB3" s="125"/>
+      <c r="AC3" s="125"/>
+      <c r="AD3" s="141"/>
+      <c r="AE3" s="141"/>
+      <c r="AF3" s="141"/>
+      <c r="AG3" s="141"/>
+      <c r="AH3" s="141"/>
+      <c r="AI3" s="141"/>
+      <c r="AJ3" s="141"/>
+      <c r="AK3" s="141"/>
+      <c r="AL3" s="141"/>
+      <c r="AM3" s="141"/>
+      <c r="AN3" s="125"/>
+      <c r="AO3" s="125"/>
+      <c r="AP3" s="125"/>
+      <c r="AQ3" s="125"/>
+      <c r="AR3" s="125"/>
       <c r="AS3" s="6"/>
       <c r="AT3" s="6"/>
       <c r="AU3" s="6"/>
       <c r="AV3" s="6"/>
-      <c r="AW3" s="69" t="s">
+      <c r="AW3" s="124" t="s">
         <v>4</v>
       </c>
-      <c r="AX3" s="67"/>
-      <c r="AY3" s="67"/>
-      <c r="AZ3" s="67"/>
-      <c r="BA3" s="67"/>
-      <c r="BB3" s="67"/>
-      <c r="BC3" s="67"/>
-      <c r="BD3" s="67"/>
-      <c r="BE3" s="67"/>
-      <c r="BF3" s="67"/>
-      <c r="BG3" s="67"/>
-      <c r="BH3" s="67"/>
-      <c r="BI3" s="67"/>
-      <c r="BJ3" s="67"/>
-      <c r="BK3" s="67"/>
-      <c r="BL3" s="67"/>
-      <c r="BM3" s="67"/>
-      <c r="BN3" s="67"/>
-      <c r="BO3" s="67"/>
-      <c r="BP3" s="67"/>
-      <c r="BQ3" s="67"/>
-      <c r="BR3" s="67"/>
-      <c r="BS3" s="67"/>
-      <c r="BT3" s="67"/>
-      <c r="BU3" s="67"/>
-      <c r="BV3" s="67"/>
-      <c r="BW3" s="67"/>
-      <c r="BX3" s="67"/>
-      <c r="BY3" s="67"/>
-      <c r="BZ3" s="67"/>
-      <c r="CA3" s="67"/>
-      <c r="CB3" s="67"/>
-      <c r="CC3" s="67"/>
-      <c r="CD3" s="67"/>
-      <c r="CE3" s="67"/>
-      <c r="CF3" s="70"/>
-      <c r="CG3" s="69" t="s">
+      <c r="AX3" s="125"/>
+      <c r="AY3" s="125"/>
+      <c r="AZ3" s="125"/>
+      <c r="BA3" s="125"/>
+      <c r="BB3" s="125"/>
+      <c r="BC3" s="125"/>
+      <c r="BD3" s="125"/>
+      <c r="BE3" s="125"/>
+      <c r="BF3" s="125"/>
+      <c r="BG3" s="125"/>
+      <c r="BH3" s="125"/>
+      <c r="BI3" s="125"/>
+      <c r="BJ3" s="125"/>
+      <c r="BK3" s="125"/>
+      <c r="BL3" s="125"/>
+      <c r="BM3" s="125"/>
+      <c r="BN3" s="125"/>
+      <c r="BO3" s="125"/>
+      <c r="BP3" s="125"/>
+      <c r="BQ3" s="125"/>
+      <c r="BR3" s="125"/>
+      <c r="BS3" s="125"/>
+      <c r="BT3" s="125"/>
+      <c r="BU3" s="125"/>
+      <c r="BV3" s="125"/>
+      <c r="BW3" s="125"/>
+      <c r="BX3" s="125"/>
+      <c r="BY3" s="125"/>
+      <c r="BZ3" s="125"/>
+      <c r="CA3" s="125"/>
+      <c r="CB3" s="125"/>
+      <c r="CC3" s="125"/>
+      <c r="CD3" s="125"/>
+      <c r="CE3" s="125"/>
+      <c r="CF3" s="129"/>
+      <c r="CG3" s="124" t="s">
         <v>5</v>
       </c>
-      <c r="CH3" s="67"/>
-      <c r="CI3" s="67"/>
-      <c r="CJ3" s="67"/>
-      <c r="CK3" s="67"/>
-      <c r="CL3" s="67"/>
-      <c r="CM3" s="67"/>
-      <c r="CN3" s="67"/>
-      <c r="CO3" s="67"/>
-      <c r="CP3" s="67"/>
-      <c r="CQ3" s="67"/>
-      <c r="CR3" s="67"/>
-      <c r="CS3" s="67"/>
-      <c r="CT3" s="67"/>
-      <c r="CU3" s="67"/>
-      <c r="CV3" s="67"/>
-      <c r="CW3" s="67"/>
-      <c r="CX3" s="67"/>
-      <c r="CY3" s="67"/>
-      <c r="CZ3" s="67"/>
-      <c r="DA3" s="67"/>
-      <c r="DB3" s="67"/>
-      <c r="DC3" s="67"/>
-      <c r="DD3" s="67"/>
-      <c r="DE3" s="67"/>
-      <c r="DF3" s="67"/>
-      <c r="DG3" s="67"/>
-      <c r="DH3" s="67"/>
-      <c r="DI3" s="67"/>
-      <c r="DJ3" s="67"/>
-      <c r="DK3" s="67"/>
-      <c r="DL3" s="67"/>
-      <c r="DM3" s="67"/>
-      <c r="DN3" s="67"/>
-      <c r="DO3" s="67"/>
-      <c r="DP3" s="70"/>
-      <c r="DQ3" s="69" t="s">
+      <c r="CH3" s="125"/>
+      <c r="CI3" s="125"/>
+      <c r="CJ3" s="125"/>
+      <c r="CK3" s="125"/>
+      <c r="CL3" s="125"/>
+      <c r="CM3" s="125"/>
+      <c r="CN3" s="125"/>
+      <c r="CO3" s="125"/>
+      <c r="CP3" s="125"/>
+      <c r="CQ3" s="125"/>
+      <c r="CR3" s="125"/>
+      <c r="CS3" s="125"/>
+      <c r="CT3" s="125"/>
+      <c r="CU3" s="125"/>
+      <c r="CV3" s="125"/>
+      <c r="CW3" s="125"/>
+      <c r="CX3" s="125"/>
+      <c r="CY3" s="125"/>
+      <c r="CZ3" s="125"/>
+      <c r="DA3" s="125"/>
+      <c r="DB3" s="125"/>
+      <c r="DC3" s="125"/>
+      <c r="DD3" s="125"/>
+      <c r="DE3" s="125"/>
+      <c r="DF3" s="125"/>
+      <c r="DG3" s="125"/>
+      <c r="DH3" s="125"/>
+      <c r="DI3" s="125"/>
+      <c r="DJ3" s="125"/>
+      <c r="DK3" s="125"/>
+      <c r="DL3" s="125"/>
+      <c r="DM3" s="125"/>
+      <c r="DN3" s="125"/>
+      <c r="DO3" s="125"/>
+      <c r="DP3" s="129"/>
+      <c r="DQ3" s="124" t="s">
         <v>6</v>
       </c>
-      <c r="DR3" s="67"/>
-      <c r="DS3" s="67"/>
-      <c r="DT3" s="67"/>
-      <c r="DU3" s="67"/>
-      <c r="DV3" s="67"/>
-      <c r="DW3" s="67"/>
-      <c r="DX3" s="67"/>
-      <c r="DY3" s="67"/>
-      <c r="DZ3" s="67"/>
-      <c r="EA3" s="67"/>
-      <c r="EB3" s="67"/>
-      <c r="EC3" s="67"/>
-      <c r="ED3" s="67"/>
-      <c r="EE3" s="67"/>
-      <c r="EF3" s="67"/>
-      <c r="EG3" s="67"/>
-      <c r="EH3" s="67"/>
-      <c r="EI3" s="67"/>
-      <c r="EJ3" s="67"/>
-      <c r="EK3" s="67"/>
-      <c r="EL3" s="67"/>
-      <c r="EM3" s="67"/>
-      <c r="EN3" s="67"/>
-      <c r="EO3" s="67"/>
-      <c r="EP3" s="67"/>
-      <c r="EQ3" s="67"/>
-      <c r="ER3" s="67"/>
-      <c r="ES3" s="67"/>
-      <c r="ET3" s="67"/>
-      <c r="EU3" s="67"/>
-      <c r="EV3" s="67"/>
-      <c r="EW3" s="67"/>
-      <c r="EX3" s="67"/>
-      <c r="EY3" s="67"/>
-      <c r="EZ3" s="70"/>
-      <c r="FA3" s="69" t="s">
+      <c r="DR3" s="125"/>
+      <c r="DS3" s="125"/>
+      <c r="DT3" s="125"/>
+      <c r="DU3" s="125"/>
+      <c r="DV3" s="125"/>
+      <c r="DW3" s="125"/>
+      <c r="DX3" s="125"/>
+      <c r="DY3" s="125"/>
+      <c r="DZ3" s="125"/>
+      <c r="EA3" s="125"/>
+      <c r="EB3" s="125"/>
+      <c r="EC3" s="125"/>
+      <c r="ED3" s="125"/>
+      <c r="EE3" s="125"/>
+      <c r="EF3" s="125"/>
+      <c r="EG3" s="125"/>
+      <c r="EH3" s="125"/>
+      <c r="EI3" s="125"/>
+      <c r="EJ3" s="125"/>
+      <c r="EK3" s="125"/>
+      <c r="EL3" s="125"/>
+      <c r="EM3" s="125"/>
+      <c r="EN3" s="125"/>
+      <c r="EO3" s="125"/>
+      <c r="EP3" s="125"/>
+      <c r="EQ3" s="125"/>
+      <c r="ER3" s="125"/>
+      <c r="ES3" s="125"/>
+      <c r="ET3" s="125"/>
+      <c r="EU3" s="125"/>
+      <c r="EV3" s="125"/>
+      <c r="EW3" s="125"/>
+      <c r="EX3" s="125"/>
+      <c r="EY3" s="125"/>
+      <c r="EZ3" s="129"/>
+      <c r="FA3" s="124" t="s">
         <v>7</v>
       </c>
-      <c r="FB3" s="67"/>
-      <c r="FC3" s="67"/>
-      <c r="FD3" s="67"/>
-      <c r="FE3" s="67"/>
-      <c r="FF3" s="67"/>
-      <c r="FG3" s="67"/>
-      <c r="FH3" s="67"/>
-      <c r="FI3" s="67"/>
-      <c r="FJ3" s="67"/>
-      <c r="FK3" s="67"/>
-      <c r="FL3" s="67"/>
-      <c r="FM3" s="67"/>
-      <c r="FN3" s="67"/>
-      <c r="FO3" s="67"/>
-      <c r="FP3" s="67"/>
-      <c r="FQ3" s="67"/>
-      <c r="FR3" s="67"/>
-      <c r="FS3" s="67"/>
-      <c r="FT3" s="67"/>
-      <c r="FU3" s="67"/>
-      <c r="FV3" s="67"/>
-      <c r="FW3" s="67"/>
-      <c r="FX3" s="67"/>
-      <c r="FY3" s="67"/>
-      <c r="FZ3" s="67"/>
-      <c r="GA3" s="67"/>
-      <c r="GB3" s="67"/>
-      <c r="GC3" s="67"/>
-      <c r="GD3" s="67"/>
-      <c r="GE3" s="67"/>
-      <c r="GF3" s="67"/>
-      <c r="GG3" s="67"/>
-      <c r="GH3" s="67"/>
-      <c r="GI3" s="67"/>
-      <c r="GJ3" s="70"/>
-      <c r="GK3" s="69" t="s">
+      <c r="FB3" s="125"/>
+      <c r="FC3" s="125"/>
+      <c r="FD3" s="125"/>
+      <c r="FE3" s="125"/>
+      <c r="FF3" s="125"/>
+      <c r="FG3" s="125"/>
+      <c r="FH3" s="125"/>
+      <c r="FI3" s="125"/>
+      <c r="FJ3" s="125"/>
+      <c r="FK3" s="125"/>
+      <c r="FL3" s="125"/>
+      <c r="FM3" s="125"/>
+      <c r="FN3" s="125"/>
+      <c r="FO3" s="125"/>
+      <c r="FP3" s="125"/>
+      <c r="FQ3" s="125"/>
+      <c r="FR3" s="125"/>
+      <c r="FS3" s="125"/>
+      <c r="FT3" s="125"/>
+      <c r="FU3" s="125"/>
+      <c r="FV3" s="125"/>
+      <c r="FW3" s="125"/>
+      <c r="FX3" s="125"/>
+      <c r="FY3" s="125"/>
+      <c r="FZ3" s="125"/>
+      <c r="GA3" s="125"/>
+      <c r="GB3" s="125"/>
+      <c r="GC3" s="125"/>
+      <c r="GD3" s="125"/>
+      <c r="GE3" s="125"/>
+      <c r="GF3" s="125"/>
+      <c r="GG3" s="125"/>
+      <c r="GH3" s="125"/>
+      <c r="GI3" s="125"/>
+      <c r="GJ3" s="129"/>
+      <c r="GK3" s="124" t="s">
         <v>8</v>
       </c>
-      <c r="GL3" s="67"/>
-      <c r="GM3" s="67"/>
-      <c r="GN3" s="67"/>
-      <c r="GO3" s="67"/>
-      <c r="GP3" s="67"/>
-      <c r="GQ3" s="67"/>
-      <c r="GR3" s="67"/>
-      <c r="GS3" s="67"/>
-      <c r="GT3" s="67"/>
-      <c r="GU3" s="67"/>
-      <c r="GV3" s="67"/>
-      <c r="GW3" s="67"/>
-      <c r="GX3" s="67"/>
-      <c r="GY3" s="67"/>
-      <c r="GZ3" s="67"/>
-      <c r="HA3" s="67"/>
-      <c r="HB3" s="67"/>
-      <c r="HC3" s="67"/>
-      <c r="HD3" s="67"/>
-      <c r="HE3" s="67"/>
-      <c r="HF3" s="67"/>
-      <c r="HG3" s="67"/>
-      <c r="HH3" s="67"/>
-      <c r="HI3" s="67"/>
-      <c r="HJ3" s="67"/>
-      <c r="HK3" s="67"/>
-      <c r="HL3" s="67"/>
-      <c r="HM3" s="67"/>
-      <c r="HN3" s="67"/>
-      <c r="HO3" s="67"/>
-      <c r="HP3" s="67"/>
-      <c r="HQ3" s="67"/>
-      <c r="HR3" s="67"/>
-      <c r="HS3" s="67"/>
-      <c r="HT3" s="70"/>
-      <c r="HU3" s="69" t="s">
+      <c r="GL3" s="125"/>
+      <c r="GM3" s="125"/>
+      <c r="GN3" s="125"/>
+      <c r="GO3" s="125"/>
+      <c r="GP3" s="125"/>
+      <c r="GQ3" s="125"/>
+      <c r="GR3" s="125"/>
+      <c r="GS3" s="125"/>
+      <c r="GT3" s="125"/>
+      <c r="GU3" s="125"/>
+      <c r="GV3" s="125"/>
+      <c r="GW3" s="125"/>
+      <c r="GX3" s="125"/>
+      <c r="GY3" s="125"/>
+      <c r="GZ3" s="125"/>
+      <c r="HA3" s="125"/>
+      <c r="HB3" s="125"/>
+      <c r="HC3" s="125"/>
+      <c r="HD3" s="125"/>
+      <c r="HE3" s="125"/>
+      <c r="HF3" s="125"/>
+      <c r="HG3" s="125"/>
+      <c r="HH3" s="125"/>
+      <c r="HI3" s="125"/>
+      <c r="HJ3" s="125"/>
+      <c r="HK3" s="125"/>
+      <c r="HL3" s="125"/>
+      <c r="HM3" s="125"/>
+      <c r="HN3" s="125"/>
+      <c r="HO3" s="125"/>
+      <c r="HP3" s="125"/>
+      <c r="HQ3" s="125"/>
+      <c r="HR3" s="125"/>
+      <c r="HS3" s="125"/>
+      <c r="HT3" s="129"/>
+      <c r="HU3" s="124" t="s">
         <v>9</v>
       </c>
-      <c r="HV3" s="67"/>
-      <c r="HW3" s="67"/>
-      <c r="HX3" s="67"/>
-      <c r="HY3" s="67"/>
-      <c r="HZ3" s="67"/>
-      <c r="IA3" s="67"/>
-      <c r="IB3" s="67"/>
-      <c r="IC3" s="67"/>
-      <c r="ID3" s="67"/>
-      <c r="IE3" s="67"/>
-      <c r="IF3" s="67"/>
-      <c r="IG3" s="67"/>
-      <c r="IH3" s="67"/>
-      <c r="II3" s="67"/>
-      <c r="IJ3" s="67"/>
-      <c r="IK3" s="67"/>
-      <c r="IL3" s="67"/>
-      <c r="IM3" s="67"/>
-      <c r="IN3" s="67"/>
-      <c r="IO3" s="67"/>
-      <c r="IP3" s="67"/>
-      <c r="IQ3" s="67"/>
-      <c r="IR3" s="67"/>
-      <c r="IS3" s="67"/>
-      <c r="IT3" s="67"/>
-      <c r="IU3" s="67"/>
-      <c r="IV3" s="67"/>
-      <c r="IW3" s="67"/>
-      <c r="IX3" s="67"/>
-      <c r="IY3" s="67"/>
-      <c r="IZ3" s="67"/>
-      <c r="JA3" s="67"/>
-      <c r="JB3" s="67"/>
-      <c r="JC3" s="67"/>
-      <c r="JD3" s="70"/>
-      <c r="JE3" s="69" t="s">
+      <c r="HV3" s="125"/>
+      <c r="HW3" s="125"/>
+      <c r="HX3" s="125"/>
+      <c r="HY3" s="125"/>
+      <c r="HZ3" s="125"/>
+      <c r="IA3" s="125"/>
+      <c r="IB3" s="125"/>
+      <c r="IC3" s="125"/>
+      <c r="ID3" s="125"/>
+      <c r="IE3" s="125"/>
+      <c r="IF3" s="125"/>
+      <c r="IG3" s="125"/>
+      <c r="IH3" s="125"/>
+      <c r="II3" s="125"/>
+      <c r="IJ3" s="125"/>
+      <c r="IK3" s="125"/>
+      <c r="IL3" s="125"/>
+      <c r="IM3" s="125"/>
+      <c r="IN3" s="125"/>
+      <c r="IO3" s="125"/>
+      <c r="IP3" s="125"/>
+      <c r="IQ3" s="125"/>
+      <c r="IR3" s="125"/>
+      <c r="IS3" s="125"/>
+      <c r="IT3" s="125"/>
+      <c r="IU3" s="125"/>
+      <c r="IV3" s="125"/>
+      <c r="IW3" s="125"/>
+      <c r="IX3" s="125"/>
+      <c r="IY3" s="125"/>
+      <c r="IZ3" s="125"/>
+      <c r="JA3" s="125"/>
+      <c r="JB3" s="125"/>
+      <c r="JC3" s="125"/>
+      <c r="JD3" s="129"/>
+      <c r="JE3" s="124" t="s">
         <v>10</v>
       </c>
-      <c r="JF3" s="67"/>
-      <c r="JG3" s="67"/>
-      <c r="JH3" s="67"/>
-      <c r="JI3" s="67"/>
-      <c r="JJ3" s="67"/>
-      <c r="JK3" s="67"/>
-      <c r="JL3" s="67"/>
-      <c r="JM3" s="67"/>
-      <c r="JN3" s="67"/>
-      <c r="JO3" s="67"/>
-      <c r="JP3" s="67"/>
-      <c r="JQ3" s="67"/>
-      <c r="JR3" s="67"/>
-      <c r="JS3" s="67"/>
-      <c r="JT3" s="67"/>
-      <c r="JU3" s="67"/>
-      <c r="JV3" s="67"/>
-      <c r="JW3" s="67"/>
-      <c r="JX3" s="67"/>
-      <c r="JY3" s="67"/>
-      <c r="JZ3" s="67"/>
-      <c r="KA3" s="67"/>
-      <c r="KB3" s="67"/>
-      <c r="KC3" s="67"/>
-      <c r="KD3" s="67"/>
-      <c r="KE3" s="67"/>
-      <c r="KF3" s="67"/>
-      <c r="KG3" s="67"/>
-      <c r="KH3" s="67"/>
-      <c r="KI3" s="67"/>
-      <c r="KJ3" s="67"/>
-      <c r="KK3" s="67"/>
-      <c r="KL3" s="67"/>
-      <c r="KM3" s="67"/>
-      <c r="KN3" s="70"/>
-      <c r="KO3" s="69" t="s">
+      <c r="JF3" s="125"/>
+      <c r="JG3" s="125"/>
+      <c r="JH3" s="125"/>
+      <c r="JI3" s="125"/>
+      <c r="JJ3" s="125"/>
+      <c r="JK3" s="125"/>
+      <c r="JL3" s="125"/>
+      <c r="JM3" s="125"/>
+      <c r="JN3" s="125"/>
+      <c r="JO3" s="125"/>
+      <c r="JP3" s="125"/>
+      <c r="JQ3" s="125"/>
+      <c r="JR3" s="125"/>
+      <c r="JS3" s="125"/>
+      <c r="JT3" s="125"/>
+      <c r="JU3" s="125"/>
+      <c r="JV3" s="125"/>
+      <c r="JW3" s="125"/>
+      <c r="JX3" s="125"/>
+      <c r="JY3" s="125"/>
+      <c r="JZ3" s="125"/>
+      <c r="KA3" s="125"/>
+      <c r="KB3" s="125"/>
+      <c r="KC3" s="125"/>
+      <c r="KD3" s="125"/>
+      <c r="KE3" s="125"/>
+      <c r="KF3" s="125"/>
+      <c r="KG3" s="125"/>
+      <c r="KH3" s="125"/>
+      <c r="KI3" s="125"/>
+      <c r="KJ3" s="125"/>
+      <c r="KK3" s="125"/>
+      <c r="KL3" s="125"/>
+      <c r="KM3" s="125"/>
+      <c r="KN3" s="129"/>
+      <c r="KO3" s="124" t="s">
         <v>11</v>
       </c>
-      <c r="KP3" s="67"/>
-      <c r="KQ3" s="67"/>
-      <c r="KR3" s="67"/>
-      <c r="KS3" s="67"/>
-      <c r="KT3" s="67"/>
-      <c r="KU3" s="67"/>
-      <c r="KV3" s="67"/>
-      <c r="KW3" s="67"/>
-      <c r="KX3" s="67"/>
-      <c r="KY3" s="67"/>
-      <c r="KZ3" s="67"/>
-      <c r="LA3" s="67"/>
-      <c r="LB3" s="67"/>
-      <c r="LC3" s="67"/>
-      <c r="LD3" s="67"/>
-      <c r="LE3" s="67"/>
-      <c r="LF3" s="67"/>
-      <c r="LG3" s="67"/>
-      <c r="LH3" s="67"/>
-      <c r="LI3" s="67"/>
-      <c r="LJ3" s="67"/>
-      <c r="LK3" s="67"/>
-      <c r="LL3" s="67"/>
-      <c r="LM3" s="67"/>
-      <c r="LN3" s="67"/>
-      <c r="LO3" s="67"/>
-      <c r="LP3" s="67"/>
-      <c r="LQ3" s="67"/>
-      <c r="LR3" s="67"/>
-      <c r="LS3" s="67"/>
-      <c r="LT3" s="67"/>
-      <c r="LU3" s="67"/>
-      <c r="LV3" s="67"/>
-      <c r="LW3" s="67"/>
-      <c r="LX3" s="67"/>
-      <c r="LY3" s="67"/>
-      <c r="LZ3" s="67"/>
-      <c r="MA3" s="67"/>
-      <c r="MB3" s="67"/>
-      <c r="MC3" s="67"/>
-      <c r="MD3" s="67"/>
-      <c r="ME3" s="67"/>
-      <c r="MF3" s="67"/>
-      <c r="MG3" s="67"/>
-      <c r="MH3" s="67"/>
-      <c r="MI3" s="67"/>
-      <c r="MJ3" s="82"/>
-      <c r="MK3" s="83" t="s">
+      <c r="KP3" s="125"/>
+      <c r="KQ3" s="125"/>
+      <c r="KR3" s="125"/>
+      <c r="KS3" s="125"/>
+      <c r="KT3" s="125"/>
+      <c r="KU3" s="125"/>
+      <c r="KV3" s="125"/>
+      <c r="KW3" s="125"/>
+      <c r="KX3" s="125"/>
+      <c r="KY3" s="125"/>
+      <c r="KZ3" s="125"/>
+      <c r="LA3" s="125"/>
+      <c r="LB3" s="125"/>
+      <c r="LC3" s="125"/>
+      <c r="LD3" s="125"/>
+      <c r="LE3" s="125"/>
+      <c r="LF3" s="125"/>
+      <c r="LG3" s="125"/>
+      <c r="LH3" s="125"/>
+      <c r="LI3" s="125"/>
+      <c r="LJ3" s="125"/>
+      <c r="LK3" s="125"/>
+      <c r="LL3" s="125"/>
+      <c r="LM3" s="125"/>
+      <c r="LN3" s="125"/>
+      <c r="LO3" s="125"/>
+      <c r="LP3" s="125"/>
+      <c r="LQ3" s="125"/>
+      <c r="LR3" s="125"/>
+      <c r="LS3" s="125"/>
+      <c r="LT3" s="125"/>
+      <c r="LU3" s="125"/>
+      <c r="LV3" s="125"/>
+      <c r="LW3" s="125"/>
+      <c r="LX3" s="125"/>
+      <c r="LY3" s="125"/>
+      <c r="LZ3" s="125"/>
+      <c r="MA3" s="125"/>
+      <c r="MB3" s="125"/>
+      <c r="MC3" s="125"/>
+      <c r="MD3" s="125"/>
+      <c r="ME3" s="125"/>
+      <c r="MF3" s="125"/>
+      <c r="MG3" s="125"/>
+      <c r="MH3" s="125"/>
+      <c r="MI3" s="125"/>
+      <c r="MJ3" s="126"/>
+      <c r="MK3" s="127" t="s">
         <v>11</v>
       </c>
-      <c r="ML3" s="67"/>
-      <c r="MM3" s="67"/>
-      <c r="MN3" s="67"/>
-      <c r="MO3" s="67"/>
-      <c r="MP3" s="67"/>
-      <c r="MQ3" s="67"/>
-      <c r="MR3" s="67"/>
-      <c r="MS3" s="67"/>
-      <c r="MT3" s="67"/>
-      <c r="MU3" s="67"/>
-      <c r="MV3" s="67"/>
-      <c r="MW3" s="67"/>
-      <c r="MX3" s="67"/>
-      <c r="MY3" s="67"/>
-      <c r="MZ3" s="67"/>
-      <c r="NA3" s="67"/>
-      <c r="NB3" s="67"/>
-      <c r="NC3" s="67"/>
-      <c r="ND3" s="67"/>
-      <c r="NE3" s="67"/>
-      <c r="NF3" s="67"/>
-      <c r="NG3" s="67"/>
-      <c r="NH3" s="67"/>
-      <c r="NI3" s="84" t="s">
+      <c r="ML3" s="125"/>
+      <c r="MM3" s="125"/>
+      <c r="MN3" s="125"/>
+      <c r="MO3" s="125"/>
+      <c r="MP3" s="125"/>
+      <c r="MQ3" s="125"/>
+      <c r="MR3" s="125"/>
+      <c r="MS3" s="125"/>
+      <c r="MT3" s="125"/>
+      <c r="MU3" s="125"/>
+      <c r="MV3" s="125"/>
+      <c r="MW3" s="125"/>
+      <c r="MX3" s="125"/>
+      <c r="MY3" s="125"/>
+      <c r="MZ3" s="125"/>
+      <c r="NA3" s="125"/>
+      <c r="NB3" s="125"/>
+      <c r="NC3" s="125"/>
+      <c r="ND3" s="125"/>
+      <c r="NE3" s="125"/>
+      <c r="NF3" s="125"/>
+      <c r="NG3" s="125"/>
+      <c r="NH3" s="125"/>
+      <c r="NI3" s="128" t="s">
         <v>12</v>
       </c>
-      <c r="NJ3" s="67"/>
-      <c r="NK3" s="67"/>
-      <c r="NL3" s="67"/>
-      <c r="NM3" s="67"/>
-      <c r="NN3" s="67"/>
-      <c r="NO3" s="67"/>
-      <c r="NP3" s="67"/>
-      <c r="NQ3" s="67"/>
-      <c r="NR3" s="67"/>
-      <c r="NS3" s="67"/>
-      <c r="NT3" s="67"/>
-      <c r="NU3" s="67"/>
-      <c r="NV3" s="67"/>
-      <c r="NW3" s="67"/>
-      <c r="NX3" s="67"/>
-      <c r="NY3" s="67"/>
-      <c r="NZ3" s="70"/>
-      <c r="OA3" s="85" t="s">
+      <c r="NJ3" s="125"/>
+      <c r="NK3" s="125"/>
+      <c r="NL3" s="125"/>
+      <c r="NM3" s="125"/>
+      <c r="NN3" s="125"/>
+      <c r="NO3" s="125"/>
+      <c r="NP3" s="125"/>
+      <c r="NQ3" s="125"/>
+      <c r="NR3" s="125"/>
+      <c r="NS3" s="125"/>
+      <c r="NT3" s="125"/>
+      <c r="NU3" s="125"/>
+      <c r="NV3" s="125"/>
+      <c r="NW3" s="125"/>
+      <c r="NX3" s="125"/>
+      <c r="NY3" s="125"/>
+      <c r="NZ3" s="129"/>
+      <c r="OA3" s="130" t="s">
         <v>13</v>
       </c>
-      <c r="OB3" s="86"/>
-      <c r="OC3" s="86"/>
-      <c r="OD3" s="86"/>
-      <c r="OE3" s="86"/>
-      <c r="OF3" s="86"/>
+      <c r="OB3" s="131"/>
+      <c r="OC3" s="131"/>
+      <c r="OD3" s="131"/>
+      <c r="OE3" s="131"/>
+      <c r="OF3" s="131"/>
     </row>
     <row r="4" spans="1:396" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="57"/>
-      <c r="B4" s="57"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
+      <c r="A4" s="64"/>
+      <c r="B4" s="64"/>
+      <c r="C4" s="64"/>
+      <c r="D4" s="64"/>
       <c r="E4" s="7"/>
-      <c r="F4" s="57"/>
+      <c r="F4" s="64"/>
       <c r="G4" s="8"/>
-      <c r="H4" s="61"/>
-      <c r="I4" s="62"/>
-      <c r="J4" s="62"/>
-      <c r="K4" s="62"/>
-      <c r="L4" s="63"/>
-      <c r="M4" s="87" t="s">
+      <c r="H4" s="135"/>
+      <c r="I4" s="136"/>
+      <c r="J4" s="136"/>
+      <c r="K4" s="136"/>
+      <c r="L4" s="137"/>
+      <c r="M4" s="91" t="s">
         <v>14</v>
       </c>
-      <c r="N4" s="88"/>
-      <c r="O4" s="88"/>
-      <c r="P4" s="88"/>
-      <c r="Q4" s="88"/>
-      <c r="R4" s="89"/>
-      <c r="S4" s="93" t="s">
+      <c r="N4" s="92"/>
+      <c r="O4" s="92"/>
+      <c r="P4" s="92"/>
+      <c r="Q4" s="92"/>
+      <c r="R4" s="93"/>
+      <c r="S4" s="97" t="s">
         <v>15</v>
       </c>
-      <c r="T4" s="93"/>
-      <c r="U4" s="93"/>
-      <c r="V4" s="93"/>
-      <c r="W4" s="93"/>
-      <c r="X4" s="93"/>
-      <c r="Y4" s="94" t="s">
+      <c r="T4" s="97"/>
+      <c r="U4" s="97"/>
+      <c r="V4" s="97"/>
+      <c r="W4" s="97"/>
+      <c r="X4" s="97"/>
+      <c r="Y4" s="79" t="s">
         <v>16</v>
       </c>
-      <c r="Z4" s="95"/>
-      <c r="AA4" s="96"/>
-      <c r="AB4" s="94" t="s">
+      <c r="Z4" s="80"/>
+      <c r="AA4" s="81"/>
+      <c r="AB4" s="79" t="s">
         <v>17</v>
       </c>
-      <c r="AC4" s="95"/>
-      <c r="AD4" s="96"/>
-      <c r="AE4" s="103" t="s">
+      <c r="AC4" s="80"/>
+      <c r="AD4" s="81"/>
+      <c r="AE4" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="AF4" s="103"/>
-      <c r="AG4" s="103"/>
-      <c r="AH4" s="103"/>
-      <c r="AI4" s="103"/>
-      <c r="AJ4" s="103"/>
-      <c r="AK4" s="103"/>
-      <c r="AL4" s="103"/>
-      <c r="AM4" s="103"/>
-      <c r="AN4" s="103" t="s">
+      <c r="AF4" s="88"/>
+      <c r="AG4" s="88"/>
+      <c r="AH4" s="88"/>
+      <c r="AI4" s="88"/>
+      <c r="AJ4" s="88"/>
+      <c r="AK4" s="88"/>
+      <c r="AL4" s="88"/>
+      <c r="AM4" s="88"/>
+      <c r="AN4" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="AO4" s="103"/>
-      <c r="AP4" s="103"/>
-      <c r="AQ4" s="103"/>
-      <c r="AR4" s="103"/>
-      <c r="AS4" s="103"/>
-      <c r="AT4" s="94" t="s">
+      <c r="AO4" s="88"/>
+      <c r="AP4" s="88"/>
+      <c r="AQ4" s="88"/>
+      <c r="AR4" s="88"/>
+      <c r="AS4" s="88"/>
+      <c r="AT4" s="79" t="s">
         <v>20</v>
       </c>
-      <c r="AU4" s="95"/>
-      <c r="AV4" s="104"/>
-      <c r="AW4" s="87" t="s">
+      <c r="AU4" s="80"/>
+      <c r="AV4" s="98"/>
+      <c r="AW4" s="91" t="s">
         <v>14</v>
       </c>
-      <c r="AX4" s="88"/>
-      <c r="AY4" s="88"/>
-      <c r="AZ4" s="88"/>
-      <c r="BA4" s="88"/>
-      <c r="BB4" s="89"/>
-      <c r="BC4" s="93" t="s">
+      <c r="AX4" s="92"/>
+      <c r="AY4" s="92"/>
+      <c r="AZ4" s="92"/>
+      <c r="BA4" s="92"/>
+      <c r="BB4" s="93"/>
+      <c r="BC4" s="97" t="s">
         <v>15</v>
       </c>
-      <c r="BD4" s="93"/>
-      <c r="BE4" s="93"/>
-      <c r="BF4" s="93"/>
-      <c r="BG4" s="93"/>
-      <c r="BH4" s="93"/>
-      <c r="BI4" s="94" t="s">
+      <c r="BD4" s="97"/>
+      <c r="BE4" s="97"/>
+      <c r="BF4" s="97"/>
+      <c r="BG4" s="97"/>
+      <c r="BH4" s="97"/>
+      <c r="BI4" s="79" t="s">
         <v>16</v>
       </c>
-      <c r="BJ4" s="95"/>
-      <c r="BK4" s="96"/>
-      <c r="BL4" s="94" t="s">
+      <c r="BJ4" s="80"/>
+      <c r="BK4" s="81"/>
+      <c r="BL4" s="79" t="s">
         <v>17</v>
       </c>
-      <c r="BM4" s="95"/>
-      <c r="BN4" s="96"/>
-      <c r="BO4" s="103" t="s">
+      <c r="BM4" s="80"/>
+      <c r="BN4" s="81"/>
+      <c r="BO4" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="BP4" s="103"/>
-      <c r="BQ4" s="103"/>
-      <c r="BR4" s="103"/>
-      <c r="BS4" s="103"/>
-      <c r="BT4" s="103"/>
-      <c r="BU4" s="103"/>
-      <c r="BV4" s="103"/>
-      <c r="BW4" s="103"/>
-      <c r="BX4" s="103" t="s">
+      <c r="BP4" s="88"/>
+      <c r="BQ4" s="88"/>
+      <c r="BR4" s="88"/>
+      <c r="BS4" s="88"/>
+      <c r="BT4" s="88"/>
+      <c r="BU4" s="88"/>
+      <c r="BV4" s="88"/>
+      <c r="BW4" s="88"/>
+      <c r="BX4" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="BY4" s="103"/>
-      <c r="BZ4" s="103"/>
-      <c r="CA4" s="103"/>
-      <c r="CB4" s="103"/>
-      <c r="CC4" s="103"/>
-      <c r="CD4" s="94" t="s">
+      <c r="BY4" s="88"/>
+      <c r="BZ4" s="88"/>
+      <c r="CA4" s="88"/>
+      <c r="CB4" s="88"/>
+      <c r="CC4" s="88"/>
+      <c r="CD4" s="79" t="s">
         <v>64</v>
       </c>
-      <c r="CE4" s="95"/>
-      <c r="CF4" s="104"/>
-      <c r="CG4" s="87" t="s">
+      <c r="CE4" s="80"/>
+      <c r="CF4" s="98"/>
+      <c r="CG4" s="91" t="s">
         <v>14</v>
       </c>
-      <c r="CH4" s="88"/>
-      <c r="CI4" s="88"/>
-      <c r="CJ4" s="88"/>
-      <c r="CK4" s="88"/>
-      <c r="CL4" s="89"/>
-      <c r="CM4" s="93" t="s">
+      <c r="CH4" s="92"/>
+      <c r="CI4" s="92"/>
+      <c r="CJ4" s="92"/>
+      <c r="CK4" s="92"/>
+      <c r="CL4" s="93"/>
+      <c r="CM4" s="97" t="s">
         <v>15</v>
       </c>
-      <c r="CN4" s="93"/>
-      <c r="CO4" s="93"/>
-      <c r="CP4" s="93"/>
-      <c r="CQ4" s="93"/>
-      <c r="CR4" s="93"/>
-      <c r="CS4" s="94" t="s">
+      <c r="CN4" s="97"/>
+      <c r="CO4" s="97"/>
+      <c r="CP4" s="97"/>
+      <c r="CQ4" s="97"/>
+      <c r="CR4" s="97"/>
+      <c r="CS4" s="79" t="s">
         <v>16</v>
       </c>
-      <c r="CT4" s="95"/>
-      <c r="CU4" s="96"/>
-      <c r="CV4" s="94" t="s">
+      <c r="CT4" s="80"/>
+      <c r="CU4" s="81"/>
+      <c r="CV4" s="79" t="s">
         <v>17</v>
       </c>
-      <c r="CW4" s="95"/>
-      <c r="CX4" s="96"/>
-      <c r="CY4" s="103" t="s">
+      <c r="CW4" s="80"/>
+      <c r="CX4" s="81"/>
+      <c r="CY4" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="CZ4" s="103"/>
-      <c r="DA4" s="103"/>
-      <c r="DB4" s="103"/>
-      <c r="DC4" s="103"/>
-      <c r="DD4" s="103"/>
-      <c r="DE4" s="103"/>
-      <c r="DF4" s="103"/>
-      <c r="DG4" s="103"/>
-      <c r="DH4" s="103" t="s">
+      <c r="CZ4" s="88"/>
+      <c r="DA4" s="88"/>
+      <c r="DB4" s="88"/>
+      <c r="DC4" s="88"/>
+      <c r="DD4" s="88"/>
+      <c r="DE4" s="88"/>
+      <c r="DF4" s="88"/>
+      <c r="DG4" s="88"/>
+      <c r="DH4" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="DI4" s="103"/>
-      <c r="DJ4" s="103"/>
-      <c r="DK4" s="103"/>
-      <c r="DL4" s="103"/>
-      <c r="DM4" s="103"/>
-      <c r="DN4" s="94" t="s">
+      <c r="DI4" s="88"/>
+      <c r="DJ4" s="88"/>
+      <c r="DK4" s="88"/>
+      <c r="DL4" s="88"/>
+      <c r="DM4" s="88"/>
+      <c r="DN4" s="79" t="s">
         <v>65</v>
       </c>
-      <c r="DO4" s="95"/>
-      <c r="DP4" s="104"/>
-      <c r="DQ4" s="87" t="s">
+      <c r="DO4" s="80"/>
+      <c r="DP4" s="98"/>
+      <c r="DQ4" s="91" t="s">
         <v>14</v>
       </c>
-      <c r="DR4" s="88"/>
-      <c r="DS4" s="88"/>
-      <c r="DT4" s="88"/>
-      <c r="DU4" s="88"/>
-      <c r="DV4" s="89"/>
-      <c r="DW4" s="93" t="s">
+      <c r="DR4" s="92"/>
+      <c r="DS4" s="92"/>
+      <c r="DT4" s="92"/>
+      <c r="DU4" s="92"/>
+      <c r="DV4" s="93"/>
+      <c r="DW4" s="97" t="s">
         <v>15</v>
       </c>
-      <c r="DX4" s="93"/>
-      <c r="DY4" s="93"/>
-      <c r="DZ4" s="93"/>
-      <c r="EA4" s="93"/>
-      <c r="EB4" s="93"/>
-      <c r="EC4" s="94" t="s">
+      <c r="DX4" s="97"/>
+      <c r="DY4" s="97"/>
+      <c r="DZ4" s="97"/>
+      <c r="EA4" s="97"/>
+      <c r="EB4" s="97"/>
+      <c r="EC4" s="79" t="s">
         <v>16</v>
       </c>
-      <c r="ED4" s="95"/>
-      <c r="EE4" s="96"/>
-      <c r="EF4" s="94" t="s">
+      <c r="ED4" s="80"/>
+      <c r="EE4" s="81"/>
+      <c r="EF4" s="79" t="s">
         <v>17</v>
       </c>
-      <c r="EG4" s="95"/>
-      <c r="EH4" s="96"/>
-      <c r="EI4" s="103" t="s">
+      <c r="EG4" s="80"/>
+      <c r="EH4" s="81"/>
+      <c r="EI4" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="EJ4" s="103"/>
-      <c r="EK4" s="103"/>
-      <c r="EL4" s="103"/>
-      <c r="EM4" s="103"/>
-      <c r="EN4" s="103"/>
-      <c r="EO4" s="103"/>
-      <c r="EP4" s="103"/>
-      <c r="EQ4" s="103"/>
-      <c r="ER4" s="103" t="s">
+      <c r="EJ4" s="88"/>
+      <c r="EK4" s="88"/>
+      <c r="EL4" s="88"/>
+      <c r="EM4" s="88"/>
+      <c r="EN4" s="88"/>
+      <c r="EO4" s="88"/>
+      <c r="EP4" s="88"/>
+      <c r="EQ4" s="88"/>
+      <c r="ER4" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="ES4" s="103"/>
-      <c r="ET4" s="103"/>
-      <c r="EU4" s="103"/>
-      <c r="EV4" s="103"/>
-      <c r="EW4" s="103"/>
-      <c r="EX4" s="94" t="s">
+      <c r="ES4" s="88"/>
+      <c r="ET4" s="88"/>
+      <c r="EU4" s="88"/>
+      <c r="EV4" s="88"/>
+      <c r="EW4" s="88"/>
+      <c r="EX4" s="79" t="s">
         <v>66</v>
       </c>
-      <c r="EY4" s="95"/>
-      <c r="EZ4" s="104"/>
-      <c r="FA4" s="87" t="s">
+      <c r="EY4" s="80"/>
+      <c r="EZ4" s="98"/>
+      <c r="FA4" s="91" t="s">
         <v>14</v>
       </c>
-      <c r="FB4" s="88"/>
-      <c r="FC4" s="88"/>
-      <c r="FD4" s="88"/>
-      <c r="FE4" s="88"/>
-      <c r="FF4" s="89"/>
-      <c r="FG4" s="93" t="s">
+      <c r="FB4" s="92"/>
+      <c r="FC4" s="92"/>
+      <c r="FD4" s="92"/>
+      <c r="FE4" s="92"/>
+      <c r="FF4" s="93"/>
+      <c r="FG4" s="97" t="s">
         <v>15</v>
       </c>
-      <c r="FH4" s="93"/>
-      <c r="FI4" s="93"/>
-      <c r="FJ4" s="93"/>
-      <c r="FK4" s="93"/>
-      <c r="FL4" s="93"/>
-      <c r="FM4" s="94" t="s">
+      <c r="FH4" s="97"/>
+      <c r="FI4" s="97"/>
+      <c r="FJ4" s="97"/>
+      <c r="FK4" s="97"/>
+      <c r="FL4" s="97"/>
+      <c r="FM4" s="79" t="s">
         <v>16</v>
       </c>
-      <c r="FN4" s="95"/>
-      <c r="FO4" s="96"/>
-      <c r="FP4" s="94" t="s">
+      <c r="FN4" s="80"/>
+      <c r="FO4" s="81"/>
+      <c r="FP4" s="79" t="s">
         <v>17</v>
       </c>
-      <c r="FQ4" s="95"/>
-      <c r="FR4" s="96"/>
-      <c r="FS4" s="103" t="s">
+      <c r="FQ4" s="80"/>
+      <c r="FR4" s="81"/>
+      <c r="FS4" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="FT4" s="103"/>
-      <c r="FU4" s="103"/>
-      <c r="FV4" s="103"/>
-      <c r="FW4" s="103"/>
-      <c r="FX4" s="103"/>
-      <c r="FY4" s="103"/>
-      <c r="FZ4" s="103"/>
-      <c r="GA4" s="103"/>
-      <c r="GB4" s="103" t="s">
+      <c r="FT4" s="88"/>
+      <c r="FU4" s="88"/>
+      <c r="FV4" s="88"/>
+      <c r="FW4" s="88"/>
+      <c r="FX4" s="88"/>
+      <c r="FY4" s="88"/>
+      <c r="FZ4" s="88"/>
+      <c r="GA4" s="88"/>
+      <c r="GB4" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="GC4" s="103"/>
-      <c r="GD4" s="103"/>
-      <c r="GE4" s="103"/>
-      <c r="GF4" s="103"/>
-      <c r="GG4" s="103"/>
-      <c r="GH4" s="94" t="s">
+      <c r="GC4" s="88"/>
+      <c r="GD4" s="88"/>
+      <c r="GE4" s="88"/>
+      <c r="GF4" s="88"/>
+      <c r="GG4" s="88"/>
+      <c r="GH4" s="79" t="s">
         <v>67</v>
       </c>
-      <c r="GI4" s="95"/>
-      <c r="GJ4" s="104"/>
-      <c r="GK4" s="87" t="s">
+      <c r="GI4" s="80"/>
+      <c r="GJ4" s="98"/>
+      <c r="GK4" s="91" t="s">
         <v>14</v>
       </c>
-      <c r="GL4" s="88"/>
-      <c r="GM4" s="88"/>
-      <c r="GN4" s="88"/>
-      <c r="GO4" s="88"/>
-      <c r="GP4" s="89"/>
-      <c r="GQ4" s="93" t="s">
+      <c r="GL4" s="92"/>
+      <c r="GM4" s="92"/>
+      <c r="GN4" s="92"/>
+      <c r="GO4" s="92"/>
+      <c r="GP4" s="93"/>
+      <c r="GQ4" s="97" t="s">
         <v>15</v>
       </c>
-      <c r="GR4" s="93"/>
-      <c r="GS4" s="93"/>
-      <c r="GT4" s="93"/>
-      <c r="GU4" s="93"/>
-      <c r="GV4" s="93"/>
-      <c r="GW4" s="94" t="s">
+      <c r="GR4" s="97"/>
+      <c r="GS4" s="97"/>
+      <c r="GT4" s="97"/>
+      <c r="GU4" s="97"/>
+      <c r="GV4" s="97"/>
+      <c r="GW4" s="79" t="s">
         <v>16</v>
       </c>
-      <c r="GX4" s="95"/>
-      <c r="GY4" s="96"/>
-      <c r="GZ4" s="94" t="s">
+      <c r="GX4" s="80"/>
+      <c r="GY4" s="81"/>
+      <c r="GZ4" s="79" t="s">
         <v>17</v>
       </c>
-      <c r="HA4" s="95"/>
-      <c r="HB4" s="96"/>
-      <c r="HC4" s="103" t="s">
+      <c r="HA4" s="80"/>
+      <c r="HB4" s="81"/>
+      <c r="HC4" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="HD4" s="103"/>
-      <c r="HE4" s="103"/>
-      <c r="HF4" s="103"/>
-      <c r="HG4" s="103"/>
-      <c r="HH4" s="103"/>
-      <c r="HI4" s="103"/>
-      <c r="HJ4" s="103"/>
-      <c r="HK4" s="103"/>
-      <c r="HL4" s="103" t="s">
+      <c r="HD4" s="88"/>
+      <c r="HE4" s="88"/>
+      <c r="HF4" s="88"/>
+      <c r="HG4" s="88"/>
+      <c r="HH4" s="88"/>
+      <c r="HI4" s="88"/>
+      <c r="HJ4" s="88"/>
+      <c r="HK4" s="88"/>
+      <c r="HL4" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="HM4" s="103"/>
-      <c r="HN4" s="103"/>
-      <c r="HO4" s="103"/>
-      <c r="HP4" s="103"/>
-      <c r="HQ4" s="103"/>
-      <c r="HR4" s="94" t="s">
+      <c r="HM4" s="88"/>
+      <c r="HN4" s="88"/>
+      <c r="HO4" s="88"/>
+      <c r="HP4" s="88"/>
+      <c r="HQ4" s="88"/>
+      <c r="HR4" s="79" t="s">
         <v>68</v>
       </c>
-      <c r="HS4" s="95"/>
-      <c r="HT4" s="104"/>
-      <c r="HU4" s="87" t="s">
+      <c r="HS4" s="80"/>
+      <c r="HT4" s="98"/>
+      <c r="HU4" s="91" t="s">
         <v>14</v>
       </c>
-      <c r="HV4" s="88"/>
-      <c r="HW4" s="88"/>
-      <c r="HX4" s="88"/>
-      <c r="HY4" s="88"/>
-      <c r="HZ4" s="89"/>
-      <c r="IA4" s="93" t="s">
+      <c r="HV4" s="92"/>
+      <c r="HW4" s="92"/>
+      <c r="HX4" s="92"/>
+      <c r="HY4" s="92"/>
+      <c r="HZ4" s="93"/>
+      <c r="IA4" s="97" t="s">
         <v>15</v>
       </c>
-      <c r="IB4" s="93"/>
-      <c r="IC4" s="93"/>
-      <c r="ID4" s="93"/>
-      <c r="IE4" s="93"/>
-      <c r="IF4" s="93"/>
-      <c r="IG4" s="94" t="s">
+      <c r="IB4" s="97"/>
+      <c r="IC4" s="97"/>
+      <c r="ID4" s="97"/>
+      <c r="IE4" s="97"/>
+      <c r="IF4" s="97"/>
+      <c r="IG4" s="79" t="s">
         <v>16</v>
       </c>
-      <c r="IH4" s="95"/>
-      <c r="II4" s="96"/>
-      <c r="IJ4" s="94" t="s">
+      <c r="IH4" s="80"/>
+      <c r="II4" s="81"/>
+      <c r="IJ4" s="79" t="s">
         <v>17</v>
       </c>
-      <c r="IK4" s="95"/>
-      <c r="IL4" s="96"/>
-      <c r="IM4" s="103" t="s">
+      <c r="IK4" s="80"/>
+      <c r="IL4" s="81"/>
+      <c r="IM4" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="IN4" s="103"/>
-      <c r="IO4" s="103"/>
-      <c r="IP4" s="103"/>
-      <c r="IQ4" s="103"/>
-      <c r="IR4" s="103"/>
-      <c r="IS4" s="103"/>
-      <c r="IT4" s="103"/>
-      <c r="IU4" s="103"/>
-      <c r="IV4" s="103" t="s">
+      <c r="IN4" s="88"/>
+      <c r="IO4" s="88"/>
+      <c r="IP4" s="88"/>
+      <c r="IQ4" s="88"/>
+      <c r="IR4" s="88"/>
+      <c r="IS4" s="88"/>
+      <c r="IT4" s="88"/>
+      <c r="IU4" s="88"/>
+      <c r="IV4" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="IW4" s="103"/>
-      <c r="IX4" s="103"/>
-      <c r="IY4" s="103"/>
-      <c r="IZ4" s="103"/>
-      <c r="JA4" s="103"/>
-      <c r="JB4" s="94" t="s">
+      <c r="IW4" s="88"/>
+      <c r="IX4" s="88"/>
+      <c r="IY4" s="88"/>
+      <c r="IZ4" s="88"/>
+      <c r="JA4" s="88"/>
+      <c r="JB4" s="79" t="s">
         <v>69</v>
       </c>
-      <c r="JC4" s="95"/>
-      <c r="JD4" s="104"/>
-      <c r="JE4" s="87" t="s">
+      <c r="JC4" s="80"/>
+      <c r="JD4" s="98"/>
+      <c r="JE4" s="91" t="s">
         <v>14</v>
       </c>
-      <c r="JF4" s="88"/>
-      <c r="JG4" s="88"/>
-      <c r="JH4" s="88"/>
-      <c r="JI4" s="88"/>
-      <c r="JJ4" s="89"/>
-      <c r="JK4" s="93" t="s">
+      <c r="JF4" s="92"/>
+      <c r="JG4" s="92"/>
+      <c r="JH4" s="92"/>
+      <c r="JI4" s="92"/>
+      <c r="JJ4" s="93"/>
+      <c r="JK4" s="97" t="s">
         <v>15</v>
       </c>
-      <c r="JL4" s="93"/>
-      <c r="JM4" s="93"/>
-      <c r="JN4" s="93"/>
-      <c r="JO4" s="93"/>
-      <c r="JP4" s="93"/>
-      <c r="JQ4" s="94" t="s">
+      <c r="JL4" s="97"/>
+      <c r="JM4" s="97"/>
+      <c r="JN4" s="97"/>
+      <c r="JO4" s="97"/>
+      <c r="JP4" s="97"/>
+      <c r="JQ4" s="79" t="s">
         <v>16</v>
       </c>
-      <c r="JR4" s="95"/>
-      <c r="JS4" s="96"/>
-      <c r="JT4" s="94" t="s">
+      <c r="JR4" s="80"/>
+      <c r="JS4" s="81"/>
+      <c r="JT4" s="79" t="s">
         <v>17</v>
       </c>
-      <c r="JU4" s="95"/>
-      <c r="JV4" s="96"/>
-      <c r="JW4" s="103" t="s">
+      <c r="JU4" s="80"/>
+      <c r="JV4" s="81"/>
+      <c r="JW4" s="88" t="s">
         <v>18</v>
       </c>
-      <c r="JX4" s="103"/>
-      <c r="JY4" s="103"/>
-      <c r="JZ4" s="103"/>
-      <c r="KA4" s="103"/>
-      <c r="KB4" s="103"/>
-      <c r="KC4" s="103"/>
-      <c r="KD4" s="103"/>
-      <c r="KE4" s="103"/>
-      <c r="KF4" s="103" t="s">
+      <c r="JX4" s="88"/>
+      <c r="JY4" s="88"/>
+      <c r="JZ4" s="88"/>
+      <c r="KA4" s="88"/>
+      <c r="KB4" s="88"/>
+      <c r="KC4" s="88"/>
+      <c r="KD4" s="88"/>
+      <c r="KE4" s="88"/>
+      <c r="KF4" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="KG4" s="103"/>
-      <c r="KH4" s="103"/>
-      <c r="KI4" s="103"/>
-      <c r="KJ4" s="103"/>
-      <c r="KK4" s="103"/>
-      <c r="KL4" s="94" t="s">
+      <c r="KG4" s="88"/>
+      <c r="KH4" s="88"/>
+      <c r="KI4" s="88"/>
+      <c r="KJ4" s="88"/>
+      <c r="KK4" s="88"/>
+      <c r="KL4" s="79" t="s">
         <v>70</v>
       </c>
-      <c r="KM4" s="95"/>
-      <c r="KN4" s="104"/>
-      <c r="KO4" s="112" t="s">
+      <c r="KM4" s="80"/>
+      <c r="KN4" s="98"/>
+      <c r="KO4" s="110" t="s">
         <v>21</v>
       </c>
-      <c r="KP4" s="113"/>
-      <c r="KQ4" s="113"/>
-      <c r="KR4" s="113"/>
-      <c r="KS4" s="113"/>
-      <c r="KT4" s="113"/>
-      <c r="KU4" s="113"/>
-      <c r="KV4" s="113"/>
-      <c r="KW4" s="113"/>
-      <c r="KX4" s="113"/>
-      <c r="KY4" s="113"/>
-      <c r="KZ4" s="113"/>
-      <c r="LA4" s="113"/>
-      <c r="LB4" s="113"/>
-      <c r="LC4" s="113"/>
-      <c r="LD4" s="113"/>
-      <c r="LE4" s="113"/>
-      <c r="LF4" s="114"/>
-      <c r="LG4" s="115" t="s">
+      <c r="KP4" s="111"/>
+      <c r="KQ4" s="111"/>
+      <c r="KR4" s="111"/>
+      <c r="KS4" s="111"/>
+      <c r="KT4" s="111"/>
+      <c r="KU4" s="111"/>
+      <c r="KV4" s="111"/>
+      <c r="KW4" s="111"/>
+      <c r="KX4" s="111"/>
+      <c r="KY4" s="111"/>
+      <c r="KZ4" s="111"/>
+      <c r="LA4" s="111"/>
+      <c r="LB4" s="111"/>
+      <c r="LC4" s="111"/>
+      <c r="LD4" s="111"/>
+      <c r="LE4" s="111"/>
+      <c r="LF4" s="112"/>
+      <c r="LG4" s="113" t="s">
         <v>15</v>
       </c>
-      <c r="LH4" s="116"/>
-      <c r="LI4" s="116"/>
-      <c r="LJ4" s="116"/>
-      <c r="LK4" s="116"/>
-      <c r="LL4" s="116"/>
-      <c r="LM4" s="116"/>
-      <c r="LN4" s="116"/>
-      <c r="LO4" s="116"/>
-      <c r="LP4" s="116"/>
-      <c r="LQ4" s="116"/>
-      <c r="LR4" s="116"/>
-      <c r="LS4" s="116"/>
-      <c r="LT4" s="116"/>
-      <c r="LU4" s="116"/>
-      <c r="LV4" s="116"/>
-      <c r="LW4" s="116"/>
-      <c r="LX4" s="117"/>
-      <c r="LY4" s="115" t="s">
+      <c r="LH4" s="114"/>
+      <c r="LI4" s="114"/>
+      <c r="LJ4" s="114"/>
+      <c r="LK4" s="114"/>
+      <c r="LL4" s="114"/>
+      <c r="LM4" s="114"/>
+      <c r="LN4" s="114"/>
+      <c r="LO4" s="114"/>
+      <c r="LP4" s="114"/>
+      <c r="LQ4" s="114"/>
+      <c r="LR4" s="114"/>
+      <c r="LS4" s="114"/>
+      <c r="LT4" s="114"/>
+      <c r="LU4" s="114"/>
+      <c r="LV4" s="114"/>
+      <c r="LW4" s="114"/>
+      <c r="LX4" s="115"/>
+      <c r="LY4" s="113" t="s">
         <v>16</v>
       </c>
-      <c r="LZ4" s="116"/>
-      <c r="MA4" s="116"/>
-      <c r="MB4" s="116"/>
-      <c r="MC4" s="116"/>
-      <c r="MD4" s="117"/>
-      <c r="ME4" s="115" t="s">
+      <c r="LZ4" s="114"/>
+      <c r="MA4" s="114"/>
+      <c r="MB4" s="114"/>
+      <c r="MC4" s="114"/>
+      <c r="MD4" s="115"/>
+      <c r="ME4" s="113" t="s">
         <v>17</v>
       </c>
-      <c r="MF4" s="116"/>
-      <c r="MG4" s="116"/>
-      <c r="MH4" s="116"/>
-      <c r="MI4" s="116"/>
-      <c r="MJ4" s="117"/>
-      <c r="MK4" s="108" t="s">
+      <c r="MF4" s="114"/>
+      <c r="MG4" s="114"/>
+      <c r="MH4" s="114"/>
+      <c r="MI4" s="114"/>
+      <c r="MJ4" s="115"/>
+      <c r="MK4" s="104" t="s">
         <v>18</v>
       </c>
-      <c r="ML4" s="109"/>
-      <c r="MM4" s="109"/>
-      <c r="MN4" s="109"/>
-      <c r="MO4" s="109"/>
-      <c r="MP4" s="109"/>
-      <c r="MQ4" s="109"/>
-      <c r="MR4" s="109"/>
-      <c r="MS4" s="109"/>
-      <c r="MT4" s="109"/>
-      <c r="MU4" s="109"/>
-      <c r="MV4" s="109"/>
-      <c r="MW4" s="109"/>
-      <c r="MX4" s="109"/>
-      <c r="MY4" s="109"/>
-      <c r="MZ4" s="109"/>
-      <c r="NA4" s="109"/>
-      <c r="NB4" s="109"/>
-      <c r="NC4" s="109"/>
-      <c r="ND4" s="109"/>
-      <c r="NE4" s="109"/>
-      <c r="NF4" s="109"/>
-      <c r="NG4" s="109"/>
-      <c r="NH4" s="109"/>
-      <c r="NI4" s="110" t="s">
+      <c r="ML4" s="105"/>
+      <c r="MM4" s="105"/>
+      <c r="MN4" s="105"/>
+      <c r="MO4" s="105"/>
+      <c r="MP4" s="105"/>
+      <c r="MQ4" s="105"/>
+      <c r="MR4" s="105"/>
+      <c r="MS4" s="105"/>
+      <c r="MT4" s="105"/>
+      <c r="MU4" s="105"/>
+      <c r="MV4" s="105"/>
+      <c r="MW4" s="105"/>
+      <c r="MX4" s="105"/>
+      <c r="MY4" s="105"/>
+      <c r="MZ4" s="105"/>
+      <c r="NA4" s="105"/>
+      <c r="NB4" s="105"/>
+      <c r="NC4" s="105"/>
+      <c r="ND4" s="105"/>
+      <c r="NE4" s="105"/>
+      <c r="NF4" s="105"/>
+      <c r="NG4" s="105"/>
+      <c r="NH4" s="105"/>
+      <c r="NI4" s="106" t="s">
         <v>22</v>
       </c>
-      <c r="NJ4" s="45" t="s">
+      <c r="NJ4" s="71" t="s">
         <v>23</v>
       </c>
-      <c r="NK4" s="47" t="s">
+      <c r="NK4" s="56" t="s">
         <v>24</v>
       </c>
-      <c r="NL4" s="47"/>
-      <c r="NM4" s="47"/>
-      <c r="NN4" s="47"/>
-      <c r="NO4" s="47" t="s">
+      <c r="NL4" s="56"/>
+      <c r="NM4" s="56"/>
+      <c r="NN4" s="56"/>
+      <c r="NO4" s="56" t="s">
         <v>25</v>
       </c>
-      <c r="NP4" s="47"/>
-      <c r="NQ4" s="47"/>
-      <c r="NR4" s="47"/>
-      <c r="NS4" s="47"/>
-      <c r="NT4" s="47"/>
-      <c r="NU4" s="73" t="s">
+      <c r="NP4" s="56"/>
+      <c r="NQ4" s="56"/>
+      <c r="NR4" s="56"/>
+      <c r="NS4" s="56"/>
+      <c r="NT4" s="56"/>
+      <c r="NU4" s="57" t="s">
         <v>26</v>
       </c>
-      <c r="NV4" s="73"/>
-      <c r="NW4" s="73"/>
-      <c r="NX4" s="73"/>
-      <c r="NY4" s="73"/>
-      <c r="NZ4" s="139"/>
-      <c r="OA4" s="85"/>
-      <c r="OB4" s="86"/>
-      <c r="OC4" s="86"/>
-      <c r="OD4" s="86"/>
-      <c r="OE4" s="86"/>
-      <c r="OF4" s="86"/>
+      <c r="NV4" s="57"/>
+      <c r="NW4" s="57"/>
+      <c r="NX4" s="57"/>
+      <c r="NY4" s="57"/>
+      <c r="NZ4" s="58"/>
+      <c r="OA4" s="130"/>
+      <c r="OB4" s="131"/>
+      <c r="OC4" s="131"/>
+      <c r="OD4" s="131"/>
+      <c r="OE4" s="131"/>
+      <c r="OF4" s="131"/>
     </row>
     <row r="5" spans="1:396" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="57"/>
-      <c r="B5" s="57"/>
-      <c r="C5" s="57"/>
-      <c r="D5" s="57"/>
+      <c r="A5" s="64"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="64"/>
+      <c r="D5" s="64"/>
       <c r="E5" s="7"/>
-      <c r="F5" s="57"/>
+      <c r="F5" s="64"/>
       <c r="G5" s="8"/>
-      <c r="H5" s="64"/>
-      <c r="I5" s="65"/>
-      <c r="J5" s="65"/>
-      <c r="K5" s="65"/>
-      <c r="L5" s="66"/>
-      <c r="M5" s="90"/>
-      <c r="N5" s="91"/>
-      <c r="O5" s="91"/>
-      <c r="P5" s="91"/>
-      <c r="Q5" s="91"/>
-      <c r="R5" s="92"/>
-      <c r="S5" s="93"/>
-      <c r="T5" s="93"/>
-      <c r="U5" s="93"/>
-      <c r="V5" s="93"/>
-      <c r="W5" s="93"/>
-      <c r="X5" s="93"/>
-      <c r="Y5" s="97"/>
-      <c r="Z5" s="98"/>
-      <c r="AA5" s="99"/>
-      <c r="AB5" s="97"/>
-      <c r="AC5" s="98"/>
-      <c r="AD5" s="99"/>
-      <c r="AE5" s="47" t="s">
+      <c r="H5" s="138"/>
+      <c r="I5" s="139"/>
+      <c r="J5" s="139"/>
+      <c r="K5" s="139"/>
+      <c r="L5" s="140"/>
+      <c r="M5" s="94"/>
+      <c r="N5" s="95"/>
+      <c r="O5" s="95"/>
+      <c r="P5" s="95"/>
+      <c r="Q5" s="95"/>
+      <c r="R5" s="96"/>
+      <c r="S5" s="97"/>
+      <c r="T5" s="97"/>
+      <c r="U5" s="97"/>
+      <c r="V5" s="97"/>
+      <c r="W5" s="97"/>
+      <c r="X5" s="97"/>
+      <c r="Y5" s="82"/>
+      <c r="Z5" s="83"/>
+      <c r="AA5" s="84"/>
+      <c r="AB5" s="82"/>
+      <c r="AC5" s="83"/>
+      <c r="AD5" s="84"/>
+      <c r="AE5" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="AF5" s="47"/>
-      <c r="AG5" s="47"/>
-      <c r="AH5" s="47"/>
-      <c r="AI5" s="47"/>
-      <c r="AJ5" s="47"/>
-      <c r="AK5" s="47"/>
-      <c r="AL5" s="47"/>
-      <c r="AM5" s="47"/>
-      <c r="AN5" s="103"/>
-      <c r="AO5" s="103"/>
-      <c r="AP5" s="103"/>
-      <c r="AQ5" s="103"/>
-      <c r="AR5" s="103"/>
-      <c r="AS5" s="103"/>
-      <c r="AT5" s="97"/>
-      <c r="AU5" s="98"/>
-      <c r="AV5" s="105"/>
-      <c r="AW5" s="90"/>
-      <c r="AX5" s="91"/>
-      <c r="AY5" s="91"/>
-      <c r="AZ5" s="91"/>
-      <c r="BA5" s="91"/>
-      <c r="BB5" s="92"/>
-      <c r="BC5" s="93"/>
-      <c r="BD5" s="93"/>
-      <c r="BE5" s="93"/>
-      <c r="BF5" s="93"/>
-      <c r="BG5" s="93"/>
-      <c r="BH5" s="93"/>
-      <c r="BI5" s="97"/>
-      <c r="BJ5" s="98"/>
-      <c r="BK5" s="99"/>
-      <c r="BL5" s="97"/>
-      <c r="BM5" s="98"/>
-      <c r="BN5" s="99"/>
-      <c r="BO5" s="47" t="s">
+      <c r="AF5" s="56"/>
+      <c r="AG5" s="56"/>
+      <c r="AH5" s="56"/>
+      <c r="AI5" s="56"/>
+      <c r="AJ5" s="56"/>
+      <c r="AK5" s="56"/>
+      <c r="AL5" s="56"/>
+      <c r="AM5" s="56"/>
+      <c r="AN5" s="88"/>
+      <c r="AO5" s="88"/>
+      <c r="AP5" s="88"/>
+      <c r="AQ5" s="88"/>
+      <c r="AR5" s="88"/>
+      <c r="AS5" s="88"/>
+      <c r="AT5" s="82"/>
+      <c r="AU5" s="83"/>
+      <c r="AV5" s="99"/>
+      <c r="AW5" s="94"/>
+      <c r="AX5" s="95"/>
+      <c r="AY5" s="95"/>
+      <c r="AZ5" s="95"/>
+      <c r="BA5" s="95"/>
+      <c r="BB5" s="96"/>
+      <c r="BC5" s="97"/>
+      <c r="BD5" s="97"/>
+      <c r="BE5" s="97"/>
+      <c r="BF5" s="97"/>
+      <c r="BG5" s="97"/>
+      <c r="BH5" s="97"/>
+      <c r="BI5" s="82"/>
+      <c r="BJ5" s="83"/>
+      <c r="BK5" s="84"/>
+      <c r="BL5" s="82"/>
+      <c r="BM5" s="83"/>
+      <c r="BN5" s="84"/>
+      <c r="BO5" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="BP5" s="47"/>
-      <c r="BQ5" s="47"/>
-      <c r="BR5" s="47"/>
-      <c r="BS5" s="47"/>
-      <c r="BT5" s="47"/>
-      <c r="BU5" s="47"/>
-      <c r="BV5" s="47"/>
-      <c r="BW5" s="47"/>
-      <c r="BX5" s="103"/>
-      <c r="BY5" s="103"/>
-      <c r="BZ5" s="103"/>
-      <c r="CA5" s="103"/>
-      <c r="CB5" s="103"/>
-      <c r="CC5" s="103"/>
-      <c r="CD5" s="97"/>
-      <c r="CE5" s="98"/>
-      <c r="CF5" s="105"/>
-      <c r="CG5" s="90"/>
-      <c r="CH5" s="91"/>
-      <c r="CI5" s="91"/>
-      <c r="CJ5" s="91"/>
-      <c r="CK5" s="91"/>
-      <c r="CL5" s="92"/>
-      <c r="CM5" s="93"/>
-      <c r="CN5" s="93"/>
-      <c r="CO5" s="93"/>
-      <c r="CP5" s="93"/>
-      <c r="CQ5" s="93"/>
-      <c r="CR5" s="93"/>
-      <c r="CS5" s="97"/>
-      <c r="CT5" s="98"/>
-      <c r="CU5" s="99"/>
-      <c r="CV5" s="97"/>
-      <c r="CW5" s="98"/>
-      <c r="CX5" s="99"/>
-      <c r="CY5" s="47" t="s">
+      <c r="BP5" s="56"/>
+      <c r="BQ5" s="56"/>
+      <c r="BR5" s="56"/>
+      <c r="BS5" s="56"/>
+      <c r="BT5" s="56"/>
+      <c r="BU5" s="56"/>
+      <c r="BV5" s="56"/>
+      <c r="BW5" s="56"/>
+      <c r="BX5" s="88"/>
+      <c r="BY5" s="88"/>
+      <c r="BZ5" s="88"/>
+      <c r="CA5" s="88"/>
+      <c r="CB5" s="88"/>
+      <c r="CC5" s="88"/>
+      <c r="CD5" s="82"/>
+      <c r="CE5" s="83"/>
+      <c r="CF5" s="99"/>
+      <c r="CG5" s="94"/>
+      <c r="CH5" s="95"/>
+      <c r="CI5" s="95"/>
+      <c r="CJ5" s="95"/>
+      <c r="CK5" s="95"/>
+      <c r="CL5" s="96"/>
+      <c r="CM5" s="97"/>
+      <c r="CN5" s="97"/>
+      <c r="CO5" s="97"/>
+      <c r="CP5" s="97"/>
+      <c r="CQ5" s="97"/>
+      <c r="CR5" s="97"/>
+      <c r="CS5" s="82"/>
+      <c r="CT5" s="83"/>
+      <c r="CU5" s="84"/>
+      <c r="CV5" s="82"/>
+      <c r="CW5" s="83"/>
+      <c r="CX5" s="84"/>
+      <c r="CY5" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="CZ5" s="47"/>
-      <c r="DA5" s="47"/>
-      <c r="DB5" s="47"/>
-      <c r="DC5" s="47"/>
-      <c r="DD5" s="47"/>
-      <c r="DE5" s="47"/>
-      <c r="DF5" s="47"/>
-      <c r="DG5" s="47"/>
-      <c r="DH5" s="103"/>
-      <c r="DI5" s="103"/>
-      <c r="DJ5" s="103"/>
-      <c r="DK5" s="103"/>
-      <c r="DL5" s="103"/>
-      <c r="DM5" s="103"/>
-      <c r="DN5" s="97"/>
-      <c r="DO5" s="98"/>
-      <c r="DP5" s="105"/>
-      <c r="DQ5" s="90"/>
-      <c r="DR5" s="91"/>
-      <c r="DS5" s="91"/>
-      <c r="DT5" s="91"/>
-      <c r="DU5" s="91"/>
-      <c r="DV5" s="92"/>
-      <c r="DW5" s="93"/>
-      <c r="DX5" s="93"/>
-      <c r="DY5" s="93"/>
-      <c r="DZ5" s="93"/>
-      <c r="EA5" s="93"/>
-      <c r="EB5" s="93"/>
-      <c r="EC5" s="97"/>
-      <c r="ED5" s="98"/>
-      <c r="EE5" s="99"/>
-      <c r="EF5" s="97"/>
-      <c r="EG5" s="98"/>
-      <c r="EH5" s="99"/>
-      <c r="EI5" s="47" t="s">
+      <c r="CZ5" s="56"/>
+      <c r="DA5" s="56"/>
+      <c r="DB5" s="56"/>
+      <c r="DC5" s="56"/>
+      <c r="DD5" s="56"/>
+      <c r="DE5" s="56"/>
+      <c r="DF5" s="56"/>
+      <c r="DG5" s="56"/>
+      <c r="DH5" s="88"/>
+      <c r="DI5" s="88"/>
+      <c r="DJ5" s="88"/>
+      <c r="DK5" s="88"/>
+      <c r="DL5" s="88"/>
+      <c r="DM5" s="88"/>
+      <c r="DN5" s="82"/>
+      <c r="DO5" s="83"/>
+      <c r="DP5" s="99"/>
+      <c r="DQ5" s="94"/>
+      <c r="DR5" s="95"/>
+      <c r="DS5" s="95"/>
+      <c r="DT5" s="95"/>
+      <c r="DU5" s="95"/>
+      <c r="DV5" s="96"/>
+      <c r="DW5" s="97"/>
+      <c r="DX5" s="97"/>
+      <c r="DY5" s="97"/>
+      <c r="DZ5" s="97"/>
+      <c r="EA5" s="97"/>
+      <c r="EB5" s="97"/>
+      <c r="EC5" s="82"/>
+      <c r="ED5" s="83"/>
+      <c r="EE5" s="84"/>
+      <c r="EF5" s="82"/>
+      <c r="EG5" s="83"/>
+      <c r="EH5" s="84"/>
+      <c r="EI5" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="EJ5" s="47"/>
-      <c r="EK5" s="47"/>
-      <c r="EL5" s="47"/>
-      <c r="EM5" s="47"/>
-      <c r="EN5" s="47"/>
-      <c r="EO5" s="47"/>
-      <c r="EP5" s="47"/>
-      <c r="EQ5" s="47"/>
-      <c r="ER5" s="103"/>
-      <c r="ES5" s="103"/>
-      <c r="ET5" s="103"/>
-      <c r="EU5" s="103"/>
-      <c r="EV5" s="103"/>
-      <c r="EW5" s="103"/>
-      <c r="EX5" s="97"/>
-      <c r="EY5" s="98"/>
-      <c r="EZ5" s="105"/>
-      <c r="FA5" s="90"/>
-      <c r="FB5" s="91"/>
-      <c r="FC5" s="91"/>
-      <c r="FD5" s="91"/>
-      <c r="FE5" s="91"/>
-      <c r="FF5" s="92"/>
-      <c r="FG5" s="93"/>
-      <c r="FH5" s="93"/>
-      <c r="FI5" s="93"/>
-      <c r="FJ5" s="93"/>
-      <c r="FK5" s="93"/>
-      <c r="FL5" s="93"/>
-      <c r="FM5" s="97"/>
-      <c r="FN5" s="98"/>
-      <c r="FO5" s="99"/>
-      <c r="FP5" s="97"/>
-      <c r="FQ5" s="98"/>
-      <c r="FR5" s="99"/>
-      <c r="FS5" s="47" t="s">
+      <c r="EJ5" s="56"/>
+      <c r="EK5" s="56"/>
+      <c r="EL5" s="56"/>
+      <c r="EM5" s="56"/>
+      <c r="EN5" s="56"/>
+      <c r="EO5" s="56"/>
+      <c r="EP5" s="56"/>
+      <c r="EQ5" s="56"/>
+      <c r="ER5" s="88"/>
+      <c r="ES5" s="88"/>
+      <c r="ET5" s="88"/>
+      <c r="EU5" s="88"/>
+      <c r="EV5" s="88"/>
+      <c r="EW5" s="88"/>
+      <c r="EX5" s="82"/>
+      <c r="EY5" s="83"/>
+      <c r="EZ5" s="99"/>
+      <c r="FA5" s="94"/>
+      <c r="FB5" s="95"/>
+      <c r="FC5" s="95"/>
+      <c r="FD5" s="95"/>
+      <c r="FE5" s="95"/>
+      <c r="FF5" s="96"/>
+      <c r="FG5" s="97"/>
+      <c r="FH5" s="97"/>
+      <c r="FI5" s="97"/>
+      <c r="FJ5" s="97"/>
+      <c r="FK5" s="97"/>
+      <c r="FL5" s="97"/>
+      <c r="FM5" s="82"/>
+      <c r="FN5" s="83"/>
+      <c r="FO5" s="84"/>
+      <c r="FP5" s="82"/>
+      <c r="FQ5" s="83"/>
+      <c r="FR5" s="84"/>
+      <c r="FS5" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="FT5" s="47"/>
-      <c r="FU5" s="47"/>
-      <c r="FV5" s="47"/>
-      <c r="FW5" s="47"/>
-      <c r="FX5" s="47"/>
-      <c r="FY5" s="47"/>
-      <c r="FZ5" s="47"/>
-      <c r="GA5" s="47"/>
-      <c r="GB5" s="103"/>
-      <c r="GC5" s="103"/>
-      <c r="GD5" s="103"/>
-      <c r="GE5" s="103"/>
-      <c r="GF5" s="103"/>
-      <c r="GG5" s="103"/>
-      <c r="GH5" s="97"/>
-      <c r="GI5" s="98"/>
-      <c r="GJ5" s="105"/>
-      <c r="GK5" s="90"/>
-      <c r="GL5" s="91"/>
-      <c r="GM5" s="91"/>
-      <c r="GN5" s="91"/>
-      <c r="GO5" s="91"/>
-      <c r="GP5" s="92"/>
-      <c r="GQ5" s="93"/>
-      <c r="GR5" s="93"/>
-      <c r="GS5" s="93"/>
-      <c r="GT5" s="93"/>
-      <c r="GU5" s="93"/>
-      <c r="GV5" s="93"/>
-      <c r="GW5" s="97"/>
-      <c r="GX5" s="98"/>
-      <c r="GY5" s="99"/>
-      <c r="GZ5" s="97"/>
-      <c r="HA5" s="98"/>
-      <c r="HB5" s="99"/>
-      <c r="HC5" s="47" t="s">
+      <c r="FT5" s="56"/>
+      <c r="FU5" s="56"/>
+      <c r="FV5" s="56"/>
+      <c r="FW5" s="56"/>
+      <c r="FX5" s="56"/>
+      <c r="FY5" s="56"/>
+      <c r="FZ5" s="56"/>
+      <c r="GA5" s="56"/>
+      <c r="GB5" s="88"/>
+      <c r="GC5" s="88"/>
+      <c r="GD5" s="88"/>
+      <c r="GE5" s="88"/>
+      <c r="GF5" s="88"/>
+      <c r="GG5" s="88"/>
+      <c r="GH5" s="82"/>
+      <c r="GI5" s="83"/>
+      <c r="GJ5" s="99"/>
+      <c r="GK5" s="94"/>
+      <c r="GL5" s="95"/>
+      <c r="GM5" s="95"/>
+      <c r="GN5" s="95"/>
+      <c r="GO5" s="95"/>
+      <c r="GP5" s="96"/>
+      <c r="GQ5" s="97"/>
+      <c r="GR5" s="97"/>
+      <c r="GS5" s="97"/>
+      <c r="GT5" s="97"/>
+      <c r="GU5" s="97"/>
+      <c r="GV5" s="97"/>
+      <c r="GW5" s="82"/>
+      <c r="GX5" s="83"/>
+      <c r="GY5" s="84"/>
+      <c r="GZ5" s="82"/>
+      <c r="HA5" s="83"/>
+      <c r="HB5" s="84"/>
+      <c r="HC5" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="HD5" s="47"/>
-      <c r="HE5" s="47"/>
-      <c r="HF5" s="47"/>
-      <c r="HG5" s="47"/>
-      <c r="HH5" s="47"/>
-      <c r="HI5" s="47"/>
-      <c r="HJ5" s="47"/>
-      <c r="HK5" s="47"/>
-      <c r="HL5" s="103"/>
-      <c r="HM5" s="103"/>
-      <c r="HN5" s="103"/>
-      <c r="HO5" s="103"/>
-      <c r="HP5" s="103"/>
-      <c r="HQ5" s="103"/>
-      <c r="HR5" s="97"/>
-      <c r="HS5" s="98"/>
-      <c r="HT5" s="105"/>
-      <c r="HU5" s="90"/>
-      <c r="HV5" s="91"/>
-      <c r="HW5" s="91"/>
-      <c r="HX5" s="91"/>
-      <c r="HY5" s="91"/>
-      <c r="HZ5" s="92"/>
-      <c r="IA5" s="93"/>
-      <c r="IB5" s="93"/>
-      <c r="IC5" s="93"/>
-      <c r="ID5" s="93"/>
-      <c r="IE5" s="93"/>
-      <c r="IF5" s="93"/>
-      <c r="IG5" s="97"/>
-      <c r="IH5" s="98"/>
-      <c r="II5" s="99"/>
-      <c r="IJ5" s="97"/>
-      <c r="IK5" s="98"/>
-      <c r="IL5" s="99"/>
-      <c r="IM5" s="47" t="s">
+      <c r="HD5" s="56"/>
+      <c r="HE5" s="56"/>
+      <c r="HF5" s="56"/>
+      <c r="HG5" s="56"/>
+      <c r="HH5" s="56"/>
+      <c r="HI5" s="56"/>
+      <c r="HJ5" s="56"/>
+      <c r="HK5" s="56"/>
+      <c r="HL5" s="88"/>
+      <c r="HM5" s="88"/>
+      <c r="HN5" s="88"/>
+      <c r="HO5" s="88"/>
+      <c r="HP5" s="88"/>
+      <c r="HQ5" s="88"/>
+      <c r="HR5" s="82"/>
+      <c r="HS5" s="83"/>
+      <c r="HT5" s="99"/>
+      <c r="HU5" s="94"/>
+      <c r="HV5" s="95"/>
+      <c r="HW5" s="95"/>
+      <c r="HX5" s="95"/>
+      <c r="HY5" s="95"/>
+      <c r="HZ5" s="96"/>
+      <c r="IA5" s="97"/>
+      <c r="IB5" s="97"/>
+      <c r="IC5" s="97"/>
+      <c r="ID5" s="97"/>
+      <c r="IE5" s="97"/>
+      <c r="IF5" s="97"/>
+      <c r="IG5" s="82"/>
+      <c r="IH5" s="83"/>
+      <c r="II5" s="84"/>
+      <c r="IJ5" s="82"/>
+      <c r="IK5" s="83"/>
+      <c r="IL5" s="84"/>
+      <c r="IM5" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="IN5" s="47"/>
-      <c r="IO5" s="47"/>
-      <c r="IP5" s="47"/>
-      <c r="IQ5" s="47"/>
-      <c r="IR5" s="47"/>
-      <c r="IS5" s="47"/>
-      <c r="IT5" s="47"/>
-      <c r="IU5" s="47"/>
-      <c r="IV5" s="103"/>
-      <c r="IW5" s="103"/>
-      <c r="IX5" s="103"/>
-      <c r="IY5" s="103"/>
-      <c r="IZ5" s="103"/>
-      <c r="JA5" s="103"/>
-      <c r="JB5" s="97"/>
-      <c r="JC5" s="98"/>
-      <c r="JD5" s="105"/>
-      <c r="JE5" s="90"/>
-      <c r="JF5" s="91"/>
-      <c r="JG5" s="91"/>
-      <c r="JH5" s="91"/>
-      <c r="JI5" s="91"/>
-      <c r="JJ5" s="92"/>
-      <c r="JK5" s="93"/>
-      <c r="JL5" s="93"/>
-      <c r="JM5" s="93"/>
-      <c r="JN5" s="93"/>
-      <c r="JO5" s="93"/>
-      <c r="JP5" s="93"/>
-      <c r="JQ5" s="97"/>
-      <c r="JR5" s="98"/>
-      <c r="JS5" s="99"/>
-      <c r="JT5" s="97"/>
-      <c r="JU5" s="98"/>
-      <c r="JV5" s="99"/>
-      <c r="JW5" s="47" t="s">
+      <c r="IN5" s="56"/>
+      <c r="IO5" s="56"/>
+      <c r="IP5" s="56"/>
+      <c r="IQ5" s="56"/>
+      <c r="IR5" s="56"/>
+      <c r="IS5" s="56"/>
+      <c r="IT5" s="56"/>
+      <c r="IU5" s="56"/>
+      <c r="IV5" s="88"/>
+      <c r="IW5" s="88"/>
+      <c r="IX5" s="88"/>
+      <c r="IY5" s="88"/>
+      <c r="IZ5" s="88"/>
+      <c r="JA5" s="88"/>
+      <c r="JB5" s="82"/>
+      <c r="JC5" s="83"/>
+      <c r="JD5" s="99"/>
+      <c r="JE5" s="94"/>
+      <c r="JF5" s="95"/>
+      <c r="JG5" s="95"/>
+      <c r="JH5" s="95"/>
+      <c r="JI5" s="95"/>
+      <c r="JJ5" s="96"/>
+      <c r="JK5" s="97"/>
+      <c r="JL5" s="97"/>
+      <c r="JM5" s="97"/>
+      <c r="JN5" s="97"/>
+      <c r="JO5" s="97"/>
+      <c r="JP5" s="97"/>
+      <c r="JQ5" s="82"/>
+      <c r="JR5" s="83"/>
+      <c r="JS5" s="84"/>
+      <c r="JT5" s="82"/>
+      <c r="JU5" s="83"/>
+      <c r="JV5" s="84"/>
+      <c r="JW5" s="56" t="s">
         <v>27</v>
       </c>
-      <c r="JX5" s="47"/>
-      <c r="JY5" s="47"/>
-      <c r="JZ5" s="47"/>
-      <c r="KA5" s="47"/>
-      <c r="KB5" s="47"/>
-      <c r="KC5" s="47"/>
-      <c r="KD5" s="47"/>
-      <c r="KE5" s="47"/>
-      <c r="KF5" s="103"/>
-      <c r="KG5" s="103"/>
-      <c r="KH5" s="103"/>
-      <c r="KI5" s="103"/>
-      <c r="KJ5" s="103"/>
-      <c r="KK5" s="103"/>
-      <c r="KL5" s="97"/>
-      <c r="KM5" s="98"/>
-      <c r="KN5" s="105"/>
-      <c r="KO5" s="121" t="s">
+      <c r="JX5" s="56"/>
+      <c r="JY5" s="56"/>
+      <c r="JZ5" s="56"/>
+      <c r="KA5" s="56"/>
+      <c r="KB5" s="56"/>
+      <c r="KC5" s="56"/>
+      <c r="KD5" s="56"/>
+      <c r="KE5" s="56"/>
+      <c r="KF5" s="88"/>
+      <c r="KG5" s="88"/>
+      <c r="KH5" s="88"/>
+      <c r="KI5" s="88"/>
+      <c r="KJ5" s="88"/>
+      <c r="KK5" s="88"/>
+      <c r="KL5" s="82"/>
+      <c r="KM5" s="83"/>
+      <c r="KN5" s="99"/>
+      <c r="KO5" s="119" t="s">
         <v>28</v>
       </c>
-      <c r="KP5" s="48" t="s">
+      <c r="KP5" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="KQ5" s="72" t="s">
-        <v>850</v>
-      </c>
-      <c r="KR5" s="73"/>
-      <c r="KS5" s="73"/>
-      <c r="KT5" s="74"/>
-      <c r="KU5" s="123" t="s">
+      <c r="KQ5" s="77" t="s">
+        <v>753</v>
+      </c>
+      <c r="KR5" s="57"/>
+      <c r="KS5" s="57"/>
+      <c r="KT5" s="78"/>
+      <c r="KU5" s="121" t="s">
         <v>30</v>
       </c>
-      <c r="KV5" s="124"/>
-      <c r="KW5" s="124"/>
-      <c r="KX5" s="124"/>
-      <c r="KY5" s="124"/>
-      <c r="KZ5" s="124"/>
-      <c r="LA5" s="124"/>
-      <c r="LB5" s="124"/>
-      <c r="LC5" s="124"/>
-      <c r="LD5" s="124"/>
-      <c r="LE5" s="124"/>
-      <c r="LF5" s="125"/>
-      <c r="LG5" s="48" t="s">
+      <c r="KV5" s="122"/>
+      <c r="KW5" s="122"/>
+      <c r="KX5" s="122"/>
+      <c r="KY5" s="122"/>
+      <c r="KZ5" s="122"/>
+      <c r="LA5" s="122"/>
+      <c r="LB5" s="122"/>
+      <c r="LC5" s="122"/>
+      <c r="LD5" s="122"/>
+      <c r="LE5" s="122"/>
+      <c r="LF5" s="123"/>
+      <c r="LG5" s="52" t="s">
         <v>31</v>
       </c>
-      <c r="LH5" s="48" t="s">
+      <c r="LH5" s="52" t="s">
         <v>29</v>
       </c>
-      <c r="LI5" s="72" t="s">
-        <v>851</v>
-      </c>
-      <c r="LJ5" s="73"/>
-      <c r="LK5" s="73"/>
-      <c r="LL5" s="74"/>
-      <c r="LM5" s="81" t="s">
+      <c r="LI5" s="77" t="s">
+        <v>754</v>
+      </c>
+      <c r="LJ5" s="57"/>
+      <c r="LK5" s="57"/>
+      <c r="LL5" s="78"/>
+      <c r="LM5" s="142" t="s">
         <v>27</v>
       </c>
-      <c r="LN5" s="81"/>
-      <c r="LO5" s="81"/>
-      <c r="LP5" s="81"/>
-      <c r="LQ5" s="81"/>
-      <c r="LR5" s="81"/>
-      <c r="LS5" s="81"/>
-      <c r="LT5" s="81"/>
-      <c r="LU5" s="81"/>
-      <c r="LV5" s="81"/>
-      <c r="LW5" s="81"/>
-      <c r="LX5" s="81"/>
-      <c r="LY5" s="118"/>
-      <c r="LZ5" s="119"/>
-      <c r="MA5" s="119"/>
-      <c r="MB5" s="119"/>
-      <c r="MC5" s="119"/>
-      <c r="MD5" s="120"/>
-      <c r="ME5" s="118"/>
-      <c r="MF5" s="119"/>
-      <c r="MG5" s="119"/>
-      <c r="MH5" s="119"/>
-      <c r="MI5" s="119"/>
-      <c r="MJ5" s="120"/>
+      <c r="LN5" s="142"/>
+      <c r="LO5" s="142"/>
+      <c r="LP5" s="142"/>
+      <c r="LQ5" s="142"/>
+      <c r="LR5" s="142"/>
+      <c r="LS5" s="142"/>
+      <c r="LT5" s="142"/>
+      <c r="LU5" s="142"/>
+      <c r="LV5" s="142"/>
+      <c r="LW5" s="142"/>
+      <c r="LX5" s="142"/>
+      <c r="LY5" s="116"/>
+      <c r="LZ5" s="117"/>
+      <c r="MA5" s="117"/>
+      <c r="MB5" s="117"/>
+      <c r="MC5" s="117"/>
+      <c r="MD5" s="118"/>
+      <c r="ME5" s="116"/>
+      <c r="MF5" s="117"/>
+      <c r="MG5" s="117"/>
+      <c r="MH5" s="117"/>
+      <c r="MI5" s="117"/>
+      <c r="MJ5" s="118"/>
       <c r="MK5" s="46" t="s">
         <v>32</v>
       </c>
       <c r="ML5" s="46" t="s">
         <v>33</v>
       </c>
-      <c r="MM5" s="72" t="s">
+      <c r="MM5" s="77" t="s">
         <v>34</v>
       </c>
-      <c r="MN5" s="73"/>
-      <c r="MO5" s="73"/>
-      <c r="MP5" s="74"/>
-      <c r="MQ5" s="50" t="s">
+      <c r="MN5" s="57"/>
+      <c r="MO5" s="57"/>
+      <c r="MP5" s="78"/>
+      <c r="MQ5" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="MR5" s="107"/>
-      <c r="MS5" s="107"/>
-      <c r="MT5" s="107"/>
-      <c r="MU5" s="107"/>
-      <c r="MV5" s="107"/>
-      <c r="MW5" s="107"/>
-      <c r="MX5" s="107"/>
-      <c r="MY5" s="107"/>
-      <c r="MZ5" s="107"/>
-      <c r="NA5" s="107"/>
-      <c r="NB5" s="107"/>
-      <c r="NC5" s="107"/>
-      <c r="ND5" s="107"/>
-      <c r="NE5" s="107"/>
-      <c r="NF5" s="107"/>
-      <c r="NG5" s="107"/>
-      <c r="NH5" s="107"/>
-      <c r="NI5" s="110"/>
-      <c r="NJ5" s="45"/>
-      <c r="NK5" s="47"/>
-      <c r="NL5" s="47"/>
-      <c r="NM5" s="47"/>
-      <c r="NN5" s="47"/>
-      <c r="NO5" s="47"/>
-      <c r="NP5" s="47"/>
-      <c r="NQ5" s="47"/>
-      <c r="NR5" s="47"/>
-      <c r="NS5" s="47"/>
-      <c r="NT5" s="47"/>
-      <c r="NU5" s="76"/>
-      <c r="NV5" s="76"/>
-      <c r="NW5" s="76"/>
-      <c r="NX5" s="76"/>
-      <c r="NY5" s="76"/>
-      <c r="NZ5" s="140"/>
-      <c r="OA5" s="85"/>
-      <c r="OB5" s="86"/>
-      <c r="OC5" s="86"/>
-      <c r="OD5" s="86"/>
-      <c r="OE5" s="86"/>
-      <c r="OF5" s="86"/>
+      <c r="MR5" s="49"/>
+      <c r="MS5" s="49"/>
+      <c r="MT5" s="49"/>
+      <c r="MU5" s="49"/>
+      <c r="MV5" s="49"/>
+      <c r="MW5" s="49"/>
+      <c r="MX5" s="49"/>
+      <c r="MY5" s="49"/>
+      <c r="MZ5" s="49"/>
+      <c r="NA5" s="49"/>
+      <c r="NB5" s="49"/>
+      <c r="NC5" s="49"/>
+      <c r="ND5" s="49"/>
+      <c r="NE5" s="49"/>
+      <c r="NF5" s="49"/>
+      <c r="NG5" s="49"/>
+      <c r="NH5" s="49"/>
+      <c r="NI5" s="106"/>
+      <c r="NJ5" s="71"/>
+      <c r="NK5" s="56"/>
+      <c r="NL5" s="56"/>
+      <c r="NM5" s="56"/>
+      <c r="NN5" s="56"/>
+      <c r="NO5" s="56"/>
+      <c r="NP5" s="56"/>
+      <c r="NQ5" s="56"/>
+      <c r="NR5" s="56"/>
+      <c r="NS5" s="56"/>
+      <c r="NT5" s="56"/>
+      <c r="NU5" s="59"/>
+      <c r="NV5" s="59"/>
+      <c r="NW5" s="59"/>
+      <c r="NX5" s="59"/>
+      <c r="NY5" s="59"/>
+      <c r="NZ5" s="60"/>
+      <c r="OA5" s="130"/>
+      <c r="OB5" s="131"/>
+      <c r="OC5" s="131"/>
+      <c r="OD5" s="131"/>
+      <c r="OE5" s="131"/>
+      <c r="OF5" s="131"/>
     </row>
     <row r="6" spans="1:396" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="57"/>
-      <c r="B6" s="57"/>
-      <c r="C6" s="57"/>
-      <c r="D6" s="57"/>
-      <c r="E6" s="57" t="s">
+      <c r="A6" s="64"/>
+      <c r="B6" s="64"/>
+      <c r="C6" s="64"/>
+      <c r="D6" s="64"/>
+      <c r="E6" s="64" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="57"/>
-      <c r="G6" s="57" t="s">
+      <c r="F6" s="64"/>
+      <c r="G6" s="64" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="56" t="s">
+      <c r="H6" s="63" t="s">
         <v>37</v>
       </c>
-      <c r="I6" s="126" t="s">
+      <c r="I6" s="101" t="s">
         <v>38</v>
       </c>
-      <c r="J6" s="127"/>
-      <c r="K6" s="127"/>
-      <c r="L6" s="128"/>
-      <c r="M6" s="50" t="s">
+      <c r="J6" s="102"/>
+      <c r="K6" s="102"/>
+      <c r="L6" s="103"/>
+      <c r="M6" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="N6" s="107"/>
-      <c r="O6" s="51"/>
-      <c r="P6" s="50" t="s">
+      <c r="N6" s="49"/>
+      <c r="O6" s="50"/>
+      <c r="P6" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="Q6" s="107"/>
-      <c r="R6" s="51"/>
-      <c r="S6" s="78" t="s">
+      <c r="Q6" s="49"/>
+      <c r="R6" s="50"/>
+      <c r="S6" s="89" t="s">
         <v>41</v>
       </c>
-      <c r="T6" s="79"/>
-      <c r="U6" s="80"/>
-      <c r="V6" s="78" t="s">
+      <c r="T6" s="61"/>
+      <c r="U6" s="90"/>
+      <c r="V6" s="89" t="s">
         <v>42</v>
       </c>
-      <c r="W6" s="79"/>
-      <c r="X6" s="80"/>
-      <c r="Y6" s="100"/>
-      <c r="Z6" s="101"/>
-      <c r="AA6" s="102"/>
-      <c r="AB6" s="100"/>
-      <c r="AC6" s="101"/>
-      <c r="AD6" s="102"/>
-      <c r="AE6" s="45" t="s">
+      <c r="W6" s="61"/>
+      <c r="X6" s="90"/>
+      <c r="Y6" s="85"/>
+      <c r="Z6" s="86"/>
+      <c r="AA6" s="87"/>
+      <c r="AB6" s="85"/>
+      <c r="AC6" s="86"/>
+      <c r="AD6" s="87"/>
+      <c r="AE6" s="71" t="s">
         <v>43</v>
       </c>
-      <c r="AF6" s="45"/>
-      <c r="AG6" s="45"/>
-      <c r="AH6" s="47" t="s">
+      <c r="AF6" s="71"/>
+      <c r="AG6" s="71"/>
+      <c r="AH6" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="AI6" s="47"/>
-      <c r="AJ6" s="47"/>
-      <c r="AK6" s="45" t="s">
+      <c r="AI6" s="56"/>
+      <c r="AJ6" s="56"/>
+      <c r="AK6" s="71" t="s">
         <v>45</v>
       </c>
-      <c r="AL6" s="45"/>
-      <c r="AM6" s="45"/>
-      <c r="AN6" s="47" t="s">
+      <c r="AL6" s="71"/>
+      <c r="AM6" s="71"/>
+      <c r="AN6" s="56" t="s">
         <v>25</v>
       </c>
-      <c r="AO6" s="47"/>
-      <c r="AP6" s="47"/>
-      <c r="AQ6" s="47" t="s">
+      <c r="AO6" s="56"/>
+      <c r="AP6" s="56"/>
+      <c r="AQ6" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="AR6" s="47"/>
-      <c r="AS6" s="47"/>
-      <c r="AT6" s="100"/>
-      <c r="AU6" s="101"/>
-      <c r="AV6" s="106"/>
-      <c r="AW6" s="50" t="s">
+      <c r="AR6" s="56"/>
+      <c r="AS6" s="56"/>
+      <c r="AT6" s="85"/>
+      <c r="AU6" s="86"/>
+      <c r="AV6" s="100"/>
+      <c r="AW6" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="AX6" s="107"/>
-      <c r="AY6" s="51"/>
-      <c r="AZ6" s="50" t="s">
+      <c r="AX6" s="49"/>
+      <c r="AY6" s="50"/>
+      <c r="AZ6" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="BA6" s="107"/>
-      <c r="BB6" s="51"/>
-      <c r="BC6" s="78" t="s">
+      <c r="BA6" s="49"/>
+      <c r="BB6" s="50"/>
+      <c r="BC6" s="89" t="s">
         <v>41</v>
       </c>
-      <c r="BD6" s="79"/>
-      <c r="BE6" s="80"/>
-      <c r="BF6" s="78" t="s">
+      <c r="BD6" s="61"/>
+      <c r="BE6" s="90"/>
+      <c r="BF6" s="89" t="s">
         <v>42</v>
       </c>
-      <c r="BG6" s="79"/>
-      <c r="BH6" s="80"/>
-      <c r="BI6" s="100"/>
-      <c r="BJ6" s="101"/>
-      <c r="BK6" s="102"/>
-      <c r="BL6" s="100"/>
-      <c r="BM6" s="101"/>
-      <c r="BN6" s="102"/>
-      <c r="BO6" s="45" t="s">
+      <c r="BG6" s="61"/>
+      <c r="BH6" s="90"/>
+      <c r="BI6" s="85"/>
+      <c r="BJ6" s="86"/>
+      <c r="BK6" s="87"/>
+      <c r="BL6" s="85"/>
+      <c r="BM6" s="86"/>
+      <c r="BN6" s="87"/>
+      <c r="BO6" s="71" t="s">
         <v>43</v>
       </c>
-      <c r="BP6" s="45"/>
-      <c r="BQ6" s="45"/>
-      <c r="BR6" s="47" t="s">
+      <c r="BP6" s="71"/>
+      <c r="BQ6" s="71"/>
+      <c r="BR6" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="BS6" s="47"/>
-      <c r="BT6" s="47"/>
-      <c r="BU6" s="45" t="s">
+      <c r="BS6" s="56"/>
+      <c r="BT6" s="56"/>
+      <c r="BU6" s="71" t="s">
         <v>45</v>
       </c>
-      <c r="BV6" s="45"/>
-      <c r="BW6" s="45"/>
-      <c r="BX6" s="47" t="s">
+      <c r="BV6" s="71"/>
+      <c r="BW6" s="71"/>
+      <c r="BX6" s="56" t="s">
         <v>25</v>
       </c>
-      <c r="BY6" s="47"/>
-      <c r="BZ6" s="47"/>
-      <c r="CA6" s="47" t="s">
+      <c r="BY6" s="56"/>
+      <c r="BZ6" s="56"/>
+      <c r="CA6" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="CB6" s="47"/>
-      <c r="CC6" s="47"/>
-      <c r="CD6" s="100"/>
-      <c r="CE6" s="101"/>
-      <c r="CF6" s="106"/>
-      <c r="CG6" s="50" t="s">
+      <c r="CB6" s="56"/>
+      <c r="CC6" s="56"/>
+      <c r="CD6" s="85"/>
+      <c r="CE6" s="86"/>
+      <c r="CF6" s="100"/>
+      <c r="CG6" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="CH6" s="107"/>
-      <c r="CI6" s="51"/>
-      <c r="CJ6" s="50" t="s">
+      <c r="CH6" s="49"/>
+      <c r="CI6" s="50"/>
+      <c r="CJ6" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="CK6" s="107"/>
-      <c r="CL6" s="51"/>
-      <c r="CM6" s="78" t="s">
+      <c r="CK6" s="49"/>
+      <c r="CL6" s="50"/>
+      <c r="CM6" s="89" t="s">
         <v>41</v>
       </c>
-      <c r="CN6" s="79"/>
-      <c r="CO6" s="80"/>
-      <c r="CP6" s="78" t="s">
+      <c r="CN6" s="61"/>
+      <c r="CO6" s="90"/>
+      <c r="CP6" s="89" t="s">
         <v>42</v>
       </c>
-      <c r="CQ6" s="79"/>
-      <c r="CR6" s="80"/>
-      <c r="CS6" s="100"/>
-      <c r="CT6" s="101"/>
-      <c r="CU6" s="102"/>
-      <c r="CV6" s="100"/>
-      <c r="CW6" s="101"/>
-      <c r="CX6" s="102"/>
-      <c r="CY6" s="45" t="s">
+      <c r="CQ6" s="61"/>
+      <c r="CR6" s="90"/>
+      <c r="CS6" s="85"/>
+      <c r="CT6" s="86"/>
+      <c r="CU6" s="87"/>
+      <c r="CV6" s="85"/>
+      <c r="CW6" s="86"/>
+      <c r="CX6" s="87"/>
+      <c r="CY6" s="71" t="s">
         <v>43</v>
       </c>
-      <c r="CZ6" s="45"/>
-      <c r="DA6" s="45"/>
-      <c r="DB6" s="47" t="s">
+      <c r="CZ6" s="71"/>
+      <c r="DA6" s="71"/>
+      <c r="DB6" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="DC6" s="47"/>
-      <c r="DD6" s="47"/>
-      <c r="DE6" s="45" t="s">
+      <c r="DC6" s="56"/>
+      <c r="DD6" s="56"/>
+      <c r="DE6" s="71" t="s">
         <v>45</v>
       </c>
-      <c r="DF6" s="45"/>
-      <c r="DG6" s="45"/>
-      <c r="DH6" s="47" t="s">
+      <c r="DF6" s="71"/>
+      <c r="DG6" s="71"/>
+      <c r="DH6" s="56" t="s">
         <v>25</v>
       </c>
-      <c r="DI6" s="47"/>
-      <c r="DJ6" s="47"/>
-      <c r="DK6" s="47" t="s">
+      <c r="DI6" s="56"/>
+      <c r="DJ6" s="56"/>
+      <c r="DK6" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="DL6" s="47"/>
-      <c r="DM6" s="47"/>
-      <c r="DN6" s="100"/>
-      <c r="DO6" s="101"/>
-      <c r="DP6" s="106"/>
-      <c r="DQ6" s="50" t="s">
+      <c r="DL6" s="56"/>
+      <c r="DM6" s="56"/>
+      <c r="DN6" s="85"/>
+      <c r="DO6" s="86"/>
+      <c r="DP6" s="100"/>
+      <c r="DQ6" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="DR6" s="107"/>
-      <c r="DS6" s="51"/>
-      <c r="DT6" s="50" t="s">
+      <c r="DR6" s="49"/>
+      <c r="DS6" s="50"/>
+      <c r="DT6" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="DU6" s="107"/>
-      <c r="DV6" s="51"/>
-      <c r="DW6" s="78" t="s">
+      <c r="DU6" s="49"/>
+      <c r="DV6" s="50"/>
+      <c r="DW6" s="89" t="s">
         <v>41</v>
       </c>
-      <c r="DX6" s="79"/>
-      <c r="DY6" s="80"/>
-      <c r="DZ6" s="78" t="s">
+      <c r="DX6" s="61"/>
+      <c r="DY6" s="90"/>
+      <c r="DZ6" s="89" t="s">
         <v>42</v>
       </c>
-      <c r="EA6" s="79"/>
-      <c r="EB6" s="80"/>
-      <c r="EC6" s="100"/>
-      <c r="ED6" s="101"/>
-      <c r="EE6" s="102"/>
-      <c r="EF6" s="100"/>
-      <c r="EG6" s="101"/>
-      <c r="EH6" s="102"/>
-      <c r="EI6" s="45" t="s">
+      <c r="EA6" s="61"/>
+      <c r="EB6" s="90"/>
+      <c r="EC6" s="85"/>
+      <c r="ED6" s="86"/>
+      <c r="EE6" s="87"/>
+      <c r="EF6" s="85"/>
+      <c r="EG6" s="86"/>
+      <c r="EH6" s="87"/>
+      <c r="EI6" s="71" t="s">
         <v>43</v>
       </c>
-      <c r="EJ6" s="45"/>
-      <c r="EK6" s="45"/>
-      <c r="EL6" s="47" t="s">
+      <c r="EJ6" s="71"/>
+      <c r="EK6" s="71"/>
+      <c r="EL6" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="EM6" s="47"/>
-      <c r="EN6" s="47"/>
-      <c r="EO6" s="45" t="s">
+      <c r="EM6" s="56"/>
+      <c r="EN6" s="56"/>
+      <c r="EO6" s="71" t="s">
         <v>45</v>
       </c>
-      <c r="EP6" s="45"/>
-      <c r="EQ6" s="45"/>
-      <c r="ER6" s="47" t="s">
+      <c r="EP6" s="71"/>
+      <c r="EQ6" s="71"/>
+      <c r="ER6" s="56" t="s">
         <v>25</v>
       </c>
-      <c r="ES6" s="47"/>
-      <c r="ET6" s="47"/>
-      <c r="EU6" s="47" t="s">
+      <c r="ES6" s="56"/>
+      <c r="ET6" s="56"/>
+      <c r="EU6" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="EV6" s="47"/>
-      <c r="EW6" s="47"/>
-      <c r="EX6" s="100"/>
-      <c r="EY6" s="101"/>
-      <c r="EZ6" s="106"/>
-      <c r="FA6" s="50" t="s">
+      <c r="EV6" s="56"/>
+      <c r="EW6" s="56"/>
+      <c r="EX6" s="85"/>
+      <c r="EY6" s="86"/>
+      <c r="EZ6" s="100"/>
+      <c r="FA6" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="FB6" s="107"/>
-      <c r="FC6" s="51"/>
-      <c r="FD6" s="50" t="s">
+      <c r="FB6" s="49"/>
+      <c r="FC6" s="50"/>
+      <c r="FD6" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="FE6" s="107"/>
-      <c r="FF6" s="51"/>
-      <c r="FG6" s="78" t="s">
+      <c r="FE6" s="49"/>
+      <c r="FF6" s="50"/>
+      <c r="FG6" s="89" t="s">
         <v>41</v>
       </c>
-      <c r="FH6" s="79"/>
-      <c r="FI6" s="80"/>
-      <c r="FJ6" s="78" t="s">
+      <c r="FH6" s="61"/>
+      <c r="FI6" s="90"/>
+      <c r="FJ6" s="89" t="s">
         <v>42</v>
       </c>
-      <c r="FK6" s="79"/>
-      <c r="FL6" s="80"/>
-      <c r="FM6" s="100"/>
-      <c r="FN6" s="101"/>
-      <c r="FO6" s="102"/>
-      <c r="FP6" s="100"/>
-      <c r="FQ6" s="101"/>
-      <c r="FR6" s="102"/>
-      <c r="FS6" s="45" t="s">
+      <c r="FK6" s="61"/>
+      <c r="FL6" s="90"/>
+      <c r="FM6" s="85"/>
+      <c r="FN6" s="86"/>
+      <c r="FO6" s="87"/>
+      <c r="FP6" s="85"/>
+      <c r="FQ6" s="86"/>
+      <c r="FR6" s="87"/>
+      <c r="FS6" s="71" t="s">
         <v>43</v>
       </c>
-      <c r="FT6" s="45"/>
-      <c r="FU6" s="45"/>
-      <c r="FV6" s="47" t="s">
+      <c r="FT6" s="71"/>
+      <c r="FU6" s="71"/>
+      <c r="FV6" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="FW6" s="47"/>
-      <c r="FX6" s="47"/>
-      <c r="FY6" s="45" t="s">
+      <c r="FW6" s="56"/>
+      <c r="FX6" s="56"/>
+      <c r="FY6" s="71" t="s">
         <v>45</v>
       </c>
-      <c r="FZ6" s="45"/>
-      <c r="GA6" s="45"/>
-      <c r="GB6" s="47" t="s">
+      <c r="FZ6" s="71"/>
+      <c r="GA6" s="71"/>
+      <c r="GB6" s="56" t="s">
         <v>25</v>
       </c>
-      <c r="GC6" s="47"/>
-      <c r="GD6" s="47"/>
-      <c r="GE6" s="47" t="s">
+      <c r="GC6" s="56"/>
+      <c r="GD6" s="56"/>
+      <c r="GE6" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="GF6" s="47"/>
-      <c r="GG6" s="47"/>
-      <c r="GH6" s="100"/>
-      <c r="GI6" s="101"/>
-      <c r="GJ6" s="106"/>
-      <c r="GK6" s="50" t="s">
+      <c r="GF6" s="56"/>
+      <c r="GG6" s="56"/>
+      <c r="GH6" s="85"/>
+      <c r="GI6" s="86"/>
+      <c r="GJ6" s="100"/>
+      <c r="GK6" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="GL6" s="107"/>
-      <c r="GM6" s="51"/>
-      <c r="GN6" s="50" t="s">
+      <c r="GL6" s="49"/>
+      <c r="GM6" s="50"/>
+      <c r="GN6" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="GO6" s="107"/>
-      <c r="GP6" s="51"/>
-      <c r="GQ6" s="78" t="s">
+      <c r="GO6" s="49"/>
+      <c r="GP6" s="50"/>
+      <c r="GQ6" s="89" t="s">
         <v>41</v>
       </c>
-      <c r="GR6" s="79"/>
-      <c r="GS6" s="80"/>
-      <c r="GT6" s="78" t="s">
+      <c r="GR6" s="61"/>
+      <c r="GS6" s="90"/>
+      <c r="GT6" s="89" t="s">
         <v>42</v>
       </c>
-      <c r="GU6" s="79"/>
-      <c r="GV6" s="80"/>
-      <c r="GW6" s="100"/>
-      <c r="GX6" s="101"/>
-      <c r="GY6" s="102"/>
-      <c r="GZ6" s="100"/>
-      <c r="HA6" s="101"/>
-      <c r="HB6" s="102"/>
-      <c r="HC6" s="45" t="s">
+      <c r="GU6" s="61"/>
+      <c r="GV6" s="90"/>
+      <c r="GW6" s="85"/>
+      <c r="GX6" s="86"/>
+      <c r="GY6" s="87"/>
+      <c r="GZ6" s="85"/>
+      <c r="HA6" s="86"/>
+      <c r="HB6" s="87"/>
+      <c r="HC6" s="71" t="s">
         <v>43</v>
       </c>
-      <c r="HD6" s="45"/>
-      <c r="HE6" s="45"/>
-      <c r="HF6" s="47" t="s">
+      <c r="HD6" s="71"/>
+      <c r="HE6" s="71"/>
+      <c r="HF6" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="HG6" s="47"/>
-      <c r="HH6" s="47"/>
-      <c r="HI6" s="45" t="s">
+      <c r="HG6" s="56"/>
+      <c r="HH6" s="56"/>
+      <c r="HI6" s="71" t="s">
         <v>45</v>
       </c>
-      <c r="HJ6" s="45"/>
-      <c r="HK6" s="45"/>
-      <c r="HL6" s="47" t="s">
+      <c r="HJ6" s="71"/>
+      <c r="HK6" s="71"/>
+      <c r="HL6" s="56" t="s">
         <v>25</v>
       </c>
-      <c r="HM6" s="47"/>
-      <c r="HN6" s="47"/>
-      <c r="HO6" s="47" t="s">
+      <c r="HM6" s="56"/>
+      <c r="HN6" s="56"/>
+      <c r="HO6" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="HP6" s="47"/>
-      <c r="HQ6" s="47"/>
-      <c r="HR6" s="100"/>
-      <c r="HS6" s="101"/>
-      <c r="HT6" s="106"/>
-      <c r="HU6" s="50" t="s">
+      <c r="HP6" s="56"/>
+      <c r="HQ6" s="56"/>
+      <c r="HR6" s="85"/>
+      <c r="HS6" s="86"/>
+      <c r="HT6" s="100"/>
+      <c r="HU6" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="HV6" s="107"/>
-      <c r="HW6" s="51"/>
-      <c r="HX6" s="50" t="s">
+      <c r="HV6" s="49"/>
+      <c r="HW6" s="50"/>
+      <c r="HX6" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="HY6" s="107"/>
-      <c r="HZ6" s="51"/>
-      <c r="IA6" s="78" t="s">
+      <c r="HY6" s="49"/>
+      <c r="HZ6" s="50"/>
+      <c r="IA6" s="89" t="s">
         <v>41</v>
       </c>
-      <c r="IB6" s="79"/>
-      <c r="IC6" s="80"/>
-      <c r="ID6" s="78" t="s">
+      <c r="IB6" s="61"/>
+      <c r="IC6" s="90"/>
+      <c r="ID6" s="89" t="s">
         <v>42</v>
       </c>
-      <c r="IE6" s="79"/>
-      <c r="IF6" s="80"/>
-      <c r="IG6" s="100"/>
-      <c r="IH6" s="101"/>
-      <c r="II6" s="102"/>
-      <c r="IJ6" s="100"/>
-      <c r="IK6" s="101"/>
-      <c r="IL6" s="102"/>
-      <c r="IM6" s="45" t="s">
+      <c r="IE6" s="61"/>
+      <c r="IF6" s="90"/>
+      <c r="IG6" s="85"/>
+      <c r="IH6" s="86"/>
+      <c r="II6" s="87"/>
+      <c r="IJ6" s="85"/>
+      <c r="IK6" s="86"/>
+      <c r="IL6" s="87"/>
+      <c r="IM6" s="71" t="s">
         <v>43</v>
       </c>
-      <c r="IN6" s="45"/>
-      <c r="IO6" s="45"/>
-      <c r="IP6" s="47" t="s">
+      <c r="IN6" s="71"/>
+      <c r="IO6" s="71"/>
+      <c r="IP6" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="IQ6" s="47"/>
-      <c r="IR6" s="47"/>
-      <c r="IS6" s="45" t="s">
+      <c r="IQ6" s="56"/>
+      <c r="IR6" s="56"/>
+      <c r="IS6" s="71" t="s">
         <v>45</v>
       </c>
-      <c r="IT6" s="45"/>
-      <c r="IU6" s="45"/>
-      <c r="IV6" s="47" t="s">
+      <c r="IT6" s="71"/>
+      <c r="IU6" s="71"/>
+      <c r="IV6" s="56" t="s">
         <v>25</v>
       </c>
-      <c r="IW6" s="47"/>
-      <c r="IX6" s="47"/>
-      <c r="IY6" s="47" t="s">
+      <c r="IW6" s="56"/>
+      <c r="IX6" s="56"/>
+      <c r="IY6" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="IZ6" s="47"/>
-      <c r="JA6" s="47"/>
-      <c r="JB6" s="100"/>
-      <c r="JC6" s="101"/>
-      <c r="JD6" s="106"/>
-      <c r="JE6" s="50" t="s">
+      <c r="IZ6" s="56"/>
+      <c r="JA6" s="56"/>
+      <c r="JB6" s="85"/>
+      <c r="JC6" s="86"/>
+      <c r="JD6" s="100"/>
+      <c r="JE6" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="JF6" s="107"/>
-      <c r="JG6" s="51"/>
-      <c r="JH6" s="50" t="s">
+      <c r="JF6" s="49"/>
+      <c r="JG6" s="50"/>
+      <c r="JH6" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="JI6" s="107"/>
-      <c r="JJ6" s="51"/>
-      <c r="JK6" s="78" t="s">
+      <c r="JI6" s="49"/>
+      <c r="JJ6" s="50"/>
+      <c r="JK6" s="89" t="s">
         <v>41</v>
       </c>
-      <c r="JL6" s="79"/>
-      <c r="JM6" s="80"/>
-      <c r="JN6" s="78" t="s">
+      <c r="JL6" s="61"/>
+      <c r="JM6" s="90"/>
+      <c r="JN6" s="89" t="s">
         <v>42</v>
       </c>
-      <c r="JO6" s="79"/>
-      <c r="JP6" s="80"/>
-      <c r="JQ6" s="100"/>
-      <c r="JR6" s="101"/>
-      <c r="JS6" s="102"/>
-      <c r="JT6" s="100"/>
-      <c r="JU6" s="101"/>
-      <c r="JV6" s="102"/>
-      <c r="JW6" s="45" t="s">
+      <c r="JO6" s="61"/>
+      <c r="JP6" s="90"/>
+      <c r="JQ6" s="85"/>
+      <c r="JR6" s="86"/>
+      <c r="JS6" s="87"/>
+      <c r="JT6" s="85"/>
+      <c r="JU6" s="86"/>
+      <c r="JV6" s="87"/>
+      <c r="JW6" s="71" t="s">
         <v>43</v>
       </c>
-      <c r="JX6" s="45"/>
-      <c r="JY6" s="45"/>
-      <c r="JZ6" s="47" t="s">
+      <c r="JX6" s="71"/>
+      <c r="JY6" s="71"/>
+      <c r="JZ6" s="56" t="s">
         <v>44</v>
       </c>
-      <c r="KA6" s="47"/>
-      <c r="KB6" s="47"/>
-      <c r="KC6" s="45" t="s">
+      <c r="KA6" s="56"/>
+      <c r="KB6" s="56"/>
+      <c r="KC6" s="71" t="s">
         <v>45</v>
       </c>
-      <c r="KD6" s="45"/>
-      <c r="KE6" s="45"/>
-      <c r="KF6" s="47" t="s">
+      <c r="KD6" s="71"/>
+      <c r="KE6" s="71"/>
+      <c r="KF6" s="56" t="s">
         <v>25</v>
       </c>
-      <c r="KG6" s="47"/>
-      <c r="KH6" s="47"/>
-      <c r="KI6" s="47" t="s">
+      <c r="KG6" s="56"/>
+      <c r="KH6" s="56"/>
+      <c r="KI6" s="56" t="s">
         <v>26</v>
       </c>
-      <c r="KJ6" s="47"/>
-      <c r="KK6" s="47"/>
-      <c r="KL6" s="100"/>
-      <c r="KM6" s="101"/>
-      <c r="KN6" s="106"/>
-      <c r="KO6" s="122"/>
-      <c r="KP6" s="49"/>
-      <c r="KQ6" s="75"/>
-      <c r="KR6" s="76"/>
-      <c r="KS6" s="76"/>
-      <c r="KT6" s="77"/>
-      <c r="KU6" s="50" t="s">
+      <c r="KJ6" s="56"/>
+      <c r="KK6" s="56"/>
+      <c r="KL6" s="85"/>
+      <c r="KM6" s="86"/>
+      <c r="KN6" s="100"/>
+      <c r="KO6" s="120"/>
+      <c r="KP6" s="53"/>
+      <c r="KQ6" s="108"/>
+      <c r="KR6" s="59"/>
+      <c r="KS6" s="59"/>
+      <c r="KT6" s="109"/>
+      <c r="KU6" s="48" t="s">
         <v>39</v>
       </c>
-      <c r="KV6" s="107"/>
-      <c r="KW6" s="107"/>
-      <c r="KX6" s="107"/>
-      <c r="KY6" s="107"/>
-      <c r="KZ6" s="51"/>
-      <c r="LA6" s="50" t="s">
+      <c r="KV6" s="49"/>
+      <c r="KW6" s="49"/>
+      <c r="KX6" s="49"/>
+      <c r="KY6" s="49"/>
+      <c r="KZ6" s="50"/>
+      <c r="LA6" s="48" t="s">
         <v>40</v>
       </c>
-      <c r="LB6" s="107"/>
-      <c r="LC6" s="107"/>
-      <c r="LD6" s="107"/>
-      <c r="LE6" s="107"/>
-      <c r="LF6" s="51"/>
-      <c r="LG6" s="49"/>
-      <c r="LH6" s="49"/>
-      <c r="LI6" s="75"/>
-      <c r="LJ6" s="76"/>
-      <c r="LK6" s="76"/>
-      <c r="LL6" s="77"/>
-      <c r="LM6" s="72" t="s">
+      <c r="LB6" s="49"/>
+      <c r="LC6" s="49"/>
+      <c r="LD6" s="49"/>
+      <c r="LE6" s="49"/>
+      <c r="LF6" s="50"/>
+      <c r="LG6" s="53"/>
+      <c r="LH6" s="53"/>
+      <c r="LI6" s="108"/>
+      <c r="LJ6" s="59"/>
+      <c r="LK6" s="59"/>
+      <c r="LL6" s="109"/>
+      <c r="LM6" s="77" t="s">
         <v>41</v>
       </c>
-      <c r="LN6" s="73"/>
-      <c r="LO6" s="73"/>
-      <c r="LP6" s="73"/>
-      <c r="LQ6" s="73"/>
-      <c r="LR6" s="74"/>
-      <c r="LS6" s="47" t="s">
+      <c r="LN6" s="57"/>
+      <c r="LO6" s="57"/>
+      <c r="LP6" s="57"/>
+      <c r="LQ6" s="57"/>
+      <c r="LR6" s="78"/>
+      <c r="LS6" s="56" t="s">
         <v>42</v>
       </c>
-      <c r="LT6" s="47"/>
-      <c r="LU6" s="47"/>
-      <c r="LV6" s="47"/>
-      <c r="LW6" s="47"/>
-      <c r="LX6" s="47"/>
-      <c r="LY6" s="45" t="s">
+      <c r="LT6" s="56"/>
+      <c r="LU6" s="56"/>
+      <c r="LV6" s="56"/>
+      <c r="LW6" s="56"/>
+      <c r="LX6" s="56"/>
+      <c r="LY6" s="71" t="s">
         <v>46</v>
       </c>
-      <c r="LZ6" s="45"/>
-      <c r="MA6" s="47" t="s">
+      <c r="LZ6" s="71"/>
+      <c r="MA6" s="56" t="s">
         <v>47</v>
       </c>
-      <c r="MB6" s="47"/>
-      <c r="MC6" s="47"/>
-      <c r="MD6" s="47"/>
-      <c r="ME6" s="45" t="s">
+      <c r="MB6" s="56"/>
+      <c r="MC6" s="56"/>
+      <c r="MD6" s="56"/>
+      <c r="ME6" s="71" t="s">
         <v>48</v>
       </c>
-      <c r="MF6" s="45"/>
-      <c r="MG6" s="47" t="s">
+      <c r="MF6" s="71"/>
+      <c r="MG6" s="56" t="s">
         <v>47</v>
       </c>
-      <c r="MH6" s="47"/>
-      <c r="MI6" s="47"/>
-      <c r="MJ6" s="47"/>
-      <c r="MK6" s="71"/>
-      <c r="ML6" s="71"/>
-      <c r="MM6" s="75"/>
-      <c r="MN6" s="76"/>
-      <c r="MO6" s="76"/>
-      <c r="MP6" s="77"/>
-      <c r="MQ6" s="50" t="s">
+      <c r="MH6" s="56"/>
+      <c r="MI6" s="56"/>
+      <c r="MJ6" s="56"/>
+      <c r="MK6" s="47"/>
+      <c r="ML6" s="47"/>
+      <c r="MM6" s="108"/>
+      <c r="MN6" s="59"/>
+      <c r="MO6" s="59"/>
+      <c r="MP6" s="109"/>
+      <c r="MQ6" s="48" t="s">
         <v>49</v>
       </c>
-      <c r="MR6" s="107"/>
-      <c r="MS6" s="107"/>
-      <c r="MT6" s="107"/>
-      <c r="MU6" s="107"/>
-      <c r="MV6" s="51"/>
-      <c r="MW6" s="50" t="s">
+      <c r="MR6" s="49"/>
+      <c r="MS6" s="49"/>
+      <c r="MT6" s="49"/>
+      <c r="MU6" s="49"/>
+      <c r="MV6" s="50"/>
+      <c r="MW6" s="48" t="s">
         <v>44</v>
       </c>
-      <c r="MX6" s="107"/>
-      <c r="MY6" s="107"/>
-      <c r="MZ6" s="107"/>
-      <c r="NA6" s="107"/>
-      <c r="NB6" s="51"/>
-      <c r="NC6" s="50" t="s">
+      <c r="MX6" s="49"/>
+      <c r="MY6" s="49"/>
+      <c r="MZ6" s="49"/>
+      <c r="NA6" s="49"/>
+      <c r="NB6" s="50"/>
+      <c r="NC6" s="48" t="s">
         <v>45</v>
       </c>
-      <c r="ND6" s="107"/>
-      <c r="NE6" s="107"/>
-      <c r="NF6" s="107"/>
-      <c r="NG6" s="107"/>
-      <c r="NH6" s="107"/>
-      <c r="NI6" s="110"/>
-      <c r="NJ6" s="45"/>
-      <c r="NK6" s="47"/>
-      <c r="NL6" s="47"/>
-      <c r="NM6" s="47"/>
-      <c r="NN6" s="47"/>
-      <c r="NO6" s="47"/>
-      <c r="NP6" s="47"/>
-      <c r="NQ6" s="47"/>
-      <c r="NR6" s="47"/>
-      <c r="NS6" s="47"/>
-      <c r="NT6" s="47"/>
-      <c r="NU6" s="79"/>
-      <c r="NV6" s="79"/>
-      <c r="NW6" s="79"/>
-      <c r="NX6" s="79"/>
-      <c r="NY6" s="79"/>
-      <c r="NZ6" s="141"/>
-      <c r="OA6" s="85"/>
-      <c r="OB6" s="86"/>
-      <c r="OC6" s="86"/>
-      <c r="OD6" s="86"/>
-      <c r="OE6" s="86"/>
-      <c r="OF6" s="86"/>
+      <c r="ND6" s="49"/>
+      <c r="NE6" s="49"/>
+      <c r="NF6" s="49"/>
+      <c r="NG6" s="49"/>
+      <c r="NH6" s="49"/>
+      <c r="NI6" s="106"/>
+      <c r="NJ6" s="71"/>
+      <c r="NK6" s="56"/>
+      <c r="NL6" s="56"/>
+      <c r="NM6" s="56"/>
+      <c r="NN6" s="56"/>
+      <c r="NO6" s="56"/>
+      <c r="NP6" s="56"/>
+      <c r="NQ6" s="56"/>
+      <c r="NR6" s="56"/>
+      <c r="NS6" s="56"/>
+      <c r="NT6" s="56"/>
+      <c r="NU6" s="61"/>
+      <c r="NV6" s="61"/>
+      <c r="NW6" s="61"/>
+      <c r="NX6" s="61"/>
+      <c r="NY6" s="61"/>
+      <c r="NZ6" s="62"/>
+      <c r="OA6" s="130"/>
+      <c r="OB6" s="131"/>
+      <c r="OC6" s="131"/>
+      <c r="OD6" s="131"/>
+      <c r="OE6" s="131"/>
+      <c r="OF6" s="131"/>
     </row>
     <row r="7" spans="1:396" s="1" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="57"/>
-      <c r="B7" s="57"/>
-      <c r="C7" s="57"/>
-      <c r="D7" s="57"/>
-      <c r="E7" s="57"/>
-      <c r="F7" s="57"/>
-      <c r="G7" s="57"/>
-      <c r="H7" s="57"/>
-      <c r="I7" s="56" t="s">
+      <c r="A7" s="64"/>
+      <c r="B7" s="64"/>
+      <c r="C7" s="64"/>
+      <c r="D7" s="64"/>
+      <c r="E7" s="64"/>
+      <c r="F7" s="64"/>
+      <c r="G7" s="64"/>
+      <c r="H7" s="64"/>
+      <c r="I7" s="63" t="s">
         <v>50</v>
       </c>
-      <c r="J7" s="129" t="s">
+      <c r="J7" s="74" t="s">
         <v>27</v>
       </c>
-      <c r="K7" s="130"/>
-      <c r="L7" s="131"/>
-      <c r="M7" s="45" t="s">
+      <c r="K7" s="75"/>
+      <c r="L7" s="76"/>
+      <c r="M7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="N7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="O7" s="48" t="s">
+      <c r="N7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="O7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="P7" s="45" t="s">
+      <c r="P7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="Q7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="R7" s="48" t="s">
+      <c r="Q7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="R7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="S7" s="45" t="s">
+      <c r="S7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="T7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="U7" s="48" t="s">
+      <c r="T7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="U7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="V7" s="45" t="s">
+      <c r="V7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="W7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="X7" s="48" t="s">
+      <c r="W7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="X7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="Y7" s="45" t="s">
+      <c r="Y7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="Z7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="AA7" s="48" t="s">
+      <c r="Z7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="AA7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="AB7" s="45" t="s">
+      <c r="AB7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="AC7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="AD7" s="48" t="s">
+      <c r="AC7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="AD7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="AE7" s="45" t="s">
+      <c r="AE7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="AF7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="AG7" s="48" t="s">
+      <c r="AF7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="AG7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="AH7" s="45" t="s">
+      <c r="AH7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="AI7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="AJ7" s="48" t="s">
+      <c r="AI7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="AJ7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="AK7" s="45" t="s">
+      <c r="AK7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="AL7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="AM7" s="48" t="s">
+      <c r="AL7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="AM7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="AN7" s="45" t="s">
+      <c r="AN7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="AO7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="AP7" s="48" t="s">
+      <c r="AO7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="AP7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="AQ7" s="45" t="s">
+      <c r="AQ7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="AR7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="AS7" s="48" t="s">
+      <c r="AR7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="AS7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="AT7" s="47" t="s">
+      <c r="AT7" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="AU7" s="47" t="s">
-        <v>853</v>
-      </c>
-      <c r="AV7" s="52" t="s">
+      <c r="AU7" s="56" t="s">
+        <v>756</v>
+      </c>
+      <c r="AV7" s="72" t="s">
         <v>52</v>
       </c>
-      <c r="AW7" s="54" t="s">
+      <c r="AW7" s="66" t="s">
         <v>51</v>
       </c>
-      <c r="AX7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="AY7" s="48" t="s">
+      <c r="AX7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="AY7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="AZ7" s="45" t="s">
+      <c r="AZ7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="BA7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="BB7" s="48" t="s">
+      <c r="BA7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="BB7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="BC7" s="45" t="s">
+      <c r="BC7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="BD7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="BE7" s="48" t="s">
+      <c r="BD7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="BE7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="BF7" s="45" t="s">
+      <c r="BF7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="BG7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="BH7" s="48" t="s">
+      <c r="BG7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="BH7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="BI7" s="45" t="s">
+      <c r="BI7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="BJ7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="BK7" s="48" t="s">
+      <c r="BJ7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="BK7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="BL7" s="45" t="s">
+      <c r="BL7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="BM7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="BN7" s="48" t="s">
+      <c r="BM7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="BN7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="BO7" s="45" t="s">
+      <c r="BO7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="BP7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="BQ7" s="48" t="s">
+      <c r="BP7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="BQ7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="BR7" s="45" t="s">
+      <c r="BR7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="BS7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="BT7" s="48" t="s">
+      <c r="BS7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="BT7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="BU7" s="45" t="s">
+      <c r="BU7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="BV7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="BW7" s="48" t="s">
+      <c r="BV7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="BW7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="BX7" s="45" t="s">
+      <c r="BX7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="BY7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="BZ7" s="48" t="s">
+      <c r="BY7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="BZ7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="CA7" s="45" t="s">
+      <c r="CA7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="CB7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="CC7" s="48" t="s">
+      <c r="CB7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="CC7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="CD7" s="47" t="s">
+      <c r="CD7" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="CE7" s="47" t="s">
-        <v>853</v>
-      </c>
-      <c r="CF7" s="52" t="s">
+      <c r="CE7" s="56" t="s">
+        <v>756</v>
+      </c>
+      <c r="CF7" s="72" t="s">
         <v>52</v>
       </c>
-      <c r="CG7" s="54" t="s">
+      <c r="CG7" s="66" t="s">
         <v>51</v>
       </c>
-      <c r="CH7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="CI7" s="48" t="s">
+      <c r="CH7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="CI7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="CJ7" s="45" t="s">
+      <c r="CJ7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="CK7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="CL7" s="48" t="s">
+      <c r="CK7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="CL7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="CM7" s="45" t="s">
+      <c r="CM7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="CN7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="CO7" s="48" t="s">
+      <c r="CN7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="CO7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="CP7" s="45" t="s">
+      <c r="CP7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="CQ7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="CR7" s="48" t="s">
+      <c r="CQ7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="CR7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="CS7" s="45" t="s">
+      <c r="CS7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="CT7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="CU7" s="48" t="s">
+      <c r="CT7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="CU7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="CV7" s="45" t="s">
+      <c r="CV7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="CW7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="CX7" s="48" t="s">
+      <c r="CW7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="CX7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="CY7" s="45" t="s">
+      <c r="CY7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="CZ7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="DA7" s="48" t="s">
+      <c r="CZ7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="DA7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="DB7" s="45" t="s">
+      <c r="DB7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="DC7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="DD7" s="48" t="s">
+      <c r="DC7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="DD7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="DE7" s="45" t="s">
+      <c r="DE7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="DF7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="DG7" s="48" t="s">
+      <c r="DF7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="DG7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="DH7" s="45" t="s">
+      <c r="DH7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="DI7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="DJ7" s="48" t="s">
+      <c r="DI7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="DJ7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="DK7" s="45" t="s">
+      <c r="DK7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="DL7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="DM7" s="48" t="s">
+      <c r="DL7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="DM7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="DN7" s="47" t="s">
+      <c r="DN7" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="DO7" s="47" t="s">
-        <v>853</v>
-      </c>
-      <c r="DP7" s="52" t="s">
+      <c r="DO7" s="56" t="s">
+        <v>756</v>
+      </c>
+      <c r="DP7" s="72" t="s">
         <v>52</v>
       </c>
-      <c r="DQ7" s="54" t="s">
+      <c r="DQ7" s="66" t="s">
         <v>51</v>
       </c>
-      <c r="DR7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="DS7" s="48" t="s">
+      <c r="DR7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="DS7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="DT7" s="45" t="s">
+      <c r="DT7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="DU7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="DV7" s="48" t="s">
+      <c r="DU7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="DV7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="DW7" s="45" t="s">
+      <c r="DW7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="DX7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="DY7" s="48" t="s">
+      <c r="DX7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="DY7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="DZ7" s="45" t="s">
+      <c r="DZ7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="EA7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="EB7" s="48" t="s">
+      <c r="EA7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="EB7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="EC7" s="45" t="s">
+      <c r="EC7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="ED7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="EE7" s="48" t="s">
+      <c r="ED7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="EE7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="EF7" s="45" t="s">
+      <c r="EF7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="EG7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="EH7" s="48" t="s">
+      <c r="EG7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="EH7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="EI7" s="45" t="s">
+      <c r="EI7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="EJ7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="EK7" s="48" t="s">
+      <c r="EJ7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="EK7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="EL7" s="45" t="s">
+      <c r="EL7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="EM7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="EN7" s="48" t="s">
+      <c r="EM7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="EN7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="EO7" s="45" t="s">
+      <c r="EO7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="EP7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="EQ7" s="48" t="s">
+      <c r="EP7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="EQ7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="ER7" s="45" t="s">
+      <c r="ER7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="ES7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="ET7" s="48" t="s">
+      <c r="ES7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="ET7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="EU7" s="45" t="s">
+      <c r="EU7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="EV7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="EW7" s="48" t="s">
+      <c r="EV7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="EW7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="EX7" s="47" t="s">
+      <c r="EX7" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="EY7" s="47" t="s">
-        <v>853</v>
-      </c>
-      <c r="EZ7" s="52" t="s">
+      <c r="EY7" s="56" t="s">
+        <v>756</v>
+      </c>
+      <c r="EZ7" s="72" t="s">
         <v>52</v>
       </c>
-      <c r="FA7" s="54" t="s">
+      <c r="FA7" s="66" t="s">
         <v>51</v>
       </c>
-      <c r="FB7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="FC7" s="48" t="s">
+      <c r="FB7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="FC7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="FD7" s="45" t="s">
+      <c r="FD7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="FE7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="FF7" s="48" t="s">
+      <c r="FE7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="FF7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="FG7" s="45" t="s">
+      <c r="FG7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="FH7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="FI7" s="48" t="s">
+      <c r="FH7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="FI7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="FJ7" s="45" t="s">
+      <c r="FJ7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="FK7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="FL7" s="48" t="s">
+      <c r="FK7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="FL7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="FM7" s="45" t="s">
+      <c r="FM7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="FN7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="FO7" s="48" t="s">
+      <c r="FN7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="FO7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="FP7" s="45" t="s">
+      <c r="FP7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="FQ7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="FR7" s="48" t="s">
+      <c r="FQ7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="FR7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="FS7" s="45" t="s">
+      <c r="FS7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="FT7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="FU7" s="48" t="s">
+      <c r="FT7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="FU7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="FV7" s="45" t="s">
+      <c r="FV7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="FW7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="FX7" s="48" t="s">
+      <c r="FW7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="FX7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="FY7" s="45" t="s">
+      <c r="FY7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="FZ7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="GA7" s="48" t="s">
+      <c r="FZ7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="GA7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="GB7" s="45" t="s">
+      <c r="GB7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="GC7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="GD7" s="48" t="s">
+      <c r="GC7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="GD7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="GE7" s="45" t="s">
+      <c r="GE7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="GF7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="GG7" s="48" t="s">
+      <c r="GF7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="GG7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="GH7" s="47" t="s">
+      <c r="GH7" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="GI7" s="47" t="s">
-        <v>853</v>
-      </c>
-      <c r="GJ7" s="52" t="s">
+      <c r="GI7" s="56" t="s">
+        <v>756</v>
+      </c>
+      <c r="GJ7" s="72" t="s">
         <v>52</v>
       </c>
-      <c r="GK7" s="54" t="s">
+      <c r="GK7" s="66" t="s">
         <v>51</v>
       </c>
-      <c r="GL7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="GM7" s="48" t="s">
+      <c r="GL7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="GM7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="GN7" s="45" t="s">
+      <c r="GN7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="GO7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="GP7" s="48" t="s">
+      <c r="GO7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="GP7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="GQ7" s="45" t="s">
+      <c r="GQ7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="GR7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="GS7" s="48" t="s">
+      <c r="GR7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="GS7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="GT7" s="45" t="s">
+      <c r="GT7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="GU7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="GV7" s="48" t="s">
+      <c r="GU7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="GV7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="GW7" s="45" t="s">
+      <c r="GW7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="GX7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="GY7" s="48" t="s">
+      <c r="GX7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="GY7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="GZ7" s="45" t="s">
+      <c r="GZ7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="HA7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="HB7" s="48" t="s">
+      <c r="HA7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="HB7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="HC7" s="45" t="s">
+      <c r="HC7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="HD7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="HE7" s="48" t="s">
+      <c r="HD7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="HE7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="HF7" s="45" t="s">
+      <c r="HF7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="HG7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="HH7" s="48" t="s">
+      <c r="HG7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="HH7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="HI7" s="45" t="s">
+      <c r="HI7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="HJ7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="HK7" s="48" t="s">
+      <c r="HJ7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="HK7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="HL7" s="45" t="s">
+      <c r="HL7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="HM7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="HN7" s="48" t="s">
+      <c r="HM7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="HN7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="HO7" s="45" t="s">
+      <c r="HO7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="HP7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="HQ7" s="48" t="s">
+      <c r="HP7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="HQ7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="HR7" s="47" t="s">
+      <c r="HR7" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="HS7" s="47" t="s">
-        <v>853</v>
-      </c>
-      <c r="HT7" s="52" t="s">
+      <c r="HS7" s="56" t="s">
+        <v>756</v>
+      </c>
+      <c r="HT7" s="72" t="s">
         <v>52</v>
       </c>
-      <c r="HU7" s="54" t="s">
+      <c r="HU7" s="66" t="s">
         <v>51</v>
       </c>
-      <c r="HV7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="HW7" s="48" t="s">
+      <c r="HV7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="HW7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="HX7" s="45" t="s">
+      <c r="HX7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="HY7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="HZ7" s="48" t="s">
+      <c r="HY7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="HZ7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="IA7" s="45" t="s">
+      <c r="IA7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="IB7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="IC7" s="48" t="s">
+      <c r="IB7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="IC7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="ID7" s="45" t="s">
+      <c r="ID7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="IE7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="IF7" s="48" t="s">
+      <c r="IE7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="IF7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="IG7" s="45" t="s">
+      <c r="IG7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="IH7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="II7" s="48" t="s">
+      <c r="IH7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="II7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="IJ7" s="45" t="s">
+      <c r="IJ7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="IK7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="IL7" s="48" t="s">
+      <c r="IK7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="IL7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="IM7" s="45" t="s">
+      <c r="IM7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="IN7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="IO7" s="48" t="s">
+      <c r="IN7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="IO7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="IP7" s="45" t="s">
+      <c r="IP7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="IQ7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="IR7" s="48" t="s">
+      <c r="IQ7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="IR7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="IS7" s="45" t="s">
+      <c r="IS7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="IT7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="IU7" s="48" t="s">
+      <c r="IT7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="IU7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="IV7" s="45" t="s">
+      <c r="IV7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="IW7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="IX7" s="48" t="s">
+      <c r="IW7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="IX7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="IY7" s="45" t="s">
+      <c r="IY7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="IZ7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="JA7" s="48" t="s">
+      <c r="IZ7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="JA7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="JB7" s="47" t="s">
+      <c r="JB7" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="JC7" s="47" t="s">
-        <v>853</v>
-      </c>
-      <c r="JD7" s="52" t="s">
+      <c r="JC7" s="56" t="s">
+        <v>756</v>
+      </c>
+      <c r="JD7" s="72" t="s">
         <v>52</v>
       </c>
-      <c r="JE7" s="54" t="s">
+      <c r="JE7" s="66" t="s">
         <v>51</v>
       </c>
-      <c r="JF7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="JG7" s="48" t="s">
+      <c r="JF7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="JG7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="JH7" s="45" t="s">
+      <c r="JH7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="JI7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="JJ7" s="48" t="s">
+      <c r="JI7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="JJ7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="JK7" s="45" t="s">
+      <c r="JK7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="JL7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="JM7" s="48" t="s">
+      <c r="JL7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="JM7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="JN7" s="45" t="s">
+      <c r="JN7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="JO7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="JP7" s="48" t="s">
+      <c r="JO7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="JP7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="JQ7" s="45" t="s">
+      <c r="JQ7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="JR7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="JS7" s="48" t="s">
+      <c r="JR7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="JS7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="JT7" s="45" t="s">
+      <c r="JT7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="JU7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="JV7" s="48" t="s">
+      <c r="JU7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="JV7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="JW7" s="45" t="s">
+      <c r="JW7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="JX7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="JY7" s="48" t="s">
+      <c r="JX7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="JY7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="JZ7" s="45" t="s">
+      <c r="JZ7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="KA7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="KB7" s="48" t="s">
+      <c r="KA7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="KB7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="KC7" s="45" t="s">
+      <c r="KC7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="KD7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="KE7" s="48" t="s">
+      <c r="KD7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="KE7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="KF7" s="45" t="s">
+      <c r="KF7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="KG7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="KH7" s="48" t="s">
+      <c r="KG7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="KH7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="KI7" s="45" t="s">
+      <c r="KI7" s="71" t="s">
         <v>51</v>
       </c>
-      <c r="KJ7" s="47" t="s">
-        <v>852</v>
-      </c>
-      <c r="KK7" s="48" t="s">
+      <c r="KJ7" s="56" t="s">
+        <v>755</v>
+      </c>
+      <c r="KK7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="KL7" s="47" t="s">
+      <c r="KL7" s="56" t="s">
         <v>53</v>
       </c>
-      <c r="KM7" s="47" t="s">
-        <v>853</v>
-      </c>
-      <c r="KN7" s="48" t="s">
+      <c r="KM7" s="56" t="s">
+        <v>756</v>
+      </c>
+      <c r="KN7" s="52" t="s">
         <v>52</v>
       </c>
-      <c r="KO7" s="122"/>
-      <c r="KP7" s="49"/>
-      <c r="KQ7" s="78"/>
-      <c r="KR7" s="79"/>
-      <c r="KS7" s="79"/>
-      <c r="KT7" s="80"/>
-      <c r="KU7" s="50" t="s">
+      <c r="KO7" s="120"/>
+      <c r="KP7" s="53"/>
+      <c r="KQ7" s="89"/>
+      <c r="KR7" s="61"/>
+      <c r="KS7" s="61"/>
+      <c r="KT7" s="90"/>
+      <c r="KU7" s="48" t="s">
         <v>54</v>
       </c>
-      <c r="KV7" s="51"/>
-      <c r="KW7" s="50" t="s">
+      <c r="KV7" s="50"/>
+      <c r="KW7" s="48" t="s">
         <v>47</v>
       </c>
-      <c r="KX7" s="107"/>
-      <c r="KY7" s="107"/>
-      <c r="KZ7" s="51"/>
-      <c r="LA7" s="50" t="s">
+      <c r="KX7" s="49"/>
+      <c r="KY7" s="49"/>
+      <c r="KZ7" s="50"/>
+      <c r="LA7" s="48" t="s">
         <v>55</v>
       </c>
-      <c r="LB7" s="51"/>
-      <c r="LC7" s="50" t="s">
+      <c r="LB7" s="50"/>
+      <c r="LC7" s="48" t="s">
         <v>47</v>
       </c>
-      <c r="LD7" s="107"/>
-      <c r="LE7" s="107"/>
-      <c r="LF7" s="51"/>
-      <c r="LG7" s="49"/>
-      <c r="LH7" s="49"/>
-      <c r="LI7" s="78"/>
-      <c r="LJ7" s="79"/>
-      <c r="LK7" s="79"/>
-      <c r="LL7" s="80"/>
-      <c r="LM7" s="50" t="s">
+      <c r="LD7" s="49"/>
+      <c r="LE7" s="49"/>
+      <c r="LF7" s="50"/>
+      <c r="LG7" s="53"/>
+      <c r="LH7" s="53"/>
+      <c r="LI7" s="89"/>
+      <c r="LJ7" s="61"/>
+      <c r="LK7" s="61"/>
+      <c r="LL7" s="90"/>
+      <c r="LM7" s="48" t="s">
         <v>56</v>
       </c>
-      <c r="LN7" s="51"/>
-      <c r="LO7" s="50" t="s">
+      <c r="LN7" s="50"/>
+      <c r="LO7" s="48" t="s">
         <v>47</v>
       </c>
-      <c r="LP7" s="107"/>
-      <c r="LQ7" s="107"/>
-      <c r="LR7" s="51"/>
-      <c r="LS7" s="47" t="s">
+      <c r="LP7" s="49"/>
+      <c r="LQ7" s="49"/>
+      <c r="LR7" s="50"/>
+      <c r="LS7" s="56" t="s">
         <v>56</v>
       </c>
-      <c r="LT7" s="47"/>
-      <c r="LU7" s="50" t="s">
+      <c r="LT7" s="56"/>
+      <c r="LU7" s="48" t="s">
         <v>47</v>
       </c>
-      <c r="LV7" s="107"/>
-      <c r="LW7" s="107"/>
-      <c r="LX7" s="51"/>
-      <c r="LY7" s="45"/>
-      <c r="LZ7" s="45"/>
-      <c r="MA7" s="47"/>
-      <c r="MB7" s="47"/>
-      <c r="MC7" s="47"/>
-      <c r="MD7" s="47"/>
-      <c r="ME7" s="45"/>
-      <c r="MF7" s="45"/>
-      <c r="MG7" s="47"/>
-      <c r="MH7" s="47"/>
-      <c r="MI7" s="47"/>
-      <c r="MJ7" s="47"/>
-      <c r="MK7" s="71"/>
-      <c r="ML7" s="71"/>
-      <c r="MM7" s="78"/>
-      <c r="MN7" s="79"/>
-      <c r="MO7" s="79"/>
-      <c r="MP7" s="80"/>
-      <c r="MQ7" s="134" t="s">
+      <c r="LV7" s="49"/>
+      <c r="LW7" s="49"/>
+      <c r="LX7" s="50"/>
+      <c r="LY7" s="71"/>
+      <c r="LZ7" s="71"/>
+      <c r="MA7" s="56"/>
+      <c r="MB7" s="56"/>
+      <c r="MC7" s="56"/>
+      <c r="MD7" s="56"/>
+      <c r="ME7" s="71"/>
+      <c r="MF7" s="71"/>
+      <c r="MG7" s="56"/>
+      <c r="MH7" s="56"/>
+      <c r="MI7" s="56"/>
+      <c r="MJ7" s="56"/>
+      <c r="MK7" s="47"/>
+      <c r="ML7" s="47"/>
+      <c r="MM7" s="89"/>
+      <c r="MN7" s="61"/>
+      <c r="MO7" s="61"/>
+      <c r="MP7" s="90"/>
+      <c r="MQ7" s="65" t="s">
         <v>56</v>
       </c>
-      <c r="MR7" s="54"/>
-      <c r="MS7" s="50" t="s">
+      <c r="MR7" s="66"/>
+      <c r="MS7" s="48" t="s">
         <v>47</v>
       </c>
-      <c r="MT7" s="107"/>
-      <c r="MU7" s="107"/>
-      <c r="MV7" s="51"/>
-      <c r="MW7" s="134" t="s">
+      <c r="MT7" s="49"/>
+      <c r="MU7" s="49"/>
+      <c r="MV7" s="50"/>
+      <c r="MW7" s="65" t="s">
         <v>56</v>
       </c>
-      <c r="MX7" s="54"/>
-      <c r="MY7" s="50" t="s">
+      <c r="MX7" s="66"/>
+      <c r="MY7" s="48" t="s">
         <v>47</v>
       </c>
-      <c r="MZ7" s="107"/>
-      <c r="NA7" s="107"/>
-      <c r="NB7" s="51"/>
-      <c r="NC7" s="134" t="s">
+      <c r="MZ7" s="49"/>
+      <c r="NA7" s="49"/>
+      <c r="NB7" s="50"/>
+      <c r="NC7" s="65" t="s">
         <v>56</v>
       </c>
-      <c r="ND7" s="54"/>
-      <c r="NE7" s="50" t="s">
+      <c r="ND7" s="66"/>
+      <c r="NE7" s="48" t="s">
         <v>47</v>
       </c>
-      <c r="NF7" s="107"/>
-      <c r="NG7" s="107"/>
-      <c r="NH7" s="107"/>
-      <c r="NI7" s="110"/>
-      <c r="NJ7" s="45"/>
-      <c r="NK7" s="47"/>
-      <c r="NL7" s="47"/>
-      <c r="NM7" s="47"/>
-      <c r="NN7" s="47"/>
-      <c r="NO7" s="134" t="s">
+      <c r="NF7" s="49"/>
+      <c r="NG7" s="49"/>
+      <c r="NH7" s="49"/>
+      <c r="NI7" s="106"/>
+      <c r="NJ7" s="71"/>
+      <c r="NK7" s="56"/>
+      <c r="NL7" s="56"/>
+      <c r="NM7" s="56"/>
+      <c r="NN7" s="56"/>
+      <c r="NO7" s="65" t="s">
         <v>56</v>
       </c>
-      <c r="NP7" s="54"/>
-      <c r="NQ7" s="50" t="s">
+      <c r="NP7" s="66"/>
+      <c r="NQ7" s="48" t="s">
         <v>47</v>
       </c>
-      <c r="NR7" s="107"/>
-      <c r="NS7" s="107"/>
-      <c r="NT7" s="51"/>
-      <c r="NU7" s="134" t="s">
+      <c r="NR7" s="49"/>
+      <c r="NS7" s="49"/>
+      <c r="NT7" s="50"/>
+      <c r="NU7" s="65" t="s">
         <v>56</v>
       </c>
-      <c r="NV7" s="54"/>
-      <c r="NW7" s="50" t="s">
+      <c r="NV7" s="66"/>
+      <c r="NW7" s="48" t="s">
         <v>47</v>
       </c>
-      <c r="NX7" s="107"/>
-      <c r="NY7" s="107"/>
-      <c r="NZ7" s="135"/>
-      <c r="OA7" s="136" t="s">
+      <c r="NX7" s="49"/>
+      <c r="NY7" s="49"/>
+      <c r="NZ7" s="51"/>
+      <c r="OA7" s="67" t="s">
         <v>57</v>
       </c>
-      <c r="OB7" s="132" t="s">
+      <c r="OB7" s="54" t="s">
         <v>58</v>
       </c>
-      <c r="OC7" s="132" t="s">
+      <c r="OC7" s="54" t="s">
         <v>57</v>
       </c>
-      <c r="OD7" s="132" t="s">
+      <c r="OD7" s="54" t="s">
         <v>58</v>
       </c>
-      <c r="OE7" s="132" t="s">
+      <c r="OE7" s="54" t="s">
         <v>57</v>
       </c>
-      <c r="OF7" s="132" t="s">
+      <c r="OF7" s="54" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:396" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="57"/>
-      <c r="B8" s="57"/>
-      <c r="C8" s="57"/>
-      <c r="D8" s="57"/>
+      <c r="A8" s="64"/>
+      <c r="B8" s="64"/>
+      <c r="C8" s="64"/>
+      <c r="D8" s="64"/>
       <c r="E8" s="7"/>
-      <c r="F8" s="57"/>
+      <c r="F8" s="64"/>
       <c r="G8" s="7"/>
-      <c r="H8" s="57"/>
-      <c r="I8" s="57"/>
-      <c r="J8" s="56" t="s">
+      <c r="H8" s="64"/>
+      <c r="I8" s="64"/>
+      <c r="J8" s="63" t="s">
         <v>59</v>
       </c>
-      <c r="K8" s="56" t="s">
+      <c r="K8" s="63" t="s">
         <v>60</v>
       </c>
-      <c r="L8" s="56" t="s">
+      <c r="L8" s="63" t="s">
         <v>61</v>
       </c>
-      <c r="M8" s="45"/>
-      <c r="N8" s="47"/>
-      <c r="O8" s="49"/>
-      <c r="P8" s="45"/>
-      <c r="Q8" s="47"/>
-      <c r="R8" s="49"/>
-      <c r="S8" s="45"/>
-      <c r="T8" s="47"/>
-      <c r="U8" s="49"/>
-      <c r="V8" s="45"/>
-      <c r="W8" s="47"/>
-      <c r="X8" s="49"/>
-      <c r="Y8" s="45"/>
-      <c r="Z8" s="47"/>
-      <c r="AA8" s="49"/>
-      <c r="AB8" s="45"/>
-      <c r="AC8" s="47"/>
-      <c r="AD8" s="49"/>
-      <c r="AE8" s="45"/>
-      <c r="AF8" s="47"/>
-      <c r="AG8" s="49"/>
-      <c r="AH8" s="45"/>
-      <c r="AI8" s="47"/>
-      <c r="AJ8" s="49"/>
-      <c r="AK8" s="45"/>
-      <c r="AL8" s="47"/>
-      <c r="AM8" s="49"/>
-      <c r="AN8" s="45"/>
-      <c r="AO8" s="47"/>
-      <c r="AP8" s="49"/>
-      <c r="AQ8" s="45"/>
-      <c r="AR8" s="47"/>
-      <c r="AS8" s="49"/>
-      <c r="AT8" s="47"/>
-      <c r="AU8" s="47"/>
-      <c r="AV8" s="53"/>
-      <c r="AW8" s="54"/>
-      <c r="AX8" s="47"/>
-      <c r="AY8" s="49"/>
-      <c r="AZ8" s="45"/>
-      <c r="BA8" s="47"/>
-      <c r="BB8" s="49"/>
-      <c r="BC8" s="45"/>
-      <c r="BD8" s="47"/>
-      <c r="BE8" s="49"/>
-      <c r="BF8" s="45"/>
-      <c r="BG8" s="47"/>
-      <c r="BH8" s="49"/>
-      <c r="BI8" s="45"/>
-      <c r="BJ8" s="47"/>
-      <c r="BK8" s="49"/>
-      <c r="BL8" s="45"/>
-      <c r="BM8" s="47"/>
-      <c r="BN8" s="49"/>
-      <c r="BO8" s="45"/>
-      <c r="BP8" s="47"/>
-      <c r="BQ8" s="49"/>
-      <c r="BR8" s="45"/>
-      <c r="BS8" s="47"/>
-      <c r="BT8" s="49"/>
-      <c r="BU8" s="45"/>
-      <c r="BV8" s="47"/>
-      <c r="BW8" s="49"/>
-      <c r="BX8" s="45"/>
-      <c r="BY8" s="47"/>
-      <c r="BZ8" s="49"/>
-      <c r="CA8" s="45"/>
-      <c r="CB8" s="47"/>
-      <c r="CC8" s="49"/>
-      <c r="CD8" s="47"/>
-      <c r="CE8" s="47"/>
-      <c r="CF8" s="53"/>
-      <c r="CG8" s="54"/>
-      <c r="CH8" s="47"/>
-      <c r="CI8" s="49"/>
-      <c r="CJ8" s="45"/>
-      <c r="CK8" s="47"/>
-      <c r="CL8" s="49"/>
-      <c r="CM8" s="45"/>
-      <c r="CN8" s="47"/>
-      <c r="CO8" s="49"/>
-      <c r="CP8" s="45"/>
-      <c r="CQ8" s="47"/>
-      <c r="CR8" s="49"/>
-      <c r="CS8" s="45"/>
-      <c r="CT8" s="47"/>
-      <c r="CU8" s="49"/>
-      <c r="CV8" s="45"/>
-      <c r="CW8" s="47"/>
-      <c r="CX8" s="49"/>
-      <c r="CY8" s="45"/>
-      <c r="CZ8" s="47"/>
-      <c r="DA8" s="49"/>
-      <c r="DB8" s="45"/>
-      <c r="DC8" s="47"/>
-      <c r="DD8" s="49"/>
-      <c r="DE8" s="45"/>
-      <c r="DF8" s="47"/>
-      <c r="DG8" s="49"/>
-      <c r="DH8" s="45"/>
-      <c r="DI8" s="47"/>
-      <c r="DJ8" s="49"/>
-      <c r="DK8" s="45"/>
-      <c r="DL8" s="47"/>
-      <c r="DM8" s="49"/>
-      <c r="DN8" s="47"/>
-      <c r="DO8" s="47"/>
-      <c r="DP8" s="53"/>
-      <c r="DQ8" s="54"/>
-      <c r="DR8" s="47"/>
-      <c r="DS8" s="49"/>
-      <c r="DT8" s="45"/>
-      <c r="DU8" s="47"/>
-      <c r="DV8" s="49"/>
-      <c r="DW8" s="45"/>
-      <c r="DX8" s="47"/>
-      <c r="DY8" s="49"/>
-      <c r="DZ8" s="45"/>
-      <c r="EA8" s="47"/>
-      <c r="EB8" s="49"/>
-      <c r="EC8" s="45"/>
-      <c r="ED8" s="47"/>
-      <c r="EE8" s="49"/>
-      <c r="EF8" s="45"/>
-      <c r="EG8" s="47"/>
-      <c r="EH8" s="49"/>
-      <c r="EI8" s="45"/>
-      <c r="EJ8" s="47"/>
-      <c r="EK8" s="49"/>
-      <c r="EL8" s="45"/>
-      <c r="EM8" s="47"/>
-      <c r="EN8" s="49"/>
-      <c r="EO8" s="45"/>
-      <c r="EP8" s="47"/>
-      <c r="EQ8" s="49"/>
-      <c r="ER8" s="45"/>
-      <c r="ES8" s="47"/>
-      <c r="ET8" s="49"/>
-      <c r="EU8" s="45"/>
-      <c r="EV8" s="47"/>
-      <c r="EW8" s="49"/>
-      <c r="EX8" s="47"/>
-      <c r="EY8" s="47"/>
-      <c r="EZ8" s="53"/>
-      <c r="FA8" s="54"/>
-      <c r="FB8" s="47"/>
-      <c r="FC8" s="49"/>
-      <c r="FD8" s="45"/>
-      <c r="FE8" s="47"/>
-      <c r="FF8" s="49"/>
-      <c r="FG8" s="45"/>
-      <c r="FH8" s="47"/>
-      <c r="FI8" s="49"/>
-      <c r="FJ8" s="45"/>
-      <c r="FK8" s="47"/>
-      <c r="FL8" s="49"/>
-      <c r="FM8" s="45"/>
-      <c r="FN8" s="47"/>
-      <c r="FO8" s="49"/>
-      <c r="FP8" s="45"/>
-      <c r="FQ8" s="47"/>
-      <c r="FR8" s="49"/>
-      <c r="FS8" s="45"/>
-      <c r="FT8" s="47"/>
-      <c r="FU8" s="49"/>
-      <c r="FV8" s="45"/>
-      <c r="FW8" s="47"/>
-      <c r="FX8" s="49"/>
-      <c r="FY8" s="45"/>
-      <c r="FZ8" s="47"/>
-      <c r="GA8" s="49"/>
-      <c r="GB8" s="45"/>
-      <c r="GC8" s="47"/>
-      <c r="GD8" s="49"/>
-      <c r="GE8" s="45"/>
-      <c r="GF8" s="47"/>
-      <c r="GG8" s="49"/>
-      <c r="GH8" s="47"/>
-      <c r="GI8" s="47"/>
-      <c r="GJ8" s="53"/>
-      <c r="GK8" s="54"/>
-      <c r="GL8" s="47"/>
-      <c r="GM8" s="49"/>
-      <c r="GN8" s="45"/>
-      <c r="GO8" s="47"/>
-      <c r="GP8" s="49"/>
-      <c r="GQ8" s="45"/>
-      <c r="GR8" s="47"/>
-      <c r="GS8" s="49"/>
-      <c r="GT8" s="45"/>
-      <c r="GU8" s="47"/>
-      <c r="GV8" s="49"/>
-      <c r="GW8" s="45"/>
-      <c r="GX8" s="47"/>
-      <c r="GY8" s="49"/>
-      <c r="GZ8" s="45"/>
-      <c r="HA8" s="47"/>
-      <c r="HB8" s="49"/>
-      <c r="HC8" s="45"/>
-      <c r="HD8" s="47"/>
-      <c r="HE8" s="49"/>
-      <c r="HF8" s="45"/>
-      <c r="HG8" s="47"/>
-      <c r="HH8" s="49"/>
-      <c r="HI8" s="45"/>
-      <c r="HJ8" s="47"/>
-      <c r="HK8" s="49"/>
-      <c r="HL8" s="45"/>
-      <c r="HM8" s="47"/>
-      <c r="HN8" s="49"/>
-      <c r="HO8" s="45"/>
-      <c r="HP8" s="47"/>
-      <c r="HQ8" s="49"/>
-      <c r="HR8" s="47"/>
-      <c r="HS8" s="47"/>
-      <c r="HT8" s="53"/>
-      <c r="HU8" s="54"/>
-      <c r="HV8" s="47"/>
-      <c r="HW8" s="49"/>
-      <c r="HX8" s="45"/>
-      <c r="HY8" s="47"/>
-      <c r="HZ8" s="49"/>
-      <c r="IA8" s="45"/>
-      <c r="IB8" s="47"/>
-      <c r="IC8" s="49"/>
-      <c r="ID8" s="45"/>
-      <c r="IE8" s="47"/>
-      <c r="IF8" s="49"/>
-      <c r="IG8" s="45"/>
-      <c r="IH8" s="47"/>
-      <c r="II8" s="49"/>
-      <c r="IJ8" s="45"/>
-      <c r="IK8" s="47"/>
-      <c r="IL8" s="49"/>
-      <c r="IM8" s="45"/>
-      <c r="IN8" s="47"/>
-      <c r="IO8" s="49"/>
-      <c r="IP8" s="45"/>
-      <c r="IQ8" s="47"/>
-      <c r="IR8" s="49"/>
-      <c r="IS8" s="45"/>
-      <c r="IT8" s="47"/>
-      <c r="IU8" s="49"/>
-      <c r="IV8" s="45"/>
-      <c r="IW8" s="47"/>
-      <c r="IX8" s="49"/>
-      <c r="IY8" s="45"/>
-      <c r="IZ8" s="47"/>
-      <c r="JA8" s="49"/>
-      <c r="JB8" s="47"/>
-      <c r="JC8" s="47"/>
-      <c r="JD8" s="53"/>
-      <c r="JE8" s="54"/>
-      <c r="JF8" s="47"/>
-      <c r="JG8" s="49"/>
-      <c r="JH8" s="45"/>
-      <c r="JI8" s="47"/>
-      <c r="JJ8" s="49"/>
-      <c r="JK8" s="45"/>
-      <c r="JL8" s="47"/>
-      <c r="JM8" s="49"/>
-      <c r="JN8" s="45"/>
-      <c r="JO8" s="47"/>
-      <c r="JP8" s="49"/>
-      <c r="JQ8" s="45"/>
-      <c r="JR8" s="47"/>
-      <c r="JS8" s="49"/>
-      <c r="JT8" s="45"/>
-      <c r="JU8" s="47"/>
-      <c r="JV8" s="49"/>
-      <c r="JW8" s="45"/>
-      <c r="JX8" s="47"/>
-      <c r="JY8" s="49"/>
-      <c r="JZ8" s="45"/>
-      <c r="KA8" s="47"/>
-      <c r="KB8" s="49"/>
-      <c r="KC8" s="45"/>
-      <c r="KD8" s="47"/>
-      <c r="KE8" s="49"/>
-      <c r="KF8" s="45"/>
-      <c r="KG8" s="47"/>
-      <c r="KH8" s="49"/>
-      <c r="KI8" s="45"/>
-      <c r="KJ8" s="47"/>
-      <c r="KK8" s="49"/>
-      <c r="KL8" s="47"/>
-      <c r="KM8" s="47"/>
-      <c r="KN8" s="49"/>
-      <c r="KO8" s="122"/>
-      <c r="KP8" s="49"/>
+      <c r="M8" s="71"/>
+      <c r="N8" s="56"/>
+      <c r="O8" s="53"/>
+      <c r="P8" s="71"/>
+      <c r="Q8" s="56"/>
+      <c r="R8" s="53"/>
+      <c r="S8" s="71"/>
+      <c r="T8" s="56"/>
+      <c r="U8" s="53"/>
+      <c r="V8" s="71"/>
+      <c r="W8" s="56"/>
+      <c r="X8" s="53"/>
+      <c r="Y8" s="71"/>
+      <c r="Z8" s="56"/>
+      <c r="AA8" s="53"/>
+      <c r="AB8" s="71"/>
+      <c r="AC8" s="56"/>
+      <c r="AD8" s="53"/>
+      <c r="AE8" s="71"/>
+      <c r="AF8" s="56"/>
+      <c r="AG8" s="53"/>
+      <c r="AH8" s="71"/>
+      <c r="AI8" s="56"/>
+      <c r="AJ8" s="53"/>
+      <c r="AK8" s="71"/>
+      <c r="AL8" s="56"/>
+      <c r="AM8" s="53"/>
+      <c r="AN8" s="71"/>
+      <c r="AO8" s="56"/>
+      <c r="AP8" s="53"/>
+      <c r="AQ8" s="71"/>
+      <c r="AR8" s="56"/>
+      <c r="AS8" s="53"/>
+      <c r="AT8" s="56"/>
+      <c r="AU8" s="56"/>
+      <c r="AV8" s="73"/>
+      <c r="AW8" s="66"/>
+      <c r="AX8" s="56"/>
+      <c r="AY8" s="53"/>
+      <c r="AZ8" s="71"/>
+      <c r="BA8" s="56"/>
+      <c r="BB8" s="53"/>
+      <c r="BC8" s="71"/>
+      <c r="BD8" s="56"/>
+      <c r="BE8" s="53"/>
+      <c r="BF8" s="71"/>
+      <c r="BG8" s="56"/>
+      <c r="BH8" s="53"/>
+      <c r="BI8" s="71"/>
+      <c r="BJ8" s="56"/>
+      <c r="BK8" s="53"/>
+      <c r="BL8" s="71"/>
+      <c r="BM8" s="56"/>
+      <c r="BN8" s="53"/>
+      <c r="BO8" s="71"/>
+      <c r="BP8" s="56"/>
+      <c r="BQ8" s="53"/>
+      <c r="BR8" s="71"/>
+      <c r="BS8" s="56"/>
+      <c r="BT8" s="53"/>
+      <c r="BU8" s="71"/>
+      <c r="BV8" s="56"/>
+      <c r="BW8" s="53"/>
+      <c r="BX8" s="71"/>
+      <c r="BY8" s="56"/>
+      <c r="BZ8" s="53"/>
+      <c r="CA8" s="71"/>
+      <c r="CB8" s="56"/>
+      <c r="CC8" s="53"/>
+      <c r="CD8" s="56"/>
+      <c r="CE8" s="56"/>
+      <c r="CF8" s="73"/>
+      <c r="CG8" s="66"/>
+      <c r="CH8" s="56"/>
+      <c r="CI8" s="53"/>
+      <c r="CJ8" s="71"/>
+      <c r="CK8" s="56"/>
+      <c r="CL8" s="53"/>
+      <c r="CM8" s="71"/>
+      <c r="CN8" s="56"/>
+      <c r="CO8" s="53"/>
+      <c r="CP8" s="71"/>
+      <c r="CQ8" s="56"/>
+      <c r="CR8" s="53"/>
+      <c r="CS8" s="71"/>
+      <c r="CT8" s="56"/>
+      <c r="CU8" s="53"/>
+      <c r="CV8" s="71"/>
+      <c r="CW8" s="56"/>
+      <c r="CX8" s="53"/>
+      <c r="CY8" s="71"/>
+      <c r="CZ8" s="56"/>
+      <c r="DA8" s="53"/>
+      <c r="DB8" s="71"/>
+      <c r="DC8" s="56"/>
+      <c r="DD8" s="53"/>
+      <c r="DE8" s="71"/>
+      <c r="DF8" s="56"/>
+      <c r="DG8" s="53"/>
+      <c r="DH8" s="71"/>
+      <c r="DI8" s="56"/>
+      <c r="DJ8" s="53"/>
+      <c r="DK8" s="71"/>
+      <c r="DL8" s="56"/>
+      <c r="DM8" s="53"/>
+      <c r="DN8" s="56"/>
+      <c r="DO8" s="56"/>
+      <c r="DP8" s="73"/>
+      <c r="DQ8" s="66"/>
+      <c r="DR8" s="56"/>
+      <c r="DS8" s="53"/>
+      <c r="DT8" s="71"/>
+      <c r="DU8" s="56"/>
+      <c r="DV8" s="53"/>
+      <c r="DW8" s="71"/>
+      <c r="DX8" s="56"/>
+      <c r="DY8" s="53"/>
+      <c r="DZ8" s="71"/>
+      <c r="EA8" s="56"/>
+      <c r="EB8" s="53"/>
+      <c r="EC8" s="71"/>
+      <c r="ED8" s="56"/>
+      <c r="EE8" s="53"/>
+      <c r="EF8" s="71"/>
+      <c r="EG8" s="56"/>
+      <c r="EH8" s="53"/>
+      <c r="EI8" s="71"/>
+      <c r="EJ8" s="56"/>
+      <c r="EK8" s="53"/>
+      <c r="EL8" s="71"/>
+      <c r="EM8" s="56"/>
+      <c r="EN8" s="53"/>
+      <c r="EO8" s="71"/>
+      <c r="EP8" s="56"/>
+      <c r="EQ8" s="53"/>
+      <c r="ER8" s="71"/>
+      <c r="ES8" s="56"/>
+      <c r="ET8" s="53"/>
+      <c r="EU8" s="71"/>
+      <c r="EV8" s="56"/>
+      <c r="EW8" s="53"/>
+      <c r="EX8" s="56"/>
+      <c r="EY8" s="56"/>
+      <c r="EZ8" s="73"/>
+      <c r="FA8" s="66"/>
+      <c r="FB8" s="56"/>
+      <c r="FC8" s="53"/>
+      <c r="FD8" s="71"/>
+      <c r="FE8" s="56"/>
+      <c r="FF8" s="53"/>
+      <c r="FG8" s="71"/>
+      <c r="FH8" s="56"/>
+      <c r="FI8" s="53"/>
+      <c r="FJ8" s="71"/>
+      <c r="FK8" s="56"/>
+      <c r="FL8" s="53"/>
+      <c r="FM8" s="71"/>
+      <c r="FN8" s="56"/>
+      <c r="FO8" s="53"/>
+      <c r="FP8" s="71"/>
+      <c r="FQ8" s="56"/>
+      <c r="FR8" s="53"/>
+      <c r="FS8" s="71"/>
+      <c r="FT8" s="56"/>
+      <c r="FU8" s="53"/>
+      <c r="FV8" s="71"/>
+      <c r="FW8" s="56"/>
+      <c r="FX8" s="53"/>
+      <c r="FY8" s="71"/>
+      <c r="FZ8" s="56"/>
+      <c r="GA8" s="53"/>
+      <c r="GB8" s="71"/>
+      <c r="GC8" s="56"/>
+      <c r="GD8" s="53"/>
+      <c r="GE8" s="71"/>
+      <c r="GF8" s="56"/>
+      <c r="GG8" s="53"/>
+      <c r="GH8" s="56"/>
+      <c r="GI8" s="56"/>
+      <c r="GJ8" s="73"/>
+      <c r="GK8" s="66"/>
+      <c r="GL8" s="56"/>
+      <c r="GM8" s="53"/>
+      <c r="GN8" s="71"/>
+      <c r="GO8" s="56"/>
+      <c r="GP8" s="53"/>
+      <c r="GQ8" s="71"/>
+      <c r="GR8" s="56"/>
+      <c r="GS8" s="53"/>
+      <c r="GT8" s="71"/>
+      <c r="GU8" s="56"/>
+      <c r="GV8" s="53"/>
+      <c r="GW8" s="71"/>
+      <c r="GX8" s="56"/>
+      <c r="GY8" s="53"/>
+      <c r="GZ8" s="71"/>
+      <c r="HA8" s="56"/>
+      <c r="HB8" s="53"/>
+      <c r="HC8" s="71"/>
+      <c r="HD8" s="56"/>
+      <c r="HE8" s="53"/>
+      <c r="HF8" s="71"/>
+      <c r="HG8" s="56"/>
+      <c r="HH8" s="53"/>
+      <c r="HI8" s="71"/>
+      <c r="HJ8" s="56"/>
+      <c r="HK8" s="53"/>
+      <c r="HL8" s="71"/>
+      <c r="HM8" s="56"/>
+      <c r="HN8" s="53"/>
+      <c r="HO8" s="71"/>
+      <c r="HP8" s="56"/>
+      <c r="HQ8" s="53"/>
+      <c r="HR8" s="56"/>
+      <c r="HS8" s="56"/>
+      <c r="HT8" s="73"/>
+      <c r="HU8" s="66"/>
+      <c r="HV8" s="56"/>
+      <c r="HW8" s="53"/>
+      <c r="HX8" s="71"/>
+      <c r="HY8" s="56"/>
+      <c r="HZ8" s="53"/>
+      <c r="IA8" s="71"/>
+      <c r="IB8" s="56"/>
+      <c r="IC8" s="53"/>
+      <c r="ID8" s="71"/>
+      <c r="IE8" s="56"/>
+      <c r="IF8" s="53"/>
+      <c r="IG8" s="71"/>
+      <c r="IH8" s="56"/>
+      <c r="II8" s="53"/>
+      <c r="IJ8" s="71"/>
+      <c r="IK8" s="56"/>
+      <c r="IL8" s="53"/>
+      <c r="IM8" s="71"/>
+      <c r="IN8" s="56"/>
+      <c r="IO8" s="53"/>
+      <c r="IP8" s="71"/>
+      <c r="IQ8" s="56"/>
+      <c r="IR8" s="53"/>
+      <c r="IS8" s="71"/>
+      <c r="IT8" s="56"/>
+      <c r="IU8" s="53"/>
+      <c r="IV8" s="71"/>
+      <c r="IW8" s="56"/>
+      <c r="IX8" s="53"/>
+      <c r="IY8" s="71"/>
+      <c r="IZ8" s="56"/>
+      <c r="JA8" s="53"/>
+      <c r="JB8" s="56"/>
+      <c r="JC8" s="56"/>
+      <c r="JD8" s="73"/>
+      <c r="JE8" s="66"/>
+      <c r="JF8" s="56"/>
+      <c r="JG8" s="53"/>
+      <c r="JH8" s="71"/>
+      <c r="JI8" s="56"/>
+      <c r="JJ8" s="53"/>
+      <c r="JK8" s="71"/>
+      <c r="JL8" s="56"/>
+      <c r="JM8" s="53"/>
+      <c r="JN8" s="71"/>
+      <c r="JO8" s="56"/>
+      <c r="JP8" s="53"/>
+      <c r="JQ8" s="71"/>
+      <c r="JR8" s="56"/>
+      <c r="JS8" s="53"/>
+      <c r="JT8" s="71"/>
+      <c r="JU8" s="56"/>
+      <c r="JV8" s="53"/>
+      <c r="JW8" s="71"/>
+      <c r="JX8" s="56"/>
+      <c r="JY8" s="53"/>
+      <c r="JZ8" s="71"/>
+      <c r="KA8" s="56"/>
+      <c r="KB8" s="53"/>
+      <c r="KC8" s="71"/>
+      <c r="KD8" s="56"/>
+      <c r="KE8" s="53"/>
+      <c r="KF8" s="71"/>
+      <c r="KG8" s="56"/>
+      <c r="KH8" s="53"/>
+      <c r="KI8" s="71"/>
+      <c r="KJ8" s="56"/>
+      <c r="KK8" s="53"/>
+      <c r="KL8" s="56"/>
+      <c r="KM8" s="56"/>
+      <c r="KN8" s="53"/>
+      <c r="KO8" s="120"/>
+      <c r="KP8" s="53"/>
       <c r="KQ8" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="KR8" s="50" t="s">
+      <c r="KR8" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="KS8" s="107"/>
-      <c r="KT8" s="51"/>
-      <c r="KU8" s="48" t="s">
+      <c r="KS8" s="49"/>
+      <c r="KT8" s="50"/>
+      <c r="KU8" s="52" t="s">
         <v>62</v>
       </c>
-      <c r="KV8" s="48" t="s">
+      <c r="KV8" s="52" t="s">
         <v>63</v>
       </c>
       <c r="KW8" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="KX8" s="50" t="s">
+      <c r="KX8" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="KY8" s="107"/>
-      <c r="KZ8" s="51"/>
-      <c r="LA8" s="48" t="s">
+      <c r="KY8" s="49"/>
+      <c r="KZ8" s="50"/>
+      <c r="LA8" s="52" t="s">
         <v>62</v>
       </c>
-      <c r="LB8" s="48" t="s">
+      <c r="LB8" s="52" t="s">
         <v>63</v>
       </c>
       <c r="LC8" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="LD8" s="50" t="s">
+      <c r="LD8" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="LE8" s="107"/>
-      <c r="LF8" s="51"/>
-      <c r="LG8" s="49"/>
-      <c r="LH8" s="49"/>
+      <c r="LE8" s="49"/>
+      <c r="LF8" s="50"/>
+      <c r="LG8" s="53"/>
+      <c r="LH8" s="53"/>
       <c r="LI8" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="LJ8" s="50" t="s">
+      <c r="LJ8" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="LK8" s="107"/>
-      <c r="LL8" s="51"/>
-      <c r="LM8" s="48" t="s">
+      <c r="LK8" s="49"/>
+      <c r="LL8" s="50"/>
+      <c r="LM8" s="52" t="s">
         <v>62</v>
       </c>
-      <c r="LN8" s="48" t="s">
+      <c r="LN8" s="52" t="s">
         <v>63</v>
       </c>
       <c r="LO8" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="LP8" s="50" t="s">
+      <c r="LP8" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="LQ8" s="107"/>
-      <c r="LR8" s="51"/>
-      <c r="LS8" s="48" t="s">
+      <c r="LQ8" s="49"/>
+      <c r="LR8" s="50"/>
+      <c r="LS8" s="52" t="s">
         <v>62</v>
       </c>
-      <c r="LT8" s="48" t="s">
+      <c r="LT8" s="52" t="s">
         <v>63</v>
       </c>
       <c r="LU8" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="LV8" s="50" t="s">
+      <c r="LV8" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="LW8" s="107"/>
-      <c r="LX8" s="51"/>
+      <c r="LW8" s="49"/>
+      <c r="LX8" s="50"/>
       <c r="LY8" s="46" t="s">
         <v>62</v>
       </c>
@@ -7461,11 +7462,11 @@
       <c r="MA8" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="MB8" s="50" t="s">
+      <c r="MB8" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="MC8" s="107"/>
-      <c r="MD8" s="51"/>
+      <c r="MC8" s="49"/>
+      <c r="MD8" s="50"/>
       <c r="ME8" s="46" t="s">
         <v>62</v>
       </c>
@@ -7475,21 +7476,21 @@
       <c r="MG8" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="MH8" s="50" t="s">
+      <c r="MH8" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="MI8" s="107"/>
-      <c r="MJ8" s="51"/>
-      <c r="MK8" s="71"/>
-      <c r="ML8" s="71"/>
+      <c r="MI8" s="49"/>
+      <c r="MJ8" s="50"/>
+      <c r="MK8" s="47"/>
+      <c r="ML8" s="47"/>
       <c r="MM8" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="MN8" s="50" t="s">
+      <c r="MN8" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="MO8" s="107"/>
-      <c r="MP8" s="51"/>
+      <c r="MO8" s="49"/>
+      <c r="MP8" s="50"/>
       <c r="MQ8" s="46" t="s">
         <v>62</v>
       </c>
@@ -7499,11 +7500,11 @@
       <c r="MS8" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="MT8" s="50" t="s">
+      <c r="MT8" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="MU8" s="107"/>
-      <c r="MV8" s="51"/>
+      <c r="MU8" s="49"/>
+      <c r="MV8" s="50"/>
       <c r="MW8" s="46" t="s">
         <v>62</v>
       </c>
@@ -7513,11 +7514,11 @@
       <c r="MY8" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="MZ8" s="50" t="s">
+      <c r="MZ8" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="NA8" s="107"/>
-      <c r="NB8" s="51"/>
+      <c r="NA8" s="49"/>
+      <c r="NB8" s="50"/>
       <c r="NC8" s="46" t="s">
         <v>62</v>
       </c>
@@ -7527,21 +7528,21 @@
       <c r="NE8" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="NF8" s="50" t="s">
+      <c r="NF8" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="NG8" s="107"/>
-      <c r="NH8" s="107"/>
-      <c r="NI8" s="110"/>
-      <c r="NJ8" s="45"/>
-      <c r="NK8" s="55" t="s">
+      <c r="NG8" s="49"/>
+      <c r="NH8" s="49"/>
+      <c r="NI8" s="106"/>
+      <c r="NJ8" s="71"/>
+      <c r="NK8" s="69" t="s">
         <v>62</v>
       </c>
-      <c r="NL8" s="50" t="s">
+      <c r="NL8" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="NM8" s="107"/>
-      <c r="NN8" s="51"/>
+      <c r="NM8" s="49"/>
+      <c r="NN8" s="50"/>
       <c r="NO8" s="46" t="s">
         <v>62</v>
       </c>
@@ -7551,11 +7552,11 @@
       <c r="NQ8" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="NR8" s="50" t="s">
+      <c r="NR8" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="NS8" s="107"/>
-      <c r="NT8" s="51"/>
+      <c r="NS8" s="49"/>
+      <c r="NT8" s="50"/>
       <c r="NU8" s="46" t="s">
         <v>62</v>
       </c>
@@ -7565,322 +7566,322 @@
       <c r="NW8" s="46" t="s">
         <v>62</v>
       </c>
-      <c r="NX8" s="50" t="s">
+      <c r="NX8" s="48" t="s">
         <v>27</v>
       </c>
-      <c r="NY8" s="107"/>
-      <c r="NZ8" s="135"/>
-      <c r="OA8" s="137"/>
-      <c r="OB8" s="133"/>
-      <c r="OC8" s="133"/>
-      <c r="OD8" s="133"/>
-      <c r="OE8" s="133"/>
-      <c r="OF8" s="133"/>
+      <c r="NY8" s="49"/>
+      <c r="NZ8" s="51"/>
+      <c r="OA8" s="68"/>
+      <c r="OB8" s="55"/>
+      <c r="OC8" s="55"/>
+      <c r="OD8" s="55"/>
+      <c r="OE8" s="55"/>
+      <c r="OF8" s="55"/>
     </row>
     <row r="9" spans="1:396" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="57"/>
-      <c r="B9" s="57"/>
-      <c r="C9" s="57"/>
-      <c r="D9" s="57"/>
+      <c r="A9" s="64"/>
+      <c r="B9" s="64"/>
+      <c r="C9" s="64"/>
+      <c r="D9" s="64"/>
       <c r="E9" s="7"/>
-      <c r="F9" s="57"/>
+      <c r="F9" s="64"/>
       <c r="G9" s="7"/>
-      <c r="H9" s="57"/>
-      <c r="I9" s="57"/>
-      <c r="J9" s="57"/>
-      <c r="K9" s="57"/>
-      <c r="L9" s="57"/>
+      <c r="H9" s="64"/>
+      <c r="I9" s="64"/>
+      <c r="J9" s="64"/>
+      <c r="K9" s="64"/>
+      <c r="L9" s="64"/>
       <c r="M9" s="46"/>
-      <c r="N9" s="48"/>
-      <c r="O9" s="49"/>
+      <c r="N9" s="52"/>
+      <c r="O9" s="53"/>
       <c r="P9" s="46"/>
-      <c r="Q9" s="48"/>
-      <c r="R9" s="49"/>
+      <c r="Q9" s="52"/>
+      <c r="R9" s="53"/>
       <c r="S9" s="46"/>
-      <c r="T9" s="48"/>
-      <c r="U9" s="49"/>
+      <c r="T9" s="52"/>
+      <c r="U9" s="53"/>
       <c r="V9" s="46"/>
-      <c r="W9" s="48"/>
-      <c r="X9" s="49"/>
+      <c r="W9" s="52"/>
+      <c r="X9" s="53"/>
       <c r="Y9" s="46"/>
-      <c r="Z9" s="48"/>
-      <c r="AA9" s="49"/>
+      <c r="Z9" s="52"/>
+      <c r="AA9" s="53"/>
       <c r="AB9" s="46"/>
-      <c r="AC9" s="48"/>
-      <c r="AD9" s="49"/>
+      <c r="AC9" s="52"/>
+      <c r="AD9" s="53"/>
       <c r="AE9" s="46"/>
-      <c r="AF9" s="48"/>
-      <c r="AG9" s="49"/>
+      <c r="AF9" s="52"/>
+      <c r="AG9" s="53"/>
       <c r="AH9" s="46"/>
-      <c r="AI9" s="48"/>
-      <c r="AJ9" s="49"/>
+      <c r="AI9" s="52"/>
+      <c r="AJ9" s="53"/>
       <c r="AK9" s="46"/>
-      <c r="AL9" s="48"/>
-      <c r="AM9" s="49"/>
+      <c r="AL9" s="52"/>
+      <c r="AM9" s="53"/>
       <c r="AN9" s="46"/>
-      <c r="AO9" s="48"/>
-      <c r="AP9" s="49"/>
+      <c r="AO9" s="52"/>
+      <c r="AP9" s="53"/>
       <c r="AQ9" s="46"/>
-      <c r="AR9" s="48"/>
-      <c r="AS9" s="49"/>
-      <c r="AT9" s="48"/>
-      <c r="AU9" s="48"/>
-      <c r="AV9" s="53"/>
-      <c r="AW9" s="55"/>
-      <c r="AX9" s="48"/>
-      <c r="AY9" s="49"/>
+      <c r="AR9" s="52"/>
+      <c r="AS9" s="53"/>
+      <c r="AT9" s="52"/>
+      <c r="AU9" s="52"/>
+      <c r="AV9" s="73"/>
+      <c r="AW9" s="69"/>
+      <c r="AX9" s="52"/>
+      <c r="AY9" s="53"/>
       <c r="AZ9" s="46"/>
-      <c r="BA9" s="48"/>
-      <c r="BB9" s="49"/>
+      <c r="BA9" s="52"/>
+      <c r="BB9" s="53"/>
       <c r="BC9" s="46"/>
-      <c r="BD9" s="48"/>
-      <c r="BE9" s="49"/>
+      <c r="BD9" s="52"/>
+      <c r="BE9" s="53"/>
       <c r="BF9" s="46"/>
-      <c r="BG9" s="48"/>
-      <c r="BH9" s="49"/>
+      <c r="BG9" s="52"/>
+      <c r="BH9" s="53"/>
       <c r="BI9" s="46"/>
-      <c r="BJ9" s="48"/>
-      <c r="BK9" s="49"/>
+      <c r="BJ9" s="52"/>
+      <c r="BK9" s="53"/>
       <c r="BL9" s="46"/>
-      <c r="BM9" s="48"/>
-      <c r="BN9" s="49"/>
+      <c r="BM9" s="52"/>
+      <c r="BN9" s="53"/>
       <c r="BO9" s="46"/>
-      <c r="BP9" s="48"/>
-      <c r="BQ9" s="49"/>
+      <c r="BP9" s="52"/>
+      <c r="BQ9" s="53"/>
       <c r="BR9" s="46"/>
-      <c r="BS9" s="48"/>
-      <c r="BT9" s="49"/>
+      <c r="BS9" s="52"/>
+      <c r="BT9" s="53"/>
       <c r="BU9" s="46"/>
-      <c r="BV9" s="48"/>
-      <c r="BW9" s="49"/>
+      <c r="BV9" s="52"/>
+      <c r="BW9" s="53"/>
       <c r="BX9" s="46"/>
-      <c r="BY9" s="48"/>
-      <c r="BZ9" s="49"/>
+      <c r="BY9" s="52"/>
+      <c r="BZ9" s="53"/>
       <c r="CA9" s="46"/>
-      <c r="CB9" s="48"/>
-      <c r="CC9" s="49"/>
-      <c r="CD9" s="48"/>
-      <c r="CE9" s="48"/>
-      <c r="CF9" s="53"/>
-      <c r="CG9" s="55"/>
-      <c r="CH9" s="48"/>
-      <c r="CI9" s="49"/>
+      <c r="CB9" s="52"/>
+      <c r="CC9" s="53"/>
+      <c r="CD9" s="52"/>
+      <c r="CE9" s="52"/>
+      <c r="CF9" s="73"/>
+      <c r="CG9" s="69"/>
+      <c r="CH9" s="52"/>
+      <c r="CI9" s="53"/>
       <c r="CJ9" s="46"/>
-      <c r="CK9" s="48"/>
-      <c r="CL9" s="49"/>
+      <c r="CK9" s="52"/>
+      <c r="CL9" s="53"/>
       <c r="CM9" s="46"/>
-      <c r="CN9" s="48"/>
-      <c r="CO9" s="49"/>
+      <c r="CN9" s="52"/>
+      <c r="CO9" s="53"/>
       <c r="CP9" s="46"/>
-      <c r="CQ9" s="48"/>
-      <c r="CR9" s="49"/>
+      <c r="CQ9" s="52"/>
+      <c r="CR9" s="53"/>
       <c r="CS9" s="46"/>
-      <c r="CT9" s="48"/>
-      <c r="CU9" s="49"/>
+      <c r="CT9" s="52"/>
+      <c r="CU9" s="53"/>
       <c r="CV9" s="46"/>
-      <c r="CW9" s="48"/>
-      <c r="CX9" s="49"/>
+      <c r="CW9" s="52"/>
+      <c r="CX9" s="53"/>
       <c r="CY9" s="46"/>
-      <c r="CZ9" s="48"/>
-      <c r="DA9" s="49"/>
+      <c r="CZ9" s="52"/>
+      <c r="DA9" s="53"/>
       <c r="DB9" s="46"/>
-      <c r="DC9" s="48"/>
-      <c r="DD9" s="49"/>
+      <c r="DC9" s="52"/>
+      <c r="DD9" s="53"/>
       <c r="DE9" s="46"/>
-      <c r="DF9" s="48"/>
-      <c r="DG9" s="49"/>
+      <c r="DF9" s="52"/>
+      <c r="DG9" s="53"/>
       <c r="DH9" s="46"/>
-      <c r="DI9" s="48"/>
-      <c r="DJ9" s="49"/>
+      <c r="DI9" s="52"/>
+      <c r="DJ9" s="53"/>
       <c r="DK9" s="46"/>
-      <c r="DL9" s="48"/>
-      <c r="DM9" s="49"/>
-      <c r="DN9" s="48"/>
-      <c r="DO9" s="48"/>
-      <c r="DP9" s="53"/>
-      <c r="DQ9" s="55"/>
-      <c r="DR9" s="48"/>
-      <c r="DS9" s="49"/>
+      <c r="DL9" s="52"/>
+      <c r="DM9" s="53"/>
+      <c r="DN9" s="52"/>
+      <c r="DO9" s="52"/>
+      <c r="DP9" s="73"/>
+      <c r="DQ9" s="69"/>
+      <c r="DR9" s="52"/>
+      <c r="DS9" s="53"/>
       <c r="DT9" s="46"/>
-      <c r="DU9" s="48"/>
-      <c r="DV9" s="49"/>
+      <c r="DU9" s="52"/>
+      <c r="DV9" s="53"/>
       <c r="DW9" s="46"/>
-      <c r="DX9" s="48"/>
-      <c r="DY9" s="49"/>
+      <c r="DX9" s="52"/>
+      <c r="DY9" s="53"/>
       <c r="DZ9" s="46"/>
-      <c r="EA9" s="48"/>
-      <c r="EB9" s="49"/>
+      <c r="EA9" s="52"/>
+      <c r="EB9" s="53"/>
       <c r="EC9" s="46"/>
-      <c r="ED9" s="48"/>
-      <c r="EE9" s="49"/>
+      <c r="ED9" s="52"/>
+      <c r="EE9" s="53"/>
       <c r="EF9" s="46"/>
-      <c r="EG9" s="48"/>
-      <c r="EH9" s="49"/>
+      <c r="EG9" s="52"/>
+      <c r="EH9" s="53"/>
       <c r="EI9" s="46"/>
-      <c r="EJ9" s="48"/>
-      <c r="EK9" s="49"/>
+      <c r="EJ9" s="52"/>
+      <c r="EK9" s="53"/>
       <c r="EL9" s="46"/>
-      <c r="EM9" s="48"/>
-      <c r="EN9" s="49"/>
+      <c r="EM9" s="52"/>
+      <c r="EN9" s="53"/>
       <c r="EO9" s="46"/>
-      <c r="EP9" s="48"/>
-      <c r="EQ9" s="49"/>
+      <c r="EP9" s="52"/>
+      <c r="EQ9" s="53"/>
       <c r="ER9" s="46"/>
-      <c r="ES9" s="48"/>
-      <c r="ET9" s="49"/>
+      <c r="ES9" s="52"/>
+      <c r="ET9" s="53"/>
       <c r="EU9" s="46"/>
-      <c r="EV9" s="48"/>
-      <c r="EW9" s="49"/>
-      <c r="EX9" s="48"/>
-      <c r="EY9" s="48"/>
-      <c r="EZ9" s="53"/>
-      <c r="FA9" s="55"/>
-      <c r="FB9" s="48"/>
-      <c r="FC9" s="49"/>
+      <c r="EV9" s="52"/>
+      <c r="EW9" s="53"/>
+      <c r="EX9" s="52"/>
+      <c r="EY9" s="52"/>
+      <c r="EZ9" s="73"/>
+      <c r="FA9" s="69"/>
+      <c r="FB9" s="52"/>
+      <c r="FC9" s="53"/>
       <c r="FD9" s="46"/>
-      <c r="FE9" s="48"/>
-      <c r="FF9" s="49"/>
+      <c r="FE9" s="52"/>
+      <c r="FF9" s="53"/>
       <c r="FG9" s="46"/>
-      <c r="FH9" s="48"/>
-      <c r="FI9" s="49"/>
+      <c r="FH9" s="52"/>
+      <c r="FI9" s="53"/>
       <c r="FJ9" s="46"/>
-      <c r="FK9" s="48"/>
-      <c r="FL9" s="49"/>
+      <c r="FK9" s="52"/>
+      <c r="FL9" s="53"/>
       <c r="FM9" s="46"/>
-      <c r="FN9" s="48"/>
-      <c r="FO9" s="49"/>
+      <c r="FN9" s="52"/>
+      <c r="FO9" s="53"/>
       <c r="FP9" s="46"/>
-      <c r="FQ9" s="48"/>
-      <c r="FR9" s="49"/>
+      <c r="FQ9" s="52"/>
+      <c r="FR9" s="53"/>
       <c r="FS9" s="46"/>
-      <c r="FT9" s="48"/>
-      <c r="FU9" s="49"/>
+      <c r="FT9" s="52"/>
+      <c r="FU9" s="53"/>
       <c r="FV9" s="46"/>
-      <c r="FW9" s="48"/>
-      <c r="FX9" s="49"/>
+      <c r="FW9" s="52"/>
+      <c r="FX9" s="53"/>
       <c r="FY9" s="46"/>
-      <c r="FZ9" s="48"/>
-      <c r="GA9" s="49"/>
+      <c r="FZ9" s="52"/>
+      <c r="GA9" s="53"/>
       <c r="GB9" s="46"/>
-      <c r="GC9" s="48"/>
-      <c r="GD9" s="49"/>
+      <c r="GC9" s="52"/>
+      <c r="GD9" s="53"/>
       <c r="GE9" s="46"/>
-      <c r="GF9" s="48"/>
-      <c r="GG9" s="49"/>
-      <c r="GH9" s="48"/>
-      <c r="GI9" s="48"/>
-      <c r="GJ9" s="53"/>
-      <c r="GK9" s="55"/>
-      <c r="GL9" s="48"/>
-      <c r="GM9" s="49"/>
+      <c r="GF9" s="52"/>
+      <c r="GG9" s="53"/>
+      <c r="GH9" s="52"/>
+      <c r="GI9" s="52"/>
+      <c r="GJ9" s="73"/>
+      <c r="GK9" s="69"/>
+      <c r="GL9" s="52"/>
+      <c r="GM9" s="53"/>
       <c r="GN9" s="46"/>
-      <c r="GO9" s="48"/>
-      <c r="GP9" s="49"/>
+      <c r="GO9" s="52"/>
+      <c r="GP9" s="53"/>
       <c r="GQ9" s="46"/>
-      <c r="GR9" s="48"/>
-      <c r="GS9" s="49"/>
+      <c r="GR9" s="52"/>
+      <c r="GS9" s="53"/>
       <c r="GT9" s="46"/>
-      <c r="GU9" s="48"/>
-      <c r="GV9" s="49"/>
+      <c r="GU9" s="52"/>
+      <c r="GV9" s="53"/>
       <c r="GW9" s="46"/>
-      <c r="GX9" s="48"/>
-      <c r="GY9" s="49"/>
+      <c r="GX9" s="52"/>
+      <c r="GY9" s="53"/>
       <c r="GZ9" s="46"/>
-      <c r="HA9" s="48"/>
-      <c r="HB9" s="49"/>
+      <c r="HA9" s="52"/>
+      <c r="HB9" s="53"/>
       <c r="HC9" s="46"/>
-      <c r="HD9" s="48"/>
-      <c r="HE9" s="49"/>
+      <c r="HD9" s="52"/>
+      <c r="HE9" s="53"/>
       <c r="HF9" s="46"/>
-      <c r="HG9" s="48"/>
-      <c r="HH9" s="49"/>
+      <c r="HG9" s="52"/>
+      <c r="HH9" s="53"/>
       <c r="HI9" s="46"/>
-      <c r="HJ9" s="48"/>
-      <c r="HK9" s="49"/>
+      <c r="HJ9" s="52"/>
+      <c r="HK9" s="53"/>
       <c r="HL9" s="46"/>
-      <c r="HM9" s="48"/>
-      <c r="HN9" s="49"/>
+      <c r="HM9" s="52"/>
+      <c r="HN9" s="53"/>
       <c r="HO9" s="46"/>
-      <c r="HP9" s="48"/>
-      <c r="HQ9" s="49"/>
-      <c r="HR9" s="48"/>
-      <c r="HS9" s="48"/>
-      <c r="HT9" s="53"/>
-      <c r="HU9" s="55"/>
-      <c r="HV9" s="48"/>
-      <c r="HW9" s="49"/>
+      <c r="HP9" s="52"/>
+      <c r="HQ9" s="53"/>
+      <c r="HR9" s="52"/>
+      <c r="HS9" s="52"/>
+      <c r="HT9" s="73"/>
+      <c r="HU9" s="69"/>
+      <c r="HV9" s="52"/>
+      <c r="HW9" s="53"/>
       <c r="HX9" s="46"/>
-      <c r="HY9" s="48"/>
-      <c r="HZ9" s="49"/>
+      <c r="HY9" s="52"/>
+      <c r="HZ9" s="53"/>
       <c r="IA9" s="46"/>
-      <c r="IB9" s="48"/>
-      <c r="IC9" s="49"/>
+      <c r="IB9" s="52"/>
+      <c r="IC9" s="53"/>
       <c r="ID9" s="46"/>
-      <c r="IE9" s="48"/>
-      <c r="IF9" s="49"/>
+      <c r="IE9" s="52"/>
+      <c r="IF9" s="53"/>
       <c r="IG9" s="46"/>
-      <c r="IH9" s="48"/>
-      <c r="II9" s="49"/>
+      <c r="IH9" s="52"/>
+      <c r="II9" s="53"/>
       <c r="IJ9" s="46"/>
-      <c r="IK9" s="48"/>
-      <c r="IL9" s="49"/>
+      <c r="IK9" s="52"/>
+      <c r="IL9" s="53"/>
       <c r="IM9" s="46"/>
-      <c r="IN9" s="48"/>
-      <c r="IO9" s="49"/>
+      <c r="IN9" s="52"/>
+      <c r="IO9" s="53"/>
       <c r="IP9" s="46"/>
-      <c r="IQ9" s="48"/>
-      <c r="IR9" s="49"/>
+      <c r="IQ9" s="52"/>
+      <c r="IR9" s="53"/>
       <c r="IS9" s="46"/>
-      <c r="IT9" s="48"/>
-      <c r="IU9" s="49"/>
+      <c r="IT9" s="52"/>
+      <c r="IU9" s="53"/>
       <c r="IV9" s="46"/>
-      <c r="IW9" s="48"/>
-      <c r="IX9" s="49"/>
+      <c r="IW9" s="52"/>
+      <c r="IX9" s="53"/>
       <c r="IY9" s="46"/>
-      <c r="IZ9" s="48"/>
-      <c r="JA9" s="49"/>
-      <c r="JB9" s="48"/>
-      <c r="JC9" s="48"/>
-      <c r="JD9" s="53"/>
-      <c r="JE9" s="55"/>
-      <c r="JF9" s="48"/>
-      <c r="JG9" s="49"/>
+      <c r="IZ9" s="52"/>
+      <c r="JA9" s="53"/>
+      <c r="JB9" s="52"/>
+      <c r="JC9" s="52"/>
+      <c r="JD9" s="73"/>
+      <c r="JE9" s="69"/>
+      <c r="JF9" s="52"/>
+      <c r="JG9" s="53"/>
       <c r="JH9" s="46"/>
-      <c r="JI9" s="48"/>
-      <c r="JJ9" s="49"/>
+      <c r="JI9" s="52"/>
+      <c r="JJ9" s="53"/>
       <c r="JK9" s="46"/>
-      <c r="JL9" s="48"/>
-      <c r="JM9" s="49"/>
+      <c r="JL9" s="52"/>
+      <c r="JM9" s="53"/>
       <c r="JN9" s="46"/>
-      <c r="JO9" s="48"/>
-      <c r="JP9" s="49"/>
+      <c r="JO9" s="52"/>
+      <c r="JP9" s="53"/>
       <c r="JQ9" s="46"/>
-      <c r="JR9" s="48"/>
-      <c r="JS9" s="49"/>
+      <c r="JR9" s="52"/>
+      <c r="JS9" s="53"/>
       <c r="JT9" s="46"/>
-      <c r="JU9" s="48"/>
-      <c r="JV9" s="49"/>
+      <c r="JU9" s="52"/>
+      <c r="JV9" s="53"/>
       <c r="JW9" s="46"/>
-      <c r="JX9" s="48"/>
-      <c r="JY9" s="49"/>
+      <c r="JX9" s="52"/>
+      <c r="JY9" s="53"/>
       <c r="JZ9" s="46"/>
-      <c r="KA9" s="48"/>
-      <c r="KB9" s="49"/>
+      <c r="KA9" s="52"/>
+      <c r="KB9" s="53"/>
       <c r="KC9" s="46"/>
-      <c r="KD9" s="48"/>
-      <c r="KE9" s="49"/>
+      <c r="KD9" s="52"/>
+      <c r="KE9" s="53"/>
       <c r="KF9" s="46"/>
-      <c r="KG9" s="48"/>
-      <c r="KH9" s="49"/>
+      <c r="KG9" s="52"/>
+      <c r="KH9" s="53"/>
       <c r="KI9" s="46"/>
-      <c r="KJ9" s="48"/>
-      <c r="KK9" s="49"/>
-      <c r="KL9" s="48"/>
-      <c r="KM9" s="48"/>
-      <c r="KN9" s="49"/>
-      <c r="KO9" s="122"/>
-      <c r="KP9" s="49"/>
-      <c r="KQ9" s="71"/>
+      <c r="KJ9" s="52"/>
+      <c r="KK9" s="53"/>
+      <c r="KL9" s="52"/>
+      <c r="KM9" s="52"/>
+      <c r="KN9" s="53"/>
+      <c r="KO9" s="120"/>
+      <c r="KP9" s="53"/>
+      <c r="KQ9" s="47"/>
       <c r="KR9" s="9" t="s">
         <v>59</v>
       </c>
@@ -7890,9 +7891,9 @@
       <c r="KT9" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="KU9" s="49"/>
-      <c r="KV9" s="49"/>
-      <c r="KW9" s="71"/>
+      <c r="KU9" s="53"/>
+      <c r="KV9" s="53"/>
+      <c r="KW9" s="47"/>
       <c r="KX9" s="9" t="s">
         <v>59</v>
       </c>
@@ -7902,9 +7903,9 @@
       <c r="KZ9" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="LA9" s="49"/>
-      <c r="LB9" s="49"/>
-      <c r="LC9" s="71"/>
+      <c r="LA9" s="53"/>
+      <c r="LB9" s="53"/>
+      <c r="LC9" s="47"/>
       <c r="LD9" s="9" t="s">
         <v>59</v>
       </c>
@@ -7914,9 +7915,9 @@
       <c r="LF9" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="LG9" s="49"/>
-      <c r="LH9" s="49"/>
-      <c r="LI9" s="71"/>
+      <c r="LG9" s="53"/>
+      <c r="LH9" s="53"/>
+      <c r="LI9" s="47"/>
       <c r="LJ9" s="9" t="s">
         <v>59</v>
       </c>
@@ -7926,9 +7927,9 @@
       <c r="LL9" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="LM9" s="49"/>
-      <c r="LN9" s="49"/>
-      <c r="LO9" s="71"/>
+      <c r="LM9" s="53"/>
+      <c r="LN9" s="53"/>
+      <c r="LO9" s="47"/>
       <c r="LP9" s="9" t="s">
         <v>59</v>
       </c>
@@ -7938,9 +7939,9 @@
       <c r="LR9" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="LS9" s="49"/>
-      <c r="LT9" s="49"/>
-      <c r="LU9" s="71"/>
+      <c r="LS9" s="53"/>
+      <c r="LT9" s="53"/>
+      <c r="LU9" s="47"/>
       <c r="LV9" s="9" t="s">
         <v>59</v>
       </c>
@@ -7950,9 +7951,9 @@
       <c r="LX9" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="LY9" s="71"/>
-      <c r="LZ9" s="71"/>
-      <c r="MA9" s="71"/>
+      <c r="LY9" s="47"/>
+      <c r="LZ9" s="47"/>
+      <c r="MA9" s="47"/>
       <c r="MB9" s="9" t="s">
         <v>59</v>
       </c>
@@ -7962,9 +7963,9 @@
       <c r="MD9" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="ME9" s="71"/>
-      <c r="MF9" s="71"/>
-      <c r="MG9" s="71"/>
+      <c r="ME9" s="47"/>
+      <c r="MF9" s="47"/>
+      <c r="MG9" s="47"/>
       <c r="MH9" s="9" t="s">
         <v>59</v>
       </c>
@@ -7974,9 +7975,9 @@
       <c r="MJ9" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="MK9" s="71"/>
-      <c r="ML9" s="71"/>
-      <c r="MM9" s="71"/>
+      <c r="MK9" s="47"/>
+      <c r="ML9" s="47"/>
+      <c r="MM9" s="47"/>
       <c r="MN9" s="9" t="s">
         <v>59</v>
       </c>
@@ -7986,9 +7987,9 @@
       <c r="MP9" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="MQ9" s="71"/>
-      <c r="MR9" s="71"/>
-      <c r="MS9" s="71"/>
+      <c r="MQ9" s="47"/>
+      <c r="MR9" s="47"/>
+      <c r="MS9" s="47"/>
       <c r="MT9" s="9" t="s">
         <v>59</v>
       </c>
@@ -7998,9 +7999,9 @@
       <c r="MV9" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="MW9" s="71"/>
-      <c r="MX9" s="71"/>
-      <c r="MY9" s="71"/>
+      <c r="MW9" s="47"/>
+      <c r="MX9" s="47"/>
+      <c r="MY9" s="47"/>
       <c r="MZ9" s="9" t="s">
         <v>59</v>
       </c>
@@ -8010,9 +8011,9 @@
       <c r="NB9" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="NC9" s="71"/>
-      <c r="ND9" s="71"/>
-      <c r="NE9" s="71"/>
+      <c r="NC9" s="47"/>
+      <c r="ND9" s="47"/>
+      <c r="NE9" s="47"/>
       <c r="NF9" s="9" t="s">
         <v>59</v>
       </c>
@@ -8022,9 +8023,9 @@
       <c r="NH9" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="NI9" s="111"/>
+      <c r="NI9" s="107"/>
       <c r="NJ9" s="46"/>
-      <c r="NK9" s="138"/>
+      <c r="NK9" s="70"/>
       <c r="NL9" s="9" t="s">
         <v>59</v>
       </c>
@@ -8034,9 +8035,9 @@
       <c r="NN9" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="NO9" s="71"/>
-      <c r="NP9" s="71"/>
-      <c r="NQ9" s="71"/>
+      <c r="NO9" s="47"/>
+      <c r="NP9" s="47"/>
+      <c r="NQ9" s="47"/>
       <c r="NR9" s="9" t="s">
         <v>59</v>
       </c>
@@ -8046,9 +8047,9 @@
       <c r="NT9" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="NU9" s="71"/>
-      <c r="NV9" s="71"/>
-      <c r="NW9" s="71"/>
+      <c r="NU9" s="47"/>
+      <c r="NV9" s="47"/>
+      <c r="NW9" s="47"/>
       <c r="NX9" s="9" t="s">
         <v>59</v>
       </c>
@@ -8081,7 +8082,7 @@
         <v>73</v>
       </c>
       <c r="G10" s="18" t="s">
-        <v>750</v>
+        <v>758</v>
       </c>
       <c r="H10" s="17" t="s">
         <v>74</v>
@@ -8105,7 +8106,7 @@
         <v>80</v>
       </c>
       <c r="O10" s="21" t="s">
-        <v>751</v>
+        <v>759</v>
       </c>
       <c r="P10" s="20" t="s">
         <v>81</v>
@@ -8114,7 +8115,7 @@
         <v>82</v>
       </c>
       <c r="R10" s="21" t="s">
-        <v>752</v>
+        <v>760</v>
       </c>
       <c r="S10" s="20" t="s">
         <v>83</v>
@@ -8123,7 +8124,7 @@
         <v>84</v>
       </c>
       <c r="U10" s="21" t="s">
-        <v>753</v>
+        <v>761</v>
       </c>
       <c r="V10" s="20" t="s">
         <v>85</v>
@@ -8132,7 +8133,7 @@
         <v>86</v>
       </c>
       <c r="X10" s="21" t="s">
-        <v>754</v>
+        <v>762</v>
       </c>
       <c r="Y10" s="20" t="s">
         <v>87</v>
@@ -8141,7 +8142,7 @@
         <v>88</v>
       </c>
       <c r="AA10" s="21" t="s">
-        <v>755</v>
+        <v>763</v>
       </c>
       <c r="AB10" s="20" t="s">
         <v>89</v>
@@ -8150,7 +8151,7 @@
         <v>90</v>
       </c>
       <c r="AD10" s="21" t="s">
-        <v>756</v>
+        <v>764</v>
       </c>
       <c r="AE10" s="20" t="s">
         <v>91</v>
@@ -8159,7 +8160,7 @@
         <v>92</v>
       </c>
       <c r="AG10" s="21" t="s">
-        <v>757</v>
+        <v>765</v>
       </c>
       <c r="AH10" s="20" t="s">
         <v>93</v>
@@ -8168,7 +8169,7 @@
         <v>94</v>
       </c>
       <c r="AJ10" s="21" t="s">
-        <v>758</v>
+        <v>766</v>
       </c>
       <c r="AK10" s="20" t="s">
         <v>95</v>
@@ -8177,7 +8178,7 @@
         <v>96</v>
       </c>
       <c r="AM10" s="21" t="s">
-        <v>759</v>
+        <v>767</v>
       </c>
       <c r="AN10" s="20" t="s">
         <v>97</v>
@@ -8186,7 +8187,7 @@
         <v>98</v>
       </c>
       <c r="AP10" s="21" t="s">
-        <v>760</v>
+        <v>768</v>
       </c>
       <c r="AQ10" s="20" t="s">
         <v>99</v>
@@ -8195,7 +8196,7 @@
         <v>100</v>
       </c>
       <c r="AS10" s="21" t="s">
-        <v>761</v>
+        <v>769</v>
       </c>
       <c r="AT10" s="17" t="s">
         <v>101</v>
@@ -8204,7 +8205,7 @@
         <v>102</v>
       </c>
       <c r="AV10" s="22" t="s">
-        <v>762</v>
+        <v>770</v>
       </c>
       <c r="AW10" s="23" t="s">
         <v>103</v>
@@ -8213,7 +8214,7 @@
         <v>104</v>
       </c>
       <c r="AY10" s="21" t="s">
-        <v>763</v>
+        <v>771</v>
       </c>
       <c r="AZ10" s="20" t="s">
         <v>105</v>
@@ -8222,7 +8223,7 @@
         <v>106</v>
       </c>
       <c r="BB10" s="21" t="s">
-        <v>764</v>
+        <v>772</v>
       </c>
       <c r="BC10" s="20" t="s">
         <v>107</v>
@@ -8231,7 +8232,7 @@
         <v>108</v>
       </c>
       <c r="BE10" s="21" t="s">
-        <v>765</v>
+        <v>773</v>
       </c>
       <c r="BF10" s="20" t="s">
         <v>109</v>
@@ -8240,7 +8241,7 @@
         <v>110</v>
       </c>
       <c r="BH10" s="21" t="s">
-        <v>766</v>
+        <v>774</v>
       </c>
       <c r="BI10" s="20" t="s">
         <v>111</v>
@@ -8249,7 +8250,7 @@
         <v>112</v>
       </c>
       <c r="BK10" s="21" t="s">
-        <v>767</v>
+        <v>775</v>
       </c>
       <c r="BL10" s="20" t="s">
         <v>113</v>
@@ -8258,7 +8259,7 @@
         <v>114</v>
       </c>
       <c r="BN10" s="21" t="s">
-        <v>768</v>
+        <v>776</v>
       </c>
       <c r="BO10" s="20" t="s">
         <v>115</v>
@@ -8267,7 +8268,7 @@
         <v>116</v>
       </c>
       <c r="BQ10" s="21" t="s">
-        <v>769</v>
+        <v>777</v>
       </c>
       <c r="BR10" s="20" t="s">
         <v>117</v>
@@ -8276,7 +8277,7 @@
         <v>118</v>
       </c>
       <c r="BT10" s="21" t="s">
-        <v>770</v>
+        <v>778</v>
       </c>
       <c r="BU10" s="20" t="s">
         <v>119</v>
@@ -8285,7 +8286,7 @@
         <v>120</v>
       </c>
       <c r="BW10" s="21" t="s">
-        <v>771</v>
+        <v>779</v>
       </c>
       <c r="BX10" s="20" t="s">
         <v>121</v>
@@ -8294,7 +8295,7 @@
         <v>122</v>
       </c>
       <c r="BZ10" s="21" t="s">
-        <v>772</v>
+        <v>780</v>
       </c>
       <c r="CA10" s="20" t="s">
         <v>123</v>
@@ -8303,7 +8304,7 @@
         <v>124</v>
       </c>
       <c r="CC10" s="21" t="s">
-        <v>773</v>
+        <v>781</v>
       </c>
       <c r="CD10" s="17" t="s">
         <v>125</v>
@@ -8312,7 +8313,7 @@
         <v>126</v>
       </c>
       <c r="CF10" s="22" t="s">
-        <v>774</v>
+        <v>782</v>
       </c>
       <c r="CG10" s="23" t="s">
         <v>127</v>
@@ -8321,7 +8322,7 @@
         <v>128</v>
       </c>
       <c r="CI10" s="21" t="s">
-        <v>775</v>
+        <v>783</v>
       </c>
       <c r="CJ10" s="20" t="s">
         <v>129</v>
@@ -8330,7 +8331,7 @@
         <v>130</v>
       </c>
       <c r="CL10" s="21" t="s">
-        <v>776</v>
+        <v>784</v>
       </c>
       <c r="CM10" s="20" t="s">
         <v>131</v>
@@ -8339,7 +8340,7 @@
         <v>132</v>
       </c>
       <c r="CO10" s="21" t="s">
-        <v>777</v>
+        <v>785</v>
       </c>
       <c r="CP10" s="20" t="s">
         <v>133</v>
@@ -8348,7 +8349,7 @@
         <v>134</v>
       </c>
       <c r="CR10" s="21" t="s">
-        <v>778</v>
+        <v>786</v>
       </c>
       <c r="CS10" s="20" t="s">
         <v>135</v>
@@ -8357,7 +8358,7 @@
         <v>136</v>
       </c>
       <c r="CU10" s="21" t="s">
-        <v>779</v>
+        <v>787</v>
       </c>
       <c r="CV10" s="20" t="s">
         <v>137</v>
@@ -8366,7 +8367,7 @@
         <v>138</v>
       </c>
       <c r="CX10" s="21" t="s">
-        <v>780</v>
+        <v>788</v>
       </c>
       <c r="CY10" s="20" t="s">
         <v>139</v>
@@ -8375,7 +8376,7 @@
         <v>140</v>
       </c>
       <c r="DA10" s="21" t="s">
-        <v>781</v>
+        <v>789</v>
       </c>
       <c r="DB10" s="20" t="s">
         <v>141</v>
@@ -8384,7 +8385,7 @@
         <v>142</v>
       </c>
       <c r="DD10" s="21" t="s">
-        <v>782</v>
+        <v>790</v>
       </c>
       <c r="DE10" s="20" t="s">
         <v>143</v>
@@ -8393,7 +8394,7 @@
         <v>144</v>
       </c>
       <c r="DG10" s="21" t="s">
-        <v>783</v>
+        <v>791</v>
       </c>
       <c r="DH10" s="20" t="s">
         <v>145</v>
@@ -8402,7 +8403,7 @@
         <v>146</v>
       </c>
       <c r="DJ10" s="21" t="s">
-        <v>784</v>
+        <v>792</v>
       </c>
       <c r="DK10" s="20" t="s">
         <v>147</v>
@@ -8411,7 +8412,7 @@
         <v>148</v>
       </c>
       <c r="DM10" s="21" t="s">
-        <v>785</v>
+        <v>793</v>
       </c>
       <c r="DN10" s="17" t="s">
         <v>149</v>
@@ -8420,7 +8421,7 @@
         <v>150</v>
       </c>
       <c r="DP10" s="22" t="s">
-        <v>786</v>
+        <v>794</v>
       </c>
       <c r="DQ10" s="23" t="s">
         <v>151</v>
@@ -8429,7 +8430,7 @@
         <v>152</v>
       </c>
       <c r="DS10" s="21" t="s">
-        <v>787</v>
+        <v>795</v>
       </c>
       <c r="DT10" s="20" t="s">
         <v>153</v>
@@ -8438,7 +8439,7 @@
         <v>154</v>
       </c>
       <c r="DV10" s="21" t="s">
-        <v>788</v>
+        <v>796</v>
       </c>
       <c r="DW10" s="20" t="s">
         <v>155</v>
@@ -8447,7 +8448,7 @@
         <v>156</v>
       </c>
       <c r="DY10" s="21" t="s">
-        <v>789</v>
+        <v>797</v>
       </c>
       <c r="DZ10" s="20" t="s">
         <v>157</v>
@@ -8456,7 +8457,7 @@
         <v>158</v>
       </c>
       <c r="EB10" s="21" t="s">
-        <v>790</v>
+        <v>798</v>
       </c>
       <c r="EC10" s="20" t="s">
         <v>159</v>
@@ -8465,7 +8466,7 @@
         <v>160</v>
       </c>
       <c r="EE10" s="21" t="s">
-        <v>791</v>
+        <v>799</v>
       </c>
       <c r="EF10" s="20" t="s">
         <v>161</v>
@@ -8474,7 +8475,7 @@
         <v>162</v>
       </c>
       <c r="EH10" s="21" t="s">
-        <v>792</v>
+        <v>800</v>
       </c>
       <c r="EI10" s="20" t="s">
         <v>163</v>
@@ -8483,7 +8484,7 @@
         <v>164</v>
       </c>
       <c r="EK10" s="21" t="s">
-        <v>793</v>
+        <v>801</v>
       </c>
       <c r="EL10" s="20" t="s">
         <v>165</v>
@@ -8492,7 +8493,7 @@
         <v>166</v>
       </c>
       <c r="EN10" s="21" t="s">
-        <v>794</v>
+        <v>802</v>
       </c>
       <c r="EO10" s="20" t="s">
         <v>167</v>
@@ -8501,7 +8502,7 @@
         <v>168</v>
       </c>
       <c r="EQ10" s="21" t="s">
-        <v>795</v>
+        <v>803</v>
       </c>
       <c r="ER10" s="20" t="s">
         <v>169</v>
@@ -8510,7 +8511,7 @@
         <v>170</v>
       </c>
       <c r="ET10" s="21" t="s">
-        <v>796</v>
+        <v>804</v>
       </c>
       <c r="EU10" s="20" t="s">
         <v>171</v>
@@ -8519,7 +8520,7 @@
         <v>172</v>
       </c>
       <c r="EW10" s="21" t="s">
-        <v>797</v>
+        <v>805</v>
       </c>
       <c r="EX10" s="17" t="s">
         <v>173</v>
@@ -8528,7 +8529,7 @@
         <v>174</v>
       </c>
       <c r="EZ10" s="22" t="s">
-        <v>798</v>
+        <v>806</v>
       </c>
       <c r="FA10" s="23" t="s">
         <v>175</v>
@@ -8537,7 +8538,7 @@
         <v>176</v>
       </c>
       <c r="FC10" s="21" t="s">
-        <v>799</v>
+        <v>807</v>
       </c>
       <c r="FD10" s="20" t="s">
         <v>177</v>
@@ -8546,7 +8547,7 @@
         <v>178</v>
       </c>
       <c r="FF10" s="21" t="s">
-        <v>800</v>
+        <v>808</v>
       </c>
       <c r="FG10" s="20" t="s">
         <v>179</v>
@@ -8555,7 +8556,7 @@
         <v>180</v>
       </c>
       <c r="FI10" s="21" t="s">
-        <v>801</v>
+        <v>809</v>
       </c>
       <c r="FJ10" s="20" t="s">
         <v>181</v>
@@ -8564,7 +8565,7 @@
         <v>182</v>
       </c>
       <c r="FL10" s="21" t="s">
-        <v>802</v>
+        <v>810</v>
       </c>
       <c r="FM10" s="20" t="s">
         <v>183</v>
@@ -8573,7 +8574,7 @@
         <v>184</v>
       </c>
       <c r="FO10" s="21" t="s">
-        <v>803</v>
+        <v>811</v>
       </c>
       <c r="FP10" s="20" t="s">
         <v>185</v>
@@ -8582,7 +8583,7 @@
         <v>186</v>
       </c>
       <c r="FR10" s="21" t="s">
-        <v>804</v>
+        <v>812</v>
       </c>
       <c r="FS10" s="20" t="s">
         <v>187</v>
@@ -8591,7 +8592,7 @@
         <v>188</v>
       </c>
       <c r="FU10" s="21" t="s">
-        <v>805</v>
+        <v>813</v>
       </c>
       <c r="FV10" s="20" t="s">
         <v>189</v>
@@ -8600,7 +8601,7 @@
         <v>190</v>
       </c>
       <c r="FX10" s="21" t="s">
-        <v>806</v>
+        <v>814</v>
       </c>
       <c r="FY10" s="20" t="s">
         <v>191</v>
@@ -8609,7 +8610,7 @@
         <v>192</v>
       </c>
       <c r="GA10" s="21" t="s">
-        <v>807</v>
+        <v>815</v>
       </c>
       <c r="GB10" s="20" t="s">
         <v>193</v>
@@ -8618,7 +8619,7 @@
         <v>194</v>
       </c>
       <c r="GD10" s="21" t="s">
-        <v>808</v>
+        <v>816</v>
       </c>
       <c r="GE10" s="20" t="s">
         <v>195</v>
@@ -8627,7 +8628,7 @@
         <v>196</v>
       </c>
       <c r="GG10" s="21" t="s">
-        <v>809</v>
+        <v>817</v>
       </c>
       <c r="GH10" s="17" t="s">
         <v>197</v>
@@ -8636,7 +8637,7 @@
         <v>198</v>
       </c>
       <c r="GJ10" s="22" t="s">
-        <v>810</v>
+        <v>818</v>
       </c>
       <c r="GK10" s="23" t="s">
         <v>199</v>
@@ -8645,7 +8646,7 @@
         <v>200</v>
       </c>
       <c r="GM10" s="21" t="s">
-        <v>811</v>
+        <v>819</v>
       </c>
       <c r="GN10" s="20" t="s">
         <v>201</v>
@@ -8654,7 +8655,7 @@
         <v>202</v>
       </c>
       <c r="GP10" s="21" t="s">
-        <v>812</v>
+        <v>820</v>
       </c>
       <c r="GQ10" s="20" t="s">
         <v>203</v>
@@ -8663,7 +8664,7 @@
         <v>204</v>
       </c>
       <c r="GS10" s="21" t="s">
-        <v>813</v>
+        <v>821</v>
       </c>
       <c r="GT10" s="20" t="s">
         <v>205</v>
@@ -8672,7 +8673,7 @@
         <v>206</v>
       </c>
       <c r="GV10" s="21" t="s">
-        <v>814</v>
+        <v>822</v>
       </c>
       <c r="GW10" s="20" t="s">
         <v>207</v>
@@ -8681,7 +8682,7 @@
         <v>208</v>
       </c>
       <c r="GY10" s="21" t="s">
-        <v>815</v>
+        <v>823</v>
       </c>
       <c r="GZ10" s="20" t="s">
         <v>209</v>
@@ -8690,7 +8691,7 @@
         <v>210</v>
       </c>
       <c r="HB10" s="21" t="s">
-        <v>816</v>
+        <v>824</v>
       </c>
       <c r="HC10" s="20" t="s">
         <v>211</v>
@@ -8699,7 +8700,7 @@
         <v>212</v>
       </c>
       <c r="HE10" s="21" t="s">
-        <v>817</v>
+        <v>825</v>
       </c>
       <c r="HF10" s="20" t="s">
         <v>213</v>
@@ -8708,7 +8709,7 @@
         <v>214</v>
       </c>
       <c r="HH10" s="21" t="s">
-        <v>818</v>
+        <v>826</v>
       </c>
       <c r="HI10" s="20" t="s">
         <v>215</v>
@@ -8717,7 +8718,7 @@
         <v>216</v>
       </c>
       <c r="HK10" s="21" t="s">
-        <v>819</v>
+        <v>827</v>
       </c>
       <c r="HL10" s="20" t="s">
         <v>217</v>
@@ -8726,7 +8727,7 @@
         <v>218</v>
       </c>
       <c r="HN10" s="21" t="s">
-        <v>820</v>
+        <v>828</v>
       </c>
       <c r="HO10" s="20" t="s">
         <v>219</v>
@@ -8735,7 +8736,7 @@
         <v>220</v>
       </c>
       <c r="HQ10" s="21" t="s">
-        <v>821</v>
+        <v>829</v>
       </c>
       <c r="HR10" s="17" t="s">
         <v>221</v>
@@ -8744,7 +8745,7 @@
         <v>222</v>
       </c>
       <c r="HT10" s="22" t="s">
-        <v>822</v>
+        <v>830</v>
       </c>
       <c r="HU10" s="23" t="s">
         <v>223</v>
@@ -8753,7 +8754,7 @@
         <v>224</v>
       </c>
       <c r="HW10" s="21" t="s">
-        <v>823</v>
+        <v>831</v>
       </c>
       <c r="HX10" s="20" t="s">
         <v>225</v>
@@ -8762,7 +8763,7 @@
         <v>226</v>
       </c>
       <c r="HZ10" s="21" t="s">
-        <v>824</v>
+        <v>832</v>
       </c>
       <c r="IA10" s="20" t="s">
         <v>227</v>
@@ -8771,7 +8772,7 @@
         <v>228</v>
       </c>
       <c r="IC10" s="21" t="s">
-        <v>825</v>
+        <v>833</v>
       </c>
       <c r="ID10" s="20" t="s">
         <v>229</v>
@@ -8780,7 +8781,7 @@
         <v>230</v>
       </c>
       <c r="IF10" s="21" t="s">
-        <v>826</v>
+        <v>834</v>
       </c>
       <c r="IG10" s="20" t="s">
         <v>231</v>
@@ -8789,7 +8790,7 @@
         <v>232</v>
       </c>
       <c r="II10" s="21" t="s">
-        <v>827</v>
+        <v>835</v>
       </c>
       <c r="IJ10" s="20" t="s">
         <v>233</v>
@@ -8798,7 +8799,7 @@
         <v>234</v>
       </c>
       <c r="IL10" s="21" t="s">
-        <v>828</v>
+        <v>836</v>
       </c>
       <c r="IM10" s="20" t="s">
         <v>235</v>
@@ -8807,7 +8808,7 @@
         <v>236</v>
       </c>
       <c r="IO10" s="21" t="s">
-        <v>829</v>
+        <v>837</v>
       </c>
       <c r="IP10" s="20" t="s">
         <v>237</v>
@@ -8816,7 +8817,7 @@
         <v>238</v>
       </c>
       <c r="IR10" s="21" t="s">
-        <v>830</v>
+        <v>838</v>
       </c>
       <c r="IS10" s="20" t="s">
         <v>239</v>
@@ -8825,7 +8826,7 @@
         <v>240</v>
       </c>
       <c r="IU10" s="21" t="s">
-        <v>831</v>
+        <v>839</v>
       </c>
       <c r="IV10" s="20" t="s">
         <v>241</v>
@@ -8834,7 +8835,7 @@
         <v>242</v>
       </c>
       <c r="IX10" s="21" t="s">
-        <v>832</v>
+        <v>840</v>
       </c>
       <c r="IY10" s="20" t="s">
         <v>243</v>
@@ -8843,7 +8844,7 @@
         <v>244</v>
       </c>
       <c r="JA10" s="21" t="s">
-        <v>833</v>
+        <v>841</v>
       </c>
       <c r="JB10" s="17" t="s">
         <v>245</v>
@@ -8852,7 +8853,7 @@
         <v>246</v>
       </c>
       <c r="JD10" s="22" t="s">
-        <v>834</v>
+        <v>842</v>
       </c>
       <c r="JE10" s="23" t="s">
         <v>247</v>
@@ -8861,7 +8862,7 @@
         <v>248</v>
       </c>
       <c r="JG10" s="21" t="s">
-        <v>835</v>
+        <v>843</v>
       </c>
       <c r="JH10" s="20" t="s">
         <v>249</v>
@@ -8870,7 +8871,7 @@
         <v>250</v>
       </c>
       <c r="JJ10" s="21" t="s">
-        <v>836</v>
+        <v>844</v>
       </c>
       <c r="JK10" s="20" t="s">
         <v>251</v>
@@ -8879,7 +8880,7 @@
         <v>252</v>
       </c>
       <c r="JM10" s="21" t="s">
-        <v>837</v>
+        <v>845</v>
       </c>
       <c r="JN10" s="20" t="s">
         <v>253</v>
@@ -8888,7 +8889,7 @@
         <v>254</v>
       </c>
       <c r="JP10" s="21" t="s">
-        <v>838</v>
+        <v>846</v>
       </c>
       <c r="JQ10" s="20" t="s">
         <v>255</v>
@@ -8897,7 +8898,7 @@
         <v>256</v>
       </c>
       <c r="JS10" s="21" t="s">
-        <v>839</v>
+        <v>847</v>
       </c>
       <c r="JT10" s="20" t="s">
         <v>257</v>
@@ -8906,7 +8907,7 @@
         <v>258</v>
       </c>
       <c r="JV10" s="21" t="s">
-        <v>840</v>
+        <v>848</v>
       </c>
       <c r="JW10" s="20" t="s">
         <v>259</v>
@@ -8915,7 +8916,7 @@
         <v>260</v>
       </c>
       <c r="JY10" s="21" t="s">
-        <v>841</v>
+        <v>849</v>
       </c>
       <c r="JZ10" s="20" t="s">
         <v>261</v>
@@ -8924,7 +8925,7 @@
         <v>262</v>
       </c>
       <c r="KB10" s="21" t="s">
-        <v>842</v>
+        <v>850</v>
       </c>
       <c r="KC10" s="20" t="s">
         <v>263</v>
@@ -8933,7 +8934,7 @@
         <v>264</v>
       </c>
       <c r="KE10" s="21" t="s">
-        <v>843</v>
+        <v>851</v>
       </c>
       <c r="KF10" s="20" t="s">
         <v>265</v>
@@ -8942,7 +8943,7 @@
         <v>266</v>
       </c>
       <c r="KH10" s="21" t="s">
-        <v>844</v>
+        <v>852</v>
       </c>
       <c r="KI10" s="20" t="s">
         <v>267</v>
@@ -8951,7 +8952,7 @@
         <v>268</v>
       </c>
       <c r="KK10" s="21" t="s">
-        <v>845</v>
+        <v>853</v>
       </c>
       <c r="KL10" s="17" t="s">
         <v>269</v>
@@ -8960,7 +8961,7 @@
         <v>270</v>
       </c>
       <c r="KN10" s="21" t="s">
-        <v>846</v>
+        <v>854</v>
       </c>
       <c r="KO10" s="24" t="s">
         <v>271</v>
@@ -10415,6 +10416,543 @@
     </row>
   </sheetData>
   <mergeCells count="561">
+    <mergeCell ref="V7:V9"/>
+    <mergeCell ref="W7:W9"/>
+    <mergeCell ref="KL7:KL9"/>
+    <mergeCell ref="KM7:KM9"/>
+    <mergeCell ref="KN7:KN9"/>
+    <mergeCell ref="KU7:KV7"/>
+    <mergeCell ref="JP7:JP9"/>
+    <mergeCell ref="JQ7:JQ9"/>
+    <mergeCell ref="JV7:JV9"/>
+    <mergeCell ref="JW7:JW9"/>
+    <mergeCell ref="IF7:IF9"/>
+    <mergeCell ref="IG7:IG9"/>
+    <mergeCell ref="IL7:IL9"/>
+    <mergeCell ref="IM7:IM9"/>
+    <mergeCell ref="GV7:GV9"/>
+    <mergeCell ref="GW7:GW9"/>
+    <mergeCell ref="HB7:HB9"/>
+    <mergeCell ref="HC7:HC9"/>
+    <mergeCell ref="FL7:FL9"/>
+    <mergeCell ref="FM7:FM9"/>
+    <mergeCell ref="FR7:FR9"/>
+    <mergeCell ref="FS7:FS9"/>
+    <mergeCell ref="DP7:DP9"/>
+    <mergeCell ref="DQ7:DQ9"/>
+    <mergeCell ref="BG7:BG9"/>
+    <mergeCell ref="BB7:BB9"/>
+    <mergeCell ref="BC7:BC9"/>
+    <mergeCell ref="AR7:AR9"/>
+    <mergeCell ref="AS7:AS9"/>
+    <mergeCell ref="AT7:AT9"/>
+    <mergeCell ref="AU7:AU9"/>
+    <mergeCell ref="AV7:AV9"/>
+    <mergeCell ref="AW7:AW9"/>
+    <mergeCell ref="AX7:AX9"/>
+    <mergeCell ref="AY7:AY9"/>
+    <mergeCell ref="AZ7:AZ9"/>
+    <mergeCell ref="BA7:BA9"/>
+    <mergeCell ref="CL7:CL9"/>
+    <mergeCell ref="CM7:CM9"/>
+    <mergeCell ref="CB7:CB9"/>
+    <mergeCell ref="CC7:CC9"/>
+    <mergeCell ref="CD7:CD9"/>
+    <mergeCell ref="CE7:CE9"/>
+    <mergeCell ref="BV7:BV9"/>
+    <mergeCell ref="BW7:BW9"/>
+    <mergeCell ref="BX7:BX9"/>
+    <mergeCell ref="BY7:BY9"/>
+    <mergeCell ref="BZ7:BZ9"/>
+    <mergeCell ref="CA7:CA9"/>
+    <mergeCell ref="DJ7:DJ9"/>
+    <mergeCell ref="DK7:DK9"/>
+    <mergeCell ref="CZ7:CZ9"/>
+    <mergeCell ref="DA7:DA9"/>
+    <mergeCell ref="DB7:DB9"/>
+    <mergeCell ref="DC7:DC9"/>
+    <mergeCell ref="CX7:CX9"/>
+    <mergeCell ref="CY7:CY9"/>
+    <mergeCell ref="CN7:CN9"/>
+    <mergeCell ref="CO7:CO9"/>
+    <mergeCell ref="CP7:CP9"/>
+    <mergeCell ref="CQ7:CQ9"/>
+    <mergeCell ref="DD7:DD9"/>
+    <mergeCell ref="DE7:DE9"/>
+    <mergeCell ref="DF7:DF9"/>
+    <mergeCell ref="DG7:DG9"/>
+    <mergeCell ref="DH7:DH9"/>
+    <mergeCell ref="DI7:DI9"/>
+    <mergeCell ref="CR7:CR9"/>
+    <mergeCell ref="CS7:CS9"/>
+    <mergeCell ref="CT7:CT9"/>
+    <mergeCell ref="CU7:CU9"/>
+    <mergeCell ref="CV7:CV9"/>
+    <mergeCell ref="CW7:CW9"/>
+    <mergeCell ref="DX7:DX9"/>
+    <mergeCell ref="DY7:DY9"/>
+    <mergeCell ref="DZ7:DZ9"/>
+    <mergeCell ref="EA7:EA9"/>
+    <mergeCell ref="DR7:DR9"/>
+    <mergeCell ref="DS7:DS9"/>
+    <mergeCell ref="DT7:DT9"/>
+    <mergeCell ref="DU7:DU9"/>
+    <mergeCell ref="DL7:DL9"/>
+    <mergeCell ref="DM7:DM9"/>
+    <mergeCell ref="DN7:DN9"/>
+    <mergeCell ref="DO7:DO9"/>
+    <mergeCell ref="DV7:DV9"/>
+    <mergeCell ref="DW7:DW9"/>
+    <mergeCell ref="EV7:EV9"/>
+    <mergeCell ref="EW7:EW9"/>
+    <mergeCell ref="EX7:EX9"/>
+    <mergeCell ref="EY7:EY9"/>
+    <mergeCell ref="ET7:ET9"/>
+    <mergeCell ref="EU7:EU9"/>
+    <mergeCell ref="EJ7:EJ9"/>
+    <mergeCell ref="EK7:EK9"/>
+    <mergeCell ref="EL7:EL9"/>
+    <mergeCell ref="EM7:EM9"/>
+    <mergeCell ref="EN7:EN9"/>
+    <mergeCell ref="EO7:EO9"/>
+    <mergeCell ref="EP7:EP9"/>
+    <mergeCell ref="EQ7:EQ9"/>
+    <mergeCell ref="ER7:ER9"/>
+    <mergeCell ref="ES7:ES9"/>
+    <mergeCell ref="GG7:GG9"/>
+    <mergeCell ref="GH7:GH9"/>
+    <mergeCell ref="GI7:GI9"/>
+    <mergeCell ref="GD7:GD9"/>
+    <mergeCell ref="GE7:GE9"/>
+    <mergeCell ref="FT7:FT9"/>
+    <mergeCell ref="FU7:FU9"/>
+    <mergeCell ref="FV7:FV9"/>
+    <mergeCell ref="FW7:FW9"/>
+    <mergeCell ref="FY7:FY9"/>
+    <mergeCell ref="FZ7:FZ9"/>
+    <mergeCell ref="GA7:GA9"/>
+    <mergeCell ref="GB7:GB9"/>
+    <mergeCell ref="GC7:GC9"/>
+    <mergeCell ref="HT7:HT9"/>
+    <mergeCell ref="HU7:HU9"/>
+    <mergeCell ref="HV7:HV9"/>
+    <mergeCell ref="HW7:HW9"/>
+    <mergeCell ref="HX7:HX9"/>
+    <mergeCell ref="HY7:HY9"/>
+    <mergeCell ref="IH7:IH9"/>
+    <mergeCell ref="II7:II9"/>
+    <mergeCell ref="IJ7:IJ9"/>
+    <mergeCell ref="IB7:IB9"/>
+    <mergeCell ref="IC7:IC9"/>
+    <mergeCell ref="ID7:ID9"/>
+    <mergeCell ref="IE7:IE9"/>
+    <mergeCell ref="HZ7:HZ9"/>
+    <mergeCell ref="IA7:IA9"/>
+    <mergeCell ref="HP7:HP9"/>
+    <mergeCell ref="HQ7:HQ9"/>
+    <mergeCell ref="HR7:HR9"/>
+    <mergeCell ref="HS7:HS9"/>
+    <mergeCell ref="HN7:HN9"/>
+    <mergeCell ref="HO7:HO9"/>
+    <mergeCell ref="HD7:HD9"/>
+    <mergeCell ref="HE7:HE9"/>
+    <mergeCell ref="HF7:HF9"/>
+    <mergeCell ref="HG7:HG9"/>
+    <mergeCell ref="A3:A9"/>
+    <mergeCell ref="B3:B9"/>
+    <mergeCell ref="C3:C9"/>
+    <mergeCell ref="D3:D9"/>
+    <mergeCell ref="F3:F9"/>
+    <mergeCell ref="H3:L5"/>
+    <mergeCell ref="M3:AR3"/>
+    <mergeCell ref="AW3:CF3"/>
+    <mergeCell ref="LY8:LY9"/>
+    <mergeCell ref="LG5:LG9"/>
+    <mergeCell ref="LH5:LH9"/>
+    <mergeCell ref="LI5:LL7"/>
+    <mergeCell ref="LM5:LX5"/>
+    <mergeCell ref="KJ7:KJ9"/>
+    <mergeCell ref="KK7:KK9"/>
+    <mergeCell ref="KH7:KH9"/>
+    <mergeCell ref="KI7:KI9"/>
+    <mergeCell ref="JX7:JX9"/>
+    <mergeCell ref="JY7:JY9"/>
+    <mergeCell ref="JZ7:JZ9"/>
+    <mergeCell ref="KA7:KA9"/>
+    <mergeCell ref="JR7:JR9"/>
+    <mergeCell ref="JS7:JS9"/>
+    <mergeCell ref="JT7:JT9"/>
+    <mergeCell ref="KO3:MJ3"/>
+    <mergeCell ref="MK3:NH3"/>
+    <mergeCell ref="NI3:NZ3"/>
+    <mergeCell ref="OA3:OF6"/>
+    <mergeCell ref="M4:R5"/>
+    <mergeCell ref="S4:X5"/>
+    <mergeCell ref="Y4:AA6"/>
+    <mergeCell ref="AB4:AD6"/>
+    <mergeCell ref="AE4:AM4"/>
+    <mergeCell ref="AN4:AS5"/>
+    <mergeCell ref="CG3:DP3"/>
+    <mergeCell ref="DQ3:EZ3"/>
+    <mergeCell ref="FA3:GJ3"/>
+    <mergeCell ref="GK3:HT3"/>
+    <mergeCell ref="HU3:JD3"/>
+    <mergeCell ref="JE3:KN3"/>
+    <mergeCell ref="HI6:HK6"/>
+    <mergeCell ref="HL6:HN6"/>
+    <mergeCell ref="CS4:CU6"/>
+    <mergeCell ref="CV4:CX6"/>
+    <mergeCell ref="AT4:AV6"/>
+    <mergeCell ref="AW4:BB5"/>
+    <mergeCell ref="BC4:BH5"/>
+    <mergeCell ref="BI4:BK6"/>
+    <mergeCell ref="DH4:DM5"/>
+    <mergeCell ref="DN4:DP6"/>
+    <mergeCell ref="DQ4:DV5"/>
+    <mergeCell ref="DW4:EB5"/>
+    <mergeCell ref="EC4:EE6"/>
+    <mergeCell ref="DE6:DG6"/>
+    <mergeCell ref="DH6:DJ6"/>
+    <mergeCell ref="DK6:DM6"/>
+    <mergeCell ref="DQ6:DS6"/>
+    <mergeCell ref="DT6:DV6"/>
+    <mergeCell ref="DW6:DY6"/>
+    <mergeCell ref="DZ6:EB6"/>
+    <mergeCell ref="GH4:GJ6"/>
+    <mergeCell ref="GK4:GP5"/>
+    <mergeCell ref="GE6:GG6"/>
+    <mergeCell ref="GK6:GM6"/>
+    <mergeCell ref="GN6:GP6"/>
+    <mergeCell ref="EF4:EH6"/>
+    <mergeCell ref="EI4:EQ4"/>
+    <mergeCell ref="ER4:EW5"/>
+    <mergeCell ref="EX4:EZ6"/>
+    <mergeCell ref="FA4:FF5"/>
+    <mergeCell ref="FG4:FL5"/>
+    <mergeCell ref="ER6:ET6"/>
+    <mergeCell ref="EU6:EW6"/>
+    <mergeCell ref="FA6:FC6"/>
+    <mergeCell ref="FD6:FF6"/>
+    <mergeCell ref="FG6:FI6"/>
+    <mergeCell ref="FJ6:FL6"/>
+    <mergeCell ref="FS6:FU6"/>
+    <mergeCell ref="FV6:FX6"/>
+    <mergeCell ref="FY6:GA6"/>
+    <mergeCell ref="GB6:GD6"/>
+    <mergeCell ref="EI6:EK6"/>
+    <mergeCell ref="EL6:EN6"/>
+    <mergeCell ref="EO6:EQ6"/>
+    <mergeCell ref="IG4:II6"/>
+    <mergeCell ref="IJ4:IL6"/>
+    <mergeCell ref="IM4:IU4"/>
+    <mergeCell ref="IV4:JA5"/>
+    <mergeCell ref="IM5:IU5"/>
+    <mergeCell ref="IP6:IR6"/>
+    <mergeCell ref="IS6:IU6"/>
+    <mergeCell ref="IV6:IX6"/>
+    <mergeCell ref="GQ4:GV5"/>
+    <mergeCell ref="GW4:GY6"/>
+    <mergeCell ref="GZ4:HB6"/>
+    <mergeCell ref="HC4:HK4"/>
+    <mergeCell ref="HL4:HQ5"/>
+    <mergeCell ref="HR4:HT6"/>
+    <mergeCell ref="GQ6:GS6"/>
+    <mergeCell ref="GT6:GV6"/>
+    <mergeCell ref="HC6:HE6"/>
+    <mergeCell ref="HF6:HH6"/>
+    <mergeCell ref="AE5:AM5"/>
+    <mergeCell ref="BO5:BW5"/>
+    <mergeCell ref="CY5:DG5"/>
+    <mergeCell ref="EI5:EQ5"/>
+    <mergeCell ref="FS5:GA5"/>
+    <mergeCell ref="HC5:HK5"/>
+    <mergeCell ref="MK4:NH4"/>
+    <mergeCell ref="NI4:NI9"/>
+    <mergeCell ref="NJ4:NJ9"/>
+    <mergeCell ref="MK5:MK9"/>
+    <mergeCell ref="ML5:ML9"/>
+    <mergeCell ref="MM5:MP7"/>
+    <mergeCell ref="MQ5:NH5"/>
+    <mergeCell ref="KF4:KK5"/>
+    <mergeCell ref="KL4:KN6"/>
+    <mergeCell ref="KO4:LF4"/>
+    <mergeCell ref="LG4:LX4"/>
+    <mergeCell ref="LY4:MD5"/>
+    <mergeCell ref="ME4:MJ5"/>
+    <mergeCell ref="KO5:KO9"/>
+    <mergeCell ref="KP5:KP9"/>
+    <mergeCell ref="KQ5:KT7"/>
+    <mergeCell ref="KU5:LF5"/>
+    <mergeCell ref="JB4:JD6"/>
+    <mergeCell ref="S6:U6"/>
+    <mergeCell ref="V6:X6"/>
+    <mergeCell ref="AE6:AG6"/>
+    <mergeCell ref="AH6:AJ6"/>
+    <mergeCell ref="AK6:AM6"/>
+    <mergeCell ref="AN6:AP6"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="H6:H9"/>
+    <mergeCell ref="I6:L6"/>
+    <mergeCell ref="M6:O6"/>
+    <mergeCell ref="P6:R6"/>
+    <mergeCell ref="AL7:AL9"/>
+    <mergeCell ref="AM7:AM9"/>
+    <mergeCell ref="AN7:AN9"/>
+    <mergeCell ref="AO7:AO9"/>
+    <mergeCell ref="AF7:AF9"/>
+    <mergeCell ref="AG7:AG9"/>
+    <mergeCell ref="AH7:AH9"/>
+    <mergeCell ref="AI7:AI9"/>
+    <mergeCell ref="AD7:AD9"/>
+    <mergeCell ref="AE7:AE9"/>
+    <mergeCell ref="T7:T9"/>
+    <mergeCell ref="U7:U9"/>
+    <mergeCell ref="CG6:CI6"/>
+    <mergeCell ref="CJ6:CL6"/>
+    <mergeCell ref="CM6:CO6"/>
+    <mergeCell ref="CP6:CR6"/>
+    <mergeCell ref="CY6:DA6"/>
+    <mergeCell ref="DB6:DD6"/>
+    <mergeCell ref="AQ6:AS6"/>
+    <mergeCell ref="AW6:AY6"/>
+    <mergeCell ref="AZ6:BB6"/>
+    <mergeCell ref="BC6:BE6"/>
+    <mergeCell ref="BF6:BH6"/>
+    <mergeCell ref="BO6:BQ6"/>
+    <mergeCell ref="BL4:BN6"/>
+    <mergeCell ref="BO4:BW4"/>
+    <mergeCell ref="BX4:CC5"/>
+    <mergeCell ref="CD4:CF6"/>
+    <mergeCell ref="CG4:CL5"/>
+    <mergeCell ref="CM4:CR5"/>
+    <mergeCell ref="BR6:BT6"/>
+    <mergeCell ref="BU6:BW6"/>
+    <mergeCell ref="BX6:BZ6"/>
+    <mergeCell ref="CA6:CC6"/>
+    <mergeCell ref="CY4:DG4"/>
+    <mergeCell ref="FM4:FO6"/>
+    <mergeCell ref="FP4:FR6"/>
+    <mergeCell ref="FS4:GA4"/>
+    <mergeCell ref="GB4:GG5"/>
+    <mergeCell ref="JH6:JJ6"/>
+    <mergeCell ref="JK6:JM6"/>
+    <mergeCell ref="JN6:JP6"/>
+    <mergeCell ref="JW6:JY6"/>
+    <mergeCell ref="HO6:HQ6"/>
+    <mergeCell ref="HU6:HW6"/>
+    <mergeCell ref="HX6:HZ6"/>
+    <mergeCell ref="IA6:IC6"/>
+    <mergeCell ref="ID6:IF6"/>
+    <mergeCell ref="IM6:IO6"/>
+    <mergeCell ref="JE4:JJ5"/>
+    <mergeCell ref="JK4:JP5"/>
+    <mergeCell ref="JQ4:JS6"/>
+    <mergeCell ref="JT4:JV6"/>
+    <mergeCell ref="JW4:KE4"/>
+    <mergeCell ref="JW5:KE5"/>
+    <mergeCell ref="JZ6:KB6"/>
+    <mergeCell ref="KC6:KE6"/>
+    <mergeCell ref="HU4:HZ5"/>
+    <mergeCell ref="IA4:IF5"/>
+    <mergeCell ref="NC6:NH6"/>
+    <mergeCell ref="I7:I9"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="M7:M9"/>
+    <mergeCell ref="N7:N9"/>
+    <mergeCell ref="O7:O9"/>
+    <mergeCell ref="P7:P9"/>
+    <mergeCell ref="Q7:Q9"/>
+    <mergeCell ref="R7:R9"/>
+    <mergeCell ref="S7:S9"/>
+    <mergeCell ref="LY6:LZ7"/>
+    <mergeCell ref="MA6:MD7"/>
+    <mergeCell ref="ME6:MF7"/>
+    <mergeCell ref="MG6:MJ7"/>
+    <mergeCell ref="MQ6:MV6"/>
+    <mergeCell ref="MW6:NB6"/>
+    <mergeCell ref="KF6:KH6"/>
+    <mergeCell ref="KI6:KK6"/>
+    <mergeCell ref="KU6:KZ6"/>
+    <mergeCell ref="LA6:LF6"/>
+    <mergeCell ref="LM6:LR6"/>
+    <mergeCell ref="LS6:LX6"/>
+    <mergeCell ref="IY6:JA6"/>
+    <mergeCell ref="JE6:JG6"/>
+    <mergeCell ref="X7:X9"/>
+    <mergeCell ref="Y7:Y9"/>
+    <mergeCell ref="Z7:Z9"/>
+    <mergeCell ref="AA7:AA9"/>
+    <mergeCell ref="AB7:AB9"/>
+    <mergeCell ref="AC7:AC9"/>
+    <mergeCell ref="AJ7:AJ9"/>
+    <mergeCell ref="AK7:AK9"/>
+    <mergeCell ref="AP7:AP9"/>
+    <mergeCell ref="AQ7:AQ9"/>
+    <mergeCell ref="CF7:CF9"/>
+    <mergeCell ref="CG7:CG9"/>
+    <mergeCell ref="CH7:CH9"/>
+    <mergeCell ref="CI7:CI9"/>
+    <mergeCell ref="CJ7:CJ9"/>
+    <mergeCell ref="CK7:CK9"/>
+    <mergeCell ref="BH7:BH9"/>
+    <mergeCell ref="BI7:BI9"/>
+    <mergeCell ref="BJ7:BJ9"/>
+    <mergeCell ref="BK7:BK9"/>
+    <mergeCell ref="BL7:BL9"/>
+    <mergeCell ref="BM7:BM9"/>
+    <mergeCell ref="BP7:BP9"/>
+    <mergeCell ref="BQ7:BQ9"/>
+    <mergeCell ref="BR7:BR9"/>
+    <mergeCell ref="BS7:BS9"/>
+    <mergeCell ref="BN7:BN9"/>
+    <mergeCell ref="BO7:BO9"/>
+    <mergeCell ref="BT7:BT9"/>
+    <mergeCell ref="BU7:BU9"/>
+    <mergeCell ref="BD7:BD9"/>
+    <mergeCell ref="BE7:BE9"/>
+    <mergeCell ref="BF7:BF9"/>
+    <mergeCell ref="EB7:EB9"/>
+    <mergeCell ref="EC7:EC9"/>
+    <mergeCell ref="ED7:ED9"/>
+    <mergeCell ref="EE7:EE9"/>
+    <mergeCell ref="EF7:EF9"/>
+    <mergeCell ref="EG7:EG9"/>
+    <mergeCell ref="EH7:EH9"/>
+    <mergeCell ref="EI7:EI9"/>
+    <mergeCell ref="FX7:FX9"/>
+    <mergeCell ref="EZ7:EZ9"/>
+    <mergeCell ref="FA7:FA9"/>
+    <mergeCell ref="FB7:FB9"/>
+    <mergeCell ref="FC7:FC9"/>
+    <mergeCell ref="FD7:FD9"/>
+    <mergeCell ref="FE7:FE9"/>
+    <mergeCell ref="FN7:FN9"/>
+    <mergeCell ref="FO7:FO9"/>
+    <mergeCell ref="FP7:FP9"/>
+    <mergeCell ref="FQ7:FQ9"/>
+    <mergeCell ref="FH7:FH9"/>
+    <mergeCell ref="FI7:FI9"/>
+    <mergeCell ref="FJ7:FJ9"/>
+    <mergeCell ref="FK7:FK9"/>
+    <mergeCell ref="FF7:FF9"/>
+    <mergeCell ref="FG7:FG9"/>
+    <mergeCell ref="HH7:HH9"/>
+    <mergeCell ref="HI7:HI9"/>
+    <mergeCell ref="HJ7:HJ9"/>
+    <mergeCell ref="HK7:HK9"/>
+    <mergeCell ref="HL7:HL9"/>
+    <mergeCell ref="HM7:HM9"/>
+    <mergeCell ref="GJ7:GJ9"/>
+    <mergeCell ref="GK7:GK9"/>
+    <mergeCell ref="GL7:GL9"/>
+    <mergeCell ref="GM7:GM9"/>
+    <mergeCell ref="GN7:GN9"/>
+    <mergeCell ref="GO7:GO9"/>
+    <mergeCell ref="GX7:GX9"/>
+    <mergeCell ref="GY7:GY9"/>
+    <mergeCell ref="GZ7:GZ9"/>
+    <mergeCell ref="HA7:HA9"/>
+    <mergeCell ref="GR7:GR9"/>
+    <mergeCell ref="GS7:GS9"/>
+    <mergeCell ref="GT7:GT9"/>
+    <mergeCell ref="GU7:GU9"/>
+    <mergeCell ref="GP7:GP9"/>
+    <mergeCell ref="GQ7:GQ9"/>
+    <mergeCell ref="GF7:GF9"/>
+    <mergeCell ref="IX7:IX9"/>
+    <mergeCell ref="IY7:IY9"/>
+    <mergeCell ref="IN7:IN9"/>
+    <mergeCell ref="IO7:IO9"/>
+    <mergeCell ref="IP7:IP9"/>
+    <mergeCell ref="IQ7:IQ9"/>
+    <mergeCell ref="IR7:IR9"/>
+    <mergeCell ref="IS7:IS9"/>
+    <mergeCell ref="IT7:IT9"/>
+    <mergeCell ref="IU7:IU9"/>
+    <mergeCell ref="IV7:IV9"/>
+    <mergeCell ref="IW7:IW9"/>
+    <mergeCell ref="IK7:IK9"/>
+    <mergeCell ref="KD7:KD9"/>
+    <mergeCell ref="KE7:KE9"/>
+    <mergeCell ref="KF7:KF9"/>
+    <mergeCell ref="KG7:KG9"/>
+    <mergeCell ref="JD7:JD9"/>
+    <mergeCell ref="JE7:JE9"/>
+    <mergeCell ref="JF7:JF9"/>
+    <mergeCell ref="JG7:JG9"/>
+    <mergeCell ref="JH7:JH9"/>
+    <mergeCell ref="JI7:JI9"/>
+    <mergeCell ref="JU7:JU9"/>
+    <mergeCell ref="JL7:JL9"/>
+    <mergeCell ref="JM7:JM9"/>
+    <mergeCell ref="JN7:JN9"/>
+    <mergeCell ref="JO7:JO9"/>
+    <mergeCell ref="JJ7:JJ9"/>
+    <mergeCell ref="JK7:JK9"/>
+    <mergeCell ref="KB7:KB9"/>
+    <mergeCell ref="KC7:KC9"/>
+    <mergeCell ref="IZ7:IZ9"/>
+    <mergeCell ref="JA7:JA9"/>
+    <mergeCell ref="JB7:JB9"/>
+    <mergeCell ref="JC7:JC9"/>
+    <mergeCell ref="OE7:OE8"/>
+    <mergeCell ref="OF7:OF8"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="KQ8:KQ9"/>
+    <mergeCell ref="KR8:KT8"/>
+    <mergeCell ref="NE7:NH7"/>
+    <mergeCell ref="NO7:NP7"/>
+    <mergeCell ref="NQ7:NT7"/>
+    <mergeCell ref="NU7:NV7"/>
+    <mergeCell ref="NW7:NZ7"/>
+    <mergeCell ref="OA7:OA8"/>
+    <mergeCell ref="NK8:NK9"/>
+    <mergeCell ref="NL8:NN8"/>
+    <mergeCell ref="NO8:NO9"/>
+    <mergeCell ref="NP8:NP9"/>
+    <mergeCell ref="LU7:LX7"/>
+    <mergeCell ref="MQ7:MR7"/>
+    <mergeCell ref="MS7:MV7"/>
+    <mergeCell ref="MW7:MX7"/>
+    <mergeCell ref="MY7:NB7"/>
+    <mergeCell ref="NC7:ND7"/>
+    <mergeCell ref="KW7:KZ7"/>
+    <mergeCell ref="KU8:KU9"/>
+    <mergeCell ref="KV8:KV9"/>
+    <mergeCell ref="KW8:KW9"/>
+    <mergeCell ref="KX8:KZ8"/>
+    <mergeCell ref="LA8:LA9"/>
+    <mergeCell ref="LB8:LB9"/>
+    <mergeCell ref="OB7:OB8"/>
+    <mergeCell ref="OC7:OC8"/>
+    <mergeCell ref="OD7:OD8"/>
+    <mergeCell ref="LA7:LB7"/>
+    <mergeCell ref="LC7:LF7"/>
+    <mergeCell ref="LM7:LN7"/>
+    <mergeCell ref="LO7:LR7"/>
+    <mergeCell ref="LS7:LT7"/>
+    <mergeCell ref="NK4:NN7"/>
+    <mergeCell ref="NO4:NT6"/>
+    <mergeCell ref="NU4:NZ6"/>
+    <mergeCell ref="LZ8:LZ9"/>
+    <mergeCell ref="MA8:MA9"/>
+    <mergeCell ref="MB8:MD8"/>
+    <mergeCell ref="LO8:LO9"/>
+    <mergeCell ref="LP8:LR8"/>
+    <mergeCell ref="LS8:LS9"/>
+    <mergeCell ref="LT8:LT9"/>
+    <mergeCell ref="LU8:LU9"/>
+    <mergeCell ref="LV8:LX8"/>
+    <mergeCell ref="LC8:LC9"/>
+    <mergeCell ref="LD8:LF8"/>
+    <mergeCell ref="LI8:LI9"/>
+    <mergeCell ref="LJ8:LL8"/>
+    <mergeCell ref="LM8:LM9"/>
+    <mergeCell ref="LN8:LN9"/>
+    <mergeCell ref="MQ8:MQ9"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="NQ8:NQ9"/>
     <mergeCell ref="NR8:NT8"/>
@@ -10439,543 +10977,6 @@
     <mergeCell ref="MH8:MJ8"/>
     <mergeCell ref="MM8:MM9"/>
     <mergeCell ref="MN8:MP8"/>
-    <mergeCell ref="LU8:LU9"/>
-    <mergeCell ref="LV8:LX8"/>
-    <mergeCell ref="LC8:LC9"/>
-    <mergeCell ref="LD8:LF8"/>
-    <mergeCell ref="LI8:LI9"/>
-    <mergeCell ref="LJ8:LL8"/>
-    <mergeCell ref="LM8:LM9"/>
-    <mergeCell ref="LN8:LN9"/>
-    <mergeCell ref="MQ8:MQ9"/>
-    <mergeCell ref="KU8:KU9"/>
-    <mergeCell ref="KV8:KV9"/>
-    <mergeCell ref="KW8:KW9"/>
-    <mergeCell ref="KX8:KZ8"/>
-    <mergeCell ref="LA8:LA9"/>
-    <mergeCell ref="LB8:LB9"/>
-    <mergeCell ref="OB7:OB8"/>
-    <mergeCell ref="OC7:OC8"/>
-    <mergeCell ref="OD7:OD8"/>
-    <mergeCell ref="LA7:LB7"/>
-    <mergeCell ref="LC7:LF7"/>
-    <mergeCell ref="LM7:LN7"/>
-    <mergeCell ref="LO7:LR7"/>
-    <mergeCell ref="LS7:LT7"/>
-    <mergeCell ref="NK4:NN7"/>
-    <mergeCell ref="NO4:NT6"/>
-    <mergeCell ref="NU4:NZ6"/>
-    <mergeCell ref="LZ8:LZ9"/>
-    <mergeCell ref="MA8:MA9"/>
-    <mergeCell ref="MB8:MD8"/>
-    <mergeCell ref="LO8:LO9"/>
-    <mergeCell ref="LP8:LR8"/>
-    <mergeCell ref="LS8:LS9"/>
-    <mergeCell ref="LT8:LT9"/>
-    <mergeCell ref="OE7:OE8"/>
-    <mergeCell ref="OF7:OF8"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="KQ8:KQ9"/>
-    <mergeCell ref="KR8:KT8"/>
-    <mergeCell ref="NE7:NH7"/>
-    <mergeCell ref="NO7:NP7"/>
-    <mergeCell ref="NQ7:NT7"/>
-    <mergeCell ref="NU7:NV7"/>
-    <mergeCell ref="NW7:NZ7"/>
-    <mergeCell ref="OA7:OA8"/>
-    <mergeCell ref="NK8:NK9"/>
-    <mergeCell ref="NL8:NN8"/>
-    <mergeCell ref="NO8:NO9"/>
-    <mergeCell ref="NP8:NP9"/>
-    <mergeCell ref="LU7:LX7"/>
-    <mergeCell ref="MQ7:MR7"/>
-    <mergeCell ref="MS7:MV7"/>
-    <mergeCell ref="MW7:MX7"/>
-    <mergeCell ref="MY7:NB7"/>
-    <mergeCell ref="NC7:ND7"/>
-    <mergeCell ref="KW7:KZ7"/>
-    <mergeCell ref="IK7:IK9"/>
-    <mergeCell ref="KD7:KD9"/>
-    <mergeCell ref="KE7:KE9"/>
-    <mergeCell ref="KF7:KF9"/>
-    <mergeCell ref="KG7:KG9"/>
-    <mergeCell ref="JD7:JD9"/>
-    <mergeCell ref="JE7:JE9"/>
-    <mergeCell ref="JF7:JF9"/>
-    <mergeCell ref="JG7:JG9"/>
-    <mergeCell ref="JH7:JH9"/>
-    <mergeCell ref="JI7:JI9"/>
-    <mergeCell ref="JU7:JU9"/>
-    <mergeCell ref="JL7:JL9"/>
-    <mergeCell ref="JM7:JM9"/>
-    <mergeCell ref="JN7:JN9"/>
-    <mergeCell ref="JO7:JO9"/>
-    <mergeCell ref="JJ7:JJ9"/>
-    <mergeCell ref="JK7:JK9"/>
-    <mergeCell ref="KB7:KB9"/>
-    <mergeCell ref="KC7:KC9"/>
-    <mergeCell ref="IZ7:IZ9"/>
-    <mergeCell ref="JA7:JA9"/>
-    <mergeCell ref="JB7:JB9"/>
-    <mergeCell ref="JC7:JC9"/>
-    <mergeCell ref="IX7:IX9"/>
-    <mergeCell ref="IY7:IY9"/>
-    <mergeCell ref="IN7:IN9"/>
-    <mergeCell ref="IO7:IO9"/>
-    <mergeCell ref="IP7:IP9"/>
-    <mergeCell ref="IQ7:IQ9"/>
-    <mergeCell ref="IR7:IR9"/>
-    <mergeCell ref="IS7:IS9"/>
-    <mergeCell ref="IT7:IT9"/>
-    <mergeCell ref="IU7:IU9"/>
-    <mergeCell ref="IV7:IV9"/>
-    <mergeCell ref="IW7:IW9"/>
-    <mergeCell ref="FG7:FG9"/>
-    <mergeCell ref="HH7:HH9"/>
-    <mergeCell ref="HI7:HI9"/>
-    <mergeCell ref="HJ7:HJ9"/>
-    <mergeCell ref="HK7:HK9"/>
-    <mergeCell ref="HL7:HL9"/>
-    <mergeCell ref="HM7:HM9"/>
-    <mergeCell ref="GJ7:GJ9"/>
-    <mergeCell ref="GK7:GK9"/>
-    <mergeCell ref="GL7:GL9"/>
-    <mergeCell ref="GM7:GM9"/>
-    <mergeCell ref="GN7:GN9"/>
-    <mergeCell ref="GO7:GO9"/>
-    <mergeCell ref="GX7:GX9"/>
-    <mergeCell ref="GY7:GY9"/>
-    <mergeCell ref="GZ7:GZ9"/>
-    <mergeCell ref="HA7:HA9"/>
-    <mergeCell ref="GR7:GR9"/>
-    <mergeCell ref="GS7:GS9"/>
-    <mergeCell ref="GT7:GT9"/>
-    <mergeCell ref="GU7:GU9"/>
-    <mergeCell ref="GP7:GP9"/>
-    <mergeCell ref="GQ7:GQ9"/>
-    <mergeCell ref="GF7:GF9"/>
-    <mergeCell ref="EB7:EB9"/>
-    <mergeCell ref="EC7:EC9"/>
-    <mergeCell ref="ED7:ED9"/>
-    <mergeCell ref="EE7:EE9"/>
-    <mergeCell ref="EF7:EF9"/>
-    <mergeCell ref="EG7:EG9"/>
-    <mergeCell ref="EH7:EH9"/>
-    <mergeCell ref="EI7:EI9"/>
-    <mergeCell ref="FX7:FX9"/>
-    <mergeCell ref="EZ7:EZ9"/>
-    <mergeCell ref="FA7:FA9"/>
-    <mergeCell ref="FB7:FB9"/>
-    <mergeCell ref="FC7:FC9"/>
-    <mergeCell ref="FD7:FD9"/>
-    <mergeCell ref="FE7:FE9"/>
-    <mergeCell ref="FN7:FN9"/>
-    <mergeCell ref="FO7:FO9"/>
-    <mergeCell ref="FP7:FP9"/>
-    <mergeCell ref="FQ7:FQ9"/>
-    <mergeCell ref="FH7:FH9"/>
-    <mergeCell ref="FI7:FI9"/>
-    <mergeCell ref="FJ7:FJ9"/>
-    <mergeCell ref="FK7:FK9"/>
-    <mergeCell ref="FF7:FF9"/>
-    <mergeCell ref="AQ7:AQ9"/>
-    <mergeCell ref="CF7:CF9"/>
-    <mergeCell ref="CG7:CG9"/>
-    <mergeCell ref="CH7:CH9"/>
-    <mergeCell ref="CI7:CI9"/>
-    <mergeCell ref="CJ7:CJ9"/>
-    <mergeCell ref="CK7:CK9"/>
-    <mergeCell ref="BH7:BH9"/>
-    <mergeCell ref="BI7:BI9"/>
-    <mergeCell ref="BJ7:BJ9"/>
-    <mergeCell ref="BK7:BK9"/>
-    <mergeCell ref="BL7:BL9"/>
-    <mergeCell ref="BM7:BM9"/>
-    <mergeCell ref="BP7:BP9"/>
-    <mergeCell ref="BQ7:BQ9"/>
-    <mergeCell ref="BR7:BR9"/>
-    <mergeCell ref="BS7:BS9"/>
-    <mergeCell ref="BN7:BN9"/>
-    <mergeCell ref="BO7:BO9"/>
-    <mergeCell ref="BT7:BT9"/>
-    <mergeCell ref="BU7:BU9"/>
-    <mergeCell ref="BD7:BD9"/>
-    <mergeCell ref="BE7:BE9"/>
-    <mergeCell ref="BF7:BF9"/>
-    <mergeCell ref="X7:X9"/>
-    <mergeCell ref="Y7:Y9"/>
-    <mergeCell ref="Z7:Z9"/>
-    <mergeCell ref="AA7:AA9"/>
-    <mergeCell ref="AB7:AB9"/>
-    <mergeCell ref="AC7:AC9"/>
-    <mergeCell ref="AJ7:AJ9"/>
-    <mergeCell ref="AK7:AK9"/>
-    <mergeCell ref="AP7:AP9"/>
-    <mergeCell ref="NC6:NH6"/>
-    <mergeCell ref="I7:I9"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="M7:M9"/>
-    <mergeCell ref="N7:N9"/>
-    <mergeCell ref="O7:O9"/>
-    <mergeCell ref="P7:P9"/>
-    <mergeCell ref="Q7:Q9"/>
-    <mergeCell ref="R7:R9"/>
-    <mergeCell ref="S7:S9"/>
-    <mergeCell ref="LY6:LZ7"/>
-    <mergeCell ref="MA6:MD7"/>
-    <mergeCell ref="ME6:MF7"/>
-    <mergeCell ref="MG6:MJ7"/>
-    <mergeCell ref="MQ6:MV6"/>
-    <mergeCell ref="MW6:NB6"/>
-    <mergeCell ref="KF6:KH6"/>
-    <mergeCell ref="KI6:KK6"/>
-    <mergeCell ref="KU6:KZ6"/>
-    <mergeCell ref="LA6:LF6"/>
-    <mergeCell ref="LM6:LR6"/>
-    <mergeCell ref="LS6:LX6"/>
-    <mergeCell ref="IY6:JA6"/>
-    <mergeCell ref="JE6:JG6"/>
-    <mergeCell ref="FM4:FO6"/>
-    <mergeCell ref="FP4:FR6"/>
-    <mergeCell ref="FS4:GA4"/>
-    <mergeCell ref="GB4:GG5"/>
-    <mergeCell ref="JH6:JJ6"/>
-    <mergeCell ref="JK6:JM6"/>
-    <mergeCell ref="JN6:JP6"/>
-    <mergeCell ref="JW6:JY6"/>
-    <mergeCell ref="HO6:HQ6"/>
-    <mergeCell ref="HU6:HW6"/>
-    <mergeCell ref="HX6:HZ6"/>
-    <mergeCell ref="IA6:IC6"/>
-    <mergeCell ref="ID6:IF6"/>
-    <mergeCell ref="IM6:IO6"/>
-    <mergeCell ref="JE4:JJ5"/>
-    <mergeCell ref="JK4:JP5"/>
-    <mergeCell ref="JQ4:JS6"/>
-    <mergeCell ref="JT4:JV6"/>
-    <mergeCell ref="JW4:KE4"/>
-    <mergeCell ref="JW5:KE5"/>
-    <mergeCell ref="JZ6:KB6"/>
-    <mergeCell ref="KC6:KE6"/>
-    <mergeCell ref="HU4:HZ5"/>
-    <mergeCell ref="IA4:IF5"/>
-    <mergeCell ref="CG6:CI6"/>
-    <mergeCell ref="CJ6:CL6"/>
-    <mergeCell ref="CM6:CO6"/>
-    <mergeCell ref="CP6:CR6"/>
-    <mergeCell ref="CY6:DA6"/>
-    <mergeCell ref="DB6:DD6"/>
-    <mergeCell ref="AQ6:AS6"/>
-    <mergeCell ref="AW6:AY6"/>
-    <mergeCell ref="AZ6:BB6"/>
-    <mergeCell ref="BC6:BE6"/>
-    <mergeCell ref="BF6:BH6"/>
-    <mergeCell ref="BO6:BQ6"/>
-    <mergeCell ref="BL4:BN6"/>
-    <mergeCell ref="BO4:BW4"/>
-    <mergeCell ref="BX4:CC5"/>
-    <mergeCell ref="CD4:CF6"/>
-    <mergeCell ref="CG4:CL5"/>
-    <mergeCell ref="CM4:CR5"/>
-    <mergeCell ref="BR6:BT6"/>
-    <mergeCell ref="BU6:BW6"/>
-    <mergeCell ref="BX6:BZ6"/>
-    <mergeCell ref="CA6:CC6"/>
-    <mergeCell ref="CY4:DG4"/>
-    <mergeCell ref="S6:U6"/>
-    <mergeCell ref="V6:X6"/>
-    <mergeCell ref="AE6:AG6"/>
-    <mergeCell ref="AH6:AJ6"/>
-    <mergeCell ref="AK6:AM6"/>
-    <mergeCell ref="AN6:AP6"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="H6:H9"/>
-    <mergeCell ref="I6:L6"/>
-    <mergeCell ref="M6:O6"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="AL7:AL9"/>
-    <mergeCell ref="AM7:AM9"/>
-    <mergeCell ref="AN7:AN9"/>
-    <mergeCell ref="AO7:AO9"/>
-    <mergeCell ref="AF7:AF9"/>
-    <mergeCell ref="AG7:AG9"/>
-    <mergeCell ref="AH7:AH9"/>
-    <mergeCell ref="AI7:AI9"/>
-    <mergeCell ref="AD7:AD9"/>
-    <mergeCell ref="AE7:AE9"/>
-    <mergeCell ref="T7:T9"/>
-    <mergeCell ref="U7:U9"/>
-    <mergeCell ref="AE5:AM5"/>
-    <mergeCell ref="BO5:BW5"/>
-    <mergeCell ref="CY5:DG5"/>
-    <mergeCell ref="EI5:EQ5"/>
-    <mergeCell ref="FS5:GA5"/>
-    <mergeCell ref="HC5:HK5"/>
-    <mergeCell ref="MK4:NH4"/>
-    <mergeCell ref="NI4:NI9"/>
-    <mergeCell ref="NJ4:NJ9"/>
-    <mergeCell ref="MK5:MK9"/>
-    <mergeCell ref="ML5:ML9"/>
-    <mergeCell ref="MM5:MP7"/>
-    <mergeCell ref="MQ5:NH5"/>
-    <mergeCell ref="KF4:KK5"/>
-    <mergeCell ref="KL4:KN6"/>
-    <mergeCell ref="KO4:LF4"/>
-    <mergeCell ref="LG4:LX4"/>
-    <mergeCell ref="LY4:MD5"/>
-    <mergeCell ref="ME4:MJ5"/>
-    <mergeCell ref="KO5:KO9"/>
-    <mergeCell ref="KP5:KP9"/>
-    <mergeCell ref="KQ5:KT7"/>
-    <mergeCell ref="KU5:LF5"/>
-    <mergeCell ref="JB4:JD6"/>
-    <mergeCell ref="IG4:II6"/>
-    <mergeCell ref="IJ4:IL6"/>
-    <mergeCell ref="IM4:IU4"/>
-    <mergeCell ref="IV4:JA5"/>
-    <mergeCell ref="IM5:IU5"/>
-    <mergeCell ref="IP6:IR6"/>
-    <mergeCell ref="IS6:IU6"/>
-    <mergeCell ref="IV6:IX6"/>
-    <mergeCell ref="GQ4:GV5"/>
-    <mergeCell ref="GW4:GY6"/>
-    <mergeCell ref="GZ4:HB6"/>
-    <mergeCell ref="HC4:HK4"/>
-    <mergeCell ref="HL4:HQ5"/>
-    <mergeCell ref="HR4:HT6"/>
-    <mergeCell ref="GQ6:GS6"/>
-    <mergeCell ref="GT6:GV6"/>
-    <mergeCell ref="HC6:HE6"/>
-    <mergeCell ref="HF6:HH6"/>
-    <mergeCell ref="GH4:GJ6"/>
-    <mergeCell ref="GK4:GP5"/>
-    <mergeCell ref="GE6:GG6"/>
-    <mergeCell ref="GK6:GM6"/>
-    <mergeCell ref="GN6:GP6"/>
-    <mergeCell ref="EF4:EH6"/>
-    <mergeCell ref="EI4:EQ4"/>
-    <mergeCell ref="ER4:EW5"/>
-    <mergeCell ref="EX4:EZ6"/>
-    <mergeCell ref="FA4:FF5"/>
-    <mergeCell ref="FG4:FL5"/>
-    <mergeCell ref="ER6:ET6"/>
-    <mergeCell ref="EU6:EW6"/>
-    <mergeCell ref="FA6:FC6"/>
-    <mergeCell ref="FD6:FF6"/>
-    <mergeCell ref="FG6:FI6"/>
-    <mergeCell ref="FJ6:FL6"/>
-    <mergeCell ref="FS6:FU6"/>
-    <mergeCell ref="FV6:FX6"/>
-    <mergeCell ref="FY6:GA6"/>
-    <mergeCell ref="GB6:GD6"/>
-    <mergeCell ref="EI6:EK6"/>
-    <mergeCell ref="EL6:EN6"/>
-    <mergeCell ref="EO6:EQ6"/>
-    <mergeCell ref="DH4:DM5"/>
-    <mergeCell ref="DN4:DP6"/>
-    <mergeCell ref="DQ4:DV5"/>
-    <mergeCell ref="DW4:EB5"/>
-    <mergeCell ref="EC4:EE6"/>
-    <mergeCell ref="DE6:DG6"/>
-    <mergeCell ref="DH6:DJ6"/>
-    <mergeCell ref="DK6:DM6"/>
-    <mergeCell ref="DQ6:DS6"/>
-    <mergeCell ref="DT6:DV6"/>
-    <mergeCell ref="DW6:DY6"/>
-    <mergeCell ref="DZ6:EB6"/>
-    <mergeCell ref="KO3:MJ3"/>
-    <mergeCell ref="MK3:NH3"/>
-    <mergeCell ref="NI3:NZ3"/>
-    <mergeCell ref="OA3:OF6"/>
-    <mergeCell ref="M4:R5"/>
-    <mergeCell ref="S4:X5"/>
-    <mergeCell ref="Y4:AA6"/>
-    <mergeCell ref="AB4:AD6"/>
-    <mergeCell ref="AE4:AM4"/>
-    <mergeCell ref="AN4:AS5"/>
-    <mergeCell ref="CG3:DP3"/>
-    <mergeCell ref="DQ3:EZ3"/>
-    <mergeCell ref="FA3:GJ3"/>
-    <mergeCell ref="GK3:HT3"/>
-    <mergeCell ref="HU3:JD3"/>
-    <mergeCell ref="JE3:KN3"/>
-    <mergeCell ref="HI6:HK6"/>
-    <mergeCell ref="HL6:HN6"/>
-    <mergeCell ref="CS4:CU6"/>
-    <mergeCell ref="CV4:CX6"/>
-    <mergeCell ref="AT4:AV6"/>
-    <mergeCell ref="AW4:BB5"/>
-    <mergeCell ref="BC4:BH5"/>
-    <mergeCell ref="BI4:BK6"/>
-    <mergeCell ref="A3:A9"/>
-    <mergeCell ref="B3:B9"/>
-    <mergeCell ref="C3:C9"/>
-    <mergeCell ref="D3:D9"/>
-    <mergeCell ref="F3:F9"/>
-    <mergeCell ref="H3:L5"/>
-    <mergeCell ref="M3:AR3"/>
-    <mergeCell ref="AW3:CF3"/>
-    <mergeCell ref="LY8:LY9"/>
-    <mergeCell ref="LG5:LG9"/>
-    <mergeCell ref="LH5:LH9"/>
-    <mergeCell ref="LI5:LL7"/>
-    <mergeCell ref="LM5:LX5"/>
-    <mergeCell ref="KJ7:KJ9"/>
-    <mergeCell ref="KK7:KK9"/>
-    <mergeCell ref="KH7:KH9"/>
-    <mergeCell ref="KI7:KI9"/>
-    <mergeCell ref="JX7:JX9"/>
-    <mergeCell ref="JY7:JY9"/>
-    <mergeCell ref="JZ7:JZ9"/>
-    <mergeCell ref="KA7:KA9"/>
-    <mergeCell ref="JR7:JR9"/>
-    <mergeCell ref="JS7:JS9"/>
-    <mergeCell ref="JT7:JT9"/>
-    <mergeCell ref="HP7:HP9"/>
-    <mergeCell ref="HQ7:HQ9"/>
-    <mergeCell ref="HR7:HR9"/>
-    <mergeCell ref="HS7:HS9"/>
-    <mergeCell ref="HN7:HN9"/>
-    <mergeCell ref="HO7:HO9"/>
-    <mergeCell ref="HD7:HD9"/>
-    <mergeCell ref="HE7:HE9"/>
-    <mergeCell ref="HF7:HF9"/>
-    <mergeCell ref="HG7:HG9"/>
-    <mergeCell ref="HT7:HT9"/>
-    <mergeCell ref="HU7:HU9"/>
-    <mergeCell ref="HV7:HV9"/>
-    <mergeCell ref="HW7:HW9"/>
-    <mergeCell ref="HX7:HX9"/>
-    <mergeCell ref="HY7:HY9"/>
-    <mergeCell ref="IH7:IH9"/>
-    <mergeCell ref="II7:II9"/>
-    <mergeCell ref="IJ7:IJ9"/>
-    <mergeCell ref="IB7:IB9"/>
-    <mergeCell ref="IC7:IC9"/>
-    <mergeCell ref="ID7:ID9"/>
-    <mergeCell ref="IE7:IE9"/>
-    <mergeCell ref="HZ7:HZ9"/>
-    <mergeCell ref="IA7:IA9"/>
-    <mergeCell ref="GG7:GG9"/>
-    <mergeCell ref="GH7:GH9"/>
-    <mergeCell ref="GI7:GI9"/>
-    <mergeCell ref="GD7:GD9"/>
-    <mergeCell ref="GE7:GE9"/>
-    <mergeCell ref="FT7:FT9"/>
-    <mergeCell ref="FU7:FU9"/>
-    <mergeCell ref="FV7:FV9"/>
-    <mergeCell ref="FW7:FW9"/>
-    <mergeCell ref="FY7:FY9"/>
-    <mergeCell ref="FZ7:FZ9"/>
-    <mergeCell ref="GA7:GA9"/>
-    <mergeCell ref="GB7:GB9"/>
-    <mergeCell ref="GC7:GC9"/>
-    <mergeCell ref="EV7:EV9"/>
-    <mergeCell ref="EW7:EW9"/>
-    <mergeCell ref="EX7:EX9"/>
-    <mergeCell ref="EY7:EY9"/>
-    <mergeCell ref="ET7:ET9"/>
-    <mergeCell ref="EU7:EU9"/>
-    <mergeCell ref="EJ7:EJ9"/>
-    <mergeCell ref="EK7:EK9"/>
-    <mergeCell ref="EL7:EL9"/>
-    <mergeCell ref="EM7:EM9"/>
-    <mergeCell ref="EN7:EN9"/>
-    <mergeCell ref="EO7:EO9"/>
-    <mergeCell ref="EP7:EP9"/>
-    <mergeCell ref="EQ7:EQ9"/>
-    <mergeCell ref="ER7:ER9"/>
-    <mergeCell ref="ES7:ES9"/>
-    <mergeCell ref="DX7:DX9"/>
-    <mergeCell ref="DY7:DY9"/>
-    <mergeCell ref="DZ7:DZ9"/>
-    <mergeCell ref="EA7:EA9"/>
-    <mergeCell ref="DR7:DR9"/>
-    <mergeCell ref="DS7:DS9"/>
-    <mergeCell ref="DT7:DT9"/>
-    <mergeCell ref="DU7:DU9"/>
-    <mergeCell ref="DL7:DL9"/>
-    <mergeCell ref="DM7:DM9"/>
-    <mergeCell ref="DN7:DN9"/>
-    <mergeCell ref="DO7:DO9"/>
-    <mergeCell ref="DV7:DV9"/>
-    <mergeCell ref="DW7:DW9"/>
-    <mergeCell ref="DJ7:DJ9"/>
-    <mergeCell ref="DK7:DK9"/>
-    <mergeCell ref="CZ7:CZ9"/>
-    <mergeCell ref="DA7:DA9"/>
-    <mergeCell ref="DB7:DB9"/>
-    <mergeCell ref="DC7:DC9"/>
-    <mergeCell ref="CX7:CX9"/>
-    <mergeCell ref="CY7:CY9"/>
-    <mergeCell ref="CN7:CN9"/>
-    <mergeCell ref="CO7:CO9"/>
-    <mergeCell ref="CP7:CP9"/>
-    <mergeCell ref="CQ7:CQ9"/>
-    <mergeCell ref="DD7:DD9"/>
-    <mergeCell ref="DE7:DE9"/>
-    <mergeCell ref="DF7:DF9"/>
-    <mergeCell ref="DG7:DG9"/>
-    <mergeCell ref="DH7:DH9"/>
-    <mergeCell ref="DI7:DI9"/>
-    <mergeCell ref="CR7:CR9"/>
-    <mergeCell ref="CS7:CS9"/>
-    <mergeCell ref="CT7:CT9"/>
-    <mergeCell ref="CU7:CU9"/>
-    <mergeCell ref="CV7:CV9"/>
-    <mergeCell ref="CW7:CW9"/>
-    <mergeCell ref="CL7:CL9"/>
-    <mergeCell ref="CM7:CM9"/>
-    <mergeCell ref="CB7:CB9"/>
-    <mergeCell ref="CC7:CC9"/>
-    <mergeCell ref="CD7:CD9"/>
-    <mergeCell ref="CE7:CE9"/>
-    <mergeCell ref="BV7:BV9"/>
-    <mergeCell ref="BW7:BW9"/>
-    <mergeCell ref="BX7:BX9"/>
-    <mergeCell ref="BY7:BY9"/>
-    <mergeCell ref="BZ7:BZ9"/>
-    <mergeCell ref="CA7:CA9"/>
-    <mergeCell ref="BG7:BG9"/>
-    <mergeCell ref="BB7:BB9"/>
-    <mergeCell ref="BC7:BC9"/>
-    <mergeCell ref="AR7:AR9"/>
-    <mergeCell ref="AS7:AS9"/>
-    <mergeCell ref="AT7:AT9"/>
-    <mergeCell ref="AU7:AU9"/>
-    <mergeCell ref="AV7:AV9"/>
-    <mergeCell ref="AW7:AW9"/>
-    <mergeCell ref="AX7:AX9"/>
-    <mergeCell ref="AY7:AY9"/>
-    <mergeCell ref="AZ7:AZ9"/>
-    <mergeCell ref="BA7:BA9"/>
-    <mergeCell ref="V7:V9"/>
-    <mergeCell ref="W7:W9"/>
-    <mergeCell ref="KL7:KL9"/>
-    <mergeCell ref="KM7:KM9"/>
-    <mergeCell ref="KN7:KN9"/>
-    <mergeCell ref="KU7:KV7"/>
-    <mergeCell ref="JP7:JP9"/>
-    <mergeCell ref="JQ7:JQ9"/>
-    <mergeCell ref="JV7:JV9"/>
-    <mergeCell ref="JW7:JW9"/>
-    <mergeCell ref="IF7:IF9"/>
-    <mergeCell ref="IG7:IG9"/>
-    <mergeCell ref="IL7:IL9"/>
-    <mergeCell ref="IM7:IM9"/>
-    <mergeCell ref="GV7:GV9"/>
-    <mergeCell ref="GW7:GW9"/>
-    <mergeCell ref="HB7:HB9"/>
-    <mergeCell ref="HC7:HC9"/>
-    <mergeCell ref="FL7:FL9"/>
-    <mergeCell ref="FM7:FM9"/>
-    <mergeCell ref="FR7:FR9"/>
-    <mergeCell ref="FS7:FS9"/>
-    <mergeCell ref="DP7:DP9"/>
-    <mergeCell ref="DQ7:DQ9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/src/main/resources/templates/summaryReportForm4.xlsx
+++ b/src/main/resources/templates/summaryReportForm4.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21231"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{023D997E-D358-40F6-A9BA-E863B52BEB3B}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D8DAFEB-67EC-45B4-9840-54ECB9E9C178}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3413,31 +3413,287 @@
     <xf numFmtId="14" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="2" fontId="3" fillId="4" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="3" fillId="4" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="2" fontId="1" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -3448,37 +3704,10 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -3489,249 +3718,20 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="4" borderId="34" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="3" fillId="4" borderId="37" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="5" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="26" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="right" vertical="center"/>
-      <protection locked="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4024,14 +4024,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:396" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="32" t="s">
+      <c r="A1" s="134" t="s">
         <v>756</v>
       </c>
-      <c r="B1" s="32"/>
-      <c r="C1" s="32"/>
-      <c r="D1" s="32"/>
-      <c r="E1" s="32"/>
-      <c r="F1" s="32"/>
+      <c r="B1" s="134"/>
+      <c r="C1" s="134"/>
+      <c r="D1" s="134"/>
+      <c r="E1" s="134"/>
+      <c r="F1" s="134"/>
       <c r="G1" s="31" t="s">
         <v>854</v>
       </c>
@@ -4043,3817 +4043,3817 @@
     </row>
     <row r="2" spans="1:396" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="3" spans="1:396" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="50" t="s">
+      <c r="A3" s="48" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="50" t="s">
+      <c r="B3" s="48" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="50" t="s">
+      <c r="C3" s="48" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="50" t="s">
+      <c r="D3" s="48" t="s">
         <v>749</v>
       </c>
       <c r="E3" s="4"/>
-      <c r="F3" s="50" t="s">
+      <c r="F3" s="48" t="s">
         <v>750</v>
       </c>
       <c r="G3" s="5"/>
-      <c r="H3" s="119" t="s">
+      <c r="H3" s="50" t="s">
         <v>751</v>
       </c>
-      <c r="I3" s="120"/>
-      <c r="J3" s="120"/>
-      <c r="K3" s="120"/>
-      <c r="L3" s="121"/>
-      <c r="M3" s="112" t="s">
+      <c r="I3" s="51"/>
+      <c r="J3" s="51"/>
+      <c r="K3" s="51"/>
+      <c r="L3" s="52"/>
+      <c r="M3" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="N3" s="112"/>
-      <c r="O3" s="112"/>
-      <c r="P3" s="112"/>
-      <c r="Q3" s="112"/>
-      <c r="R3" s="112"/>
-      <c r="S3" s="112"/>
-      <c r="T3" s="112"/>
-      <c r="U3" s="112"/>
-      <c r="V3" s="112"/>
-      <c r="W3" s="112"/>
-      <c r="X3" s="112"/>
-      <c r="Y3" s="112"/>
-      <c r="Z3" s="112"/>
-      <c r="AA3" s="112"/>
-      <c r="AB3" s="112"/>
-      <c r="AC3" s="112"/>
-      <c r="AD3" s="128"/>
-      <c r="AE3" s="128"/>
-      <c r="AF3" s="128"/>
-      <c r="AG3" s="128"/>
-      <c r="AH3" s="128"/>
-      <c r="AI3" s="128"/>
-      <c r="AJ3" s="128"/>
-      <c r="AK3" s="128"/>
-      <c r="AL3" s="128"/>
-      <c r="AM3" s="128"/>
-      <c r="AN3" s="112"/>
-      <c r="AO3" s="112"/>
-      <c r="AP3" s="112"/>
-      <c r="AQ3" s="112"/>
-      <c r="AR3" s="112"/>
+      <c r="N3" s="59"/>
+      <c r="O3" s="59"/>
+      <c r="P3" s="59"/>
+      <c r="Q3" s="59"/>
+      <c r="R3" s="59"/>
+      <c r="S3" s="59"/>
+      <c r="T3" s="59"/>
+      <c r="U3" s="59"/>
+      <c r="V3" s="59"/>
+      <c r="W3" s="59"/>
+      <c r="X3" s="59"/>
+      <c r="Y3" s="59"/>
+      <c r="Z3" s="59"/>
+      <c r="AA3" s="59"/>
+      <c r="AB3" s="59"/>
+      <c r="AC3" s="59"/>
+      <c r="AD3" s="60"/>
+      <c r="AE3" s="60"/>
+      <c r="AF3" s="60"/>
+      <c r="AG3" s="60"/>
+      <c r="AH3" s="60"/>
+      <c r="AI3" s="60"/>
+      <c r="AJ3" s="60"/>
+      <c r="AK3" s="60"/>
+      <c r="AL3" s="60"/>
+      <c r="AM3" s="60"/>
+      <c r="AN3" s="59"/>
+      <c r="AO3" s="59"/>
+      <c r="AP3" s="59"/>
+      <c r="AQ3" s="59"/>
+      <c r="AR3" s="59"/>
       <c r="AS3" s="6"/>
       <c r="AT3" s="6"/>
       <c r="AU3" s="6"/>
       <c r="AV3" s="6"/>
-      <c r="AW3" s="111" t="s">
+      <c r="AW3" s="61" t="s">
         <v>4</v>
       </c>
-      <c r="AX3" s="112"/>
-      <c r="AY3" s="112"/>
-      <c r="AZ3" s="112"/>
-      <c r="BA3" s="112"/>
-      <c r="BB3" s="112"/>
-      <c r="BC3" s="112"/>
-      <c r="BD3" s="112"/>
-      <c r="BE3" s="112"/>
-      <c r="BF3" s="112"/>
-      <c r="BG3" s="112"/>
-      <c r="BH3" s="112"/>
-      <c r="BI3" s="112"/>
-      <c r="BJ3" s="112"/>
-      <c r="BK3" s="112"/>
-      <c r="BL3" s="112"/>
-      <c r="BM3" s="112"/>
-      <c r="BN3" s="112"/>
-      <c r="BO3" s="112"/>
-      <c r="BP3" s="112"/>
-      <c r="BQ3" s="112"/>
-      <c r="BR3" s="112"/>
-      <c r="BS3" s="112"/>
-      <c r="BT3" s="112"/>
-      <c r="BU3" s="112"/>
-      <c r="BV3" s="112"/>
-      <c r="BW3" s="112"/>
-      <c r="BX3" s="112"/>
-      <c r="BY3" s="112"/>
-      <c r="BZ3" s="112"/>
-      <c r="CA3" s="112"/>
-      <c r="CB3" s="112"/>
-      <c r="CC3" s="112"/>
-      <c r="CD3" s="112"/>
-      <c r="CE3" s="112"/>
-      <c r="CF3" s="116"/>
-      <c r="CG3" s="111" t="s">
+      <c r="AX3" s="59"/>
+      <c r="AY3" s="59"/>
+      <c r="AZ3" s="59"/>
+      <c r="BA3" s="59"/>
+      <c r="BB3" s="59"/>
+      <c r="BC3" s="59"/>
+      <c r="BD3" s="59"/>
+      <c r="BE3" s="59"/>
+      <c r="BF3" s="59"/>
+      <c r="BG3" s="59"/>
+      <c r="BH3" s="59"/>
+      <c r="BI3" s="59"/>
+      <c r="BJ3" s="59"/>
+      <c r="BK3" s="59"/>
+      <c r="BL3" s="59"/>
+      <c r="BM3" s="59"/>
+      <c r="BN3" s="59"/>
+      <c r="BO3" s="59"/>
+      <c r="BP3" s="59"/>
+      <c r="BQ3" s="59"/>
+      <c r="BR3" s="59"/>
+      <c r="BS3" s="59"/>
+      <c r="BT3" s="59"/>
+      <c r="BU3" s="59"/>
+      <c r="BV3" s="59"/>
+      <c r="BW3" s="59"/>
+      <c r="BX3" s="59"/>
+      <c r="BY3" s="59"/>
+      <c r="BZ3" s="59"/>
+      <c r="CA3" s="59"/>
+      <c r="CB3" s="59"/>
+      <c r="CC3" s="59"/>
+      <c r="CD3" s="59"/>
+      <c r="CE3" s="59"/>
+      <c r="CF3" s="62"/>
+      <c r="CG3" s="61" t="s">
         <v>5</v>
       </c>
-      <c r="CH3" s="112"/>
-      <c r="CI3" s="112"/>
-      <c r="CJ3" s="112"/>
-      <c r="CK3" s="112"/>
-      <c r="CL3" s="112"/>
-      <c r="CM3" s="112"/>
-      <c r="CN3" s="112"/>
-      <c r="CO3" s="112"/>
-      <c r="CP3" s="112"/>
-      <c r="CQ3" s="112"/>
-      <c r="CR3" s="112"/>
-      <c r="CS3" s="112"/>
-      <c r="CT3" s="112"/>
-      <c r="CU3" s="112"/>
-      <c r="CV3" s="112"/>
-      <c r="CW3" s="112"/>
-      <c r="CX3" s="112"/>
-      <c r="CY3" s="112"/>
-      <c r="CZ3" s="112"/>
-      <c r="DA3" s="112"/>
-      <c r="DB3" s="112"/>
-      <c r="DC3" s="112"/>
-      <c r="DD3" s="112"/>
-      <c r="DE3" s="112"/>
-      <c r="DF3" s="112"/>
-      <c r="DG3" s="112"/>
-      <c r="DH3" s="112"/>
-      <c r="DI3" s="112"/>
-      <c r="DJ3" s="112"/>
-      <c r="DK3" s="112"/>
-      <c r="DL3" s="112"/>
-      <c r="DM3" s="112"/>
-      <c r="DN3" s="112"/>
-      <c r="DO3" s="112"/>
-      <c r="DP3" s="116"/>
-      <c r="DQ3" s="111" t="s">
+      <c r="CH3" s="59"/>
+      <c r="CI3" s="59"/>
+      <c r="CJ3" s="59"/>
+      <c r="CK3" s="59"/>
+      <c r="CL3" s="59"/>
+      <c r="CM3" s="59"/>
+      <c r="CN3" s="59"/>
+      <c r="CO3" s="59"/>
+      <c r="CP3" s="59"/>
+      <c r="CQ3" s="59"/>
+      <c r="CR3" s="59"/>
+      <c r="CS3" s="59"/>
+      <c r="CT3" s="59"/>
+      <c r="CU3" s="59"/>
+      <c r="CV3" s="59"/>
+      <c r="CW3" s="59"/>
+      <c r="CX3" s="59"/>
+      <c r="CY3" s="59"/>
+      <c r="CZ3" s="59"/>
+      <c r="DA3" s="59"/>
+      <c r="DB3" s="59"/>
+      <c r="DC3" s="59"/>
+      <c r="DD3" s="59"/>
+      <c r="DE3" s="59"/>
+      <c r="DF3" s="59"/>
+      <c r="DG3" s="59"/>
+      <c r="DH3" s="59"/>
+      <c r="DI3" s="59"/>
+      <c r="DJ3" s="59"/>
+      <c r="DK3" s="59"/>
+      <c r="DL3" s="59"/>
+      <c r="DM3" s="59"/>
+      <c r="DN3" s="59"/>
+      <c r="DO3" s="59"/>
+      <c r="DP3" s="62"/>
+      <c r="DQ3" s="61" t="s">
         <v>6</v>
       </c>
-      <c r="DR3" s="112"/>
-      <c r="DS3" s="112"/>
-      <c r="DT3" s="112"/>
-      <c r="DU3" s="112"/>
-      <c r="DV3" s="112"/>
-      <c r="DW3" s="112"/>
-      <c r="DX3" s="112"/>
-      <c r="DY3" s="112"/>
-      <c r="DZ3" s="112"/>
-      <c r="EA3" s="112"/>
-      <c r="EB3" s="112"/>
-      <c r="EC3" s="112"/>
-      <c r="ED3" s="112"/>
-      <c r="EE3" s="112"/>
-      <c r="EF3" s="112"/>
-      <c r="EG3" s="112"/>
-      <c r="EH3" s="112"/>
-      <c r="EI3" s="112"/>
-      <c r="EJ3" s="112"/>
-      <c r="EK3" s="112"/>
-      <c r="EL3" s="112"/>
-      <c r="EM3" s="112"/>
-      <c r="EN3" s="112"/>
-      <c r="EO3" s="112"/>
-      <c r="EP3" s="112"/>
-      <c r="EQ3" s="112"/>
-      <c r="ER3" s="112"/>
-      <c r="ES3" s="112"/>
-      <c r="ET3" s="112"/>
-      <c r="EU3" s="112"/>
-      <c r="EV3" s="112"/>
-      <c r="EW3" s="112"/>
-      <c r="EX3" s="112"/>
-      <c r="EY3" s="112"/>
-      <c r="EZ3" s="116"/>
-      <c r="FA3" s="111" t="s">
+      <c r="DR3" s="59"/>
+      <c r="DS3" s="59"/>
+      <c r="DT3" s="59"/>
+      <c r="DU3" s="59"/>
+      <c r="DV3" s="59"/>
+      <c r="DW3" s="59"/>
+      <c r="DX3" s="59"/>
+      <c r="DY3" s="59"/>
+      <c r="DZ3" s="59"/>
+      <c r="EA3" s="59"/>
+      <c r="EB3" s="59"/>
+      <c r="EC3" s="59"/>
+      <c r="ED3" s="59"/>
+      <c r="EE3" s="59"/>
+      <c r="EF3" s="59"/>
+      <c r="EG3" s="59"/>
+      <c r="EH3" s="59"/>
+      <c r="EI3" s="59"/>
+      <c r="EJ3" s="59"/>
+      <c r="EK3" s="59"/>
+      <c r="EL3" s="59"/>
+      <c r="EM3" s="59"/>
+      <c r="EN3" s="59"/>
+      <c r="EO3" s="59"/>
+      <c r="EP3" s="59"/>
+      <c r="EQ3" s="59"/>
+      <c r="ER3" s="59"/>
+      <c r="ES3" s="59"/>
+      <c r="ET3" s="59"/>
+      <c r="EU3" s="59"/>
+      <c r="EV3" s="59"/>
+      <c r="EW3" s="59"/>
+      <c r="EX3" s="59"/>
+      <c r="EY3" s="59"/>
+      <c r="EZ3" s="62"/>
+      <c r="FA3" s="61" t="s">
         <v>7</v>
       </c>
-      <c r="FB3" s="112"/>
-      <c r="FC3" s="112"/>
-      <c r="FD3" s="112"/>
-      <c r="FE3" s="112"/>
-      <c r="FF3" s="112"/>
-      <c r="FG3" s="112"/>
-      <c r="FH3" s="112"/>
-      <c r="FI3" s="112"/>
-      <c r="FJ3" s="112"/>
-      <c r="FK3" s="112"/>
-      <c r="FL3" s="112"/>
-      <c r="FM3" s="112"/>
-      <c r="FN3" s="112"/>
-      <c r="FO3" s="112"/>
-      <c r="FP3" s="112"/>
-      <c r="FQ3" s="112"/>
-      <c r="FR3" s="112"/>
-      <c r="FS3" s="112"/>
-      <c r="FT3" s="112"/>
-      <c r="FU3" s="112"/>
-      <c r="FV3" s="112"/>
-      <c r="FW3" s="112"/>
-      <c r="FX3" s="112"/>
-      <c r="FY3" s="112"/>
-      <c r="FZ3" s="112"/>
-      <c r="GA3" s="112"/>
-      <c r="GB3" s="112"/>
-      <c r="GC3" s="112"/>
-      <c r="GD3" s="112"/>
-      <c r="GE3" s="112"/>
-      <c r="GF3" s="112"/>
-      <c r="GG3" s="112"/>
-      <c r="GH3" s="112"/>
-      <c r="GI3" s="112"/>
-      <c r="GJ3" s="116"/>
-      <c r="GK3" s="111" t="s">
+      <c r="FB3" s="59"/>
+      <c r="FC3" s="59"/>
+      <c r="FD3" s="59"/>
+      <c r="FE3" s="59"/>
+      <c r="FF3" s="59"/>
+      <c r="FG3" s="59"/>
+      <c r="FH3" s="59"/>
+      <c r="FI3" s="59"/>
+      <c r="FJ3" s="59"/>
+      <c r="FK3" s="59"/>
+      <c r="FL3" s="59"/>
+      <c r="FM3" s="59"/>
+      <c r="FN3" s="59"/>
+      <c r="FO3" s="59"/>
+      <c r="FP3" s="59"/>
+      <c r="FQ3" s="59"/>
+      <c r="FR3" s="59"/>
+      <c r="FS3" s="59"/>
+      <c r="FT3" s="59"/>
+      <c r="FU3" s="59"/>
+      <c r="FV3" s="59"/>
+      <c r="FW3" s="59"/>
+      <c r="FX3" s="59"/>
+      <c r="FY3" s="59"/>
+      <c r="FZ3" s="59"/>
+      <c r="GA3" s="59"/>
+      <c r="GB3" s="59"/>
+      <c r="GC3" s="59"/>
+      <c r="GD3" s="59"/>
+      <c r="GE3" s="59"/>
+      <c r="GF3" s="59"/>
+      <c r="GG3" s="59"/>
+      <c r="GH3" s="59"/>
+      <c r="GI3" s="59"/>
+      <c r="GJ3" s="62"/>
+      <c r="GK3" s="61" t="s">
         <v>8</v>
       </c>
-      <c r="GL3" s="112"/>
-      <c r="GM3" s="112"/>
-      <c r="GN3" s="112"/>
-      <c r="GO3" s="112"/>
-      <c r="GP3" s="112"/>
-      <c r="GQ3" s="112"/>
-      <c r="GR3" s="112"/>
-      <c r="GS3" s="112"/>
-      <c r="GT3" s="112"/>
-      <c r="GU3" s="112"/>
-      <c r="GV3" s="112"/>
-      <c r="GW3" s="112"/>
-      <c r="GX3" s="112"/>
-      <c r="GY3" s="112"/>
-      <c r="GZ3" s="112"/>
-      <c r="HA3" s="112"/>
-      <c r="HB3" s="112"/>
-      <c r="HC3" s="112"/>
-      <c r="HD3" s="112"/>
-      <c r="HE3" s="112"/>
-      <c r="HF3" s="112"/>
-      <c r="HG3" s="112"/>
-      <c r="HH3" s="112"/>
-      <c r="HI3" s="112"/>
-      <c r="HJ3" s="112"/>
-      <c r="HK3" s="112"/>
-      <c r="HL3" s="112"/>
-      <c r="HM3" s="112"/>
-      <c r="HN3" s="112"/>
-      <c r="HO3" s="112"/>
-      <c r="HP3" s="112"/>
-      <c r="HQ3" s="112"/>
-      <c r="HR3" s="112"/>
-      <c r="HS3" s="112"/>
-      <c r="HT3" s="116"/>
-      <c r="HU3" s="111" t="s">
+      <c r="GL3" s="59"/>
+      <c r="GM3" s="59"/>
+      <c r="GN3" s="59"/>
+      <c r="GO3" s="59"/>
+      <c r="GP3" s="59"/>
+      <c r="GQ3" s="59"/>
+      <c r="GR3" s="59"/>
+      <c r="GS3" s="59"/>
+      <c r="GT3" s="59"/>
+      <c r="GU3" s="59"/>
+      <c r="GV3" s="59"/>
+      <c r="GW3" s="59"/>
+      <c r="GX3" s="59"/>
+      <c r="GY3" s="59"/>
+      <c r="GZ3" s="59"/>
+      <c r="HA3" s="59"/>
+      <c r="HB3" s="59"/>
+      <c r="HC3" s="59"/>
+      <c r="HD3" s="59"/>
+      <c r="HE3" s="59"/>
+      <c r="HF3" s="59"/>
+      <c r="HG3" s="59"/>
+      <c r="HH3" s="59"/>
+      <c r="HI3" s="59"/>
+      <c r="HJ3" s="59"/>
+      <c r="HK3" s="59"/>
+      <c r="HL3" s="59"/>
+      <c r="HM3" s="59"/>
+      <c r="HN3" s="59"/>
+      <c r="HO3" s="59"/>
+      <c r="HP3" s="59"/>
+      <c r="HQ3" s="59"/>
+      <c r="HR3" s="59"/>
+      <c r="HS3" s="59"/>
+      <c r="HT3" s="62"/>
+      <c r="HU3" s="61" t="s">
         <v>9</v>
       </c>
-      <c r="HV3" s="112"/>
-      <c r="HW3" s="112"/>
-      <c r="HX3" s="112"/>
-      <c r="HY3" s="112"/>
-      <c r="HZ3" s="112"/>
-      <c r="IA3" s="112"/>
-      <c r="IB3" s="112"/>
-      <c r="IC3" s="112"/>
-      <c r="ID3" s="112"/>
-      <c r="IE3" s="112"/>
-      <c r="IF3" s="112"/>
-      <c r="IG3" s="112"/>
-      <c r="IH3" s="112"/>
-      <c r="II3" s="112"/>
-      <c r="IJ3" s="112"/>
-      <c r="IK3" s="112"/>
-      <c r="IL3" s="112"/>
-      <c r="IM3" s="112"/>
-      <c r="IN3" s="112"/>
-      <c r="IO3" s="112"/>
-      <c r="IP3" s="112"/>
-      <c r="IQ3" s="112"/>
-      <c r="IR3" s="112"/>
-      <c r="IS3" s="112"/>
-      <c r="IT3" s="112"/>
-      <c r="IU3" s="112"/>
-      <c r="IV3" s="112"/>
-      <c r="IW3" s="112"/>
-      <c r="IX3" s="112"/>
-      <c r="IY3" s="112"/>
-      <c r="IZ3" s="112"/>
-      <c r="JA3" s="112"/>
-      <c r="JB3" s="112"/>
-      <c r="JC3" s="112"/>
-      <c r="JD3" s="116"/>
-      <c r="JE3" s="111" t="s">
+      <c r="HV3" s="59"/>
+      <c r="HW3" s="59"/>
+      <c r="HX3" s="59"/>
+      <c r="HY3" s="59"/>
+      <c r="HZ3" s="59"/>
+      <c r="IA3" s="59"/>
+      <c r="IB3" s="59"/>
+      <c r="IC3" s="59"/>
+      <c r="ID3" s="59"/>
+      <c r="IE3" s="59"/>
+      <c r="IF3" s="59"/>
+      <c r="IG3" s="59"/>
+      <c r="IH3" s="59"/>
+      <c r="II3" s="59"/>
+      <c r="IJ3" s="59"/>
+      <c r="IK3" s="59"/>
+      <c r="IL3" s="59"/>
+      <c r="IM3" s="59"/>
+      <c r="IN3" s="59"/>
+      <c r="IO3" s="59"/>
+      <c r="IP3" s="59"/>
+      <c r="IQ3" s="59"/>
+      <c r="IR3" s="59"/>
+      <c r="IS3" s="59"/>
+      <c r="IT3" s="59"/>
+      <c r="IU3" s="59"/>
+      <c r="IV3" s="59"/>
+      <c r="IW3" s="59"/>
+      <c r="IX3" s="59"/>
+      <c r="IY3" s="59"/>
+      <c r="IZ3" s="59"/>
+      <c r="JA3" s="59"/>
+      <c r="JB3" s="59"/>
+      <c r="JC3" s="59"/>
+      <c r="JD3" s="62"/>
+      <c r="JE3" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="JF3" s="112"/>
-      <c r="JG3" s="112"/>
-      <c r="JH3" s="112"/>
-      <c r="JI3" s="112"/>
-      <c r="JJ3" s="112"/>
-      <c r="JK3" s="112"/>
-      <c r="JL3" s="112"/>
-      <c r="JM3" s="112"/>
-      <c r="JN3" s="112"/>
-      <c r="JO3" s="112"/>
-      <c r="JP3" s="112"/>
-      <c r="JQ3" s="112"/>
-      <c r="JR3" s="112"/>
-      <c r="JS3" s="112"/>
-      <c r="JT3" s="112"/>
-      <c r="JU3" s="112"/>
-      <c r="JV3" s="112"/>
-      <c r="JW3" s="112"/>
-      <c r="JX3" s="112"/>
-      <c r="JY3" s="112"/>
-      <c r="JZ3" s="112"/>
-      <c r="KA3" s="112"/>
-      <c r="KB3" s="112"/>
-      <c r="KC3" s="112"/>
-      <c r="KD3" s="112"/>
-      <c r="KE3" s="112"/>
-      <c r="KF3" s="112"/>
-      <c r="KG3" s="112"/>
-      <c r="KH3" s="112"/>
-      <c r="KI3" s="112"/>
-      <c r="KJ3" s="112"/>
-      <c r="KK3" s="112"/>
-      <c r="KL3" s="112"/>
-      <c r="KM3" s="112"/>
-      <c r="KN3" s="116"/>
-      <c r="KO3" s="111" t="s">
+      <c r="JF3" s="59"/>
+      <c r="JG3" s="59"/>
+      <c r="JH3" s="59"/>
+      <c r="JI3" s="59"/>
+      <c r="JJ3" s="59"/>
+      <c r="JK3" s="59"/>
+      <c r="JL3" s="59"/>
+      <c r="JM3" s="59"/>
+      <c r="JN3" s="59"/>
+      <c r="JO3" s="59"/>
+      <c r="JP3" s="59"/>
+      <c r="JQ3" s="59"/>
+      <c r="JR3" s="59"/>
+      <c r="JS3" s="59"/>
+      <c r="JT3" s="59"/>
+      <c r="JU3" s="59"/>
+      <c r="JV3" s="59"/>
+      <c r="JW3" s="59"/>
+      <c r="JX3" s="59"/>
+      <c r="JY3" s="59"/>
+      <c r="JZ3" s="59"/>
+      <c r="KA3" s="59"/>
+      <c r="KB3" s="59"/>
+      <c r="KC3" s="59"/>
+      <c r="KD3" s="59"/>
+      <c r="KE3" s="59"/>
+      <c r="KF3" s="59"/>
+      <c r="KG3" s="59"/>
+      <c r="KH3" s="59"/>
+      <c r="KI3" s="59"/>
+      <c r="KJ3" s="59"/>
+      <c r="KK3" s="59"/>
+      <c r="KL3" s="59"/>
+      <c r="KM3" s="59"/>
+      <c r="KN3" s="62"/>
+      <c r="KO3" s="61" t="s">
         <v>11</v>
       </c>
-      <c r="KP3" s="112"/>
-      <c r="KQ3" s="112"/>
-      <c r="KR3" s="112"/>
-      <c r="KS3" s="112"/>
-      <c r="KT3" s="112"/>
-      <c r="KU3" s="112"/>
-      <c r="KV3" s="112"/>
-      <c r="KW3" s="112"/>
-      <c r="KX3" s="112"/>
-      <c r="KY3" s="112"/>
-      <c r="KZ3" s="112"/>
-      <c r="LA3" s="112"/>
-      <c r="LB3" s="112"/>
-      <c r="LC3" s="112"/>
-      <c r="LD3" s="112"/>
-      <c r="LE3" s="112"/>
-      <c r="LF3" s="112"/>
-      <c r="LG3" s="112"/>
-      <c r="LH3" s="112"/>
-      <c r="LI3" s="112"/>
-      <c r="LJ3" s="112"/>
-      <c r="LK3" s="112"/>
-      <c r="LL3" s="112"/>
-      <c r="LM3" s="112"/>
-      <c r="LN3" s="112"/>
-      <c r="LO3" s="112"/>
-      <c r="LP3" s="112"/>
-      <c r="LQ3" s="112"/>
-      <c r="LR3" s="112"/>
-      <c r="LS3" s="112"/>
-      <c r="LT3" s="112"/>
-      <c r="LU3" s="112"/>
-      <c r="LV3" s="112"/>
-      <c r="LW3" s="112"/>
-      <c r="LX3" s="112"/>
-      <c r="LY3" s="112"/>
-      <c r="LZ3" s="112"/>
-      <c r="MA3" s="112"/>
-      <c r="MB3" s="112"/>
-      <c r="MC3" s="112"/>
-      <c r="MD3" s="112"/>
-      <c r="ME3" s="112"/>
-      <c r="MF3" s="112"/>
-      <c r="MG3" s="112"/>
-      <c r="MH3" s="112"/>
-      <c r="MI3" s="112"/>
-      <c r="MJ3" s="113"/>
-      <c r="MK3" s="114" t="s">
+      <c r="KP3" s="59"/>
+      <c r="KQ3" s="59"/>
+      <c r="KR3" s="59"/>
+      <c r="KS3" s="59"/>
+      <c r="KT3" s="59"/>
+      <c r="KU3" s="59"/>
+      <c r="KV3" s="59"/>
+      <c r="KW3" s="59"/>
+      <c r="KX3" s="59"/>
+      <c r="KY3" s="59"/>
+      <c r="KZ3" s="59"/>
+      <c r="LA3" s="59"/>
+      <c r="LB3" s="59"/>
+      <c r="LC3" s="59"/>
+      <c r="LD3" s="59"/>
+      <c r="LE3" s="59"/>
+      <c r="LF3" s="59"/>
+      <c r="LG3" s="59"/>
+      <c r="LH3" s="59"/>
+      <c r="LI3" s="59"/>
+      <c r="LJ3" s="59"/>
+      <c r="LK3" s="59"/>
+      <c r="LL3" s="59"/>
+      <c r="LM3" s="59"/>
+      <c r="LN3" s="59"/>
+      <c r="LO3" s="59"/>
+      <c r="LP3" s="59"/>
+      <c r="LQ3" s="59"/>
+      <c r="LR3" s="59"/>
+      <c r="LS3" s="59"/>
+      <c r="LT3" s="59"/>
+      <c r="LU3" s="59"/>
+      <c r="LV3" s="59"/>
+      <c r="LW3" s="59"/>
+      <c r="LX3" s="59"/>
+      <c r="LY3" s="59"/>
+      <c r="LZ3" s="59"/>
+      <c r="MA3" s="59"/>
+      <c r="MB3" s="59"/>
+      <c r="MC3" s="59"/>
+      <c r="MD3" s="59"/>
+      <c r="ME3" s="59"/>
+      <c r="MF3" s="59"/>
+      <c r="MG3" s="59"/>
+      <c r="MH3" s="59"/>
+      <c r="MI3" s="59"/>
+      <c r="MJ3" s="74"/>
+      <c r="MK3" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="ML3" s="112"/>
-      <c r="MM3" s="112"/>
-      <c r="MN3" s="112"/>
-      <c r="MO3" s="112"/>
-      <c r="MP3" s="112"/>
-      <c r="MQ3" s="112"/>
-      <c r="MR3" s="112"/>
-      <c r="MS3" s="112"/>
-      <c r="MT3" s="112"/>
-      <c r="MU3" s="112"/>
-      <c r="MV3" s="112"/>
-      <c r="MW3" s="112"/>
-      <c r="MX3" s="112"/>
-      <c r="MY3" s="112"/>
-      <c r="MZ3" s="112"/>
-      <c r="NA3" s="112"/>
-      <c r="NB3" s="112"/>
-      <c r="NC3" s="112"/>
-      <c r="ND3" s="112"/>
-      <c r="NE3" s="112"/>
-      <c r="NF3" s="112"/>
-      <c r="NG3" s="112"/>
-      <c r="NH3" s="112"/>
-      <c r="NI3" s="115" t="s">
+      <c r="ML3" s="59"/>
+      <c r="MM3" s="59"/>
+      <c r="MN3" s="59"/>
+      <c r="MO3" s="59"/>
+      <c r="MP3" s="59"/>
+      <c r="MQ3" s="59"/>
+      <c r="MR3" s="59"/>
+      <c r="MS3" s="59"/>
+      <c r="MT3" s="59"/>
+      <c r="MU3" s="59"/>
+      <c r="MV3" s="59"/>
+      <c r="MW3" s="59"/>
+      <c r="MX3" s="59"/>
+      <c r="MY3" s="59"/>
+      <c r="MZ3" s="59"/>
+      <c r="NA3" s="59"/>
+      <c r="NB3" s="59"/>
+      <c r="NC3" s="59"/>
+      <c r="ND3" s="59"/>
+      <c r="NE3" s="59"/>
+      <c r="NF3" s="59"/>
+      <c r="NG3" s="59"/>
+      <c r="NH3" s="59"/>
+      <c r="NI3" s="76" t="s">
         <v>12</v>
       </c>
-      <c r="NJ3" s="112"/>
-      <c r="NK3" s="112"/>
-      <c r="NL3" s="112"/>
-      <c r="NM3" s="112"/>
-      <c r="NN3" s="112"/>
-      <c r="NO3" s="112"/>
-      <c r="NP3" s="112"/>
-      <c r="NQ3" s="112"/>
-      <c r="NR3" s="112"/>
-      <c r="NS3" s="112"/>
-      <c r="NT3" s="112"/>
-      <c r="NU3" s="112"/>
-      <c r="NV3" s="112"/>
-      <c r="NW3" s="112"/>
-      <c r="NX3" s="112"/>
-      <c r="NY3" s="112"/>
-      <c r="NZ3" s="116"/>
-      <c r="OA3" s="117" t="s">
+      <c r="NJ3" s="59"/>
+      <c r="NK3" s="59"/>
+      <c r="NL3" s="59"/>
+      <c r="NM3" s="59"/>
+      <c r="NN3" s="59"/>
+      <c r="NO3" s="59"/>
+      <c r="NP3" s="59"/>
+      <c r="NQ3" s="59"/>
+      <c r="NR3" s="59"/>
+      <c r="NS3" s="59"/>
+      <c r="NT3" s="59"/>
+      <c r="NU3" s="59"/>
+      <c r="NV3" s="59"/>
+      <c r="NW3" s="59"/>
+      <c r="NX3" s="59"/>
+      <c r="NY3" s="59"/>
+      <c r="NZ3" s="62"/>
+      <c r="OA3" s="77" t="s">
         <v>13</v>
       </c>
-      <c r="OB3" s="118"/>
-      <c r="OC3" s="118"/>
-      <c r="OD3" s="118"/>
-      <c r="OE3" s="118"/>
-      <c r="OF3" s="118"/>
+      <c r="OB3" s="78"/>
+      <c r="OC3" s="78"/>
+      <c r="OD3" s="78"/>
+      <c r="OE3" s="78"/>
+      <c r="OF3" s="78"/>
     </row>
     <row r="4" spans="1:396" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="51"/>
-      <c r="B4" s="51"/>
-      <c r="C4" s="51"/>
-      <c r="D4" s="51"/>
+      <c r="A4" s="49"/>
+      <c r="B4" s="49"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
       <c r="E4" s="7"/>
-      <c r="F4" s="51"/>
+      <c r="F4" s="49"/>
       <c r="G4" s="8"/>
-      <c r="H4" s="122"/>
-      <c r="I4" s="123"/>
-      <c r="J4" s="123"/>
-      <c r="K4" s="123"/>
-      <c r="L4" s="124"/>
-      <c r="M4" s="78" t="s">
+      <c r="H4" s="53"/>
+      <c r="I4" s="54"/>
+      <c r="J4" s="54"/>
+      <c r="K4" s="54"/>
+      <c r="L4" s="55"/>
+      <c r="M4" s="79" t="s">
         <v>14</v>
       </c>
-      <c r="N4" s="79"/>
-      <c r="O4" s="79"/>
-      <c r="P4" s="79"/>
-      <c r="Q4" s="79"/>
-      <c r="R4" s="80"/>
-      <c r="S4" s="84" t="s">
+      <c r="N4" s="80"/>
+      <c r="O4" s="80"/>
+      <c r="P4" s="80"/>
+      <c r="Q4" s="80"/>
+      <c r="R4" s="81"/>
+      <c r="S4" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="T4" s="84"/>
-      <c r="U4" s="84"/>
-      <c r="V4" s="84"/>
-      <c r="W4" s="84"/>
-      <c r="X4" s="84"/>
-      <c r="Y4" s="66" t="s">
+      <c r="T4" s="85"/>
+      <c r="U4" s="85"/>
+      <c r="V4" s="85"/>
+      <c r="W4" s="85"/>
+      <c r="X4" s="85"/>
+      <c r="Y4" s="86" t="s">
         <v>16</v>
       </c>
-      <c r="Z4" s="67"/>
-      <c r="AA4" s="68"/>
-      <c r="AB4" s="66" t="s">
+      <c r="Z4" s="87"/>
+      <c r="AA4" s="88"/>
+      <c r="AB4" s="86" t="s">
         <v>17</v>
       </c>
-      <c r="AC4" s="67"/>
-      <c r="AD4" s="68"/>
-      <c r="AE4" s="75" t="s">
+      <c r="AC4" s="87"/>
+      <c r="AD4" s="88"/>
+      <c r="AE4" s="95" t="s">
         <v>18</v>
       </c>
-      <c r="AF4" s="75"/>
-      <c r="AG4" s="75"/>
-      <c r="AH4" s="75"/>
-      <c r="AI4" s="75"/>
-      <c r="AJ4" s="75"/>
-      <c r="AK4" s="75"/>
-      <c r="AL4" s="75"/>
-      <c r="AM4" s="75"/>
-      <c r="AN4" s="75" t="s">
+      <c r="AF4" s="95"/>
+      <c r="AG4" s="95"/>
+      <c r="AH4" s="95"/>
+      <c r="AI4" s="95"/>
+      <c r="AJ4" s="95"/>
+      <c r="AK4" s="95"/>
+      <c r="AL4" s="95"/>
+      <c r="AM4" s="95"/>
+      <c r="AN4" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="AO4" s="75"/>
-      <c r="AP4" s="75"/>
-      <c r="AQ4" s="75"/>
-      <c r="AR4" s="75"/>
-      <c r="AS4" s="75"/>
-      <c r="AT4" s="66" t="s">
+      <c r="AO4" s="95"/>
+      <c r="AP4" s="95"/>
+      <c r="AQ4" s="95"/>
+      <c r="AR4" s="95"/>
+      <c r="AS4" s="95"/>
+      <c r="AT4" s="86" t="s">
         <v>20</v>
       </c>
-      <c r="AU4" s="67"/>
-      <c r="AV4" s="85"/>
-      <c r="AW4" s="78" t="s">
+      <c r="AU4" s="87"/>
+      <c r="AV4" s="96"/>
+      <c r="AW4" s="79" t="s">
         <v>14</v>
       </c>
-      <c r="AX4" s="79"/>
-      <c r="AY4" s="79"/>
-      <c r="AZ4" s="79"/>
-      <c r="BA4" s="79"/>
-      <c r="BB4" s="80"/>
-      <c r="BC4" s="84" t="s">
+      <c r="AX4" s="80"/>
+      <c r="AY4" s="80"/>
+      <c r="AZ4" s="80"/>
+      <c r="BA4" s="80"/>
+      <c r="BB4" s="81"/>
+      <c r="BC4" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="BD4" s="84"/>
-      <c r="BE4" s="84"/>
-      <c r="BF4" s="84"/>
-      <c r="BG4" s="84"/>
-      <c r="BH4" s="84"/>
-      <c r="BI4" s="66" t="s">
+      <c r="BD4" s="85"/>
+      <c r="BE4" s="85"/>
+      <c r="BF4" s="85"/>
+      <c r="BG4" s="85"/>
+      <c r="BH4" s="85"/>
+      <c r="BI4" s="86" t="s">
         <v>16</v>
       </c>
-      <c r="BJ4" s="67"/>
-      <c r="BK4" s="68"/>
-      <c r="BL4" s="66" t="s">
+      <c r="BJ4" s="87"/>
+      <c r="BK4" s="88"/>
+      <c r="BL4" s="86" t="s">
         <v>17</v>
       </c>
-      <c r="BM4" s="67"/>
-      <c r="BN4" s="68"/>
-      <c r="BO4" s="75" t="s">
+      <c r="BM4" s="87"/>
+      <c r="BN4" s="88"/>
+      <c r="BO4" s="95" t="s">
         <v>18</v>
       </c>
-      <c r="BP4" s="75"/>
-      <c r="BQ4" s="75"/>
-      <c r="BR4" s="75"/>
-      <c r="BS4" s="75"/>
-      <c r="BT4" s="75"/>
-      <c r="BU4" s="75"/>
-      <c r="BV4" s="75"/>
-      <c r="BW4" s="75"/>
-      <c r="BX4" s="75" t="s">
+      <c r="BP4" s="95"/>
+      <c r="BQ4" s="95"/>
+      <c r="BR4" s="95"/>
+      <c r="BS4" s="95"/>
+      <c r="BT4" s="95"/>
+      <c r="BU4" s="95"/>
+      <c r="BV4" s="95"/>
+      <c r="BW4" s="95"/>
+      <c r="BX4" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="BY4" s="75"/>
-      <c r="BZ4" s="75"/>
-      <c r="CA4" s="75"/>
-      <c r="CB4" s="75"/>
-      <c r="CC4" s="75"/>
-      <c r="CD4" s="66" t="s">
+      <c r="BY4" s="95"/>
+      <c r="BZ4" s="95"/>
+      <c r="CA4" s="95"/>
+      <c r="CB4" s="95"/>
+      <c r="CC4" s="95"/>
+      <c r="CD4" s="86" t="s">
         <v>64</v>
       </c>
-      <c r="CE4" s="67"/>
-      <c r="CF4" s="85"/>
-      <c r="CG4" s="78" t="s">
+      <c r="CE4" s="87"/>
+      <c r="CF4" s="96"/>
+      <c r="CG4" s="79" t="s">
         <v>14</v>
       </c>
-      <c r="CH4" s="79"/>
-      <c r="CI4" s="79"/>
-      <c r="CJ4" s="79"/>
-      <c r="CK4" s="79"/>
-      <c r="CL4" s="80"/>
-      <c r="CM4" s="84" t="s">
+      <c r="CH4" s="80"/>
+      <c r="CI4" s="80"/>
+      <c r="CJ4" s="80"/>
+      <c r="CK4" s="80"/>
+      <c r="CL4" s="81"/>
+      <c r="CM4" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="CN4" s="84"/>
-      <c r="CO4" s="84"/>
-      <c r="CP4" s="84"/>
-      <c r="CQ4" s="84"/>
-      <c r="CR4" s="84"/>
-      <c r="CS4" s="66" t="s">
+      <c r="CN4" s="85"/>
+      <c r="CO4" s="85"/>
+      <c r="CP4" s="85"/>
+      <c r="CQ4" s="85"/>
+      <c r="CR4" s="85"/>
+      <c r="CS4" s="86" t="s">
         <v>16</v>
       </c>
-      <c r="CT4" s="67"/>
-      <c r="CU4" s="68"/>
-      <c r="CV4" s="66" t="s">
+      <c r="CT4" s="87"/>
+      <c r="CU4" s="88"/>
+      <c r="CV4" s="86" t="s">
         <v>17</v>
       </c>
-      <c r="CW4" s="67"/>
-      <c r="CX4" s="68"/>
-      <c r="CY4" s="75" t="s">
+      <c r="CW4" s="87"/>
+      <c r="CX4" s="88"/>
+      <c r="CY4" s="95" t="s">
         <v>18</v>
       </c>
-      <c r="CZ4" s="75"/>
-      <c r="DA4" s="75"/>
-      <c r="DB4" s="75"/>
-      <c r="DC4" s="75"/>
-      <c r="DD4" s="75"/>
-      <c r="DE4" s="75"/>
-      <c r="DF4" s="75"/>
-      <c r="DG4" s="75"/>
-      <c r="DH4" s="75" t="s">
+      <c r="CZ4" s="95"/>
+      <c r="DA4" s="95"/>
+      <c r="DB4" s="95"/>
+      <c r="DC4" s="95"/>
+      <c r="DD4" s="95"/>
+      <c r="DE4" s="95"/>
+      <c r="DF4" s="95"/>
+      <c r="DG4" s="95"/>
+      <c r="DH4" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="DI4" s="75"/>
-      <c r="DJ4" s="75"/>
-      <c r="DK4" s="75"/>
-      <c r="DL4" s="75"/>
-      <c r="DM4" s="75"/>
-      <c r="DN4" s="66" t="s">
+      <c r="DI4" s="95"/>
+      <c r="DJ4" s="95"/>
+      <c r="DK4" s="95"/>
+      <c r="DL4" s="95"/>
+      <c r="DM4" s="95"/>
+      <c r="DN4" s="86" t="s">
         <v>65</v>
       </c>
-      <c r="DO4" s="67"/>
-      <c r="DP4" s="85"/>
-      <c r="DQ4" s="78" t="s">
+      <c r="DO4" s="87"/>
+      <c r="DP4" s="96"/>
+      <c r="DQ4" s="79" t="s">
         <v>14</v>
       </c>
-      <c r="DR4" s="79"/>
-      <c r="DS4" s="79"/>
-      <c r="DT4" s="79"/>
-      <c r="DU4" s="79"/>
-      <c r="DV4" s="80"/>
-      <c r="DW4" s="84" t="s">
+      <c r="DR4" s="80"/>
+      <c r="DS4" s="80"/>
+      <c r="DT4" s="80"/>
+      <c r="DU4" s="80"/>
+      <c r="DV4" s="81"/>
+      <c r="DW4" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="DX4" s="84"/>
-      <c r="DY4" s="84"/>
-      <c r="DZ4" s="84"/>
-      <c r="EA4" s="84"/>
-      <c r="EB4" s="84"/>
-      <c r="EC4" s="66" t="s">
+      <c r="DX4" s="85"/>
+      <c r="DY4" s="85"/>
+      <c r="DZ4" s="85"/>
+      <c r="EA4" s="85"/>
+      <c r="EB4" s="85"/>
+      <c r="EC4" s="86" t="s">
         <v>16</v>
       </c>
-      <c r="ED4" s="67"/>
-      <c r="EE4" s="68"/>
-      <c r="EF4" s="66" t="s">
+      <c r="ED4" s="87"/>
+      <c r="EE4" s="88"/>
+      <c r="EF4" s="86" t="s">
         <v>17</v>
       </c>
-      <c r="EG4" s="67"/>
-      <c r="EH4" s="68"/>
-      <c r="EI4" s="75" t="s">
+      <c r="EG4" s="87"/>
+      <c r="EH4" s="88"/>
+      <c r="EI4" s="95" t="s">
         <v>18</v>
       </c>
-      <c r="EJ4" s="75"/>
-      <c r="EK4" s="75"/>
-      <c r="EL4" s="75"/>
-      <c r="EM4" s="75"/>
-      <c r="EN4" s="75"/>
-      <c r="EO4" s="75"/>
-      <c r="EP4" s="75"/>
-      <c r="EQ4" s="75"/>
-      <c r="ER4" s="75" t="s">
+      <c r="EJ4" s="95"/>
+      <c r="EK4" s="95"/>
+      <c r="EL4" s="95"/>
+      <c r="EM4" s="95"/>
+      <c r="EN4" s="95"/>
+      <c r="EO4" s="95"/>
+      <c r="EP4" s="95"/>
+      <c r="EQ4" s="95"/>
+      <c r="ER4" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="ES4" s="75"/>
-      <c r="ET4" s="75"/>
-      <c r="EU4" s="75"/>
-      <c r="EV4" s="75"/>
-      <c r="EW4" s="75"/>
-      <c r="EX4" s="66" t="s">
+      <c r="ES4" s="95"/>
+      <c r="ET4" s="95"/>
+      <c r="EU4" s="95"/>
+      <c r="EV4" s="95"/>
+      <c r="EW4" s="95"/>
+      <c r="EX4" s="86" t="s">
         <v>66</v>
       </c>
-      <c r="EY4" s="67"/>
-      <c r="EZ4" s="85"/>
-      <c r="FA4" s="78" t="s">
+      <c r="EY4" s="87"/>
+      <c r="EZ4" s="96"/>
+      <c r="FA4" s="79" t="s">
         <v>14</v>
       </c>
-      <c r="FB4" s="79"/>
-      <c r="FC4" s="79"/>
-      <c r="FD4" s="79"/>
-      <c r="FE4" s="79"/>
-      <c r="FF4" s="80"/>
-      <c r="FG4" s="84" t="s">
+      <c r="FB4" s="80"/>
+      <c r="FC4" s="80"/>
+      <c r="FD4" s="80"/>
+      <c r="FE4" s="80"/>
+      <c r="FF4" s="81"/>
+      <c r="FG4" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="FH4" s="84"/>
-      <c r="FI4" s="84"/>
-      <c r="FJ4" s="84"/>
-      <c r="FK4" s="84"/>
-      <c r="FL4" s="84"/>
-      <c r="FM4" s="66" t="s">
+      <c r="FH4" s="85"/>
+      <c r="FI4" s="85"/>
+      <c r="FJ4" s="85"/>
+      <c r="FK4" s="85"/>
+      <c r="FL4" s="85"/>
+      <c r="FM4" s="86" t="s">
         <v>16</v>
       </c>
-      <c r="FN4" s="67"/>
-      <c r="FO4" s="68"/>
-      <c r="FP4" s="66" t="s">
+      <c r="FN4" s="87"/>
+      <c r="FO4" s="88"/>
+      <c r="FP4" s="86" t="s">
         <v>17</v>
       </c>
-      <c r="FQ4" s="67"/>
-      <c r="FR4" s="68"/>
-      <c r="FS4" s="75" t="s">
+      <c r="FQ4" s="87"/>
+      <c r="FR4" s="88"/>
+      <c r="FS4" s="95" t="s">
         <v>18</v>
       </c>
-      <c r="FT4" s="75"/>
-      <c r="FU4" s="75"/>
-      <c r="FV4" s="75"/>
-      <c r="FW4" s="75"/>
-      <c r="FX4" s="75"/>
-      <c r="FY4" s="75"/>
-      <c r="FZ4" s="75"/>
-      <c r="GA4" s="75"/>
-      <c r="GB4" s="75" t="s">
+      <c r="FT4" s="95"/>
+      <c r="FU4" s="95"/>
+      <c r="FV4" s="95"/>
+      <c r="FW4" s="95"/>
+      <c r="FX4" s="95"/>
+      <c r="FY4" s="95"/>
+      <c r="FZ4" s="95"/>
+      <c r="GA4" s="95"/>
+      <c r="GB4" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="GC4" s="75"/>
-      <c r="GD4" s="75"/>
-      <c r="GE4" s="75"/>
-      <c r="GF4" s="75"/>
-      <c r="GG4" s="75"/>
-      <c r="GH4" s="66" t="s">
+      <c r="GC4" s="95"/>
+      <c r="GD4" s="95"/>
+      <c r="GE4" s="95"/>
+      <c r="GF4" s="95"/>
+      <c r="GG4" s="95"/>
+      <c r="GH4" s="86" t="s">
         <v>67</v>
       </c>
-      <c r="GI4" s="67"/>
-      <c r="GJ4" s="85"/>
-      <c r="GK4" s="78" t="s">
+      <c r="GI4" s="87"/>
+      <c r="GJ4" s="96"/>
+      <c r="GK4" s="79" t="s">
         <v>14</v>
       </c>
-      <c r="GL4" s="79"/>
-      <c r="GM4" s="79"/>
-      <c r="GN4" s="79"/>
-      <c r="GO4" s="79"/>
-      <c r="GP4" s="80"/>
-      <c r="GQ4" s="84" t="s">
+      <c r="GL4" s="80"/>
+      <c r="GM4" s="80"/>
+      <c r="GN4" s="80"/>
+      <c r="GO4" s="80"/>
+      <c r="GP4" s="81"/>
+      <c r="GQ4" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="GR4" s="84"/>
-      <c r="GS4" s="84"/>
-      <c r="GT4" s="84"/>
-      <c r="GU4" s="84"/>
-      <c r="GV4" s="84"/>
-      <c r="GW4" s="66" t="s">
+      <c r="GR4" s="85"/>
+      <c r="GS4" s="85"/>
+      <c r="GT4" s="85"/>
+      <c r="GU4" s="85"/>
+      <c r="GV4" s="85"/>
+      <c r="GW4" s="86" t="s">
         <v>16</v>
       </c>
-      <c r="GX4" s="67"/>
-      <c r="GY4" s="68"/>
-      <c r="GZ4" s="66" t="s">
+      <c r="GX4" s="87"/>
+      <c r="GY4" s="88"/>
+      <c r="GZ4" s="86" t="s">
         <v>17</v>
       </c>
-      <c r="HA4" s="67"/>
-      <c r="HB4" s="68"/>
-      <c r="HC4" s="75" t="s">
+      <c r="HA4" s="87"/>
+      <c r="HB4" s="88"/>
+      <c r="HC4" s="95" t="s">
         <v>18</v>
       </c>
-      <c r="HD4" s="75"/>
-      <c r="HE4" s="75"/>
-      <c r="HF4" s="75"/>
-      <c r="HG4" s="75"/>
-      <c r="HH4" s="75"/>
-      <c r="HI4" s="75"/>
-      <c r="HJ4" s="75"/>
-      <c r="HK4" s="75"/>
-      <c r="HL4" s="75" t="s">
+      <c r="HD4" s="95"/>
+      <c r="HE4" s="95"/>
+      <c r="HF4" s="95"/>
+      <c r="HG4" s="95"/>
+      <c r="HH4" s="95"/>
+      <c r="HI4" s="95"/>
+      <c r="HJ4" s="95"/>
+      <c r="HK4" s="95"/>
+      <c r="HL4" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="HM4" s="75"/>
-      <c r="HN4" s="75"/>
-      <c r="HO4" s="75"/>
-      <c r="HP4" s="75"/>
-      <c r="HQ4" s="75"/>
-      <c r="HR4" s="66" t="s">
+      <c r="HM4" s="95"/>
+      <c r="HN4" s="95"/>
+      <c r="HO4" s="95"/>
+      <c r="HP4" s="95"/>
+      <c r="HQ4" s="95"/>
+      <c r="HR4" s="86" t="s">
         <v>68</v>
       </c>
-      <c r="HS4" s="67"/>
-      <c r="HT4" s="85"/>
-      <c r="HU4" s="78" t="s">
+      <c r="HS4" s="87"/>
+      <c r="HT4" s="96"/>
+      <c r="HU4" s="79" t="s">
         <v>14</v>
       </c>
-      <c r="HV4" s="79"/>
-      <c r="HW4" s="79"/>
-      <c r="HX4" s="79"/>
-      <c r="HY4" s="79"/>
-      <c r="HZ4" s="80"/>
-      <c r="IA4" s="84" t="s">
+      <c r="HV4" s="80"/>
+      <c r="HW4" s="80"/>
+      <c r="HX4" s="80"/>
+      <c r="HY4" s="80"/>
+      <c r="HZ4" s="81"/>
+      <c r="IA4" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="IB4" s="84"/>
-      <c r="IC4" s="84"/>
-      <c r="ID4" s="84"/>
-      <c r="IE4" s="84"/>
-      <c r="IF4" s="84"/>
-      <c r="IG4" s="66" t="s">
+      <c r="IB4" s="85"/>
+      <c r="IC4" s="85"/>
+      <c r="ID4" s="85"/>
+      <c r="IE4" s="85"/>
+      <c r="IF4" s="85"/>
+      <c r="IG4" s="86" t="s">
         <v>16</v>
       </c>
-      <c r="IH4" s="67"/>
-      <c r="II4" s="68"/>
-      <c r="IJ4" s="66" t="s">
+      <c r="IH4" s="87"/>
+      <c r="II4" s="88"/>
+      <c r="IJ4" s="86" t="s">
         <v>17</v>
       </c>
-      <c r="IK4" s="67"/>
-      <c r="IL4" s="68"/>
-      <c r="IM4" s="75" t="s">
+      <c r="IK4" s="87"/>
+      <c r="IL4" s="88"/>
+      <c r="IM4" s="95" t="s">
         <v>18</v>
       </c>
-      <c r="IN4" s="75"/>
-      <c r="IO4" s="75"/>
-      <c r="IP4" s="75"/>
-      <c r="IQ4" s="75"/>
-      <c r="IR4" s="75"/>
-      <c r="IS4" s="75"/>
-      <c r="IT4" s="75"/>
-      <c r="IU4" s="75"/>
-      <c r="IV4" s="75" t="s">
+      <c r="IN4" s="95"/>
+      <c r="IO4" s="95"/>
+      <c r="IP4" s="95"/>
+      <c r="IQ4" s="95"/>
+      <c r="IR4" s="95"/>
+      <c r="IS4" s="95"/>
+      <c r="IT4" s="95"/>
+      <c r="IU4" s="95"/>
+      <c r="IV4" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="IW4" s="75"/>
-      <c r="IX4" s="75"/>
-      <c r="IY4" s="75"/>
-      <c r="IZ4" s="75"/>
-      <c r="JA4" s="75"/>
-      <c r="JB4" s="66" t="s">
+      <c r="IW4" s="95"/>
+      <c r="IX4" s="95"/>
+      <c r="IY4" s="95"/>
+      <c r="IZ4" s="95"/>
+      <c r="JA4" s="95"/>
+      <c r="JB4" s="86" t="s">
         <v>69</v>
       </c>
-      <c r="JC4" s="67"/>
-      <c r="JD4" s="85"/>
-      <c r="JE4" s="78" t="s">
+      <c r="JC4" s="87"/>
+      <c r="JD4" s="96"/>
+      <c r="JE4" s="79" t="s">
         <v>14</v>
       </c>
-      <c r="JF4" s="79"/>
-      <c r="JG4" s="79"/>
-      <c r="JH4" s="79"/>
-      <c r="JI4" s="79"/>
-      <c r="JJ4" s="80"/>
-      <c r="JK4" s="84" t="s">
+      <c r="JF4" s="80"/>
+      <c r="JG4" s="80"/>
+      <c r="JH4" s="80"/>
+      <c r="JI4" s="80"/>
+      <c r="JJ4" s="81"/>
+      <c r="JK4" s="85" t="s">
         <v>15</v>
       </c>
-      <c r="JL4" s="84"/>
-      <c r="JM4" s="84"/>
-      <c r="JN4" s="84"/>
-      <c r="JO4" s="84"/>
-      <c r="JP4" s="84"/>
-      <c r="JQ4" s="66" t="s">
+      <c r="JL4" s="85"/>
+      <c r="JM4" s="85"/>
+      <c r="JN4" s="85"/>
+      <c r="JO4" s="85"/>
+      <c r="JP4" s="85"/>
+      <c r="JQ4" s="86" t="s">
         <v>16</v>
       </c>
-      <c r="JR4" s="67"/>
-      <c r="JS4" s="68"/>
-      <c r="JT4" s="66" t="s">
+      <c r="JR4" s="87"/>
+      <c r="JS4" s="88"/>
+      <c r="JT4" s="86" t="s">
         <v>17</v>
       </c>
-      <c r="JU4" s="67"/>
-      <c r="JV4" s="68"/>
-      <c r="JW4" s="75" t="s">
+      <c r="JU4" s="87"/>
+      <c r="JV4" s="88"/>
+      <c r="JW4" s="95" t="s">
         <v>18</v>
       </c>
-      <c r="JX4" s="75"/>
-      <c r="JY4" s="75"/>
-      <c r="JZ4" s="75"/>
-      <c r="KA4" s="75"/>
-      <c r="KB4" s="75"/>
-      <c r="KC4" s="75"/>
-      <c r="KD4" s="75"/>
-      <c r="KE4" s="75"/>
-      <c r="KF4" s="75" t="s">
+      <c r="JX4" s="95"/>
+      <c r="JY4" s="95"/>
+      <c r="JZ4" s="95"/>
+      <c r="KA4" s="95"/>
+      <c r="KB4" s="95"/>
+      <c r="KC4" s="95"/>
+      <c r="KD4" s="95"/>
+      <c r="KE4" s="95"/>
+      <c r="KF4" s="95" t="s">
         <v>19</v>
       </c>
-      <c r="KG4" s="75"/>
-      <c r="KH4" s="75"/>
-      <c r="KI4" s="75"/>
-      <c r="KJ4" s="75"/>
-      <c r="KK4" s="75"/>
-      <c r="KL4" s="66" t="s">
+      <c r="KG4" s="95"/>
+      <c r="KH4" s="95"/>
+      <c r="KI4" s="95"/>
+      <c r="KJ4" s="95"/>
+      <c r="KK4" s="95"/>
+      <c r="KL4" s="86" t="s">
         <v>70</v>
       </c>
-      <c r="KM4" s="67"/>
-      <c r="KN4" s="85"/>
-      <c r="KO4" s="97" t="s">
+      <c r="KM4" s="87"/>
+      <c r="KN4" s="96"/>
+      <c r="KO4" s="104" t="s">
         <v>21</v>
       </c>
-      <c r="KP4" s="98"/>
-      <c r="KQ4" s="98"/>
-      <c r="KR4" s="98"/>
-      <c r="KS4" s="98"/>
-      <c r="KT4" s="98"/>
-      <c r="KU4" s="98"/>
-      <c r="KV4" s="98"/>
-      <c r="KW4" s="98"/>
-      <c r="KX4" s="98"/>
-      <c r="KY4" s="98"/>
-      <c r="KZ4" s="98"/>
-      <c r="LA4" s="98"/>
-      <c r="LB4" s="98"/>
-      <c r="LC4" s="98"/>
-      <c r="LD4" s="98"/>
-      <c r="LE4" s="98"/>
-      <c r="LF4" s="99"/>
-      <c r="LG4" s="100" t="s">
+      <c r="KP4" s="105"/>
+      <c r="KQ4" s="105"/>
+      <c r="KR4" s="105"/>
+      <c r="KS4" s="105"/>
+      <c r="KT4" s="105"/>
+      <c r="KU4" s="105"/>
+      <c r="KV4" s="105"/>
+      <c r="KW4" s="105"/>
+      <c r="KX4" s="105"/>
+      <c r="KY4" s="105"/>
+      <c r="KZ4" s="105"/>
+      <c r="LA4" s="105"/>
+      <c r="LB4" s="105"/>
+      <c r="LC4" s="105"/>
+      <c r="LD4" s="105"/>
+      <c r="LE4" s="105"/>
+      <c r="LF4" s="106"/>
+      <c r="LG4" s="107" t="s">
         <v>15</v>
       </c>
-      <c r="LH4" s="101"/>
-      <c r="LI4" s="101"/>
-      <c r="LJ4" s="101"/>
-      <c r="LK4" s="101"/>
-      <c r="LL4" s="101"/>
-      <c r="LM4" s="101"/>
-      <c r="LN4" s="101"/>
-      <c r="LO4" s="101"/>
-      <c r="LP4" s="101"/>
-      <c r="LQ4" s="101"/>
-      <c r="LR4" s="101"/>
-      <c r="LS4" s="101"/>
-      <c r="LT4" s="101"/>
-      <c r="LU4" s="101"/>
-      <c r="LV4" s="101"/>
-      <c r="LW4" s="101"/>
-      <c r="LX4" s="102"/>
-      <c r="LY4" s="100" t="s">
+      <c r="LH4" s="108"/>
+      <c r="LI4" s="108"/>
+      <c r="LJ4" s="108"/>
+      <c r="LK4" s="108"/>
+      <c r="LL4" s="108"/>
+      <c r="LM4" s="108"/>
+      <c r="LN4" s="108"/>
+      <c r="LO4" s="108"/>
+      <c r="LP4" s="108"/>
+      <c r="LQ4" s="108"/>
+      <c r="LR4" s="108"/>
+      <c r="LS4" s="108"/>
+      <c r="LT4" s="108"/>
+      <c r="LU4" s="108"/>
+      <c r="LV4" s="108"/>
+      <c r="LW4" s="108"/>
+      <c r="LX4" s="109"/>
+      <c r="LY4" s="107" t="s">
         <v>16</v>
       </c>
-      <c r="LZ4" s="101"/>
-      <c r="MA4" s="101"/>
-      <c r="MB4" s="101"/>
-      <c r="MC4" s="101"/>
-      <c r="MD4" s="102"/>
-      <c r="ME4" s="100" t="s">
+      <c r="LZ4" s="108"/>
+      <c r="MA4" s="108"/>
+      <c r="MB4" s="108"/>
+      <c r="MC4" s="108"/>
+      <c r="MD4" s="109"/>
+      <c r="ME4" s="107" t="s">
         <v>17</v>
       </c>
-      <c r="MF4" s="101"/>
-      <c r="MG4" s="101"/>
-      <c r="MH4" s="101"/>
-      <c r="MI4" s="101"/>
-      <c r="MJ4" s="102"/>
-      <c r="MK4" s="91" t="s">
+      <c r="MF4" s="108"/>
+      <c r="MG4" s="108"/>
+      <c r="MH4" s="108"/>
+      <c r="MI4" s="108"/>
+      <c r="MJ4" s="109"/>
+      <c r="MK4" s="100" t="s">
         <v>18</v>
       </c>
-      <c r="ML4" s="92"/>
-      <c r="MM4" s="92"/>
-      <c r="MN4" s="92"/>
-      <c r="MO4" s="92"/>
-      <c r="MP4" s="92"/>
-      <c r="MQ4" s="92"/>
-      <c r="MR4" s="92"/>
-      <c r="MS4" s="92"/>
-      <c r="MT4" s="92"/>
-      <c r="MU4" s="92"/>
-      <c r="MV4" s="92"/>
-      <c r="MW4" s="92"/>
-      <c r="MX4" s="92"/>
-      <c r="MY4" s="92"/>
-      <c r="MZ4" s="92"/>
-      <c r="NA4" s="92"/>
-      <c r="NB4" s="92"/>
-      <c r="NC4" s="92"/>
-      <c r="ND4" s="92"/>
-      <c r="NE4" s="92"/>
-      <c r="NF4" s="92"/>
-      <c r="NG4" s="92"/>
-      <c r="NH4" s="92"/>
-      <c r="NI4" s="93" t="s">
+      <c r="ML4" s="101"/>
+      <c r="MM4" s="101"/>
+      <c r="MN4" s="101"/>
+      <c r="MO4" s="101"/>
+      <c r="MP4" s="101"/>
+      <c r="MQ4" s="101"/>
+      <c r="MR4" s="101"/>
+      <c r="MS4" s="101"/>
+      <c r="MT4" s="101"/>
+      <c r="MU4" s="101"/>
+      <c r="MV4" s="101"/>
+      <c r="MW4" s="101"/>
+      <c r="MX4" s="101"/>
+      <c r="MY4" s="101"/>
+      <c r="MZ4" s="101"/>
+      <c r="NA4" s="101"/>
+      <c r="NB4" s="101"/>
+      <c r="NC4" s="101"/>
+      <c r="ND4" s="101"/>
+      <c r="NE4" s="101"/>
+      <c r="NF4" s="101"/>
+      <c r="NG4" s="101"/>
+      <c r="NH4" s="101"/>
+      <c r="NI4" s="102" t="s">
         <v>22</v>
       </c>
-      <c r="NJ4" s="58" t="s">
+      <c r="NJ4" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="NK4" s="43" t="s">
+      <c r="NK4" s="39" t="s">
         <v>24</v>
       </c>
-      <c r="NL4" s="43"/>
-      <c r="NM4" s="43"/>
-      <c r="NN4" s="43"/>
-      <c r="NO4" s="43" t="s">
+      <c r="NL4" s="39"/>
+      <c r="NM4" s="39"/>
+      <c r="NN4" s="39"/>
+      <c r="NO4" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="NP4" s="43"/>
-      <c r="NQ4" s="43"/>
-      <c r="NR4" s="43"/>
-      <c r="NS4" s="43"/>
-      <c r="NT4" s="43"/>
-      <c r="NU4" s="44" t="s">
+      <c r="NP4" s="39"/>
+      <c r="NQ4" s="39"/>
+      <c r="NR4" s="39"/>
+      <c r="NS4" s="39"/>
+      <c r="NT4" s="39"/>
+      <c r="NU4" s="65" t="s">
         <v>26</v>
       </c>
-      <c r="NV4" s="44"/>
-      <c r="NW4" s="44"/>
-      <c r="NX4" s="44"/>
-      <c r="NY4" s="44"/>
-      <c r="NZ4" s="45"/>
-      <c r="OA4" s="117"/>
-      <c r="OB4" s="118"/>
-      <c r="OC4" s="118"/>
-      <c r="OD4" s="118"/>
-      <c r="OE4" s="118"/>
-      <c r="OF4" s="118"/>
+      <c r="NV4" s="65"/>
+      <c r="NW4" s="65"/>
+      <c r="NX4" s="65"/>
+      <c r="NY4" s="65"/>
+      <c r="NZ4" s="131"/>
+      <c r="OA4" s="77"/>
+      <c r="OB4" s="78"/>
+      <c r="OC4" s="78"/>
+      <c r="OD4" s="78"/>
+      <c r="OE4" s="78"/>
+      <c r="OF4" s="78"/>
     </row>
     <row r="5" spans="1:396" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="51"/>
-      <c r="B5" s="51"/>
-      <c r="C5" s="51"/>
-      <c r="D5" s="51"/>
+      <c r="A5" s="49"/>
+      <c r="B5" s="49"/>
+      <c r="C5" s="49"/>
+      <c r="D5" s="49"/>
       <c r="E5" s="7"/>
-      <c r="F5" s="51"/>
+      <c r="F5" s="49"/>
       <c r="G5" s="8"/>
-      <c r="H5" s="125"/>
-      <c r="I5" s="126"/>
-      <c r="J5" s="126"/>
-      <c r="K5" s="126"/>
-      <c r="L5" s="127"/>
-      <c r="M5" s="81"/>
-      <c r="N5" s="82"/>
-      <c r="O5" s="82"/>
-      <c r="P5" s="82"/>
-      <c r="Q5" s="82"/>
-      <c r="R5" s="83"/>
-      <c r="S5" s="84"/>
-      <c r="T5" s="84"/>
-      <c r="U5" s="84"/>
-      <c r="V5" s="84"/>
-      <c r="W5" s="84"/>
-      <c r="X5" s="84"/>
-      <c r="Y5" s="69"/>
-      <c r="Z5" s="70"/>
-      <c r="AA5" s="71"/>
-      <c r="AB5" s="69"/>
-      <c r="AC5" s="70"/>
-      <c r="AD5" s="71"/>
-      <c r="AE5" s="43" t="s">
+      <c r="H5" s="56"/>
+      <c r="I5" s="57"/>
+      <c r="J5" s="57"/>
+      <c r="K5" s="57"/>
+      <c r="L5" s="58"/>
+      <c r="M5" s="82"/>
+      <c r="N5" s="83"/>
+      <c r="O5" s="83"/>
+      <c r="P5" s="83"/>
+      <c r="Q5" s="83"/>
+      <c r="R5" s="84"/>
+      <c r="S5" s="85"/>
+      <c r="T5" s="85"/>
+      <c r="U5" s="85"/>
+      <c r="V5" s="85"/>
+      <c r="W5" s="85"/>
+      <c r="X5" s="85"/>
+      <c r="Y5" s="89"/>
+      <c r="Z5" s="90"/>
+      <c r="AA5" s="91"/>
+      <c r="AB5" s="89"/>
+      <c r="AC5" s="90"/>
+      <c r="AD5" s="91"/>
+      <c r="AE5" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="AF5" s="43"/>
-      <c r="AG5" s="43"/>
-      <c r="AH5" s="43"/>
-      <c r="AI5" s="43"/>
-      <c r="AJ5" s="43"/>
-      <c r="AK5" s="43"/>
-      <c r="AL5" s="43"/>
-      <c r="AM5" s="43"/>
-      <c r="AN5" s="75"/>
-      <c r="AO5" s="75"/>
-      <c r="AP5" s="75"/>
-      <c r="AQ5" s="75"/>
-      <c r="AR5" s="75"/>
-      <c r="AS5" s="75"/>
-      <c r="AT5" s="69"/>
-      <c r="AU5" s="70"/>
-      <c r="AV5" s="86"/>
-      <c r="AW5" s="81"/>
-      <c r="AX5" s="82"/>
-      <c r="AY5" s="82"/>
-      <c r="AZ5" s="82"/>
-      <c r="BA5" s="82"/>
-      <c r="BB5" s="83"/>
-      <c r="BC5" s="84"/>
-      <c r="BD5" s="84"/>
-      <c r="BE5" s="84"/>
-      <c r="BF5" s="84"/>
-      <c r="BG5" s="84"/>
-      <c r="BH5" s="84"/>
-      <c r="BI5" s="69"/>
-      <c r="BJ5" s="70"/>
-      <c r="BK5" s="71"/>
-      <c r="BL5" s="69"/>
-      <c r="BM5" s="70"/>
-      <c r="BN5" s="71"/>
-      <c r="BO5" s="43" t="s">
+      <c r="AF5" s="39"/>
+      <c r="AG5" s="39"/>
+      <c r="AH5" s="39"/>
+      <c r="AI5" s="39"/>
+      <c r="AJ5" s="39"/>
+      <c r="AK5" s="39"/>
+      <c r="AL5" s="39"/>
+      <c r="AM5" s="39"/>
+      <c r="AN5" s="95"/>
+      <c r="AO5" s="95"/>
+      <c r="AP5" s="95"/>
+      <c r="AQ5" s="95"/>
+      <c r="AR5" s="95"/>
+      <c r="AS5" s="95"/>
+      <c r="AT5" s="89"/>
+      <c r="AU5" s="90"/>
+      <c r="AV5" s="97"/>
+      <c r="AW5" s="82"/>
+      <c r="AX5" s="83"/>
+      <c r="AY5" s="83"/>
+      <c r="AZ5" s="83"/>
+      <c r="BA5" s="83"/>
+      <c r="BB5" s="84"/>
+      <c r="BC5" s="85"/>
+      <c r="BD5" s="85"/>
+      <c r="BE5" s="85"/>
+      <c r="BF5" s="85"/>
+      <c r="BG5" s="85"/>
+      <c r="BH5" s="85"/>
+      <c r="BI5" s="89"/>
+      <c r="BJ5" s="90"/>
+      <c r="BK5" s="91"/>
+      <c r="BL5" s="89"/>
+      <c r="BM5" s="90"/>
+      <c r="BN5" s="91"/>
+      <c r="BO5" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="BP5" s="43"/>
-      <c r="BQ5" s="43"/>
-      <c r="BR5" s="43"/>
-      <c r="BS5" s="43"/>
-      <c r="BT5" s="43"/>
-      <c r="BU5" s="43"/>
-      <c r="BV5" s="43"/>
-      <c r="BW5" s="43"/>
-      <c r="BX5" s="75"/>
-      <c r="BY5" s="75"/>
-      <c r="BZ5" s="75"/>
-      <c r="CA5" s="75"/>
-      <c r="CB5" s="75"/>
-      <c r="CC5" s="75"/>
-      <c r="CD5" s="69"/>
-      <c r="CE5" s="70"/>
-      <c r="CF5" s="86"/>
-      <c r="CG5" s="81"/>
-      <c r="CH5" s="82"/>
-      <c r="CI5" s="82"/>
-      <c r="CJ5" s="82"/>
-      <c r="CK5" s="82"/>
-      <c r="CL5" s="83"/>
-      <c r="CM5" s="84"/>
-      <c r="CN5" s="84"/>
-      <c r="CO5" s="84"/>
-      <c r="CP5" s="84"/>
-      <c r="CQ5" s="84"/>
-      <c r="CR5" s="84"/>
-      <c r="CS5" s="69"/>
-      <c r="CT5" s="70"/>
-      <c r="CU5" s="71"/>
-      <c r="CV5" s="69"/>
-      <c r="CW5" s="70"/>
-      <c r="CX5" s="71"/>
-      <c r="CY5" s="43" t="s">
+      <c r="BP5" s="39"/>
+      <c r="BQ5" s="39"/>
+      <c r="BR5" s="39"/>
+      <c r="BS5" s="39"/>
+      <c r="BT5" s="39"/>
+      <c r="BU5" s="39"/>
+      <c r="BV5" s="39"/>
+      <c r="BW5" s="39"/>
+      <c r="BX5" s="95"/>
+      <c r="BY5" s="95"/>
+      <c r="BZ5" s="95"/>
+      <c r="CA5" s="95"/>
+      <c r="CB5" s="95"/>
+      <c r="CC5" s="95"/>
+      <c r="CD5" s="89"/>
+      <c r="CE5" s="90"/>
+      <c r="CF5" s="97"/>
+      <c r="CG5" s="82"/>
+      <c r="CH5" s="83"/>
+      <c r="CI5" s="83"/>
+      <c r="CJ5" s="83"/>
+      <c r="CK5" s="83"/>
+      <c r="CL5" s="84"/>
+      <c r="CM5" s="85"/>
+      <c r="CN5" s="85"/>
+      <c r="CO5" s="85"/>
+      <c r="CP5" s="85"/>
+      <c r="CQ5" s="85"/>
+      <c r="CR5" s="85"/>
+      <c r="CS5" s="89"/>
+      <c r="CT5" s="90"/>
+      <c r="CU5" s="91"/>
+      <c r="CV5" s="89"/>
+      <c r="CW5" s="90"/>
+      <c r="CX5" s="91"/>
+      <c r="CY5" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="CZ5" s="43"/>
-      <c r="DA5" s="43"/>
-      <c r="DB5" s="43"/>
-      <c r="DC5" s="43"/>
-      <c r="DD5" s="43"/>
-      <c r="DE5" s="43"/>
-      <c r="DF5" s="43"/>
-      <c r="DG5" s="43"/>
-      <c r="DH5" s="75"/>
-      <c r="DI5" s="75"/>
-      <c r="DJ5" s="75"/>
-      <c r="DK5" s="75"/>
-      <c r="DL5" s="75"/>
-      <c r="DM5" s="75"/>
-      <c r="DN5" s="69"/>
-      <c r="DO5" s="70"/>
-      <c r="DP5" s="86"/>
-      <c r="DQ5" s="81"/>
-      <c r="DR5" s="82"/>
-      <c r="DS5" s="82"/>
-      <c r="DT5" s="82"/>
-      <c r="DU5" s="82"/>
-      <c r="DV5" s="83"/>
-      <c r="DW5" s="84"/>
-      <c r="DX5" s="84"/>
-      <c r="DY5" s="84"/>
-      <c r="DZ5" s="84"/>
-      <c r="EA5" s="84"/>
-      <c r="EB5" s="84"/>
-      <c r="EC5" s="69"/>
-      <c r="ED5" s="70"/>
-      <c r="EE5" s="71"/>
-      <c r="EF5" s="69"/>
-      <c r="EG5" s="70"/>
-      <c r="EH5" s="71"/>
-      <c r="EI5" s="43" t="s">
+      <c r="CZ5" s="39"/>
+      <c r="DA5" s="39"/>
+      <c r="DB5" s="39"/>
+      <c r="DC5" s="39"/>
+      <c r="DD5" s="39"/>
+      <c r="DE5" s="39"/>
+      <c r="DF5" s="39"/>
+      <c r="DG5" s="39"/>
+      <c r="DH5" s="95"/>
+      <c r="DI5" s="95"/>
+      <c r="DJ5" s="95"/>
+      <c r="DK5" s="95"/>
+      <c r="DL5" s="95"/>
+      <c r="DM5" s="95"/>
+      <c r="DN5" s="89"/>
+      <c r="DO5" s="90"/>
+      <c r="DP5" s="97"/>
+      <c r="DQ5" s="82"/>
+      <c r="DR5" s="83"/>
+      <c r="DS5" s="83"/>
+      <c r="DT5" s="83"/>
+      <c r="DU5" s="83"/>
+      <c r="DV5" s="84"/>
+      <c r="DW5" s="85"/>
+      <c r="DX5" s="85"/>
+      <c r="DY5" s="85"/>
+      <c r="DZ5" s="85"/>
+      <c r="EA5" s="85"/>
+      <c r="EB5" s="85"/>
+      <c r="EC5" s="89"/>
+      <c r="ED5" s="90"/>
+      <c r="EE5" s="91"/>
+      <c r="EF5" s="89"/>
+      <c r="EG5" s="90"/>
+      <c r="EH5" s="91"/>
+      <c r="EI5" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="EJ5" s="43"/>
-      <c r="EK5" s="43"/>
-      <c r="EL5" s="43"/>
-      <c r="EM5" s="43"/>
-      <c r="EN5" s="43"/>
-      <c r="EO5" s="43"/>
-      <c r="EP5" s="43"/>
-      <c r="EQ5" s="43"/>
-      <c r="ER5" s="75"/>
-      <c r="ES5" s="75"/>
-      <c r="ET5" s="75"/>
-      <c r="EU5" s="75"/>
-      <c r="EV5" s="75"/>
-      <c r="EW5" s="75"/>
-      <c r="EX5" s="69"/>
-      <c r="EY5" s="70"/>
-      <c r="EZ5" s="86"/>
-      <c r="FA5" s="81"/>
-      <c r="FB5" s="82"/>
-      <c r="FC5" s="82"/>
-      <c r="FD5" s="82"/>
-      <c r="FE5" s="82"/>
-      <c r="FF5" s="83"/>
-      <c r="FG5" s="84"/>
-      <c r="FH5" s="84"/>
-      <c r="FI5" s="84"/>
-      <c r="FJ5" s="84"/>
-      <c r="FK5" s="84"/>
-      <c r="FL5" s="84"/>
-      <c r="FM5" s="69"/>
-      <c r="FN5" s="70"/>
-      <c r="FO5" s="71"/>
-      <c r="FP5" s="69"/>
-      <c r="FQ5" s="70"/>
-      <c r="FR5" s="71"/>
-      <c r="FS5" s="43" t="s">
+      <c r="EJ5" s="39"/>
+      <c r="EK5" s="39"/>
+      <c r="EL5" s="39"/>
+      <c r="EM5" s="39"/>
+      <c r="EN5" s="39"/>
+      <c r="EO5" s="39"/>
+      <c r="EP5" s="39"/>
+      <c r="EQ5" s="39"/>
+      <c r="ER5" s="95"/>
+      <c r="ES5" s="95"/>
+      <c r="ET5" s="95"/>
+      <c r="EU5" s="95"/>
+      <c r="EV5" s="95"/>
+      <c r="EW5" s="95"/>
+      <c r="EX5" s="89"/>
+      <c r="EY5" s="90"/>
+      <c r="EZ5" s="97"/>
+      <c r="FA5" s="82"/>
+      <c r="FB5" s="83"/>
+      <c r="FC5" s="83"/>
+      <c r="FD5" s="83"/>
+      <c r="FE5" s="83"/>
+      <c r="FF5" s="84"/>
+      <c r="FG5" s="85"/>
+      <c r="FH5" s="85"/>
+      <c r="FI5" s="85"/>
+      <c r="FJ5" s="85"/>
+      <c r="FK5" s="85"/>
+      <c r="FL5" s="85"/>
+      <c r="FM5" s="89"/>
+      <c r="FN5" s="90"/>
+      <c r="FO5" s="91"/>
+      <c r="FP5" s="89"/>
+      <c r="FQ5" s="90"/>
+      <c r="FR5" s="91"/>
+      <c r="FS5" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="FT5" s="43"/>
-      <c r="FU5" s="43"/>
-      <c r="FV5" s="43"/>
-      <c r="FW5" s="43"/>
-      <c r="FX5" s="43"/>
-      <c r="FY5" s="43"/>
-      <c r="FZ5" s="43"/>
-      <c r="GA5" s="43"/>
-      <c r="GB5" s="75"/>
-      <c r="GC5" s="75"/>
-      <c r="GD5" s="75"/>
-      <c r="GE5" s="75"/>
-      <c r="GF5" s="75"/>
-      <c r="GG5" s="75"/>
-      <c r="GH5" s="69"/>
-      <c r="GI5" s="70"/>
-      <c r="GJ5" s="86"/>
-      <c r="GK5" s="81"/>
-      <c r="GL5" s="82"/>
-      <c r="GM5" s="82"/>
-      <c r="GN5" s="82"/>
-      <c r="GO5" s="82"/>
-      <c r="GP5" s="83"/>
-      <c r="GQ5" s="84"/>
-      <c r="GR5" s="84"/>
-      <c r="GS5" s="84"/>
-      <c r="GT5" s="84"/>
-      <c r="GU5" s="84"/>
-      <c r="GV5" s="84"/>
-      <c r="GW5" s="69"/>
-      <c r="GX5" s="70"/>
-      <c r="GY5" s="71"/>
-      <c r="GZ5" s="69"/>
-      <c r="HA5" s="70"/>
-      <c r="HB5" s="71"/>
-      <c r="HC5" s="43" t="s">
+      <c r="FT5" s="39"/>
+      <c r="FU5" s="39"/>
+      <c r="FV5" s="39"/>
+      <c r="FW5" s="39"/>
+      <c r="FX5" s="39"/>
+      <c r="FY5" s="39"/>
+      <c r="FZ5" s="39"/>
+      <c r="GA5" s="39"/>
+      <c r="GB5" s="95"/>
+      <c r="GC5" s="95"/>
+      <c r="GD5" s="95"/>
+      <c r="GE5" s="95"/>
+      <c r="GF5" s="95"/>
+      <c r="GG5" s="95"/>
+      <c r="GH5" s="89"/>
+      <c r="GI5" s="90"/>
+      <c r="GJ5" s="97"/>
+      <c r="GK5" s="82"/>
+      <c r="GL5" s="83"/>
+      <c r="GM5" s="83"/>
+      <c r="GN5" s="83"/>
+      <c r="GO5" s="83"/>
+      <c r="GP5" s="84"/>
+      <c r="GQ5" s="85"/>
+      <c r="GR5" s="85"/>
+      <c r="GS5" s="85"/>
+      <c r="GT5" s="85"/>
+      <c r="GU5" s="85"/>
+      <c r="GV5" s="85"/>
+      <c r="GW5" s="89"/>
+      <c r="GX5" s="90"/>
+      <c r="GY5" s="91"/>
+      <c r="GZ5" s="89"/>
+      <c r="HA5" s="90"/>
+      <c r="HB5" s="91"/>
+      <c r="HC5" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="HD5" s="43"/>
-      <c r="HE5" s="43"/>
-      <c r="HF5" s="43"/>
-      <c r="HG5" s="43"/>
-      <c r="HH5" s="43"/>
-      <c r="HI5" s="43"/>
-      <c r="HJ5" s="43"/>
-      <c r="HK5" s="43"/>
-      <c r="HL5" s="75"/>
-      <c r="HM5" s="75"/>
-      <c r="HN5" s="75"/>
-      <c r="HO5" s="75"/>
-      <c r="HP5" s="75"/>
-      <c r="HQ5" s="75"/>
-      <c r="HR5" s="69"/>
-      <c r="HS5" s="70"/>
-      <c r="HT5" s="86"/>
-      <c r="HU5" s="81"/>
-      <c r="HV5" s="82"/>
-      <c r="HW5" s="82"/>
-      <c r="HX5" s="82"/>
-      <c r="HY5" s="82"/>
-      <c r="HZ5" s="83"/>
-      <c r="IA5" s="84"/>
-      <c r="IB5" s="84"/>
-      <c r="IC5" s="84"/>
-      <c r="ID5" s="84"/>
-      <c r="IE5" s="84"/>
-      <c r="IF5" s="84"/>
-      <c r="IG5" s="69"/>
-      <c r="IH5" s="70"/>
-      <c r="II5" s="71"/>
-      <c r="IJ5" s="69"/>
-      <c r="IK5" s="70"/>
-      <c r="IL5" s="71"/>
-      <c r="IM5" s="43" t="s">
+      <c r="HD5" s="39"/>
+      <c r="HE5" s="39"/>
+      <c r="HF5" s="39"/>
+      <c r="HG5" s="39"/>
+      <c r="HH5" s="39"/>
+      <c r="HI5" s="39"/>
+      <c r="HJ5" s="39"/>
+      <c r="HK5" s="39"/>
+      <c r="HL5" s="95"/>
+      <c r="HM5" s="95"/>
+      <c r="HN5" s="95"/>
+      <c r="HO5" s="95"/>
+      <c r="HP5" s="95"/>
+      <c r="HQ5" s="95"/>
+      <c r="HR5" s="89"/>
+      <c r="HS5" s="90"/>
+      <c r="HT5" s="97"/>
+      <c r="HU5" s="82"/>
+      <c r="HV5" s="83"/>
+      <c r="HW5" s="83"/>
+      <c r="HX5" s="83"/>
+      <c r="HY5" s="83"/>
+      <c r="HZ5" s="84"/>
+      <c r="IA5" s="85"/>
+      <c r="IB5" s="85"/>
+      <c r="IC5" s="85"/>
+      <c r="ID5" s="85"/>
+      <c r="IE5" s="85"/>
+      <c r="IF5" s="85"/>
+      <c r="IG5" s="89"/>
+      <c r="IH5" s="90"/>
+      <c r="II5" s="91"/>
+      <c r="IJ5" s="89"/>
+      <c r="IK5" s="90"/>
+      <c r="IL5" s="91"/>
+      <c r="IM5" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="IN5" s="43"/>
-      <c r="IO5" s="43"/>
-      <c r="IP5" s="43"/>
-      <c r="IQ5" s="43"/>
-      <c r="IR5" s="43"/>
-      <c r="IS5" s="43"/>
-      <c r="IT5" s="43"/>
-      <c r="IU5" s="43"/>
-      <c r="IV5" s="75"/>
-      <c r="IW5" s="75"/>
-      <c r="IX5" s="75"/>
-      <c r="IY5" s="75"/>
-      <c r="IZ5" s="75"/>
-      <c r="JA5" s="75"/>
-      <c r="JB5" s="69"/>
-      <c r="JC5" s="70"/>
-      <c r="JD5" s="86"/>
-      <c r="JE5" s="81"/>
-      <c r="JF5" s="82"/>
-      <c r="JG5" s="82"/>
-      <c r="JH5" s="82"/>
-      <c r="JI5" s="82"/>
-      <c r="JJ5" s="83"/>
-      <c r="JK5" s="84"/>
-      <c r="JL5" s="84"/>
-      <c r="JM5" s="84"/>
-      <c r="JN5" s="84"/>
-      <c r="JO5" s="84"/>
-      <c r="JP5" s="84"/>
-      <c r="JQ5" s="69"/>
-      <c r="JR5" s="70"/>
-      <c r="JS5" s="71"/>
-      <c r="JT5" s="69"/>
-      <c r="JU5" s="70"/>
-      <c r="JV5" s="71"/>
-      <c r="JW5" s="43" t="s">
+      <c r="IN5" s="39"/>
+      <c r="IO5" s="39"/>
+      <c r="IP5" s="39"/>
+      <c r="IQ5" s="39"/>
+      <c r="IR5" s="39"/>
+      <c r="IS5" s="39"/>
+      <c r="IT5" s="39"/>
+      <c r="IU5" s="39"/>
+      <c r="IV5" s="95"/>
+      <c r="IW5" s="95"/>
+      <c r="IX5" s="95"/>
+      <c r="IY5" s="95"/>
+      <c r="IZ5" s="95"/>
+      <c r="JA5" s="95"/>
+      <c r="JB5" s="89"/>
+      <c r="JC5" s="90"/>
+      <c r="JD5" s="97"/>
+      <c r="JE5" s="82"/>
+      <c r="JF5" s="83"/>
+      <c r="JG5" s="83"/>
+      <c r="JH5" s="83"/>
+      <c r="JI5" s="83"/>
+      <c r="JJ5" s="84"/>
+      <c r="JK5" s="85"/>
+      <c r="JL5" s="85"/>
+      <c r="JM5" s="85"/>
+      <c r="JN5" s="85"/>
+      <c r="JO5" s="85"/>
+      <c r="JP5" s="85"/>
+      <c r="JQ5" s="89"/>
+      <c r="JR5" s="90"/>
+      <c r="JS5" s="91"/>
+      <c r="JT5" s="89"/>
+      <c r="JU5" s="90"/>
+      <c r="JV5" s="91"/>
+      <c r="JW5" s="39" t="s">
         <v>27</v>
       </c>
-      <c r="JX5" s="43"/>
-      <c r="JY5" s="43"/>
-      <c r="JZ5" s="43"/>
-      <c r="KA5" s="43"/>
-      <c r="KB5" s="43"/>
-      <c r="KC5" s="43"/>
-      <c r="KD5" s="43"/>
-      <c r="KE5" s="43"/>
-      <c r="KF5" s="75"/>
-      <c r="KG5" s="75"/>
-      <c r="KH5" s="75"/>
-      <c r="KI5" s="75"/>
-      <c r="KJ5" s="75"/>
-      <c r="KK5" s="75"/>
-      <c r="KL5" s="69"/>
-      <c r="KM5" s="70"/>
-      <c r="KN5" s="86"/>
-      <c r="KO5" s="106" t="s">
+      <c r="JX5" s="39"/>
+      <c r="JY5" s="39"/>
+      <c r="JZ5" s="39"/>
+      <c r="KA5" s="39"/>
+      <c r="KB5" s="39"/>
+      <c r="KC5" s="39"/>
+      <c r="KD5" s="39"/>
+      <c r="KE5" s="39"/>
+      <c r="KF5" s="95"/>
+      <c r="KG5" s="95"/>
+      <c r="KH5" s="95"/>
+      <c r="KI5" s="95"/>
+      <c r="KJ5" s="95"/>
+      <c r="KK5" s="95"/>
+      <c r="KL5" s="89"/>
+      <c r="KM5" s="90"/>
+      <c r="KN5" s="97"/>
+      <c r="KO5" s="113" t="s">
         <v>28</v>
       </c>
-      <c r="KP5" s="39" t="s">
+      <c r="KP5" s="40" t="s">
         <v>29</v>
       </c>
       <c r="KQ5" s="64" t="s">
         <v>752</v>
       </c>
-      <c r="KR5" s="44"/>
-      <c r="KS5" s="44"/>
-      <c r="KT5" s="65"/>
-      <c r="KU5" s="108" t="s">
+      <c r="KR5" s="65"/>
+      <c r="KS5" s="65"/>
+      <c r="KT5" s="66"/>
+      <c r="KU5" s="115" t="s">
         <v>30</v>
       </c>
-      <c r="KV5" s="109"/>
-      <c r="KW5" s="109"/>
-      <c r="KX5" s="109"/>
-      <c r="KY5" s="109"/>
-      <c r="KZ5" s="109"/>
-      <c r="LA5" s="109"/>
-      <c r="LB5" s="109"/>
-      <c r="LC5" s="109"/>
-      <c r="LD5" s="109"/>
-      <c r="LE5" s="109"/>
-      <c r="LF5" s="110"/>
-      <c r="LG5" s="39" t="s">
+      <c r="KV5" s="116"/>
+      <c r="KW5" s="116"/>
+      <c r="KX5" s="116"/>
+      <c r="KY5" s="116"/>
+      <c r="KZ5" s="116"/>
+      <c r="LA5" s="116"/>
+      <c r="LB5" s="116"/>
+      <c r="LC5" s="116"/>
+      <c r="LD5" s="116"/>
+      <c r="LE5" s="116"/>
+      <c r="LF5" s="117"/>
+      <c r="LG5" s="40" t="s">
         <v>31</v>
       </c>
-      <c r="LH5" s="39" t="s">
+      <c r="LH5" s="40" t="s">
         <v>29</v>
       </c>
       <c r="LI5" s="64" t="s">
         <v>753</v>
       </c>
-      <c r="LJ5" s="44"/>
-      <c r="LK5" s="44"/>
-      <c r="LL5" s="65"/>
-      <c r="LM5" s="129" t="s">
+      <c r="LJ5" s="65"/>
+      <c r="LK5" s="65"/>
+      <c r="LL5" s="66"/>
+      <c r="LM5" s="73" t="s">
         <v>27</v>
       </c>
-      <c r="LN5" s="129"/>
-      <c r="LO5" s="129"/>
-      <c r="LP5" s="129"/>
-      <c r="LQ5" s="129"/>
-      <c r="LR5" s="129"/>
-      <c r="LS5" s="129"/>
-      <c r="LT5" s="129"/>
-      <c r="LU5" s="129"/>
-      <c r="LV5" s="129"/>
-      <c r="LW5" s="129"/>
-      <c r="LX5" s="129"/>
-      <c r="LY5" s="103"/>
-      <c r="LZ5" s="104"/>
-      <c r="MA5" s="104"/>
-      <c r="MB5" s="104"/>
-      <c r="MC5" s="104"/>
-      <c r="MD5" s="105"/>
-      <c r="ME5" s="103"/>
-      <c r="MF5" s="104"/>
-      <c r="MG5" s="104"/>
-      <c r="MH5" s="104"/>
-      <c r="MI5" s="104"/>
-      <c r="MJ5" s="105"/>
-      <c r="MK5" s="33" t="s">
+      <c r="LN5" s="73"/>
+      <c r="LO5" s="73"/>
+      <c r="LP5" s="73"/>
+      <c r="LQ5" s="73"/>
+      <c r="LR5" s="73"/>
+      <c r="LS5" s="73"/>
+      <c r="LT5" s="73"/>
+      <c r="LU5" s="73"/>
+      <c r="LV5" s="73"/>
+      <c r="LW5" s="73"/>
+      <c r="LX5" s="73"/>
+      <c r="LY5" s="110"/>
+      <c r="LZ5" s="111"/>
+      <c r="MA5" s="111"/>
+      <c r="MB5" s="111"/>
+      <c r="MC5" s="111"/>
+      <c r="MD5" s="112"/>
+      <c r="ME5" s="110"/>
+      <c r="MF5" s="111"/>
+      <c r="MG5" s="111"/>
+      <c r="MH5" s="111"/>
+      <c r="MI5" s="111"/>
+      <c r="MJ5" s="112"/>
+      <c r="MK5" s="38" t="s">
         <v>32</v>
       </c>
-      <c r="ML5" s="33" t="s">
+      <c r="ML5" s="38" t="s">
         <v>33</v>
       </c>
       <c r="MM5" s="64" t="s">
         <v>34</v>
       </c>
-      <c r="MN5" s="44"/>
-      <c r="MO5" s="44"/>
-      <c r="MP5" s="65"/>
-      <c r="MQ5" s="35" t="s">
+      <c r="MN5" s="65"/>
+      <c r="MO5" s="65"/>
+      <c r="MP5" s="66"/>
+      <c r="MQ5" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="MR5" s="36"/>
-      <c r="MS5" s="36"/>
-      <c r="MT5" s="36"/>
-      <c r="MU5" s="36"/>
-      <c r="MV5" s="36"/>
-      <c r="MW5" s="36"/>
-      <c r="MX5" s="36"/>
-      <c r="MY5" s="36"/>
-      <c r="MZ5" s="36"/>
-      <c r="NA5" s="36"/>
-      <c r="NB5" s="36"/>
-      <c r="NC5" s="36"/>
-      <c r="ND5" s="36"/>
-      <c r="NE5" s="36"/>
-      <c r="NF5" s="36"/>
-      <c r="NG5" s="36"/>
-      <c r="NH5" s="36"/>
-      <c r="NI5" s="93"/>
-      <c r="NJ5" s="58"/>
-      <c r="NK5" s="43"/>
-      <c r="NL5" s="43"/>
-      <c r="NM5" s="43"/>
-      <c r="NN5" s="43"/>
-      <c r="NO5" s="43"/>
-      <c r="NP5" s="43"/>
-      <c r="NQ5" s="43"/>
-      <c r="NR5" s="43"/>
-      <c r="NS5" s="43"/>
-      <c r="NT5" s="43"/>
-      <c r="NU5" s="46"/>
-      <c r="NV5" s="46"/>
-      <c r="NW5" s="46"/>
-      <c r="NX5" s="46"/>
-      <c r="NY5" s="46"/>
-      <c r="NZ5" s="47"/>
-      <c r="OA5" s="117"/>
-      <c r="OB5" s="118"/>
-      <c r="OC5" s="118"/>
-      <c r="OD5" s="118"/>
-      <c r="OE5" s="118"/>
-      <c r="OF5" s="118"/>
+      <c r="MR5" s="99"/>
+      <c r="MS5" s="99"/>
+      <c r="MT5" s="99"/>
+      <c r="MU5" s="99"/>
+      <c r="MV5" s="99"/>
+      <c r="MW5" s="99"/>
+      <c r="MX5" s="99"/>
+      <c r="MY5" s="99"/>
+      <c r="MZ5" s="99"/>
+      <c r="NA5" s="99"/>
+      <c r="NB5" s="99"/>
+      <c r="NC5" s="99"/>
+      <c r="ND5" s="99"/>
+      <c r="NE5" s="99"/>
+      <c r="NF5" s="99"/>
+      <c r="NG5" s="99"/>
+      <c r="NH5" s="99"/>
+      <c r="NI5" s="102"/>
+      <c r="NJ5" s="37"/>
+      <c r="NK5" s="39"/>
+      <c r="NL5" s="39"/>
+      <c r="NM5" s="39"/>
+      <c r="NN5" s="39"/>
+      <c r="NO5" s="39"/>
+      <c r="NP5" s="39"/>
+      <c r="NQ5" s="39"/>
+      <c r="NR5" s="39"/>
+      <c r="NS5" s="39"/>
+      <c r="NT5" s="39"/>
+      <c r="NU5" s="68"/>
+      <c r="NV5" s="68"/>
+      <c r="NW5" s="68"/>
+      <c r="NX5" s="68"/>
+      <c r="NY5" s="68"/>
+      <c r="NZ5" s="132"/>
+      <c r="OA5" s="77"/>
+      <c r="OB5" s="78"/>
+      <c r="OC5" s="78"/>
+      <c r="OD5" s="78"/>
+      <c r="OE5" s="78"/>
+      <c r="OF5" s="78"/>
     </row>
     <row r="6" spans="1:396" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="51"/>
-      <c r="B6" s="51"/>
-      <c r="C6" s="51"/>
-      <c r="D6" s="51"/>
-      <c r="E6" s="51" t="s">
+      <c r="A6" s="49"/>
+      <c r="B6" s="49"/>
+      <c r="C6" s="49"/>
+      <c r="D6" s="49"/>
+      <c r="E6" s="49" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="51"/>
-      <c r="G6" s="51" t="s">
+      <c r="F6" s="49"/>
+      <c r="G6" s="49" t="s">
         <v>36</v>
       </c>
-      <c r="H6" s="50" t="s">
+      <c r="H6" s="48" t="s">
         <v>37</v>
       </c>
-      <c r="I6" s="88" t="s">
+      <c r="I6" s="118" t="s">
         <v>38</v>
       </c>
-      <c r="J6" s="89"/>
-      <c r="K6" s="89"/>
-      <c r="L6" s="90"/>
-      <c r="M6" s="35" t="s">
+      <c r="J6" s="119"/>
+      <c r="K6" s="119"/>
+      <c r="L6" s="120"/>
+      <c r="M6" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="N6" s="36"/>
-      <c r="O6" s="37"/>
-      <c r="P6" s="35" t="s">
+      <c r="N6" s="99"/>
+      <c r="O6" s="43"/>
+      <c r="P6" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="Q6" s="36"/>
-      <c r="R6" s="37"/>
-      <c r="S6" s="76" t="s">
+      <c r="Q6" s="99"/>
+      <c r="R6" s="43"/>
+      <c r="S6" s="70" t="s">
         <v>41</v>
       </c>
-      <c r="T6" s="48"/>
-      <c r="U6" s="77"/>
-      <c r="V6" s="76" t="s">
+      <c r="T6" s="71"/>
+      <c r="U6" s="72"/>
+      <c r="V6" s="70" t="s">
         <v>42</v>
       </c>
-      <c r="W6" s="48"/>
-      <c r="X6" s="77"/>
-      <c r="Y6" s="72"/>
-      <c r="Z6" s="73"/>
-      <c r="AA6" s="74"/>
-      <c r="AB6" s="72"/>
-      <c r="AC6" s="73"/>
-      <c r="AD6" s="74"/>
-      <c r="AE6" s="58" t="s">
+      <c r="W6" s="71"/>
+      <c r="X6" s="72"/>
+      <c r="Y6" s="92"/>
+      <c r="Z6" s="93"/>
+      <c r="AA6" s="94"/>
+      <c r="AB6" s="92"/>
+      <c r="AC6" s="93"/>
+      <c r="AD6" s="94"/>
+      <c r="AE6" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="AF6" s="58"/>
-      <c r="AG6" s="58"/>
-      <c r="AH6" s="43" t="s">
+      <c r="AF6" s="37"/>
+      <c r="AG6" s="37"/>
+      <c r="AH6" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="AI6" s="43"/>
-      <c r="AJ6" s="43"/>
-      <c r="AK6" s="58" t="s">
+      <c r="AI6" s="39"/>
+      <c r="AJ6" s="39"/>
+      <c r="AK6" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="AL6" s="58"/>
-      <c r="AM6" s="58"/>
-      <c r="AN6" s="43" t="s">
+      <c r="AL6" s="37"/>
+      <c r="AM6" s="37"/>
+      <c r="AN6" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="AO6" s="43"/>
-      <c r="AP6" s="43"/>
-      <c r="AQ6" s="43" t="s">
+      <c r="AO6" s="39"/>
+      <c r="AP6" s="39"/>
+      <c r="AQ6" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="AR6" s="43"/>
-      <c r="AS6" s="43"/>
-      <c r="AT6" s="72"/>
-      <c r="AU6" s="73"/>
-      <c r="AV6" s="87"/>
-      <c r="AW6" s="35" t="s">
+      <c r="AR6" s="39"/>
+      <c r="AS6" s="39"/>
+      <c r="AT6" s="92"/>
+      <c r="AU6" s="93"/>
+      <c r="AV6" s="98"/>
+      <c r="AW6" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="AX6" s="36"/>
-      <c r="AY6" s="37"/>
-      <c r="AZ6" s="35" t="s">
+      <c r="AX6" s="99"/>
+      <c r="AY6" s="43"/>
+      <c r="AZ6" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="BA6" s="36"/>
-      <c r="BB6" s="37"/>
-      <c r="BC6" s="76" t="s">
+      <c r="BA6" s="99"/>
+      <c r="BB6" s="43"/>
+      <c r="BC6" s="70" t="s">
         <v>41</v>
       </c>
-      <c r="BD6" s="48"/>
-      <c r="BE6" s="77"/>
-      <c r="BF6" s="76" t="s">
+      <c r="BD6" s="71"/>
+      <c r="BE6" s="72"/>
+      <c r="BF6" s="70" t="s">
         <v>42</v>
       </c>
-      <c r="BG6" s="48"/>
-      <c r="BH6" s="77"/>
-      <c r="BI6" s="72"/>
-      <c r="BJ6" s="73"/>
-      <c r="BK6" s="74"/>
-      <c r="BL6" s="72"/>
-      <c r="BM6" s="73"/>
-      <c r="BN6" s="74"/>
-      <c r="BO6" s="58" t="s">
+      <c r="BG6" s="71"/>
+      <c r="BH6" s="72"/>
+      <c r="BI6" s="92"/>
+      <c r="BJ6" s="93"/>
+      <c r="BK6" s="94"/>
+      <c r="BL6" s="92"/>
+      <c r="BM6" s="93"/>
+      <c r="BN6" s="94"/>
+      <c r="BO6" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="BP6" s="58"/>
-      <c r="BQ6" s="58"/>
-      <c r="BR6" s="43" t="s">
+      <c r="BP6" s="37"/>
+      <c r="BQ6" s="37"/>
+      <c r="BR6" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="BS6" s="43"/>
-      <c r="BT6" s="43"/>
-      <c r="BU6" s="58" t="s">
+      <c r="BS6" s="39"/>
+      <c r="BT6" s="39"/>
+      <c r="BU6" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="BV6" s="58"/>
-      <c r="BW6" s="58"/>
-      <c r="BX6" s="43" t="s">
+      <c r="BV6" s="37"/>
+      <c r="BW6" s="37"/>
+      <c r="BX6" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="BY6" s="43"/>
-      <c r="BZ6" s="43"/>
-      <c r="CA6" s="43" t="s">
+      <c r="BY6" s="39"/>
+      <c r="BZ6" s="39"/>
+      <c r="CA6" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="CB6" s="43"/>
-      <c r="CC6" s="43"/>
-      <c r="CD6" s="72"/>
-      <c r="CE6" s="73"/>
-      <c r="CF6" s="87"/>
-      <c r="CG6" s="35" t="s">
+      <c r="CB6" s="39"/>
+      <c r="CC6" s="39"/>
+      <c r="CD6" s="92"/>
+      <c r="CE6" s="93"/>
+      <c r="CF6" s="98"/>
+      <c r="CG6" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="CH6" s="36"/>
-      <c r="CI6" s="37"/>
-      <c r="CJ6" s="35" t="s">
+      <c r="CH6" s="99"/>
+      <c r="CI6" s="43"/>
+      <c r="CJ6" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="CK6" s="36"/>
-      <c r="CL6" s="37"/>
-      <c r="CM6" s="76" t="s">
+      <c r="CK6" s="99"/>
+      <c r="CL6" s="43"/>
+      <c r="CM6" s="70" t="s">
         <v>41</v>
       </c>
-      <c r="CN6" s="48"/>
-      <c r="CO6" s="77"/>
-      <c r="CP6" s="76" t="s">
+      <c r="CN6" s="71"/>
+      <c r="CO6" s="72"/>
+      <c r="CP6" s="70" t="s">
         <v>42</v>
       </c>
-      <c r="CQ6" s="48"/>
-      <c r="CR6" s="77"/>
-      <c r="CS6" s="72"/>
-      <c r="CT6" s="73"/>
-      <c r="CU6" s="74"/>
-      <c r="CV6" s="72"/>
-      <c r="CW6" s="73"/>
-      <c r="CX6" s="74"/>
-      <c r="CY6" s="58" t="s">
+      <c r="CQ6" s="71"/>
+      <c r="CR6" s="72"/>
+      <c r="CS6" s="92"/>
+      <c r="CT6" s="93"/>
+      <c r="CU6" s="94"/>
+      <c r="CV6" s="92"/>
+      <c r="CW6" s="93"/>
+      <c r="CX6" s="94"/>
+      <c r="CY6" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="CZ6" s="58"/>
-      <c r="DA6" s="58"/>
-      <c r="DB6" s="43" t="s">
+      <c r="CZ6" s="37"/>
+      <c r="DA6" s="37"/>
+      <c r="DB6" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="DC6" s="43"/>
-      <c r="DD6" s="43"/>
-      <c r="DE6" s="58" t="s">
+      <c r="DC6" s="39"/>
+      <c r="DD6" s="39"/>
+      <c r="DE6" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="DF6" s="58"/>
-      <c r="DG6" s="58"/>
-      <c r="DH6" s="43" t="s">
+      <c r="DF6" s="37"/>
+      <c r="DG6" s="37"/>
+      <c r="DH6" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="DI6" s="43"/>
-      <c r="DJ6" s="43"/>
-      <c r="DK6" s="43" t="s">
+      <c r="DI6" s="39"/>
+      <c r="DJ6" s="39"/>
+      <c r="DK6" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="DL6" s="43"/>
-      <c r="DM6" s="43"/>
-      <c r="DN6" s="72"/>
-      <c r="DO6" s="73"/>
-      <c r="DP6" s="87"/>
-      <c r="DQ6" s="35" t="s">
+      <c r="DL6" s="39"/>
+      <c r="DM6" s="39"/>
+      <c r="DN6" s="92"/>
+      <c r="DO6" s="93"/>
+      <c r="DP6" s="98"/>
+      <c r="DQ6" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="DR6" s="36"/>
-      <c r="DS6" s="37"/>
-      <c r="DT6" s="35" t="s">
+      <c r="DR6" s="99"/>
+      <c r="DS6" s="43"/>
+      <c r="DT6" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="DU6" s="36"/>
-      <c r="DV6" s="37"/>
-      <c r="DW6" s="76" t="s">
+      <c r="DU6" s="99"/>
+      <c r="DV6" s="43"/>
+      <c r="DW6" s="70" t="s">
         <v>41</v>
       </c>
-      <c r="DX6" s="48"/>
-      <c r="DY6" s="77"/>
-      <c r="DZ6" s="76" t="s">
+      <c r="DX6" s="71"/>
+      <c r="DY6" s="72"/>
+      <c r="DZ6" s="70" t="s">
         <v>42</v>
       </c>
-      <c r="EA6" s="48"/>
-      <c r="EB6" s="77"/>
-      <c r="EC6" s="72"/>
-      <c r="ED6" s="73"/>
-      <c r="EE6" s="74"/>
-      <c r="EF6" s="72"/>
-      <c r="EG6" s="73"/>
-      <c r="EH6" s="74"/>
-      <c r="EI6" s="58" t="s">
+      <c r="EA6" s="71"/>
+      <c r="EB6" s="72"/>
+      <c r="EC6" s="92"/>
+      <c r="ED6" s="93"/>
+      <c r="EE6" s="94"/>
+      <c r="EF6" s="92"/>
+      <c r="EG6" s="93"/>
+      <c r="EH6" s="94"/>
+      <c r="EI6" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="EJ6" s="58"/>
-      <c r="EK6" s="58"/>
-      <c r="EL6" s="43" t="s">
+      <c r="EJ6" s="37"/>
+      <c r="EK6" s="37"/>
+      <c r="EL6" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="EM6" s="43"/>
-      <c r="EN6" s="43"/>
-      <c r="EO6" s="58" t="s">
+      <c r="EM6" s="39"/>
+      <c r="EN6" s="39"/>
+      <c r="EO6" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="EP6" s="58"/>
-      <c r="EQ6" s="58"/>
-      <c r="ER6" s="43" t="s">
+      <c r="EP6" s="37"/>
+      <c r="EQ6" s="37"/>
+      <c r="ER6" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="ES6" s="43"/>
-      <c r="ET6" s="43"/>
-      <c r="EU6" s="43" t="s">
+      <c r="ES6" s="39"/>
+      <c r="ET6" s="39"/>
+      <c r="EU6" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="EV6" s="43"/>
-      <c r="EW6" s="43"/>
-      <c r="EX6" s="72"/>
-      <c r="EY6" s="73"/>
-      <c r="EZ6" s="87"/>
-      <c r="FA6" s="35" t="s">
+      <c r="EV6" s="39"/>
+      <c r="EW6" s="39"/>
+      <c r="EX6" s="92"/>
+      <c r="EY6" s="93"/>
+      <c r="EZ6" s="98"/>
+      <c r="FA6" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="FB6" s="36"/>
-      <c r="FC6" s="37"/>
-      <c r="FD6" s="35" t="s">
+      <c r="FB6" s="99"/>
+      <c r="FC6" s="43"/>
+      <c r="FD6" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="FE6" s="36"/>
-      <c r="FF6" s="37"/>
-      <c r="FG6" s="76" t="s">
+      <c r="FE6" s="99"/>
+      <c r="FF6" s="43"/>
+      <c r="FG6" s="70" t="s">
         <v>41</v>
       </c>
-      <c r="FH6" s="48"/>
-      <c r="FI6" s="77"/>
-      <c r="FJ6" s="76" t="s">
+      <c r="FH6" s="71"/>
+      <c r="FI6" s="72"/>
+      <c r="FJ6" s="70" t="s">
         <v>42</v>
       </c>
-      <c r="FK6" s="48"/>
-      <c r="FL6" s="77"/>
-      <c r="FM6" s="72"/>
-      <c r="FN6" s="73"/>
-      <c r="FO6" s="74"/>
-      <c r="FP6" s="72"/>
-      <c r="FQ6" s="73"/>
-      <c r="FR6" s="74"/>
-      <c r="FS6" s="58" t="s">
+      <c r="FK6" s="71"/>
+      <c r="FL6" s="72"/>
+      <c r="FM6" s="92"/>
+      <c r="FN6" s="93"/>
+      <c r="FO6" s="94"/>
+      <c r="FP6" s="92"/>
+      <c r="FQ6" s="93"/>
+      <c r="FR6" s="94"/>
+      <c r="FS6" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="FT6" s="58"/>
-      <c r="FU6" s="58"/>
-      <c r="FV6" s="43" t="s">
+      <c r="FT6" s="37"/>
+      <c r="FU6" s="37"/>
+      <c r="FV6" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="FW6" s="43"/>
-      <c r="FX6" s="43"/>
-      <c r="FY6" s="58" t="s">
+      <c r="FW6" s="39"/>
+      <c r="FX6" s="39"/>
+      <c r="FY6" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="FZ6" s="58"/>
-      <c r="GA6" s="58"/>
-      <c r="GB6" s="43" t="s">
+      <c r="FZ6" s="37"/>
+      <c r="GA6" s="37"/>
+      <c r="GB6" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="GC6" s="43"/>
-      <c r="GD6" s="43"/>
-      <c r="GE6" s="43" t="s">
+      <c r="GC6" s="39"/>
+      <c r="GD6" s="39"/>
+      <c r="GE6" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="GF6" s="43"/>
-      <c r="GG6" s="43"/>
-      <c r="GH6" s="72"/>
-      <c r="GI6" s="73"/>
-      <c r="GJ6" s="87"/>
-      <c r="GK6" s="35" t="s">
+      <c r="GF6" s="39"/>
+      <c r="GG6" s="39"/>
+      <c r="GH6" s="92"/>
+      <c r="GI6" s="93"/>
+      <c r="GJ6" s="98"/>
+      <c r="GK6" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="GL6" s="36"/>
-      <c r="GM6" s="37"/>
-      <c r="GN6" s="35" t="s">
+      <c r="GL6" s="99"/>
+      <c r="GM6" s="43"/>
+      <c r="GN6" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="GO6" s="36"/>
-      <c r="GP6" s="37"/>
-      <c r="GQ6" s="76" t="s">
+      <c r="GO6" s="99"/>
+      <c r="GP6" s="43"/>
+      <c r="GQ6" s="70" t="s">
         <v>41</v>
       </c>
-      <c r="GR6" s="48"/>
-      <c r="GS6" s="77"/>
-      <c r="GT6" s="76" t="s">
+      <c r="GR6" s="71"/>
+      <c r="GS6" s="72"/>
+      <c r="GT6" s="70" t="s">
         <v>42</v>
       </c>
-      <c r="GU6" s="48"/>
-      <c r="GV6" s="77"/>
-      <c r="GW6" s="72"/>
-      <c r="GX6" s="73"/>
-      <c r="GY6" s="74"/>
-      <c r="GZ6" s="72"/>
-      <c r="HA6" s="73"/>
-      <c r="HB6" s="74"/>
-      <c r="HC6" s="58" t="s">
+      <c r="GU6" s="71"/>
+      <c r="GV6" s="72"/>
+      <c r="GW6" s="92"/>
+      <c r="GX6" s="93"/>
+      <c r="GY6" s="94"/>
+      <c r="GZ6" s="92"/>
+      <c r="HA6" s="93"/>
+      <c r="HB6" s="94"/>
+      <c r="HC6" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="HD6" s="58"/>
-      <c r="HE6" s="58"/>
-      <c r="HF6" s="43" t="s">
+      <c r="HD6" s="37"/>
+      <c r="HE6" s="37"/>
+      <c r="HF6" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="HG6" s="43"/>
-      <c r="HH6" s="43"/>
-      <c r="HI6" s="58" t="s">
+      <c r="HG6" s="39"/>
+      <c r="HH6" s="39"/>
+      <c r="HI6" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="HJ6" s="58"/>
-      <c r="HK6" s="58"/>
-      <c r="HL6" s="43" t="s">
+      <c r="HJ6" s="37"/>
+      <c r="HK6" s="37"/>
+      <c r="HL6" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="HM6" s="43"/>
-      <c r="HN6" s="43"/>
-      <c r="HO6" s="43" t="s">
+      <c r="HM6" s="39"/>
+      <c r="HN6" s="39"/>
+      <c r="HO6" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="HP6" s="43"/>
-      <c r="HQ6" s="43"/>
-      <c r="HR6" s="72"/>
-      <c r="HS6" s="73"/>
-      <c r="HT6" s="87"/>
-      <c r="HU6" s="35" t="s">
+      <c r="HP6" s="39"/>
+      <c r="HQ6" s="39"/>
+      <c r="HR6" s="92"/>
+      <c r="HS6" s="93"/>
+      <c r="HT6" s="98"/>
+      <c r="HU6" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="HV6" s="36"/>
-      <c r="HW6" s="37"/>
-      <c r="HX6" s="35" t="s">
+      <c r="HV6" s="99"/>
+      <c r="HW6" s="43"/>
+      <c r="HX6" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="HY6" s="36"/>
-      <c r="HZ6" s="37"/>
-      <c r="IA6" s="76" t="s">
+      <c r="HY6" s="99"/>
+      <c r="HZ6" s="43"/>
+      <c r="IA6" s="70" t="s">
         <v>41</v>
       </c>
-      <c r="IB6" s="48"/>
-      <c r="IC6" s="77"/>
-      <c r="ID6" s="76" t="s">
+      <c r="IB6" s="71"/>
+      <c r="IC6" s="72"/>
+      <c r="ID6" s="70" t="s">
         <v>42</v>
       </c>
-      <c r="IE6" s="48"/>
-      <c r="IF6" s="77"/>
-      <c r="IG6" s="72"/>
-      <c r="IH6" s="73"/>
-      <c r="II6" s="74"/>
-      <c r="IJ6" s="72"/>
-      <c r="IK6" s="73"/>
-      <c r="IL6" s="74"/>
-      <c r="IM6" s="58" t="s">
+      <c r="IE6" s="71"/>
+      <c r="IF6" s="72"/>
+      <c r="IG6" s="92"/>
+      <c r="IH6" s="93"/>
+      <c r="II6" s="94"/>
+      <c r="IJ6" s="92"/>
+      <c r="IK6" s="93"/>
+      <c r="IL6" s="94"/>
+      <c r="IM6" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="IN6" s="58"/>
-      <c r="IO6" s="58"/>
-      <c r="IP6" s="43" t="s">
+      <c r="IN6" s="37"/>
+      <c r="IO6" s="37"/>
+      <c r="IP6" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="IQ6" s="43"/>
-      <c r="IR6" s="43"/>
-      <c r="IS6" s="58" t="s">
+      <c r="IQ6" s="39"/>
+      <c r="IR6" s="39"/>
+      <c r="IS6" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="IT6" s="58"/>
-      <c r="IU6" s="58"/>
-      <c r="IV6" s="43" t="s">
+      <c r="IT6" s="37"/>
+      <c r="IU6" s="37"/>
+      <c r="IV6" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="IW6" s="43"/>
-      <c r="IX6" s="43"/>
-      <c r="IY6" s="43" t="s">
+      <c r="IW6" s="39"/>
+      <c r="IX6" s="39"/>
+      <c r="IY6" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="IZ6" s="43"/>
-      <c r="JA6" s="43"/>
-      <c r="JB6" s="72"/>
-      <c r="JC6" s="73"/>
-      <c r="JD6" s="87"/>
-      <c r="JE6" s="35" t="s">
+      <c r="IZ6" s="39"/>
+      <c r="JA6" s="39"/>
+      <c r="JB6" s="92"/>
+      <c r="JC6" s="93"/>
+      <c r="JD6" s="98"/>
+      <c r="JE6" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="JF6" s="36"/>
-      <c r="JG6" s="37"/>
-      <c r="JH6" s="35" t="s">
+      <c r="JF6" s="99"/>
+      <c r="JG6" s="43"/>
+      <c r="JH6" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="JI6" s="36"/>
-      <c r="JJ6" s="37"/>
-      <c r="JK6" s="76" t="s">
+      <c r="JI6" s="99"/>
+      <c r="JJ6" s="43"/>
+      <c r="JK6" s="70" t="s">
         <v>41</v>
       </c>
-      <c r="JL6" s="48"/>
-      <c r="JM6" s="77"/>
-      <c r="JN6" s="76" t="s">
+      <c r="JL6" s="71"/>
+      <c r="JM6" s="72"/>
+      <c r="JN6" s="70" t="s">
         <v>42</v>
       </c>
-      <c r="JO6" s="48"/>
-      <c r="JP6" s="77"/>
-      <c r="JQ6" s="72"/>
-      <c r="JR6" s="73"/>
-      <c r="JS6" s="74"/>
-      <c r="JT6" s="72"/>
-      <c r="JU6" s="73"/>
-      <c r="JV6" s="74"/>
-      <c r="JW6" s="58" t="s">
+      <c r="JO6" s="71"/>
+      <c r="JP6" s="72"/>
+      <c r="JQ6" s="92"/>
+      <c r="JR6" s="93"/>
+      <c r="JS6" s="94"/>
+      <c r="JT6" s="92"/>
+      <c r="JU6" s="93"/>
+      <c r="JV6" s="94"/>
+      <c r="JW6" s="37" t="s">
         <v>43</v>
       </c>
-      <c r="JX6" s="58"/>
-      <c r="JY6" s="58"/>
-      <c r="JZ6" s="43" t="s">
+      <c r="JX6" s="37"/>
+      <c r="JY6" s="37"/>
+      <c r="JZ6" s="39" t="s">
         <v>44</v>
       </c>
-      <c r="KA6" s="43"/>
-      <c r="KB6" s="43"/>
-      <c r="KC6" s="58" t="s">
+      <c r="KA6" s="39"/>
+      <c r="KB6" s="39"/>
+      <c r="KC6" s="37" t="s">
         <v>45</v>
       </c>
-      <c r="KD6" s="58"/>
-      <c r="KE6" s="58"/>
-      <c r="KF6" s="43" t="s">
+      <c r="KD6" s="37"/>
+      <c r="KE6" s="37"/>
+      <c r="KF6" s="39" t="s">
         <v>25</v>
       </c>
-      <c r="KG6" s="43"/>
-      <c r="KH6" s="43"/>
-      <c r="KI6" s="43" t="s">
+      <c r="KG6" s="39"/>
+      <c r="KH6" s="39"/>
+      <c r="KI6" s="39" t="s">
         <v>26</v>
       </c>
-      <c r="KJ6" s="43"/>
-      <c r="KK6" s="43"/>
-      <c r="KL6" s="72"/>
-      <c r="KM6" s="73"/>
-      <c r="KN6" s="87"/>
-      <c r="KO6" s="107"/>
-      <c r="KP6" s="40"/>
-      <c r="KQ6" s="95"/>
-      <c r="KR6" s="46"/>
-      <c r="KS6" s="46"/>
-      <c r="KT6" s="96"/>
-      <c r="KU6" s="35" t="s">
+      <c r="KJ6" s="39"/>
+      <c r="KK6" s="39"/>
+      <c r="KL6" s="92"/>
+      <c r="KM6" s="93"/>
+      <c r="KN6" s="98"/>
+      <c r="KO6" s="114"/>
+      <c r="KP6" s="41"/>
+      <c r="KQ6" s="67"/>
+      <c r="KR6" s="68"/>
+      <c r="KS6" s="68"/>
+      <c r="KT6" s="69"/>
+      <c r="KU6" s="42" t="s">
         <v>39</v>
       </c>
-      <c r="KV6" s="36"/>
-      <c r="KW6" s="36"/>
-      <c r="KX6" s="36"/>
-      <c r="KY6" s="36"/>
-      <c r="KZ6" s="37"/>
-      <c r="LA6" s="35" t="s">
+      <c r="KV6" s="99"/>
+      <c r="KW6" s="99"/>
+      <c r="KX6" s="99"/>
+      <c r="KY6" s="99"/>
+      <c r="KZ6" s="43"/>
+      <c r="LA6" s="42" t="s">
         <v>40</v>
       </c>
-      <c r="LB6" s="36"/>
-      <c r="LC6" s="36"/>
-      <c r="LD6" s="36"/>
-      <c r="LE6" s="36"/>
-      <c r="LF6" s="37"/>
-      <c r="LG6" s="40"/>
-      <c r="LH6" s="40"/>
-      <c r="LI6" s="95"/>
-      <c r="LJ6" s="46"/>
-      <c r="LK6" s="46"/>
-      <c r="LL6" s="96"/>
+      <c r="LB6" s="99"/>
+      <c r="LC6" s="99"/>
+      <c r="LD6" s="99"/>
+      <c r="LE6" s="99"/>
+      <c r="LF6" s="43"/>
+      <c r="LG6" s="41"/>
+      <c r="LH6" s="41"/>
+      <c r="LI6" s="67"/>
+      <c r="LJ6" s="68"/>
+      <c r="LK6" s="68"/>
+      <c r="LL6" s="69"/>
       <c r="LM6" s="64" t="s">
         <v>41</v>
       </c>
-      <c r="LN6" s="44"/>
-      <c r="LO6" s="44"/>
-      <c r="LP6" s="44"/>
-      <c r="LQ6" s="44"/>
-      <c r="LR6" s="65"/>
-      <c r="LS6" s="43" t="s">
+      <c r="LN6" s="65"/>
+      <c r="LO6" s="65"/>
+      <c r="LP6" s="65"/>
+      <c r="LQ6" s="65"/>
+      <c r="LR6" s="66"/>
+      <c r="LS6" s="39" t="s">
         <v>42</v>
       </c>
-      <c r="LT6" s="43"/>
-      <c r="LU6" s="43"/>
-      <c r="LV6" s="43"/>
-      <c r="LW6" s="43"/>
-      <c r="LX6" s="43"/>
-      <c r="LY6" s="58" t="s">
+      <c r="LT6" s="39"/>
+      <c r="LU6" s="39"/>
+      <c r="LV6" s="39"/>
+      <c r="LW6" s="39"/>
+      <c r="LX6" s="39"/>
+      <c r="LY6" s="37" t="s">
         <v>46</v>
       </c>
-      <c r="LZ6" s="58"/>
-      <c r="MA6" s="43" t="s">
+      <c r="LZ6" s="37"/>
+      <c r="MA6" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="MB6" s="43"/>
-      <c r="MC6" s="43"/>
-      <c r="MD6" s="43"/>
-      <c r="ME6" s="58" t="s">
+      <c r="MB6" s="39"/>
+      <c r="MC6" s="39"/>
+      <c r="MD6" s="39"/>
+      <c r="ME6" s="37" t="s">
         <v>48</v>
       </c>
-      <c r="MF6" s="58"/>
-      <c r="MG6" s="43" t="s">
+      <c r="MF6" s="37"/>
+      <c r="MG6" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="MH6" s="43"/>
-      <c r="MI6" s="43"/>
-      <c r="MJ6" s="43"/>
-      <c r="MK6" s="34"/>
-      <c r="ML6" s="34"/>
-      <c r="MM6" s="95"/>
-      <c r="MN6" s="46"/>
-      <c r="MO6" s="46"/>
-      <c r="MP6" s="96"/>
-      <c r="MQ6" s="35" t="s">
+      <c r="MH6" s="39"/>
+      <c r="MI6" s="39"/>
+      <c r="MJ6" s="39"/>
+      <c r="MK6" s="63"/>
+      <c r="ML6" s="63"/>
+      <c r="MM6" s="67"/>
+      <c r="MN6" s="68"/>
+      <c r="MO6" s="68"/>
+      <c r="MP6" s="69"/>
+      <c r="MQ6" s="42" t="s">
         <v>49</v>
       </c>
-      <c r="MR6" s="36"/>
-      <c r="MS6" s="36"/>
-      <c r="MT6" s="36"/>
-      <c r="MU6" s="36"/>
-      <c r="MV6" s="37"/>
-      <c r="MW6" s="35" t="s">
+      <c r="MR6" s="99"/>
+      <c r="MS6" s="99"/>
+      <c r="MT6" s="99"/>
+      <c r="MU6" s="99"/>
+      <c r="MV6" s="43"/>
+      <c r="MW6" s="42" t="s">
         <v>44</v>
       </c>
-      <c r="MX6" s="36"/>
-      <c r="MY6" s="36"/>
-      <c r="MZ6" s="36"/>
-      <c r="NA6" s="36"/>
-      <c r="NB6" s="37"/>
-      <c r="NC6" s="35" t="s">
+      <c r="MX6" s="99"/>
+      <c r="MY6" s="99"/>
+      <c r="MZ6" s="99"/>
+      <c r="NA6" s="99"/>
+      <c r="NB6" s="43"/>
+      <c r="NC6" s="42" t="s">
         <v>45</v>
       </c>
-      <c r="ND6" s="36"/>
-      <c r="NE6" s="36"/>
-      <c r="NF6" s="36"/>
-      <c r="NG6" s="36"/>
-      <c r="NH6" s="36"/>
-      <c r="NI6" s="93"/>
-      <c r="NJ6" s="58"/>
-      <c r="NK6" s="43"/>
-      <c r="NL6" s="43"/>
-      <c r="NM6" s="43"/>
-      <c r="NN6" s="43"/>
-      <c r="NO6" s="43"/>
-      <c r="NP6" s="43"/>
-      <c r="NQ6" s="43"/>
-      <c r="NR6" s="43"/>
-      <c r="NS6" s="43"/>
-      <c r="NT6" s="43"/>
-      <c r="NU6" s="48"/>
-      <c r="NV6" s="48"/>
-      <c r="NW6" s="48"/>
-      <c r="NX6" s="48"/>
-      <c r="NY6" s="48"/>
-      <c r="NZ6" s="49"/>
-      <c r="OA6" s="117"/>
-      <c r="OB6" s="118"/>
-      <c r="OC6" s="118"/>
-      <c r="OD6" s="118"/>
-      <c r="OE6" s="118"/>
-      <c r="OF6" s="118"/>
+      <c r="ND6" s="99"/>
+      <c r="NE6" s="99"/>
+      <c r="NF6" s="99"/>
+      <c r="NG6" s="99"/>
+      <c r="NH6" s="99"/>
+      <c r="NI6" s="102"/>
+      <c r="NJ6" s="37"/>
+      <c r="NK6" s="39"/>
+      <c r="NL6" s="39"/>
+      <c r="NM6" s="39"/>
+      <c r="NN6" s="39"/>
+      <c r="NO6" s="39"/>
+      <c r="NP6" s="39"/>
+      <c r="NQ6" s="39"/>
+      <c r="NR6" s="39"/>
+      <c r="NS6" s="39"/>
+      <c r="NT6" s="39"/>
+      <c r="NU6" s="71"/>
+      <c r="NV6" s="71"/>
+      <c r="NW6" s="71"/>
+      <c r="NX6" s="71"/>
+      <c r="NY6" s="71"/>
+      <c r="NZ6" s="133"/>
+      <c r="OA6" s="77"/>
+      <c r="OB6" s="78"/>
+      <c r="OC6" s="78"/>
+      <c r="OD6" s="78"/>
+      <c r="OE6" s="78"/>
+      <c r="OF6" s="78"/>
     </row>
     <row r="7" spans="1:396" s="1" customFormat="1" ht="45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="51"/>
-      <c r="B7" s="51"/>
-      <c r="C7" s="51"/>
-      <c r="D7" s="51"/>
-      <c r="E7" s="51"/>
-      <c r="F7" s="51"/>
-      <c r="G7" s="51"/>
-      <c r="H7" s="51"/>
-      <c r="I7" s="50" t="s">
+      <c r="A7" s="49"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="49"/>
+      <c r="H7" s="49"/>
+      <c r="I7" s="48" t="s">
         <v>50</v>
       </c>
-      <c r="J7" s="61" t="s">
+      <c r="J7" s="121" t="s">
         <v>27</v>
       </c>
-      <c r="K7" s="62"/>
-      <c r="L7" s="63"/>
-      <c r="M7" s="58" t="s">
+      <c r="K7" s="122"/>
+      <c r="L7" s="123"/>
+      <c r="M7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="N7" s="43" t="s">
+      <c r="N7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="O7" s="39" t="s">
+      <c r="O7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="P7" s="58" t="s">
+      <c r="P7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="Q7" s="43" t="s">
+      <c r="Q7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="R7" s="39" t="s">
+      <c r="R7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="S7" s="58" t="s">
+      <c r="S7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="T7" s="43" t="s">
+      <c r="T7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="U7" s="39" t="s">
+      <c r="U7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="V7" s="58" t="s">
+      <c r="V7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="W7" s="43" t="s">
+      <c r="W7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="X7" s="39" t="s">
+      <c r="X7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="Y7" s="58" t="s">
+      <c r="Y7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="Z7" s="43" t="s">
+      <c r="Z7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="AA7" s="39" t="s">
+      <c r="AA7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="AB7" s="58" t="s">
+      <c r="AB7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="AC7" s="43" t="s">
+      <c r="AC7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="AD7" s="39" t="s">
+      <c r="AD7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="AE7" s="58" t="s">
+      <c r="AE7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="AF7" s="43" t="s">
+      <c r="AF7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="AG7" s="39" t="s">
+      <c r="AG7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="AH7" s="58" t="s">
+      <c r="AH7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="AI7" s="43" t="s">
+      <c r="AI7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="AJ7" s="39" t="s">
+      <c r="AJ7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="AK7" s="58" t="s">
+      <c r="AK7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="AL7" s="43" t="s">
+      <c r="AL7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="AM7" s="39" t="s">
+      <c r="AM7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="AN7" s="58" t="s">
+      <c r="AN7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="AO7" s="43" t="s">
+      <c r="AO7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="AP7" s="39" t="s">
+      <c r="AP7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="AQ7" s="58" t="s">
+      <c r="AQ7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="AR7" s="43" t="s">
+      <c r="AR7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="AS7" s="39" t="s">
+      <c r="AS7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="AT7" s="43" t="s">
+      <c r="AT7" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="AU7" s="43" t="s">
+      <c r="AU7" s="39" t="s">
         <v>755</v>
       </c>
-      <c r="AV7" s="59" t="s">
+      <c r="AV7" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="AW7" s="53" t="s">
+      <c r="AW7" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="AX7" s="43" t="s">
+      <c r="AX7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="AY7" s="39" t="s">
+      <c r="AY7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="AZ7" s="58" t="s">
+      <c r="AZ7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="BA7" s="43" t="s">
+      <c r="BA7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="BB7" s="39" t="s">
+      <c r="BB7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="BC7" s="58" t="s">
+      <c r="BC7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="BD7" s="43" t="s">
+      <c r="BD7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="BE7" s="39" t="s">
+      <c r="BE7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="BF7" s="58" t="s">
+      <c r="BF7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="BG7" s="43" t="s">
+      <c r="BG7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="BH7" s="39" t="s">
+      <c r="BH7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="BI7" s="58" t="s">
+      <c r="BI7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="BJ7" s="43" t="s">
+      <c r="BJ7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="BK7" s="39" t="s">
+      <c r="BK7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="BL7" s="58" t="s">
+      <c r="BL7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="BM7" s="43" t="s">
+      <c r="BM7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="BN7" s="39" t="s">
+      <c r="BN7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="BO7" s="58" t="s">
+      <c r="BO7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="BP7" s="43" t="s">
+      <c r="BP7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="BQ7" s="39" t="s">
+      <c r="BQ7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="BR7" s="58" t="s">
+      <c r="BR7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="BS7" s="43" t="s">
+      <c r="BS7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="BT7" s="39" t="s">
+      <c r="BT7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="BU7" s="58" t="s">
+      <c r="BU7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="BV7" s="43" t="s">
+      <c r="BV7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="BW7" s="39" t="s">
+      <c r="BW7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="BX7" s="58" t="s">
+      <c r="BX7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="BY7" s="43" t="s">
+      <c r="BY7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="BZ7" s="39" t="s">
+      <c r="BZ7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="CA7" s="58" t="s">
+      <c r="CA7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="CB7" s="43" t="s">
+      <c r="CB7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="CC7" s="39" t="s">
+      <c r="CC7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="CD7" s="43" t="s">
+      <c r="CD7" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="CE7" s="43" t="s">
+      <c r="CE7" s="39" t="s">
         <v>755</v>
       </c>
-      <c r="CF7" s="59" t="s">
+      <c r="CF7" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="CG7" s="53" t="s">
+      <c r="CG7" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="CH7" s="43" t="s">
+      <c r="CH7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="CI7" s="39" t="s">
+      <c r="CI7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="CJ7" s="58" t="s">
+      <c r="CJ7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="CK7" s="43" t="s">
+      <c r="CK7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="CL7" s="39" t="s">
+      <c r="CL7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="CM7" s="58" t="s">
+      <c r="CM7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="CN7" s="43" t="s">
+      <c r="CN7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="CO7" s="39" t="s">
+      <c r="CO7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="CP7" s="58" t="s">
+      <c r="CP7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="CQ7" s="43" t="s">
+      <c r="CQ7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="CR7" s="39" t="s">
+      <c r="CR7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="CS7" s="58" t="s">
+      <c r="CS7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="CT7" s="43" t="s">
+      <c r="CT7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="CU7" s="39" t="s">
+      <c r="CU7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="CV7" s="58" t="s">
+      <c r="CV7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="CW7" s="43" t="s">
+      <c r="CW7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="CX7" s="39" t="s">
+      <c r="CX7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="CY7" s="58" t="s">
+      <c r="CY7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="CZ7" s="43" t="s">
+      <c r="CZ7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="DA7" s="39" t="s">
+      <c r="DA7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="DB7" s="58" t="s">
+      <c r="DB7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="DC7" s="43" t="s">
+      <c r="DC7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="DD7" s="39" t="s">
+      <c r="DD7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="DE7" s="58" t="s">
+      <c r="DE7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="DF7" s="43" t="s">
+      <c r="DF7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="DG7" s="39" t="s">
+      <c r="DG7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="DH7" s="58" t="s">
+      <c r="DH7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="DI7" s="43" t="s">
+      <c r="DI7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="DJ7" s="39" t="s">
+      <c r="DJ7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="DK7" s="58" t="s">
+      <c r="DK7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="DL7" s="43" t="s">
+      <c r="DL7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="DM7" s="39" t="s">
+      <c r="DM7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="DN7" s="43" t="s">
+      <c r="DN7" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="DO7" s="43" t="s">
+      <c r="DO7" s="39" t="s">
         <v>755</v>
       </c>
-      <c r="DP7" s="59" t="s">
+      <c r="DP7" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="DQ7" s="53" t="s">
+      <c r="DQ7" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="DR7" s="43" t="s">
+      <c r="DR7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="DS7" s="39" t="s">
+      <c r="DS7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="DT7" s="58" t="s">
+      <c r="DT7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="DU7" s="43" t="s">
+      <c r="DU7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="DV7" s="39" t="s">
+      <c r="DV7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="DW7" s="58" t="s">
+      <c r="DW7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="DX7" s="43" t="s">
+      <c r="DX7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="DY7" s="39" t="s">
+      <c r="DY7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="DZ7" s="58" t="s">
+      <c r="DZ7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="EA7" s="43" t="s">
+      <c r="EA7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="EB7" s="39" t="s">
+      <c r="EB7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="EC7" s="58" t="s">
+      <c r="EC7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="ED7" s="43" t="s">
+      <c r="ED7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="EE7" s="39" t="s">
+      <c r="EE7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="EF7" s="58" t="s">
+      <c r="EF7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="EG7" s="43" t="s">
+      <c r="EG7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="EH7" s="39" t="s">
+      <c r="EH7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="EI7" s="58" t="s">
+      <c r="EI7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="EJ7" s="43" t="s">
+      <c r="EJ7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="EK7" s="39" t="s">
+      <c r="EK7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="EL7" s="58" t="s">
+      <c r="EL7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="EM7" s="43" t="s">
+      <c r="EM7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="EN7" s="39" t="s">
+      <c r="EN7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="EO7" s="58" t="s">
+      <c r="EO7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="EP7" s="43" t="s">
+      <c r="EP7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="EQ7" s="39" t="s">
+      <c r="EQ7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="ER7" s="58" t="s">
+      <c r="ER7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="ES7" s="43" t="s">
+      <c r="ES7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="ET7" s="39" t="s">
+      <c r="ET7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="EU7" s="58" t="s">
+      <c r="EU7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="EV7" s="43" t="s">
+      <c r="EV7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="EW7" s="39" t="s">
+      <c r="EW7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="EX7" s="43" t="s">
+      <c r="EX7" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="EY7" s="43" t="s">
+      <c r="EY7" s="39" t="s">
         <v>755</v>
       </c>
-      <c r="EZ7" s="59" t="s">
+      <c r="EZ7" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="FA7" s="53" t="s">
+      <c r="FA7" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="FB7" s="43" t="s">
+      <c r="FB7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="FC7" s="39" t="s">
+      <c r="FC7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="FD7" s="58" t="s">
+      <c r="FD7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="FE7" s="43" t="s">
+      <c r="FE7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="FF7" s="39" t="s">
+      <c r="FF7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="FG7" s="58" t="s">
+      <c r="FG7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="FH7" s="43" t="s">
+      <c r="FH7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="FI7" s="39" t="s">
+      <c r="FI7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="FJ7" s="58" t="s">
+      <c r="FJ7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="FK7" s="43" t="s">
+      <c r="FK7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="FL7" s="39" t="s">
+      <c r="FL7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="FM7" s="58" t="s">
+      <c r="FM7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="FN7" s="43" t="s">
+      <c r="FN7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="FO7" s="39" t="s">
+      <c r="FO7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="FP7" s="58" t="s">
+      <c r="FP7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="FQ7" s="43" t="s">
+      <c r="FQ7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="FR7" s="39" t="s">
+      <c r="FR7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="FS7" s="58" t="s">
+      <c r="FS7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="FT7" s="43" t="s">
+      <c r="FT7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="FU7" s="39" t="s">
+      <c r="FU7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="FV7" s="58" t="s">
+      <c r="FV7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="FW7" s="43" t="s">
+      <c r="FW7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="FX7" s="39" t="s">
+      <c r="FX7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="FY7" s="58" t="s">
+      <c r="FY7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="FZ7" s="43" t="s">
+      <c r="FZ7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="GA7" s="39" t="s">
+      <c r="GA7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="GB7" s="58" t="s">
+      <c r="GB7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="GC7" s="43" t="s">
+      <c r="GC7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="GD7" s="39" t="s">
+      <c r="GD7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="GE7" s="58" t="s">
+      <c r="GE7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="GF7" s="43" t="s">
+      <c r="GF7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="GG7" s="39" t="s">
+      <c r="GG7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="GH7" s="43" t="s">
+      <c r="GH7" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="GI7" s="43" t="s">
+      <c r="GI7" s="39" t="s">
         <v>755</v>
       </c>
-      <c r="GJ7" s="59" t="s">
+      <c r="GJ7" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="GK7" s="53" t="s">
+      <c r="GK7" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="GL7" s="43" t="s">
+      <c r="GL7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="GM7" s="39" t="s">
+      <c r="GM7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="GN7" s="58" t="s">
+      <c r="GN7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="GO7" s="43" t="s">
+      <c r="GO7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="GP7" s="39" t="s">
+      <c r="GP7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="GQ7" s="58" t="s">
+      <c r="GQ7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="GR7" s="43" t="s">
+      <c r="GR7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="GS7" s="39" t="s">
+      <c r="GS7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="GT7" s="58" t="s">
+      <c r="GT7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="GU7" s="43" t="s">
+      <c r="GU7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="GV7" s="39" t="s">
+      <c r="GV7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="GW7" s="58" t="s">
+      <c r="GW7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="GX7" s="43" t="s">
+      <c r="GX7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="GY7" s="39" t="s">
+      <c r="GY7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="GZ7" s="58" t="s">
+      <c r="GZ7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="HA7" s="43" t="s">
+      <c r="HA7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="HB7" s="39" t="s">
+      <c r="HB7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="HC7" s="58" t="s">
+      <c r="HC7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="HD7" s="43" t="s">
+      <c r="HD7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="HE7" s="39" t="s">
+      <c r="HE7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="HF7" s="58" t="s">
+      <c r="HF7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="HG7" s="43" t="s">
+      <c r="HG7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="HH7" s="39" t="s">
+      <c r="HH7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="HI7" s="58" t="s">
+      <c r="HI7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="HJ7" s="43" t="s">
+      <c r="HJ7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="HK7" s="39" t="s">
+      <c r="HK7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="HL7" s="58" t="s">
+      <c r="HL7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="HM7" s="43" t="s">
+      <c r="HM7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="HN7" s="39" t="s">
+      <c r="HN7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="HO7" s="58" t="s">
+      <c r="HO7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="HP7" s="43" t="s">
+      <c r="HP7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="HQ7" s="39" t="s">
+      <c r="HQ7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="HR7" s="43" t="s">
+      <c r="HR7" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="HS7" s="43" t="s">
+      <c r="HS7" s="39" t="s">
         <v>755</v>
       </c>
-      <c r="HT7" s="59" t="s">
+      <c r="HT7" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="HU7" s="53" t="s">
+      <c r="HU7" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="HV7" s="43" t="s">
+      <c r="HV7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="HW7" s="39" t="s">
+      <c r="HW7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="HX7" s="58" t="s">
+      <c r="HX7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="HY7" s="43" t="s">
+      <c r="HY7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="HZ7" s="39" t="s">
+      <c r="HZ7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="IA7" s="58" t="s">
+      <c r="IA7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="IB7" s="43" t="s">
+      <c r="IB7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="IC7" s="39" t="s">
+      <c r="IC7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="ID7" s="58" t="s">
+      <c r="ID7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="IE7" s="43" t="s">
+      <c r="IE7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="IF7" s="39" t="s">
+      <c r="IF7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="IG7" s="58" t="s">
+      <c r="IG7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="IH7" s="43" t="s">
+      <c r="IH7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="II7" s="39" t="s">
+      <c r="II7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="IJ7" s="58" t="s">
+      <c r="IJ7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="IK7" s="43" t="s">
+      <c r="IK7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="IL7" s="39" t="s">
+      <c r="IL7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="IM7" s="58" t="s">
+      <c r="IM7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="IN7" s="43" t="s">
+      <c r="IN7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="IO7" s="39" t="s">
+      <c r="IO7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="IP7" s="58" t="s">
+      <c r="IP7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="IQ7" s="43" t="s">
+      <c r="IQ7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="IR7" s="39" t="s">
+      <c r="IR7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="IS7" s="58" t="s">
+      <c r="IS7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="IT7" s="43" t="s">
+      <c r="IT7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="IU7" s="39" t="s">
+      <c r="IU7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="IV7" s="58" t="s">
+      <c r="IV7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="IW7" s="43" t="s">
+      <c r="IW7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="IX7" s="39" t="s">
+      <c r="IX7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="IY7" s="58" t="s">
+      <c r="IY7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="IZ7" s="43" t="s">
+      <c r="IZ7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="JA7" s="39" t="s">
+      <c r="JA7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="JB7" s="43" t="s">
+      <c r="JB7" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="JC7" s="43" t="s">
+      <c r="JC7" s="39" t="s">
         <v>755</v>
       </c>
-      <c r="JD7" s="59" t="s">
+      <c r="JD7" s="44" t="s">
         <v>52</v>
       </c>
-      <c r="JE7" s="53" t="s">
+      <c r="JE7" s="46" t="s">
         <v>51</v>
       </c>
-      <c r="JF7" s="43" t="s">
+      <c r="JF7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="JG7" s="39" t="s">
+      <c r="JG7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="JH7" s="58" t="s">
+      <c r="JH7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="JI7" s="43" t="s">
+      <c r="JI7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="JJ7" s="39" t="s">
+      <c r="JJ7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="JK7" s="58" t="s">
+      <c r="JK7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="JL7" s="43" t="s">
+      <c r="JL7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="JM7" s="39" t="s">
+      <c r="JM7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="JN7" s="58" t="s">
+      <c r="JN7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="JO7" s="43" t="s">
+      <c r="JO7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="JP7" s="39" t="s">
+      <c r="JP7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="JQ7" s="58" t="s">
+      <c r="JQ7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="JR7" s="43" t="s">
+      <c r="JR7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="JS7" s="39" t="s">
+      <c r="JS7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="JT7" s="58" t="s">
+      <c r="JT7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="JU7" s="43" t="s">
+      <c r="JU7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="JV7" s="39" t="s">
+      <c r="JV7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="JW7" s="58" t="s">
+      <c r="JW7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="JX7" s="43" t="s">
+      <c r="JX7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="JY7" s="39" t="s">
+      <c r="JY7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="JZ7" s="58" t="s">
+      <c r="JZ7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="KA7" s="43" t="s">
+      <c r="KA7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="KB7" s="39" t="s">
+      <c r="KB7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="KC7" s="58" t="s">
+      <c r="KC7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="KD7" s="43" t="s">
+      <c r="KD7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="KE7" s="39" t="s">
+      <c r="KE7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="KF7" s="58" t="s">
+      <c r="KF7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="KG7" s="43" t="s">
+      <c r="KG7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="KH7" s="39" t="s">
+      <c r="KH7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="KI7" s="58" t="s">
+      <c r="KI7" s="37" t="s">
         <v>51</v>
       </c>
-      <c r="KJ7" s="43" t="s">
+      <c r="KJ7" s="39" t="s">
         <v>754</v>
       </c>
-      <c r="KK7" s="39" t="s">
+      <c r="KK7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="KL7" s="43" t="s">
+      <c r="KL7" s="39" t="s">
         <v>53</v>
       </c>
-      <c r="KM7" s="43" t="s">
+      <c r="KM7" s="39" t="s">
         <v>755</v>
       </c>
-      <c r="KN7" s="39" t="s">
+      <c r="KN7" s="40" t="s">
         <v>52</v>
       </c>
-      <c r="KO7" s="107"/>
-      <c r="KP7" s="40"/>
-      <c r="KQ7" s="76"/>
-      <c r="KR7" s="48"/>
-      <c r="KS7" s="48"/>
-      <c r="KT7" s="77"/>
-      <c r="KU7" s="35" t="s">
+      <c r="KO7" s="114"/>
+      <c r="KP7" s="41"/>
+      <c r="KQ7" s="70"/>
+      <c r="KR7" s="71"/>
+      <c r="KS7" s="71"/>
+      <c r="KT7" s="72"/>
+      <c r="KU7" s="42" t="s">
         <v>54</v>
       </c>
-      <c r="KV7" s="37"/>
-      <c r="KW7" s="35" t="s">
+      <c r="KV7" s="43"/>
+      <c r="KW7" s="42" t="s">
         <v>47</v>
       </c>
-      <c r="KX7" s="36"/>
-      <c r="KY7" s="36"/>
-      <c r="KZ7" s="37"/>
-      <c r="LA7" s="35" t="s">
+      <c r="KX7" s="99"/>
+      <c r="KY7" s="99"/>
+      <c r="KZ7" s="43"/>
+      <c r="LA7" s="42" t="s">
         <v>55</v>
       </c>
-      <c r="LB7" s="37"/>
-      <c r="LC7" s="35" t="s">
+      <c r="LB7" s="43"/>
+      <c r="LC7" s="42" t="s">
         <v>47</v>
       </c>
-      <c r="LD7" s="36"/>
-      <c r="LE7" s="36"/>
-      <c r="LF7" s="37"/>
-      <c r="LG7" s="40"/>
-      <c r="LH7" s="40"/>
-      <c r="LI7" s="76"/>
-      <c r="LJ7" s="48"/>
-      <c r="LK7" s="48"/>
-      <c r="LL7" s="77"/>
-      <c r="LM7" s="35" t="s">
+      <c r="LD7" s="99"/>
+      <c r="LE7" s="99"/>
+      <c r="LF7" s="43"/>
+      <c r="LG7" s="41"/>
+      <c r="LH7" s="41"/>
+      <c r="LI7" s="70"/>
+      <c r="LJ7" s="71"/>
+      <c r="LK7" s="71"/>
+      <c r="LL7" s="72"/>
+      <c r="LM7" s="42" t="s">
         <v>56</v>
       </c>
-      <c r="LN7" s="37"/>
-      <c r="LO7" s="35" t="s">
+      <c r="LN7" s="43"/>
+      <c r="LO7" s="42" t="s">
         <v>47</v>
       </c>
-      <c r="LP7" s="36"/>
-      <c r="LQ7" s="36"/>
-      <c r="LR7" s="37"/>
-      <c r="LS7" s="43" t="s">
+      <c r="LP7" s="99"/>
+      <c r="LQ7" s="99"/>
+      <c r="LR7" s="43"/>
+      <c r="LS7" s="39" t="s">
         <v>56</v>
       </c>
-      <c r="LT7" s="43"/>
-      <c r="LU7" s="35" t="s">
+      <c r="LT7" s="39"/>
+      <c r="LU7" s="42" t="s">
         <v>47</v>
       </c>
-      <c r="LV7" s="36"/>
-      <c r="LW7" s="36"/>
-      <c r="LX7" s="37"/>
-      <c r="LY7" s="58"/>
-      <c r="LZ7" s="58"/>
-      <c r="MA7" s="43"/>
-      <c r="MB7" s="43"/>
-      <c r="MC7" s="43"/>
-      <c r="MD7" s="43"/>
-      <c r="ME7" s="58"/>
-      <c r="MF7" s="58"/>
-      <c r="MG7" s="43"/>
-      <c r="MH7" s="43"/>
-      <c r="MI7" s="43"/>
-      <c r="MJ7" s="43"/>
-      <c r="MK7" s="34"/>
-      <c r="ML7" s="34"/>
-      <c r="MM7" s="76"/>
-      <c r="MN7" s="48"/>
-      <c r="MO7" s="48"/>
-      <c r="MP7" s="77"/>
-      <c r="MQ7" s="52" t="s">
+      <c r="LV7" s="99"/>
+      <c r="LW7" s="99"/>
+      <c r="LX7" s="43"/>
+      <c r="LY7" s="37"/>
+      <c r="LZ7" s="37"/>
+      <c r="MA7" s="39"/>
+      <c r="MB7" s="39"/>
+      <c r="MC7" s="39"/>
+      <c r="MD7" s="39"/>
+      <c r="ME7" s="37"/>
+      <c r="MF7" s="37"/>
+      <c r="MG7" s="39"/>
+      <c r="MH7" s="39"/>
+      <c r="MI7" s="39"/>
+      <c r="MJ7" s="39"/>
+      <c r="MK7" s="63"/>
+      <c r="ML7" s="63"/>
+      <c r="MM7" s="70"/>
+      <c r="MN7" s="71"/>
+      <c r="MO7" s="71"/>
+      <c r="MP7" s="72"/>
+      <c r="MQ7" s="126" t="s">
         <v>56</v>
       </c>
-      <c r="MR7" s="53"/>
-      <c r="MS7" s="35" t="s">
+      <c r="MR7" s="46"/>
+      <c r="MS7" s="42" t="s">
         <v>47</v>
       </c>
-      <c r="MT7" s="36"/>
-      <c r="MU7" s="36"/>
-      <c r="MV7" s="37"/>
-      <c r="MW7" s="52" t="s">
+      <c r="MT7" s="99"/>
+      <c r="MU7" s="99"/>
+      <c r="MV7" s="43"/>
+      <c r="MW7" s="126" t="s">
         <v>56</v>
       </c>
-      <c r="MX7" s="53"/>
-      <c r="MY7" s="35" t="s">
+      <c r="MX7" s="46"/>
+      <c r="MY7" s="42" t="s">
         <v>47</v>
       </c>
-      <c r="MZ7" s="36"/>
-      <c r="NA7" s="36"/>
-      <c r="NB7" s="37"/>
-      <c r="NC7" s="52" t="s">
+      <c r="MZ7" s="99"/>
+      <c r="NA7" s="99"/>
+      <c r="NB7" s="43"/>
+      <c r="NC7" s="126" t="s">
         <v>56</v>
       </c>
-      <c r="ND7" s="53"/>
-      <c r="NE7" s="35" t="s">
+      <c r="ND7" s="46"/>
+      <c r="NE7" s="42" t="s">
         <v>47</v>
       </c>
-      <c r="NF7" s="36"/>
-      <c r="NG7" s="36"/>
-      <c r="NH7" s="36"/>
-      <c r="NI7" s="93"/>
-      <c r="NJ7" s="58"/>
-      <c r="NK7" s="43"/>
-      <c r="NL7" s="43"/>
-      <c r="NM7" s="43"/>
-      <c r="NN7" s="43"/>
-      <c r="NO7" s="52" t="s">
+      <c r="NF7" s="99"/>
+      <c r="NG7" s="99"/>
+      <c r="NH7" s="99"/>
+      <c r="NI7" s="102"/>
+      <c r="NJ7" s="37"/>
+      <c r="NK7" s="39"/>
+      <c r="NL7" s="39"/>
+      <c r="NM7" s="39"/>
+      <c r="NN7" s="39"/>
+      <c r="NO7" s="126" t="s">
         <v>56</v>
       </c>
-      <c r="NP7" s="53"/>
-      <c r="NQ7" s="35" t="s">
+      <c r="NP7" s="46"/>
+      <c r="NQ7" s="42" t="s">
         <v>47</v>
       </c>
-      <c r="NR7" s="36"/>
-      <c r="NS7" s="36"/>
-      <c r="NT7" s="37"/>
-      <c r="NU7" s="52" t="s">
+      <c r="NR7" s="99"/>
+      <c r="NS7" s="99"/>
+      <c r="NT7" s="43"/>
+      <c r="NU7" s="126" t="s">
         <v>56</v>
       </c>
-      <c r="NV7" s="53"/>
-      <c r="NW7" s="35" t="s">
+      <c r="NV7" s="46"/>
+      <c r="NW7" s="42" t="s">
         <v>47</v>
       </c>
-      <c r="NX7" s="36"/>
-      <c r="NY7" s="36"/>
-      <c r="NZ7" s="38"/>
-      <c r="OA7" s="54" t="s">
+      <c r="NX7" s="99"/>
+      <c r="NY7" s="99"/>
+      <c r="NZ7" s="127"/>
+      <c r="OA7" s="128" t="s">
         <v>57</v>
       </c>
-      <c r="OB7" s="41" t="s">
+      <c r="OB7" s="124" t="s">
         <v>58</v>
       </c>
-      <c r="OC7" s="41" t="s">
+      <c r="OC7" s="124" t="s">
         <v>57</v>
       </c>
-      <c r="OD7" s="41" t="s">
+      <c r="OD7" s="124" t="s">
         <v>58</v>
       </c>
-      <c r="OE7" s="41" t="s">
+      <c r="OE7" s="124" t="s">
         <v>57</v>
       </c>
-      <c r="OF7" s="41" t="s">
+      <c r="OF7" s="124" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:396" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="51"/>
-      <c r="B8" s="51"/>
-      <c r="C8" s="51"/>
-      <c r="D8" s="51"/>
+      <c r="A8" s="49"/>
+      <c r="B8" s="49"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="49"/>
       <c r="E8" s="7"/>
-      <c r="F8" s="51"/>
+      <c r="F8" s="49"/>
       <c r="G8" s="7"/>
-      <c r="H8" s="51"/>
-      <c r="I8" s="51"/>
-      <c r="J8" s="50" t="s">
+      <c r="H8" s="49"/>
+      <c r="I8" s="49"/>
+      <c r="J8" s="48" t="s">
         <v>59</v>
       </c>
-      <c r="K8" s="50" t="s">
+      <c r="K8" s="48" t="s">
         <v>60</v>
       </c>
-      <c r="L8" s="50" t="s">
+      <c r="L8" s="48" t="s">
         <v>61</v>
       </c>
-      <c r="M8" s="58"/>
-      <c r="N8" s="43"/>
-      <c r="O8" s="40"/>
-      <c r="P8" s="58"/>
-      <c r="Q8" s="43"/>
-      <c r="R8" s="40"/>
-      <c r="S8" s="58"/>
-      <c r="T8" s="43"/>
-      <c r="U8" s="40"/>
-      <c r="V8" s="58"/>
-      <c r="W8" s="43"/>
-      <c r="X8" s="40"/>
-      <c r="Y8" s="58"/>
-      <c r="Z8" s="43"/>
-      <c r="AA8" s="40"/>
-      <c r="AB8" s="58"/>
-      <c r="AC8" s="43"/>
-      <c r="AD8" s="40"/>
-      <c r="AE8" s="58"/>
-      <c r="AF8" s="43"/>
-      <c r="AG8" s="40"/>
-      <c r="AH8" s="58"/>
-      <c r="AI8" s="43"/>
-      <c r="AJ8" s="40"/>
-      <c r="AK8" s="58"/>
-      <c r="AL8" s="43"/>
-      <c r="AM8" s="40"/>
-      <c r="AN8" s="58"/>
-      <c r="AO8" s="43"/>
-      <c r="AP8" s="40"/>
-      <c r="AQ8" s="58"/>
-      <c r="AR8" s="43"/>
-      <c r="AS8" s="40"/>
-      <c r="AT8" s="43"/>
-      <c r="AU8" s="43"/>
-      <c r="AV8" s="60"/>
-      <c r="AW8" s="53"/>
-      <c r="AX8" s="43"/>
-      <c r="AY8" s="40"/>
-      <c r="AZ8" s="58"/>
-      <c r="BA8" s="43"/>
-      <c r="BB8" s="40"/>
-      <c r="BC8" s="58"/>
-      <c r="BD8" s="43"/>
-      <c r="BE8" s="40"/>
-      <c r="BF8" s="58"/>
-      <c r="BG8" s="43"/>
-      <c r="BH8" s="40"/>
-      <c r="BI8" s="58"/>
-      <c r="BJ8" s="43"/>
-      <c r="BK8" s="40"/>
-      <c r="BL8" s="58"/>
-      <c r="BM8" s="43"/>
-      <c r="BN8" s="40"/>
-      <c r="BO8" s="58"/>
-      <c r="BP8" s="43"/>
-      <c r="BQ8" s="40"/>
-      <c r="BR8" s="58"/>
-      <c r="BS8" s="43"/>
-      <c r="BT8" s="40"/>
-      <c r="BU8" s="58"/>
-      <c r="BV8" s="43"/>
-      <c r="BW8" s="40"/>
-      <c r="BX8" s="58"/>
-      <c r="BY8" s="43"/>
-      <c r="BZ8" s="40"/>
-      <c r="CA8" s="58"/>
-      <c r="CB8" s="43"/>
-      <c r="CC8" s="40"/>
-      <c r="CD8" s="43"/>
-      <c r="CE8" s="43"/>
-      <c r="CF8" s="60"/>
-      <c r="CG8" s="53"/>
-      <c r="CH8" s="43"/>
-      <c r="CI8" s="40"/>
-      <c r="CJ8" s="58"/>
-      <c r="CK8" s="43"/>
-      <c r="CL8" s="40"/>
-      <c r="CM8" s="58"/>
-      <c r="CN8" s="43"/>
-      <c r="CO8" s="40"/>
-      <c r="CP8" s="58"/>
-      <c r="CQ8" s="43"/>
-      <c r="CR8" s="40"/>
-      <c r="CS8" s="58"/>
-      <c r="CT8" s="43"/>
-      <c r="CU8" s="40"/>
-      <c r="CV8" s="58"/>
-      <c r="CW8" s="43"/>
-      <c r="CX8" s="40"/>
-      <c r="CY8" s="58"/>
-      <c r="CZ8" s="43"/>
-      <c r="DA8" s="40"/>
-      <c r="DB8" s="58"/>
-      <c r="DC8" s="43"/>
-      <c r="DD8" s="40"/>
-      <c r="DE8" s="58"/>
-      <c r="DF8" s="43"/>
-      <c r="DG8" s="40"/>
-      <c r="DH8" s="58"/>
-      <c r="DI8" s="43"/>
-      <c r="DJ8" s="40"/>
-      <c r="DK8" s="58"/>
-      <c r="DL8" s="43"/>
-      <c r="DM8" s="40"/>
-      <c r="DN8" s="43"/>
-      <c r="DO8" s="43"/>
-      <c r="DP8" s="60"/>
-      <c r="DQ8" s="53"/>
-      <c r="DR8" s="43"/>
-      <c r="DS8" s="40"/>
-      <c r="DT8" s="58"/>
-      <c r="DU8" s="43"/>
-      <c r="DV8" s="40"/>
-      <c r="DW8" s="58"/>
-      <c r="DX8" s="43"/>
-      <c r="DY8" s="40"/>
-      <c r="DZ8" s="58"/>
-      <c r="EA8" s="43"/>
-      <c r="EB8" s="40"/>
-      <c r="EC8" s="58"/>
-      <c r="ED8" s="43"/>
-      <c r="EE8" s="40"/>
-      <c r="EF8" s="58"/>
-      <c r="EG8" s="43"/>
-      <c r="EH8" s="40"/>
-      <c r="EI8" s="58"/>
-      <c r="EJ8" s="43"/>
-      <c r="EK8" s="40"/>
-      <c r="EL8" s="58"/>
-      <c r="EM8" s="43"/>
-      <c r="EN8" s="40"/>
-      <c r="EO8" s="58"/>
-      <c r="EP8" s="43"/>
-      <c r="EQ8" s="40"/>
-      <c r="ER8" s="58"/>
-      <c r="ES8" s="43"/>
-      <c r="ET8" s="40"/>
-      <c r="EU8" s="58"/>
-      <c r="EV8" s="43"/>
-      <c r="EW8" s="40"/>
-      <c r="EX8" s="43"/>
-      <c r="EY8" s="43"/>
-      <c r="EZ8" s="60"/>
-      <c r="FA8" s="53"/>
-      <c r="FB8" s="43"/>
-      <c r="FC8" s="40"/>
-      <c r="FD8" s="58"/>
-      <c r="FE8" s="43"/>
-      <c r="FF8" s="40"/>
-      <c r="FG8" s="58"/>
-      <c r="FH8" s="43"/>
-      <c r="FI8" s="40"/>
-      <c r="FJ8" s="58"/>
-      <c r="FK8" s="43"/>
-      <c r="FL8" s="40"/>
-      <c r="FM8" s="58"/>
-      <c r="FN8" s="43"/>
-      <c r="FO8" s="40"/>
-      <c r="FP8" s="58"/>
-      <c r="FQ8" s="43"/>
-      <c r="FR8" s="40"/>
-      <c r="FS8" s="58"/>
-      <c r="FT8" s="43"/>
-      <c r="FU8" s="40"/>
-      <c r="FV8" s="58"/>
-      <c r="FW8" s="43"/>
-      <c r="FX8" s="40"/>
-      <c r="FY8" s="58"/>
-      <c r="FZ8" s="43"/>
-      <c r="GA8" s="40"/>
-      <c r="GB8" s="58"/>
-      <c r="GC8" s="43"/>
-      <c r="GD8" s="40"/>
-      <c r="GE8" s="58"/>
-      <c r="GF8" s="43"/>
-      <c r="GG8" s="40"/>
-      <c r="GH8" s="43"/>
-      <c r="GI8" s="43"/>
-      <c r="GJ8" s="60"/>
-      <c r="GK8" s="53"/>
-      <c r="GL8" s="43"/>
-      <c r="GM8" s="40"/>
-      <c r="GN8" s="58"/>
-      <c r="GO8" s="43"/>
-      <c r="GP8" s="40"/>
-      <c r="GQ8" s="58"/>
-      <c r="GR8" s="43"/>
-      <c r="GS8" s="40"/>
-      <c r="GT8" s="58"/>
-      <c r="GU8" s="43"/>
-      <c r="GV8" s="40"/>
-      <c r="GW8" s="58"/>
-      <c r="GX8" s="43"/>
-      <c r="GY8" s="40"/>
-      <c r="GZ8" s="58"/>
-      <c r="HA8" s="43"/>
-      <c r="HB8" s="40"/>
-      <c r="HC8" s="58"/>
-      <c r="HD8" s="43"/>
-      <c r="HE8" s="40"/>
-      <c r="HF8" s="58"/>
-      <c r="HG8" s="43"/>
-      <c r="HH8" s="40"/>
-      <c r="HI8" s="58"/>
-      <c r="HJ8" s="43"/>
-      <c r="HK8" s="40"/>
-      <c r="HL8" s="58"/>
-      <c r="HM8" s="43"/>
-      <c r="HN8" s="40"/>
-      <c r="HO8" s="58"/>
-      <c r="HP8" s="43"/>
-      <c r="HQ8" s="40"/>
-      <c r="HR8" s="43"/>
-      <c r="HS8" s="43"/>
-      <c r="HT8" s="60"/>
-      <c r="HU8" s="53"/>
-      <c r="HV8" s="43"/>
-      <c r="HW8" s="40"/>
-      <c r="HX8" s="58"/>
-      <c r="HY8" s="43"/>
-      <c r="HZ8" s="40"/>
-      <c r="IA8" s="58"/>
-      <c r="IB8" s="43"/>
-      <c r="IC8" s="40"/>
-      <c r="ID8" s="58"/>
-      <c r="IE8" s="43"/>
-      <c r="IF8" s="40"/>
-      <c r="IG8" s="58"/>
-      <c r="IH8" s="43"/>
-      <c r="II8" s="40"/>
-      <c r="IJ8" s="58"/>
-      <c r="IK8" s="43"/>
-      <c r="IL8" s="40"/>
-      <c r="IM8" s="58"/>
-      <c r="IN8" s="43"/>
-      <c r="IO8" s="40"/>
-      <c r="IP8" s="58"/>
-      <c r="IQ8" s="43"/>
-      <c r="IR8" s="40"/>
-      <c r="IS8" s="58"/>
-      <c r="IT8" s="43"/>
-      <c r="IU8" s="40"/>
-      <c r="IV8" s="58"/>
-      <c r="IW8" s="43"/>
-      <c r="IX8" s="40"/>
-      <c r="IY8" s="58"/>
-      <c r="IZ8" s="43"/>
-      <c r="JA8" s="40"/>
-      <c r="JB8" s="43"/>
-      <c r="JC8" s="43"/>
-      <c r="JD8" s="60"/>
-      <c r="JE8" s="53"/>
-      <c r="JF8" s="43"/>
-      <c r="JG8" s="40"/>
-      <c r="JH8" s="58"/>
-      <c r="JI8" s="43"/>
-      <c r="JJ8" s="40"/>
-      <c r="JK8" s="58"/>
-      <c r="JL8" s="43"/>
-      <c r="JM8" s="40"/>
-      <c r="JN8" s="58"/>
-      <c r="JO8" s="43"/>
-      <c r="JP8" s="40"/>
-      <c r="JQ8" s="58"/>
-      <c r="JR8" s="43"/>
-      <c r="JS8" s="40"/>
-      <c r="JT8" s="58"/>
-      <c r="JU8" s="43"/>
-      <c r="JV8" s="40"/>
-      <c r="JW8" s="58"/>
-      <c r="JX8" s="43"/>
-      <c r="JY8" s="40"/>
-      <c r="JZ8" s="58"/>
-      <c r="KA8" s="43"/>
-      <c r="KB8" s="40"/>
-      <c r="KC8" s="58"/>
-      <c r="KD8" s="43"/>
-      <c r="KE8" s="40"/>
-      <c r="KF8" s="58"/>
-      <c r="KG8" s="43"/>
-      <c r="KH8" s="40"/>
-      <c r="KI8" s="58"/>
-      <c r="KJ8" s="43"/>
-      <c r="KK8" s="40"/>
-      <c r="KL8" s="43"/>
-      <c r="KM8" s="43"/>
-      <c r="KN8" s="40"/>
-      <c r="KO8" s="107"/>
-      <c r="KP8" s="40"/>
-      <c r="KQ8" s="33" t="s">
+      <c r="M8" s="37"/>
+      <c r="N8" s="39"/>
+      <c r="O8" s="41"/>
+      <c r="P8" s="37"/>
+      <c r="Q8" s="39"/>
+      <c r="R8" s="41"/>
+      <c r="S8" s="37"/>
+      <c r="T8" s="39"/>
+      <c r="U8" s="41"/>
+      <c r="V8" s="37"/>
+      <c r="W8" s="39"/>
+      <c r="X8" s="41"/>
+      <c r="Y8" s="37"/>
+      <c r="Z8" s="39"/>
+      <c r="AA8" s="41"/>
+      <c r="AB8" s="37"/>
+      <c r="AC8" s="39"/>
+      <c r="AD8" s="41"/>
+      <c r="AE8" s="37"/>
+      <c r="AF8" s="39"/>
+      <c r="AG8" s="41"/>
+      <c r="AH8" s="37"/>
+      <c r="AI8" s="39"/>
+      <c r="AJ8" s="41"/>
+      <c r="AK8" s="37"/>
+      <c r="AL8" s="39"/>
+      <c r="AM8" s="41"/>
+      <c r="AN8" s="37"/>
+      <c r="AO8" s="39"/>
+      <c r="AP8" s="41"/>
+      <c r="AQ8" s="37"/>
+      <c r="AR8" s="39"/>
+      <c r="AS8" s="41"/>
+      <c r="AT8" s="39"/>
+      <c r="AU8" s="39"/>
+      <c r="AV8" s="45"/>
+      <c r="AW8" s="46"/>
+      <c r="AX8" s="39"/>
+      <c r="AY8" s="41"/>
+      <c r="AZ8" s="37"/>
+      <c r="BA8" s="39"/>
+      <c r="BB8" s="41"/>
+      <c r="BC8" s="37"/>
+      <c r="BD8" s="39"/>
+      <c r="BE8" s="41"/>
+      <c r="BF8" s="37"/>
+      <c r="BG8" s="39"/>
+      <c r="BH8" s="41"/>
+      <c r="BI8" s="37"/>
+      <c r="BJ8" s="39"/>
+      <c r="BK8" s="41"/>
+      <c r="BL8" s="37"/>
+      <c r="BM8" s="39"/>
+      <c r="BN8" s="41"/>
+      <c r="BO8" s="37"/>
+      <c r="BP8" s="39"/>
+      <c r="BQ8" s="41"/>
+      <c r="BR8" s="37"/>
+      <c r="BS8" s="39"/>
+      <c r="BT8" s="41"/>
+      <c r="BU8" s="37"/>
+      <c r="BV8" s="39"/>
+      <c r="BW8" s="41"/>
+      <c r="BX8" s="37"/>
+      <c r="BY8" s="39"/>
+      <c r="BZ8" s="41"/>
+      <c r="CA8" s="37"/>
+      <c r="CB8" s="39"/>
+      <c r="CC8" s="41"/>
+      <c r="CD8" s="39"/>
+      <c r="CE8" s="39"/>
+      <c r="CF8" s="45"/>
+      <c r="CG8" s="46"/>
+      <c r="CH8" s="39"/>
+      <c r="CI8" s="41"/>
+      <c r="CJ8" s="37"/>
+      <c r="CK8" s="39"/>
+      <c r="CL8" s="41"/>
+      <c r="CM8" s="37"/>
+      <c r="CN8" s="39"/>
+      <c r="CO8" s="41"/>
+      <c r="CP8" s="37"/>
+      <c r="CQ8" s="39"/>
+      <c r="CR8" s="41"/>
+      <c r="CS8" s="37"/>
+      <c r="CT8" s="39"/>
+      <c r="CU8" s="41"/>
+      <c r="CV8" s="37"/>
+      <c r="CW8" s="39"/>
+      <c r="CX8" s="41"/>
+      <c r="CY8" s="37"/>
+      <c r="CZ8" s="39"/>
+      <c r="DA8" s="41"/>
+      <c r="DB8" s="37"/>
+      <c r="DC8" s="39"/>
+      <c r="DD8" s="41"/>
+      <c r="DE8" s="37"/>
+      <c r="DF8" s="39"/>
+      <c r="DG8" s="41"/>
+      <c r="DH8" s="37"/>
+      <c r="DI8" s="39"/>
+      <c r="DJ8" s="41"/>
+      <c r="DK8" s="37"/>
+      <c r="DL8" s="39"/>
+      <c r="DM8" s="41"/>
+      <c r="DN8" s="39"/>
+      <c r="DO8" s="39"/>
+      <c r="DP8" s="45"/>
+      <c r="DQ8" s="46"/>
+      <c r="DR8" s="39"/>
+      <c r="DS8" s="41"/>
+      <c r="DT8" s="37"/>
+      <c r="DU8" s="39"/>
+      <c r="DV8" s="41"/>
+      <c r="DW8" s="37"/>
+      <c r="DX8" s="39"/>
+      <c r="DY8" s="41"/>
+      <c r="DZ8" s="37"/>
+      <c r="EA8" s="39"/>
+      <c r="EB8" s="41"/>
+      <c r="EC8" s="37"/>
+      <c r="ED8" s="39"/>
+      <c r="EE8" s="41"/>
+      <c r="EF8" s="37"/>
+      <c r="EG8" s="39"/>
+      <c r="EH8" s="41"/>
+      <c r="EI8" s="37"/>
+      <c r="EJ8" s="39"/>
+      <c r="EK8" s="41"/>
+      <c r="EL8" s="37"/>
+      <c r="EM8" s="39"/>
+      <c r="EN8" s="41"/>
+      <c r="EO8" s="37"/>
+      <c r="EP8" s="39"/>
+      <c r="EQ8" s="41"/>
+      <c r="ER8" s="37"/>
+      <c r="ES8" s="39"/>
+      <c r="ET8" s="41"/>
+      <c r="EU8" s="37"/>
+      <c r="EV8" s="39"/>
+      <c r="EW8" s="41"/>
+      <c r="EX8" s="39"/>
+      <c r="EY8" s="39"/>
+      <c r="EZ8" s="45"/>
+      <c r="FA8" s="46"/>
+      <c r="FB8" s="39"/>
+      <c r="FC8" s="41"/>
+      <c r="FD8" s="37"/>
+      <c r="FE8" s="39"/>
+      <c r="FF8" s="41"/>
+      <c r="FG8" s="37"/>
+      <c r="FH8" s="39"/>
+      <c r="FI8" s="41"/>
+      <c r="FJ8" s="37"/>
+      <c r="FK8" s="39"/>
+      <c r="FL8" s="41"/>
+      <c r="FM8" s="37"/>
+      <c r="FN8" s="39"/>
+      <c r="FO8" s="41"/>
+      <c r="FP8" s="37"/>
+      <c r="FQ8" s="39"/>
+      <c r="FR8" s="41"/>
+      <c r="FS8" s="37"/>
+      <c r="FT8" s="39"/>
+      <c r="FU8" s="41"/>
+      <c r="FV8" s="37"/>
+      <c r="FW8" s="39"/>
+      <c r="FX8" s="41"/>
+      <c r="FY8" s="37"/>
+      <c r="FZ8" s="39"/>
+      <c r="GA8" s="41"/>
+      <c r="GB8" s="37"/>
+      <c r="GC8" s="39"/>
+      <c r="GD8" s="41"/>
+      <c r="GE8" s="37"/>
+      <c r="GF8" s="39"/>
+      <c r="GG8" s="41"/>
+      <c r="GH8" s="39"/>
+      <c r="GI8" s="39"/>
+      <c r="GJ8" s="45"/>
+      <c r="GK8" s="46"/>
+      <c r="GL8" s="39"/>
+      <c r="GM8" s="41"/>
+      <c r="GN8" s="37"/>
+      <c r="GO8" s="39"/>
+      <c r="GP8" s="41"/>
+      <c r="GQ8" s="37"/>
+      <c r="GR8" s="39"/>
+      <c r="GS8" s="41"/>
+      <c r="GT8" s="37"/>
+      <c r="GU8" s="39"/>
+      <c r="GV8" s="41"/>
+      <c r="GW8" s="37"/>
+      <c r="GX8" s="39"/>
+      <c r="GY8" s="41"/>
+      <c r="GZ8" s="37"/>
+      <c r="HA8" s="39"/>
+      <c r="HB8" s="41"/>
+      <c r="HC8" s="37"/>
+      <c r="HD8" s="39"/>
+      <c r="HE8" s="41"/>
+      <c r="HF8" s="37"/>
+      <c r="HG8" s="39"/>
+      <c r="HH8" s="41"/>
+      <c r="HI8" s="37"/>
+      <c r="HJ8" s="39"/>
+      <c r="HK8" s="41"/>
+      <c r="HL8" s="37"/>
+      <c r="HM8" s="39"/>
+      <c r="HN8" s="41"/>
+      <c r="HO8" s="37"/>
+      <c r="HP8" s="39"/>
+      <c r="HQ8" s="41"/>
+      <c r="HR8" s="39"/>
+      <c r="HS8" s="39"/>
+      <c r="HT8" s="45"/>
+      <c r="HU8" s="46"/>
+      <c r="HV8" s="39"/>
+      <c r="HW8" s="41"/>
+      <c r="HX8" s="37"/>
+      <c r="HY8" s="39"/>
+      <c r="HZ8" s="41"/>
+      <c r="IA8" s="37"/>
+      <c r="IB8" s="39"/>
+      <c r="IC8" s="41"/>
+      <c r="ID8" s="37"/>
+      <c r="IE8" s="39"/>
+      <c r="IF8" s="41"/>
+      <c r="IG8" s="37"/>
+      <c r="IH8" s="39"/>
+      <c r="II8" s="41"/>
+      <c r="IJ8" s="37"/>
+      <c r="IK8" s="39"/>
+      <c r="IL8" s="41"/>
+      <c r="IM8" s="37"/>
+      <c r="IN8" s="39"/>
+      <c r="IO8" s="41"/>
+      <c r="IP8" s="37"/>
+      <c r="IQ8" s="39"/>
+      <c r="IR8" s="41"/>
+      <c r="IS8" s="37"/>
+      <c r="IT8" s="39"/>
+      <c r="IU8" s="41"/>
+      <c r="IV8" s="37"/>
+      <c r="IW8" s="39"/>
+      <c r="IX8" s="41"/>
+      <c r="IY8" s="37"/>
+      <c r="IZ8" s="39"/>
+      <c r="JA8" s="41"/>
+      <c r="JB8" s="39"/>
+      <c r="JC8" s="39"/>
+      <c r="JD8" s="45"/>
+      <c r="JE8" s="46"/>
+      <c r="JF8" s="39"/>
+      <c r="JG8" s="41"/>
+      <c r="JH8" s="37"/>
+      <c r="JI8" s="39"/>
+      <c r="JJ8" s="41"/>
+      <c r="JK8" s="37"/>
+      <c r="JL8" s="39"/>
+      <c r="JM8" s="41"/>
+      <c r="JN8" s="37"/>
+      <c r="JO8" s="39"/>
+      <c r="JP8" s="41"/>
+      <c r="JQ8" s="37"/>
+      <c r="JR8" s="39"/>
+      <c r="JS8" s="41"/>
+      <c r="JT8" s="37"/>
+      <c r="JU8" s="39"/>
+      <c r="JV8" s="41"/>
+      <c r="JW8" s="37"/>
+      <c r="JX8" s="39"/>
+      <c r="JY8" s="41"/>
+      <c r="JZ8" s="37"/>
+      <c r="KA8" s="39"/>
+      <c r="KB8" s="41"/>
+      <c r="KC8" s="37"/>
+      <c r="KD8" s="39"/>
+      <c r="KE8" s="41"/>
+      <c r="KF8" s="37"/>
+      <c r="KG8" s="39"/>
+      <c r="KH8" s="41"/>
+      <c r="KI8" s="37"/>
+      <c r="KJ8" s="39"/>
+      <c r="KK8" s="41"/>
+      <c r="KL8" s="39"/>
+      <c r="KM8" s="39"/>
+      <c r="KN8" s="41"/>
+      <c r="KO8" s="114"/>
+      <c r="KP8" s="41"/>
+      <c r="KQ8" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="KR8" s="35" t="s">
+      <c r="KR8" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="KS8" s="36"/>
-      <c r="KT8" s="37"/>
-      <c r="KU8" s="39" t="s">
+      <c r="KS8" s="99"/>
+      <c r="KT8" s="43"/>
+      <c r="KU8" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="KV8" s="39" t="s">
+      <c r="KV8" s="40" t="s">
         <v>63</v>
       </c>
-      <c r="KW8" s="33" t="s">
+      <c r="KW8" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="KX8" s="35" t="s">
+      <c r="KX8" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="KY8" s="36"/>
-      <c r="KZ8" s="37"/>
-      <c r="LA8" s="39" t="s">
+      <c r="KY8" s="99"/>
+      <c r="KZ8" s="43"/>
+      <c r="LA8" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="LB8" s="39" t="s">
+      <c r="LB8" s="40" t="s">
         <v>63</v>
       </c>
-      <c r="LC8" s="33" t="s">
+      <c r="LC8" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="LD8" s="35" t="s">
+      <c r="LD8" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="LE8" s="36"/>
-      <c r="LF8" s="37"/>
-      <c r="LG8" s="40"/>
-      <c r="LH8" s="40"/>
-      <c r="LI8" s="33" t="s">
+      <c r="LE8" s="99"/>
+      <c r="LF8" s="43"/>
+      <c r="LG8" s="41"/>
+      <c r="LH8" s="41"/>
+      <c r="LI8" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="LJ8" s="35" t="s">
+      <c r="LJ8" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="LK8" s="36"/>
-      <c r="LL8" s="37"/>
-      <c r="LM8" s="39" t="s">
+      <c r="LK8" s="99"/>
+      <c r="LL8" s="43"/>
+      <c r="LM8" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="LN8" s="39" t="s">
+      <c r="LN8" s="40" t="s">
         <v>63</v>
       </c>
-      <c r="LO8" s="33" t="s">
+      <c r="LO8" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="LP8" s="35" t="s">
+      <c r="LP8" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="LQ8" s="36"/>
-      <c r="LR8" s="37"/>
-      <c r="LS8" s="39" t="s">
+      <c r="LQ8" s="99"/>
+      <c r="LR8" s="43"/>
+      <c r="LS8" s="40" t="s">
         <v>62</v>
       </c>
-      <c r="LT8" s="39" t="s">
+      <c r="LT8" s="40" t="s">
         <v>63</v>
       </c>
-      <c r="LU8" s="33" t="s">
+      <c r="LU8" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="LV8" s="35" t="s">
+      <c r="LV8" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="LW8" s="36"/>
-      <c r="LX8" s="37"/>
-      <c r="LY8" s="33" t="s">
+      <c r="LW8" s="99"/>
+      <c r="LX8" s="43"/>
+      <c r="LY8" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="LZ8" s="33" t="s">
+      <c r="LZ8" s="38" t="s">
         <v>63</v>
       </c>
-      <c r="MA8" s="33" t="s">
+      <c r="MA8" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="MB8" s="35" t="s">
+      <c r="MB8" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="MC8" s="36"/>
-      <c r="MD8" s="37"/>
-      <c r="ME8" s="33" t="s">
+      <c r="MC8" s="99"/>
+      <c r="MD8" s="43"/>
+      <c r="ME8" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="MF8" s="33" t="s">
+      <c r="MF8" s="38" t="s">
         <v>63</v>
       </c>
-      <c r="MG8" s="33" t="s">
+      <c r="MG8" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="MH8" s="35" t="s">
+      <c r="MH8" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="MI8" s="36"/>
-      <c r="MJ8" s="37"/>
-      <c r="MK8" s="34"/>
-      <c r="ML8" s="34"/>
-      <c r="MM8" s="33" t="s">
+      <c r="MI8" s="99"/>
+      <c r="MJ8" s="43"/>
+      <c r="MK8" s="63"/>
+      <c r="ML8" s="63"/>
+      <c r="MM8" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="MN8" s="35" t="s">
+      <c r="MN8" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="MO8" s="36"/>
-      <c r="MP8" s="37"/>
-      <c r="MQ8" s="33" t="s">
+      <c r="MO8" s="99"/>
+      <c r="MP8" s="43"/>
+      <c r="MQ8" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="MR8" s="33" t="s">
+      <c r="MR8" s="38" t="s">
         <v>63</v>
       </c>
-      <c r="MS8" s="33" t="s">
+      <c r="MS8" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="MT8" s="35" t="s">
+      <c r="MT8" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="MU8" s="36"/>
-      <c r="MV8" s="37"/>
-      <c r="MW8" s="33" t="s">
+      <c r="MU8" s="99"/>
+      <c r="MV8" s="43"/>
+      <c r="MW8" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="MX8" s="33" t="s">
+      <c r="MX8" s="38" t="s">
         <v>63</v>
       </c>
-      <c r="MY8" s="33" t="s">
+      <c r="MY8" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="MZ8" s="35" t="s">
+      <c r="MZ8" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="NA8" s="36"/>
-      <c r="NB8" s="37"/>
-      <c r="NC8" s="33" t="s">
+      <c r="NA8" s="99"/>
+      <c r="NB8" s="43"/>
+      <c r="NC8" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="ND8" s="33" t="s">
+      <c r="ND8" s="38" t="s">
         <v>63</v>
       </c>
-      <c r="NE8" s="33" t="s">
+      <c r="NE8" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="NF8" s="35" t="s">
+      <c r="NF8" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="NG8" s="36"/>
-      <c r="NH8" s="36"/>
-      <c r="NI8" s="93"/>
-      <c r="NJ8" s="58"/>
-      <c r="NK8" s="56" t="s">
+      <c r="NG8" s="99"/>
+      <c r="NH8" s="99"/>
+      <c r="NI8" s="102"/>
+      <c r="NJ8" s="37"/>
+      <c r="NK8" s="47" t="s">
         <v>62</v>
       </c>
-      <c r="NL8" s="35" t="s">
+      <c r="NL8" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="NM8" s="36"/>
-      <c r="NN8" s="37"/>
-      <c r="NO8" s="33" t="s">
+      <c r="NM8" s="99"/>
+      <c r="NN8" s="43"/>
+      <c r="NO8" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="NP8" s="33" t="s">
+      <c r="NP8" s="38" t="s">
         <v>63</v>
       </c>
-      <c r="NQ8" s="33" t="s">
+      <c r="NQ8" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="NR8" s="35" t="s">
+      <c r="NR8" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="NS8" s="36"/>
-      <c r="NT8" s="37"/>
-      <c r="NU8" s="33" t="s">
+      <c r="NS8" s="99"/>
+      <c r="NT8" s="43"/>
+      <c r="NU8" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="NV8" s="33" t="s">
+      <c r="NV8" s="38" t="s">
         <v>63</v>
       </c>
-      <c r="NW8" s="33" t="s">
+      <c r="NW8" s="38" t="s">
         <v>62</v>
       </c>
-      <c r="NX8" s="35" t="s">
+      <c r="NX8" s="42" t="s">
         <v>27</v>
       </c>
-      <c r="NY8" s="36"/>
-      <c r="NZ8" s="38"/>
-      <c r="OA8" s="55"/>
-      <c r="OB8" s="42"/>
-      <c r="OC8" s="42"/>
-      <c r="OD8" s="42"/>
-      <c r="OE8" s="42"/>
-      <c r="OF8" s="42"/>
+      <c r="NY8" s="99"/>
+      <c r="NZ8" s="127"/>
+      <c r="OA8" s="129"/>
+      <c r="OB8" s="125"/>
+      <c r="OC8" s="125"/>
+      <c r="OD8" s="125"/>
+      <c r="OE8" s="125"/>
+      <c r="OF8" s="125"/>
     </row>
     <row r="9" spans="1:396" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="51"/>
-      <c r="B9" s="51"/>
-      <c r="C9" s="51"/>
-      <c r="D9" s="51"/>
+      <c r="A9" s="49"/>
+      <c r="B9" s="49"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="49"/>
       <c r="E9" s="7"/>
-      <c r="F9" s="51"/>
+      <c r="F9" s="49"/>
       <c r="G9" s="7"/>
-      <c r="H9" s="51"/>
-      <c r="I9" s="51"/>
-      <c r="J9" s="51"/>
-      <c r="K9" s="51"/>
-      <c r="L9" s="51"/>
-      <c r="M9" s="33"/>
-      <c r="N9" s="39"/>
-      <c r="O9" s="40"/>
-      <c r="P9" s="33"/>
-      <c r="Q9" s="39"/>
-      <c r="R9" s="40"/>
-      <c r="S9" s="33"/>
-      <c r="T9" s="39"/>
-      <c r="U9" s="40"/>
-      <c r="V9" s="33"/>
-      <c r="W9" s="39"/>
-      <c r="X9" s="40"/>
-      <c r="Y9" s="33"/>
-      <c r="Z9" s="39"/>
-      <c r="AA9" s="40"/>
-      <c r="AB9" s="33"/>
-      <c r="AC9" s="39"/>
-      <c r="AD9" s="40"/>
-      <c r="AE9" s="33"/>
-      <c r="AF9" s="39"/>
-      <c r="AG9" s="40"/>
-      <c r="AH9" s="33"/>
-      <c r="AI9" s="39"/>
-      <c r="AJ9" s="40"/>
-      <c r="AK9" s="33"/>
-      <c r="AL9" s="39"/>
-      <c r="AM9" s="40"/>
-      <c r="AN9" s="33"/>
-      <c r="AO9" s="39"/>
-      <c r="AP9" s="40"/>
-      <c r="AQ9" s="33"/>
-      <c r="AR9" s="39"/>
-      <c r="AS9" s="40"/>
-      <c r="AT9" s="39"/>
-      <c r="AU9" s="39"/>
-      <c r="AV9" s="60"/>
-      <c r="AW9" s="56"/>
-      <c r="AX9" s="39"/>
-      <c r="AY9" s="40"/>
-      <c r="AZ9" s="33"/>
-      <c r="BA9" s="39"/>
-      <c r="BB9" s="40"/>
-      <c r="BC9" s="33"/>
-      <c r="BD9" s="39"/>
-      <c r="BE9" s="40"/>
-      <c r="BF9" s="33"/>
-      <c r="BG9" s="39"/>
-      <c r="BH9" s="40"/>
-      <c r="BI9" s="33"/>
-      <c r="BJ9" s="39"/>
-      <c r="BK9" s="40"/>
-      <c r="BL9" s="33"/>
-      <c r="BM9" s="39"/>
-      <c r="BN9" s="40"/>
-      <c r="BO9" s="33"/>
-      <c r="BP9" s="39"/>
-      <c r="BQ9" s="40"/>
-      <c r="BR9" s="33"/>
-      <c r="BS9" s="39"/>
-      <c r="BT9" s="40"/>
-      <c r="BU9" s="33"/>
-      <c r="BV9" s="39"/>
-      <c r="BW9" s="40"/>
-      <c r="BX9" s="33"/>
-      <c r="BY9" s="39"/>
-      <c r="BZ9" s="40"/>
-      <c r="CA9" s="33"/>
-      <c r="CB9" s="39"/>
-      <c r="CC9" s="40"/>
-      <c r="CD9" s="39"/>
-      <c r="CE9" s="39"/>
-      <c r="CF9" s="60"/>
-      <c r="CG9" s="56"/>
-      <c r="CH9" s="39"/>
-      <c r="CI9" s="40"/>
-      <c r="CJ9" s="33"/>
-      <c r="CK9" s="39"/>
-      <c r="CL9" s="40"/>
-      <c r="CM9" s="33"/>
-      <c r="CN9" s="39"/>
-      <c r="CO9" s="40"/>
-      <c r="CP9" s="33"/>
-      <c r="CQ9" s="39"/>
-      <c r="CR9" s="40"/>
-      <c r="CS9" s="33"/>
-      <c r="CT9" s="39"/>
-      <c r="CU9" s="40"/>
-      <c r="CV9" s="33"/>
-      <c r="CW9" s="39"/>
-      <c r="CX9" s="40"/>
-      <c r="CY9" s="33"/>
-      <c r="CZ9" s="39"/>
-      <c r="DA9" s="40"/>
-      <c r="DB9" s="33"/>
-      <c r="DC9" s="39"/>
-      <c r="DD9" s="40"/>
-      <c r="DE9" s="33"/>
-      <c r="DF9" s="39"/>
-      <c r="DG9" s="40"/>
-      <c r="DH9" s="33"/>
-      <c r="DI9" s="39"/>
-      <c r="DJ9" s="40"/>
-      <c r="DK9" s="33"/>
-      <c r="DL9" s="39"/>
-      <c r="DM9" s="40"/>
-      <c r="DN9" s="39"/>
-      <c r="DO9" s="39"/>
-      <c r="DP9" s="60"/>
-      <c r="DQ9" s="56"/>
-      <c r="DR9" s="39"/>
-      <c r="DS9" s="40"/>
-      <c r="DT9" s="33"/>
-      <c r="DU9" s="39"/>
-      <c r="DV9" s="40"/>
-      <c r="DW9" s="33"/>
-      <c r="DX9" s="39"/>
-      <c r="DY9" s="40"/>
-      <c r="DZ9" s="33"/>
-      <c r="EA9" s="39"/>
-      <c r="EB9" s="40"/>
-      <c r="EC9" s="33"/>
-      <c r="ED9" s="39"/>
-      <c r="EE9" s="40"/>
-      <c r="EF9" s="33"/>
-      <c r="EG9" s="39"/>
-      <c r="EH9" s="40"/>
-      <c r="EI9" s="33"/>
-      <c r="EJ9" s="39"/>
-      <c r="EK9" s="40"/>
-      <c r="EL9" s="33"/>
-      <c r="EM9" s="39"/>
-      <c r="EN9" s="40"/>
-      <c r="EO9" s="33"/>
-      <c r="EP9" s="39"/>
-      <c r="EQ9" s="40"/>
-      <c r="ER9" s="33"/>
-      <c r="ES9" s="39"/>
-      <c r="ET9" s="40"/>
-      <c r="EU9" s="33"/>
-      <c r="EV9" s="39"/>
-      <c r="EW9" s="40"/>
-      <c r="EX9" s="39"/>
-      <c r="EY9" s="39"/>
-      <c r="EZ9" s="60"/>
-      <c r="FA9" s="56"/>
-      <c r="FB9" s="39"/>
-      <c r="FC9" s="40"/>
-      <c r="FD9" s="33"/>
-      <c r="FE9" s="39"/>
-      <c r="FF9" s="40"/>
-      <c r="FG9" s="33"/>
-      <c r="FH9" s="39"/>
-      <c r="FI9" s="40"/>
-      <c r="FJ9" s="33"/>
-      <c r="FK9" s="39"/>
-      <c r="FL9" s="40"/>
-      <c r="FM9" s="33"/>
-      <c r="FN9" s="39"/>
-      <c r="FO9" s="40"/>
-      <c r="FP9" s="33"/>
-      <c r="FQ9" s="39"/>
-      <c r="FR9" s="40"/>
-      <c r="FS9" s="33"/>
-      <c r="FT9" s="39"/>
-      <c r="FU9" s="40"/>
-      <c r="FV9" s="33"/>
-      <c r="FW9" s="39"/>
-      <c r="FX9" s="40"/>
-      <c r="FY9" s="33"/>
-      <c r="FZ9" s="39"/>
-      <c r="GA9" s="40"/>
-      <c r="GB9" s="33"/>
-      <c r="GC9" s="39"/>
-      <c r="GD9" s="40"/>
-      <c r="GE9" s="33"/>
-      <c r="GF9" s="39"/>
-      <c r="GG9" s="40"/>
-      <c r="GH9" s="39"/>
-      <c r="GI9" s="39"/>
-      <c r="GJ9" s="60"/>
-      <c r="GK9" s="56"/>
-      <c r="GL9" s="39"/>
-      <c r="GM9" s="40"/>
-      <c r="GN9" s="33"/>
-      <c r="GO9" s="39"/>
-      <c r="GP9" s="40"/>
-      <c r="GQ9" s="33"/>
-      <c r="GR9" s="39"/>
-      <c r="GS9" s="40"/>
-      <c r="GT9" s="33"/>
-      <c r="GU9" s="39"/>
-      <c r="GV9" s="40"/>
-      <c r="GW9" s="33"/>
-      <c r="GX9" s="39"/>
-      <c r="GY9" s="40"/>
-      <c r="GZ9" s="33"/>
-      <c r="HA9" s="39"/>
-      <c r="HB9" s="40"/>
-      <c r="HC9" s="33"/>
-      <c r="HD9" s="39"/>
-      <c r="HE9" s="40"/>
-      <c r="HF9" s="33"/>
-      <c r="HG9" s="39"/>
-      <c r="HH9" s="40"/>
-      <c r="HI9" s="33"/>
-      <c r="HJ9" s="39"/>
-      <c r="HK9" s="40"/>
-      <c r="HL9" s="33"/>
-      <c r="HM9" s="39"/>
-      <c r="HN9" s="40"/>
-      <c r="HO9" s="33"/>
-      <c r="HP9" s="39"/>
-      <c r="HQ9" s="40"/>
-      <c r="HR9" s="39"/>
-      <c r="HS9" s="39"/>
-      <c r="HT9" s="60"/>
-      <c r="HU9" s="56"/>
-      <c r="HV9" s="39"/>
-      <c r="HW9" s="40"/>
-      <c r="HX9" s="33"/>
-      <c r="HY9" s="39"/>
-      <c r="HZ9" s="40"/>
-      <c r="IA9" s="33"/>
-      <c r="IB9" s="39"/>
-      <c r="IC9" s="40"/>
-      <c r="ID9" s="33"/>
-      <c r="IE9" s="39"/>
-      <c r="IF9" s="40"/>
-      <c r="IG9" s="33"/>
-      <c r="IH9" s="39"/>
-      <c r="II9" s="40"/>
-      <c r="IJ9" s="33"/>
-      <c r="IK9" s="39"/>
-      <c r="IL9" s="40"/>
-      <c r="IM9" s="33"/>
-      <c r="IN9" s="39"/>
-      <c r="IO9" s="40"/>
-      <c r="IP9" s="33"/>
-      <c r="IQ9" s="39"/>
-      <c r="IR9" s="40"/>
-      <c r="IS9" s="33"/>
-      <c r="IT9" s="39"/>
-      <c r="IU9" s="40"/>
-      <c r="IV9" s="33"/>
-      <c r="IW9" s="39"/>
-      <c r="IX9" s="40"/>
-      <c r="IY9" s="33"/>
-      <c r="IZ9" s="39"/>
-      <c r="JA9" s="40"/>
-      <c r="JB9" s="39"/>
-      <c r="JC9" s="39"/>
-      <c r="JD9" s="60"/>
-      <c r="JE9" s="56"/>
-      <c r="JF9" s="39"/>
-      <c r="JG9" s="40"/>
-      <c r="JH9" s="33"/>
-      <c r="JI9" s="39"/>
-      <c r="JJ9" s="40"/>
-      <c r="JK9" s="33"/>
-      <c r="JL9" s="39"/>
-      <c r="JM9" s="40"/>
-      <c r="JN9" s="33"/>
-      <c r="JO9" s="39"/>
-      <c r="JP9" s="40"/>
-      <c r="JQ9" s="33"/>
-      <c r="JR9" s="39"/>
-      <c r="JS9" s="40"/>
-      <c r="JT9" s="33"/>
-      <c r="JU9" s="39"/>
-      <c r="JV9" s="40"/>
-      <c r="JW9" s="33"/>
-      <c r="JX9" s="39"/>
-      <c r="JY9" s="40"/>
-      <c r="JZ9" s="33"/>
-      <c r="KA9" s="39"/>
-      <c r="KB9" s="40"/>
-      <c r="KC9" s="33"/>
-      <c r="KD9" s="39"/>
-      <c r="KE9" s="40"/>
-      <c r="KF9" s="33"/>
-      <c r="KG9" s="39"/>
-      <c r="KH9" s="40"/>
-      <c r="KI9" s="33"/>
-      <c r="KJ9" s="39"/>
-      <c r="KK9" s="40"/>
-      <c r="KL9" s="39"/>
-      <c r="KM9" s="39"/>
-      <c r="KN9" s="40"/>
-      <c r="KO9" s="107"/>
-      <c r="KP9" s="40"/>
-      <c r="KQ9" s="34"/>
+      <c r="H9" s="49"/>
+      <c r="I9" s="49"/>
+      <c r="J9" s="49"/>
+      <c r="K9" s="49"/>
+      <c r="L9" s="49"/>
+      <c r="M9" s="38"/>
+      <c r="N9" s="40"/>
+      <c r="O9" s="41"/>
+      <c r="P9" s="38"/>
+      <c r="Q9" s="40"/>
+      <c r="R9" s="41"/>
+      <c r="S9" s="38"/>
+      <c r="T9" s="40"/>
+      <c r="U9" s="41"/>
+      <c r="V9" s="38"/>
+      <c r="W9" s="40"/>
+      <c r="X9" s="41"/>
+      <c r="Y9" s="38"/>
+      <c r="Z9" s="40"/>
+      <c r="AA9" s="41"/>
+      <c r="AB9" s="38"/>
+      <c r="AC9" s="40"/>
+      <c r="AD9" s="41"/>
+      <c r="AE9" s="38"/>
+      <c r="AF9" s="40"/>
+      <c r="AG9" s="41"/>
+      <c r="AH9" s="38"/>
+      <c r="AI9" s="40"/>
+      <c r="AJ9" s="41"/>
+      <c r="AK9" s="38"/>
+      <c r="AL9" s="40"/>
+      <c r="AM9" s="41"/>
+      <c r="AN9" s="38"/>
+      <c r="AO9" s="40"/>
+      <c r="AP9" s="41"/>
+      <c r="AQ9" s="38"/>
+      <c r="AR9" s="40"/>
+      <c r="AS9" s="41"/>
+      <c r="AT9" s="40"/>
+      <c r="AU9" s="40"/>
+      <c r="AV9" s="45"/>
+      <c r="AW9" s="47"/>
+      <c r="AX9" s="40"/>
+      <c r="AY9" s="41"/>
+      <c r="AZ9" s="38"/>
+      <c r="BA9" s="40"/>
+      <c r="BB9" s="41"/>
+      <c r="BC9" s="38"/>
+      <c r="BD9" s="40"/>
+      <c r="BE9" s="41"/>
+      <c r="BF9" s="38"/>
+      <c r="BG9" s="40"/>
+      <c r="BH9" s="41"/>
+      <c r="BI9" s="38"/>
+      <c r="BJ9" s="40"/>
+      <c r="BK9" s="41"/>
+      <c r="BL9" s="38"/>
+      <c r="BM9" s="40"/>
+      <c r="BN9" s="41"/>
+      <c r="BO9" s="38"/>
+      <c r="BP9" s="40"/>
+      <c r="BQ9" s="41"/>
+      <c r="BR9" s="38"/>
+      <c r="BS9" s="40"/>
+      <c r="BT9" s="41"/>
+      <c r="BU9" s="38"/>
+      <c r="BV9" s="40"/>
+      <c r="BW9" s="41"/>
+      <c r="BX9" s="38"/>
+      <c r="BY9" s="40"/>
+      <c r="BZ9" s="41"/>
+      <c r="CA9" s="38"/>
+      <c r="CB9" s="40"/>
+      <c r="CC9" s="41"/>
+      <c r="CD9" s="40"/>
+      <c r="CE9" s="40"/>
+      <c r="CF9" s="45"/>
+      <c r="CG9" s="47"/>
+      <c r="CH9" s="40"/>
+      <c r="CI9" s="41"/>
+      <c r="CJ9" s="38"/>
+      <c r="CK9" s="40"/>
+      <c r="CL9" s="41"/>
+      <c r="CM9" s="38"/>
+      <c r="CN9" s="40"/>
+      <c r="CO9" s="41"/>
+      <c r="CP9" s="38"/>
+      <c r="CQ9" s="40"/>
+      <c r="CR9" s="41"/>
+      <c r="CS9" s="38"/>
+      <c r="CT9" s="40"/>
+      <c r="CU9" s="41"/>
+      <c r="CV9" s="38"/>
+      <c r="CW9" s="40"/>
+      <c r="CX9" s="41"/>
+      <c r="CY9" s="38"/>
+      <c r="CZ9" s="40"/>
+      <c r="DA9" s="41"/>
+      <c r="DB9" s="38"/>
+      <c r="DC9" s="40"/>
+      <c r="DD9" s="41"/>
+      <c r="DE9" s="38"/>
+      <c r="DF9" s="40"/>
+      <c r="DG9" s="41"/>
+      <c r="DH9" s="38"/>
+      <c r="DI9" s="40"/>
+      <c r="DJ9" s="41"/>
+      <c r="DK9" s="38"/>
+      <c r="DL9" s="40"/>
+      <c r="DM9" s="41"/>
+      <c r="DN9" s="40"/>
+      <c r="DO9" s="40"/>
+      <c r="DP9" s="45"/>
+      <c r="DQ9" s="47"/>
+      <c r="DR9" s="40"/>
+      <c r="DS9" s="41"/>
+      <c r="DT9" s="38"/>
+      <c r="DU9" s="40"/>
+      <c r="DV9" s="41"/>
+      <c r="DW9" s="38"/>
+      <c r="DX9" s="40"/>
+      <c r="DY9" s="41"/>
+      <c r="DZ9" s="38"/>
+      <c r="EA9" s="40"/>
+      <c r="EB9" s="41"/>
+      <c r="EC9" s="38"/>
+      <c r="ED9" s="40"/>
+      <c r="EE9" s="41"/>
+      <c r="EF9" s="38"/>
+      <c r="EG9" s="40"/>
+      <c r="EH9" s="41"/>
+      <c r="EI9" s="38"/>
+      <c r="EJ9" s="40"/>
+      <c r="EK9" s="41"/>
+      <c r="EL9" s="38"/>
+      <c r="EM9" s="40"/>
+      <c r="EN9" s="41"/>
+      <c r="EO9" s="38"/>
+      <c r="EP9" s="40"/>
+      <c r="EQ9" s="41"/>
+      <c r="ER9" s="38"/>
+      <c r="ES9" s="40"/>
+      <c r="ET9" s="41"/>
+      <c r="EU9" s="38"/>
+      <c r="EV9" s="40"/>
+      <c r="EW9" s="41"/>
+      <c r="EX9" s="40"/>
+      <c r="EY9" s="40"/>
+      <c r="EZ9" s="45"/>
+      <c r="FA9" s="47"/>
+      <c r="FB9" s="40"/>
+      <c r="FC9" s="41"/>
+      <c r="FD9" s="38"/>
+      <c r="FE9" s="40"/>
+      <c r="FF9" s="41"/>
+      <c r="FG9" s="38"/>
+      <c r="FH9" s="40"/>
+      <c r="FI9" s="41"/>
+      <c r="FJ9" s="38"/>
+      <c r="FK9" s="40"/>
+      <c r="FL9" s="41"/>
+      <c r="FM9" s="38"/>
+      <c r="FN9" s="40"/>
+      <c r="FO9" s="41"/>
+      <c r="FP9" s="38"/>
+      <c r="FQ9" s="40"/>
+      <c r="FR9" s="41"/>
+      <c r="FS9" s="38"/>
+      <c r="FT9" s="40"/>
+      <c r="FU9" s="41"/>
+      <c r="FV9" s="38"/>
+      <c r="FW9" s="40"/>
+      <c r="FX9" s="41"/>
+      <c r="FY9" s="38"/>
+      <c r="FZ9" s="40"/>
+      <c r="GA9" s="41"/>
+      <c r="GB9" s="38"/>
+      <c r="GC9" s="40"/>
+      <c r="GD9" s="41"/>
+      <c r="GE9" s="38"/>
+      <c r="GF9" s="40"/>
+      <c r="GG9" s="41"/>
+      <c r="GH9" s="40"/>
+      <c r="GI9" s="40"/>
+      <c r="GJ9" s="45"/>
+      <c r="GK9" s="47"/>
+      <c r="GL9" s="40"/>
+      <c r="GM9" s="41"/>
+      <c r="GN9" s="38"/>
+      <c r="GO9" s="40"/>
+      <c r="GP9" s="41"/>
+      <c r="GQ9" s="38"/>
+      <c r="GR9" s="40"/>
+      <c r="GS9" s="41"/>
+      <c r="GT9" s="38"/>
+      <c r="GU9" s="40"/>
+      <c r="GV9" s="41"/>
+      <c r="GW9" s="38"/>
+      <c r="GX9" s="40"/>
+      <c r="GY9" s="41"/>
+      <c r="GZ9" s="38"/>
+      <c r="HA9" s="40"/>
+      <c r="HB9" s="41"/>
+      <c r="HC9" s="38"/>
+      <c r="HD9" s="40"/>
+      <c r="HE9" s="41"/>
+      <c r="HF9" s="38"/>
+      <c r="HG9" s="40"/>
+      <c r="HH9" s="41"/>
+      <c r="HI9" s="38"/>
+      <c r="HJ9" s="40"/>
+      <c r="HK9" s="41"/>
+      <c r="HL9" s="38"/>
+      <c r="HM9" s="40"/>
+      <c r="HN9" s="41"/>
+      <c r="HO9" s="38"/>
+      <c r="HP9" s="40"/>
+      <c r="HQ9" s="41"/>
+      <c r="HR9" s="40"/>
+      <c r="HS9" s="40"/>
+      <c r="HT9" s="45"/>
+      <c r="HU9" s="47"/>
+      <c r="HV9" s="40"/>
+      <c r="HW9" s="41"/>
+      <c r="HX9" s="38"/>
+      <c r="HY9" s="40"/>
+      <c r="HZ9" s="41"/>
+      <c r="IA9" s="38"/>
+      <c r="IB9" s="40"/>
+      <c r="IC9" s="41"/>
+      <c r="ID9" s="38"/>
+      <c r="IE9" s="40"/>
+      <c r="IF9" s="41"/>
+      <c r="IG9" s="38"/>
+      <c r="IH9" s="40"/>
+      <c r="II9" s="41"/>
+      <c r="IJ9" s="38"/>
+      <c r="IK9" s="40"/>
+      <c r="IL9" s="41"/>
+      <c r="IM9" s="38"/>
+      <c r="IN9" s="40"/>
+      <c r="IO9" s="41"/>
+      <c r="IP9" s="38"/>
+      <c r="IQ9" s="40"/>
+      <c r="IR9" s="41"/>
+      <c r="IS9" s="38"/>
+      <c r="IT9" s="40"/>
+      <c r="IU9" s="41"/>
+      <c r="IV9" s="38"/>
+      <c r="IW9" s="40"/>
+      <c r="IX9" s="41"/>
+      <c r="IY9" s="38"/>
+      <c r="IZ9" s="40"/>
+      <c r="JA9" s="41"/>
+      <c r="JB9" s="40"/>
+      <c r="JC9" s="40"/>
+      <c r="JD9" s="45"/>
+      <c r="JE9" s="47"/>
+      <c r="JF9" s="40"/>
+      <c r="JG9" s="41"/>
+      <c r="JH9" s="38"/>
+      <c r="JI9" s="40"/>
+      <c r="JJ9" s="41"/>
+      <c r="JK9" s="38"/>
+      <c r="JL9" s="40"/>
+      <c r="JM9" s="41"/>
+      <c r="JN9" s="38"/>
+      <c r="JO9" s="40"/>
+      <c r="JP9" s="41"/>
+      <c r="JQ9" s="38"/>
+      <c r="JR9" s="40"/>
+      <c r="JS9" s="41"/>
+      <c r="JT9" s="38"/>
+      <c r="JU9" s="40"/>
+      <c r="JV9" s="41"/>
+      <c r="JW9" s="38"/>
+      <c r="JX9" s="40"/>
+      <c r="JY9" s="41"/>
+      <c r="JZ9" s="38"/>
+      <c r="KA9" s="40"/>
+      <c r="KB9" s="41"/>
+      <c r="KC9" s="38"/>
+      <c r="KD9" s="40"/>
+      <c r="KE9" s="41"/>
+      <c r="KF9" s="38"/>
+      <c r="KG9" s="40"/>
+      <c r="KH9" s="41"/>
+      <c r="KI9" s="38"/>
+      <c r="KJ9" s="40"/>
+      <c r="KK9" s="41"/>
+      <c r="KL9" s="40"/>
+      <c r="KM9" s="40"/>
+      <c r="KN9" s="41"/>
+      <c r="KO9" s="114"/>
+      <c r="KP9" s="41"/>
+      <c r="KQ9" s="63"/>
       <c r="KR9" s="9" t="s">
         <v>59</v>
       </c>
@@ -7863,9 +7863,9 @@
       <c r="KT9" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="KU9" s="40"/>
-      <c r="KV9" s="40"/>
-      <c r="KW9" s="34"/>
+      <c r="KU9" s="41"/>
+      <c r="KV9" s="41"/>
+      <c r="KW9" s="63"/>
       <c r="KX9" s="9" t="s">
         <v>59</v>
       </c>
@@ -7875,9 +7875,9 @@
       <c r="KZ9" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="LA9" s="40"/>
-      <c r="LB9" s="40"/>
-      <c r="LC9" s="34"/>
+      <c r="LA9" s="41"/>
+      <c r="LB9" s="41"/>
+      <c r="LC9" s="63"/>
       <c r="LD9" s="9" t="s">
         <v>59</v>
       </c>
@@ -7887,9 +7887,9 @@
       <c r="LF9" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="LG9" s="40"/>
-      <c r="LH9" s="40"/>
-      <c r="LI9" s="34"/>
+      <c r="LG9" s="41"/>
+      <c r="LH9" s="41"/>
+      <c r="LI9" s="63"/>
       <c r="LJ9" s="9" t="s">
         <v>59</v>
       </c>
@@ -7899,9 +7899,9 @@
       <c r="LL9" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="LM9" s="40"/>
-      <c r="LN9" s="40"/>
-      <c r="LO9" s="34"/>
+      <c r="LM9" s="41"/>
+      <c r="LN9" s="41"/>
+      <c r="LO9" s="63"/>
       <c r="LP9" s="9" t="s">
         <v>59</v>
       </c>
@@ -7911,9 +7911,9 @@
       <c r="LR9" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="LS9" s="40"/>
-      <c r="LT9" s="40"/>
-      <c r="LU9" s="34"/>
+      <c r="LS9" s="41"/>
+      <c r="LT9" s="41"/>
+      <c r="LU9" s="63"/>
       <c r="LV9" s="9" t="s">
         <v>59</v>
       </c>
@@ -7923,9 +7923,9 @@
       <c r="LX9" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="LY9" s="34"/>
-      <c r="LZ9" s="34"/>
-      <c r="MA9" s="34"/>
+      <c r="LY9" s="63"/>
+      <c r="LZ9" s="63"/>
+      <c r="MA9" s="63"/>
       <c r="MB9" s="9" t="s">
         <v>59</v>
       </c>
@@ -7935,9 +7935,9 @@
       <c r="MD9" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="ME9" s="34"/>
-      <c r="MF9" s="34"/>
-      <c r="MG9" s="34"/>
+      <c r="ME9" s="63"/>
+      <c r="MF9" s="63"/>
+      <c r="MG9" s="63"/>
       <c r="MH9" s="9" t="s">
         <v>59</v>
       </c>
@@ -7947,9 +7947,9 @@
       <c r="MJ9" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="MK9" s="34"/>
-      <c r="ML9" s="34"/>
-      <c r="MM9" s="34"/>
+      <c r="MK9" s="63"/>
+      <c r="ML9" s="63"/>
+      <c r="MM9" s="63"/>
       <c r="MN9" s="9" t="s">
         <v>59</v>
       </c>
@@ -7959,9 +7959,9 @@
       <c r="MP9" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="MQ9" s="34"/>
-      <c r="MR9" s="34"/>
-      <c r="MS9" s="34"/>
+      <c r="MQ9" s="63"/>
+      <c r="MR9" s="63"/>
+      <c r="MS9" s="63"/>
       <c r="MT9" s="9" t="s">
         <v>59</v>
       </c>
@@ -7971,9 +7971,9 @@
       <c r="MV9" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="MW9" s="34"/>
-      <c r="MX9" s="34"/>
-      <c r="MY9" s="34"/>
+      <c r="MW9" s="63"/>
+      <c r="MX9" s="63"/>
+      <c r="MY9" s="63"/>
       <c r="MZ9" s="9" t="s">
         <v>59</v>
       </c>
@@ -7983,9 +7983,9 @@
       <c r="NB9" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="NC9" s="34"/>
-      <c r="ND9" s="34"/>
-      <c r="NE9" s="34"/>
+      <c r="NC9" s="63"/>
+      <c r="ND9" s="63"/>
+      <c r="NE9" s="63"/>
       <c r="NF9" s="9" t="s">
         <v>59</v>
       </c>
@@ -7995,9 +7995,9 @@
       <c r="NH9" s="11" t="s">
         <v>61</v>
       </c>
-      <c r="NI9" s="94"/>
-      <c r="NJ9" s="33"/>
-      <c r="NK9" s="57"/>
+      <c r="NI9" s="103"/>
+      <c r="NJ9" s="38"/>
+      <c r="NK9" s="130"/>
       <c r="NL9" s="9" t="s">
         <v>59</v>
       </c>
@@ -8007,9 +8007,9 @@
       <c r="NN9" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="NO9" s="34"/>
-      <c r="NP9" s="34"/>
-      <c r="NQ9" s="34"/>
+      <c r="NO9" s="63"/>
+      <c r="NP9" s="63"/>
+      <c r="NQ9" s="63"/>
       <c r="NR9" s="9" t="s">
         <v>59</v>
       </c>
@@ -8019,9 +8019,9 @@
       <c r="NT9" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="NU9" s="34"/>
-      <c r="NV9" s="34"/>
-      <c r="NW9" s="34"/>
+      <c r="NU9" s="63"/>
+      <c r="NV9" s="63"/>
+      <c r="NW9" s="63"/>
       <c r="NX9" s="9" t="s">
         <v>59</v>
       </c>
@@ -8179,7 +8179,7 @@
       <c r="AV10" s="19" t="s">
         <v>769</v>
       </c>
-      <c r="AW10" s="130" t="s">
+      <c r="AW10" s="32" t="s">
         <v>102</v>
       </c>
       <c r="AX10" s="17" t="s">
@@ -8287,7 +8287,7 @@
       <c r="CF10" s="19" t="s">
         <v>781</v>
       </c>
-      <c r="CG10" s="130" t="s">
+      <c r="CG10" s="32" t="s">
         <v>126</v>
       </c>
       <c r="CH10" s="17" t="s">
@@ -8395,7 +8395,7 @@
       <c r="DP10" s="19" t="s">
         <v>793</v>
       </c>
-      <c r="DQ10" s="130" t="s">
+      <c r="DQ10" s="32" t="s">
         <v>150</v>
       </c>
       <c r="DR10" s="17" t="s">
@@ -8503,7 +8503,7 @@
       <c r="EZ10" s="19" t="s">
         <v>805</v>
       </c>
-      <c r="FA10" s="130" t="s">
+      <c r="FA10" s="32" t="s">
         <v>174</v>
       </c>
       <c r="FB10" s="17" t="s">
@@ -8611,7 +8611,7 @@
       <c r="GJ10" s="19" t="s">
         <v>817</v>
       </c>
-      <c r="GK10" s="130" t="s">
+      <c r="GK10" s="32" t="s">
         <v>198</v>
       </c>
       <c r="GL10" s="17" t="s">
@@ -8719,7 +8719,7 @@
       <c r="HT10" s="19" t="s">
         <v>829</v>
       </c>
-      <c r="HU10" s="130" t="s">
+      <c r="HU10" s="32" t="s">
         <v>222</v>
       </c>
       <c r="HV10" s="17" t="s">
@@ -8827,7 +8827,7 @@
       <c r="JD10" s="19" t="s">
         <v>841</v>
       </c>
-      <c r="JE10" s="130" t="s">
+      <c r="JE10" s="32" t="s">
         <v>246</v>
       </c>
       <c r="JF10" s="17" t="s">
@@ -9205,12 +9205,12 @@
       <c r="NZ10" s="19" t="s">
         <v>359</v>
       </c>
-      <c r="OA10" s="130"/>
+      <c r="OA10" s="32"/>
       <c r="OB10" s="17"/>
       <c r="OC10" s="17"/>
       <c r="OD10" s="17"/>
       <c r="OE10" s="17"/>
-      <c r="OF10" s="131"/>
+      <c r="OF10" s="33"/>
     </row>
     <row r="11" spans="1:396" s="3" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="22"/>
@@ -9353,7 +9353,7 @@
       <c r="AV11" s="25" t="s">
         <v>406</v>
       </c>
-      <c r="AW11" s="132" t="s">
+      <c r="AW11" s="34" t="s">
         <v>407</v>
       </c>
       <c r="AX11" s="23" t="s">
@@ -9461,7 +9461,7 @@
       <c r="CF11" s="25" t="s">
         <v>442</v>
       </c>
-      <c r="CG11" s="132" t="s">
+      <c r="CG11" s="34" t="s">
         <v>443</v>
       </c>
       <c r="CH11" s="23" t="s">
@@ -9569,7 +9569,7 @@
       <c r="DP11" s="25" t="s">
         <v>478</v>
       </c>
-      <c r="DQ11" s="132" t="s">
+      <c r="DQ11" s="34" t="s">
         <v>479</v>
       </c>
       <c r="DR11" s="23" t="s">
@@ -9677,7 +9677,7 @@
       <c r="EZ11" s="25" t="s">
         <v>514</v>
       </c>
-      <c r="FA11" s="132" t="s">
+      <c r="FA11" s="34" t="s">
         <v>515</v>
       </c>
       <c r="FB11" s="23" t="s">
@@ -9785,7 +9785,7 @@
       <c r="GJ11" s="25" t="s">
         <v>550</v>
       </c>
-      <c r="GK11" s="132" t="s">
+      <c r="GK11" s="34" t="s">
         <v>551</v>
       </c>
       <c r="GL11" s="23" t="s">
@@ -9893,7 +9893,7 @@
       <c r="HT11" s="25" t="s">
         <v>586</v>
       </c>
-      <c r="HU11" s="132" t="s">
+      <c r="HU11" s="34" t="s">
         <v>587</v>
       </c>
       <c r="HV11" s="23" t="s">
@@ -10001,7 +10001,7 @@
       <c r="JD11" s="25" t="s">
         <v>622</v>
       </c>
-      <c r="JE11" s="132" t="s">
+      <c r="JE11" s="34" t="s">
         <v>623</v>
       </c>
       <c r="JF11" s="23" t="s">
@@ -10379,15 +10379,552 @@
       <c r="NZ11" s="25" t="s">
         <v>748</v>
       </c>
-      <c r="OA11" s="133"/>
-      <c r="OB11" s="134"/>
-      <c r="OC11" s="134"/>
-      <c r="OD11" s="134"/>
-      <c r="OE11" s="134"/>
-      <c r="OF11" s="134"/>
+      <c r="OA11" s="35"/>
+      <c r="OB11" s="36"/>
+      <c r="OC11" s="36"/>
+      <c r="OD11" s="36"/>
+      <c r="OE11" s="36"/>
+      <c r="OF11" s="36"/>
     </row>
   </sheetData>
   <mergeCells count="561">
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="NQ8:NQ9"/>
+    <mergeCell ref="NR8:NT8"/>
+    <mergeCell ref="NU8:NU9"/>
+    <mergeCell ref="NV8:NV9"/>
+    <mergeCell ref="NW8:NW9"/>
+    <mergeCell ref="NX8:NZ8"/>
+    <mergeCell ref="MY8:MY9"/>
+    <mergeCell ref="MZ8:NB8"/>
+    <mergeCell ref="NC8:NC9"/>
+    <mergeCell ref="ND8:ND9"/>
+    <mergeCell ref="NE8:NE9"/>
+    <mergeCell ref="NF8:NH8"/>
+    <mergeCell ref="MR8:MR9"/>
+    <mergeCell ref="MS8:MS9"/>
+    <mergeCell ref="MT8:MV8"/>
+    <mergeCell ref="MW8:MW9"/>
+    <mergeCell ref="MX8:MX9"/>
+    <mergeCell ref="ME8:ME9"/>
+    <mergeCell ref="MF8:MF9"/>
+    <mergeCell ref="MG8:MG9"/>
+    <mergeCell ref="MH8:MJ8"/>
+    <mergeCell ref="MM8:MM9"/>
+    <mergeCell ref="MN8:MP8"/>
+    <mergeCell ref="LU8:LU9"/>
+    <mergeCell ref="LV8:LX8"/>
+    <mergeCell ref="LC8:LC9"/>
+    <mergeCell ref="LD8:LF8"/>
+    <mergeCell ref="LI8:LI9"/>
+    <mergeCell ref="LJ8:LL8"/>
+    <mergeCell ref="LM8:LM9"/>
+    <mergeCell ref="LN8:LN9"/>
+    <mergeCell ref="MQ8:MQ9"/>
+    <mergeCell ref="KU8:KU9"/>
+    <mergeCell ref="KV8:KV9"/>
+    <mergeCell ref="KW8:KW9"/>
+    <mergeCell ref="KX8:KZ8"/>
+    <mergeCell ref="LA8:LA9"/>
+    <mergeCell ref="LB8:LB9"/>
+    <mergeCell ref="OB7:OB8"/>
+    <mergeCell ref="OC7:OC8"/>
+    <mergeCell ref="OD7:OD8"/>
+    <mergeCell ref="LA7:LB7"/>
+    <mergeCell ref="LC7:LF7"/>
+    <mergeCell ref="LM7:LN7"/>
+    <mergeCell ref="LO7:LR7"/>
+    <mergeCell ref="LS7:LT7"/>
+    <mergeCell ref="NK4:NN7"/>
+    <mergeCell ref="NO4:NT6"/>
+    <mergeCell ref="NU4:NZ6"/>
+    <mergeCell ref="LZ8:LZ9"/>
+    <mergeCell ref="MA8:MA9"/>
+    <mergeCell ref="MB8:MD8"/>
+    <mergeCell ref="LO8:LO9"/>
+    <mergeCell ref="LP8:LR8"/>
+    <mergeCell ref="LS8:LS9"/>
+    <mergeCell ref="LT8:LT9"/>
+    <mergeCell ref="OE7:OE8"/>
+    <mergeCell ref="OF7:OF8"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="KQ8:KQ9"/>
+    <mergeCell ref="KR8:KT8"/>
+    <mergeCell ref="NE7:NH7"/>
+    <mergeCell ref="NO7:NP7"/>
+    <mergeCell ref="NQ7:NT7"/>
+    <mergeCell ref="NU7:NV7"/>
+    <mergeCell ref="NW7:NZ7"/>
+    <mergeCell ref="OA7:OA8"/>
+    <mergeCell ref="NK8:NK9"/>
+    <mergeCell ref="NL8:NN8"/>
+    <mergeCell ref="NO8:NO9"/>
+    <mergeCell ref="NP8:NP9"/>
+    <mergeCell ref="LU7:LX7"/>
+    <mergeCell ref="MQ7:MR7"/>
+    <mergeCell ref="MS7:MV7"/>
+    <mergeCell ref="MW7:MX7"/>
+    <mergeCell ref="MY7:NB7"/>
+    <mergeCell ref="NC7:ND7"/>
+    <mergeCell ref="KW7:KZ7"/>
+    <mergeCell ref="IK7:IK9"/>
+    <mergeCell ref="KD7:KD9"/>
+    <mergeCell ref="KE7:KE9"/>
+    <mergeCell ref="KF7:KF9"/>
+    <mergeCell ref="KG7:KG9"/>
+    <mergeCell ref="JD7:JD9"/>
+    <mergeCell ref="JE7:JE9"/>
+    <mergeCell ref="JF7:JF9"/>
+    <mergeCell ref="JG7:JG9"/>
+    <mergeCell ref="JH7:JH9"/>
+    <mergeCell ref="JI7:JI9"/>
+    <mergeCell ref="JU7:JU9"/>
+    <mergeCell ref="JL7:JL9"/>
+    <mergeCell ref="JM7:JM9"/>
+    <mergeCell ref="JN7:JN9"/>
+    <mergeCell ref="JO7:JO9"/>
+    <mergeCell ref="JJ7:JJ9"/>
+    <mergeCell ref="JK7:JK9"/>
+    <mergeCell ref="KB7:KB9"/>
+    <mergeCell ref="KC7:KC9"/>
+    <mergeCell ref="IZ7:IZ9"/>
+    <mergeCell ref="JA7:JA9"/>
+    <mergeCell ref="JB7:JB9"/>
+    <mergeCell ref="JC7:JC9"/>
+    <mergeCell ref="IX7:IX9"/>
+    <mergeCell ref="IY7:IY9"/>
+    <mergeCell ref="IN7:IN9"/>
+    <mergeCell ref="IO7:IO9"/>
+    <mergeCell ref="IP7:IP9"/>
+    <mergeCell ref="IQ7:IQ9"/>
+    <mergeCell ref="IR7:IR9"/>
+    <mergeCell ref="IS7:IS9"/>
+    <mergeCell ref="IT7:IT9"/>
+    <mergeCell ref="IU7:IU9"/>
+    <mergeCell ref="IV7:IV9"/>
+    <mergeCell ref="IW7:IW9"/>
+    <mergeCell ref="FG7:FG9"/>
+    <mergeCell ref="HH7:HH9"/>
+    <mergeCell ref="HI7:HI9"/>
+    <mergeCell ref="HJ7:HJ9"/>
+    <mergeCell ref="HK7:HK9"/>
+    <mergeCell ref="HL7:HL9"/>
+    <mergeCell ref="HM7:HM9"/>
+    <mergeCell ref="GJ7:GJ9"/>
+    <mergeCell ref="GK7:GK9"/>
+    <mergeCell ref="GL7:GL9"/>
+    <mergeCell ref="GM7:GM9"/>
+    <mergeCell ref="GN7:GN9"/>
+    <mergeCell ref="GO7:GO9"/>
+    <mergeCell ref="GX7:GX9"/>
+    <mergeCell ref="GY7:GY9"/>
+    <mergeCell ref="GZ7:GZ9"/>
+    <mergeCell ref="HA7:HA9"/>
+    <mergeCell ref="GR7:GR9"/>
+    <mergeCell ref="GS7:GS9"/>
+    <mergeCell ref="GT7:GT9"/>
+    <mergeCell ref="GU7:GU9"/>
+    <mergeCell ref="GP7:GP9"/>
+    <mergeCell ref="GQ7:GQ9"/>
+    <mergeCell ref="GF7:GF9"/>
+    <mergeCell ref="EB7:EB9"/>
+    <mergeCell ref="EC7:EC9"/>
+    <mergeCell ref="ED7:ED9"/>
+    <mergeCell ref="EE7:EE9"/>
+    <mergeCell ref="EF7:EF9"/>
+    <mergeCell ref="EG7:EG9"/>
+    <mergeCell ref="EH7:EH9"/>
+    <mergeCell ref="EI7:EI9"/>
+    <mergeCell ref="FX7:FX9"/>
+    <mergeCell ref="EZ7:EZ9"/>
+    <mergeCell ref="FA7:FA9"/>
+    <mergeCell ref="FB7:FB9"/>
+    <mergeCell ref="FC7:FC9"/>
+    <mergeCell ref="FD7:FD9"/>
+    <mergeCell ref="FE7:FE9"/>
+    <mergeCell ref="FN7:FN9"/>
+    <mergeCell ref="FO7:FO9"/>
+    <mergeCell ref="FP7:FP9"/>
+    <mergeCell ref="FQ7:FQ9"/>
+    <mergeCell ref="FH7:FH9"/>
+    <mergeCell ref="FI7:FI9"/>
+    <mergeCell ref="FJ7:FJ9"/>
+    <mergeCell ref="FK7:FK9"/>
+    <mergeCell ref="FF7:FF9"/>
+    <mergeCell ref="AQ7:AQ9"/>
+    <mergeCell ref="CF7:CF9"/>
+    <mergeCell ref="CG7:CG9"/>
+    <mergeCell ref="CH7:CH9"/>
+    <mergeCell ref="CI7:CI9"/>
+    <mergeCell ref="CJ7:CJ9"/>
+    <mergeCell ref="CK7:CK9"/>
+    <mergeCell ref="BH7:BH9"/>
+    <mergeCell ref="BI7:BI9"/>
+    <mergeCell ref="BJ7:BJ9"/>
+    <mergeCell ref="BK7:BK9"/>
+    <mergeCell ref="BL7:BL9"/>
+    <mergeCell ref="BM7:BM9"/>
+    <mergeCell ref="BP7:BP9"/>
+    <mergeCell ref="BQ7:BQ9"/>
+    <mergeCell ref="BR7:BR9"/>
+    <mergeCell ref="BS7:BS9"/>
+    <mergeCell ref="BN7:BN9"/>
+    <mergeCell ref="BO7:BO9"/>
+    <mergeCell ref="BT7:BT9"/>
+    <mergeCell ref="BU7:BU9"/>
+    <mergeCell ref="BD7:BD9"/>
+    <mergeCell ref="BE7:BE9"/>
+    <mergeCell ref="BF7:BF9"/>
+    <mergeCell ref="X7:X9"/>
+    <mergeCell ref="Y7:Y9"/>
+    <mergeCell ref="Z7:Z9"/>
+    <mergeCell ref="AA7:AA9"/>
+    <mergeCell ref="AB7:AB9"/>
+    <mergeCell ref="AC7:AC9"/>
+    <mergeCell ref="AJ7:AJ9"/>
+    <mergeCell ref="AK7:AK9"/>
+    <mergeCell ref="AP7:AP9"/>
+    <mergeCell ref="NC6:NH6"/>
+    <mergeCell ref="I7:I9"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="M7:M9"/>
+    <mergeCell ref="N7:N9"/>
+    <mergeCell ref="O7:O9"/>
+    <mergeCell ref="P7:P9"/>
+    <mergeCell ref="Q7:Q9"/>
+    <mergeCell ref="R7:R9"/>
+    <mergeCell ref="S7:S9"/>
+    <mergeCell ref="LY6:LZ7"/>
+    <mergeCell ref="MA6:MD7"/>
+    <mergeCell ref="ME6:MF7"/>
+    <mergeCell ref="MG6:MJ7"/>
+    <mergeCell ref="MQ6:MV6"/>
+    <mergeCell ref="MW6:NB6"/>
+    <mergeCell ref="KF6:KH6"/>
+    <mergeCell ref="KI6:KK6"/>
+    <mergeCell ref="KU6:KZ6"/>
+    <mergeCell ref="LA6:LF6"/>
+    <mergeCell ref="LM6:LR6"/>
+    <mergeCell ref="LS6:LX6"/>
+    <mergeCell ref="IY6:JA6"/>
+    <mergeCell ref="JE6:JG6"/>
+    <mergeCell ref="FM4:FO6"/>
+    <mergeCell ref="FP4:FR6"/>
+    <mergeCell ref="FS4:GA4"/>
+    <mergeCell ref="GB4:GG5"/>
+    <mergeCell ref="JH6:JJ6"/>
+    <mergeCell ref="JK6:JM6"/>
+    <mergeCell ref="JN6:JP6"/>
+    <mergeCell ref="JW6:JY6"/>
+    <mergeCell ref="HO6:HQ6"/>
+    <mergeCell ref="HU6:HW6"/>
+    <mergeCell ref="HX6:HZ6"/>
+    <mergeCell ref="IA6:IC6"/>
+    <mergeCell ref="ID6:IF6"/>
+    <mergeCell ref="IM6:IO6"/>
+    <mergeCell ref="JE4:JJ5"/>
+    <mergeCell ref="JK4:JP5"/>
+    <mergeCell ref="JQ4:JS6"/>
+    <mergeCell ref="JT4:JV6"/>
+    <mergeCell ref="JW4:KE4"/>
+    <mergeCell ref="JW5:KE5"/>
+    <mergeCell ref="JZ6:KB6"/>
+    <mergeCell ref="KC6:KE6"/>
+    <mergeCell ref="HU4:HZ5"/>
+    <mergeCell ref="IA4:IF5"/>
+    <mergeCell ref="CG6:CI6"/>
+    <mergeCell ref="CJ6:CL6"/>
+    <mergeCell ref="CM6:CO6"/>
+    <mergeCell ref="CP6:CR6"/>
+    <mergeCell ref="CY6:DA6"/>
+    <mergeCell ref="DB6:DD6"/>
+    <mergeCell ref="AQ6:AS6"/>
+    <mergeCell ref="AW6:AY6"/>
+    <mergeCell ref="AZ6:BB6"/>
+    <mergeCell ref="BC6:BE6"/>
+    <mergeCell ref="BF6:BH6"/>
+    <mergeCell ref="BO6:BQ6"/>
+    <mergeCell ref="BL4:BN6"/>
+    <mergeCell ref="BO4:BW4"/>
+    <mergeCell ref="BX4:CC5"/>
+    <mergeCell ref="CD4:CF6"/>
+    <mergeCell ref="CG4:CL5"/>
+    <mergeCell ref="CM4:CR5"/>
+    <mergeCell ref="BR6:BT6"/>
+    <mergeCell ref="BU6:BW6"/>
+    <mergeCell ref="BX6:BZ6"/>
+    <mergeCell ref="CA6:CC6"/>
+    <mergeCell ref="CY4:DG4"/>
+    <mergeCell ref="S6:U6"/>
+    <mergeCell ref="V6:X6"/>
+    <mergeCell ref="AE6:AG6"/>
+    <mergeCell ref="AH6:AJ6"/>
+    <mergeCell ref="AK6:AM6"/>
+    <mergeCell ref="AN6:AP6"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="G6:G7"/>
+    <mergeCell ref="H6:H9"/>
+    <mergeCell ref="I6:L6"/>
+    <mergeCell ref="M6:O6"/>
+    <mergeCell ref="P6:R6"/>
+    <mergeCell ref="AL7:AL9"/>
+    <mergeCell ref="AM7:AM9"/>
+    <mergeCell ref="AN7:AN9"/>
+    <mergeCell ref="AO7:AO9"/>
+    <mergeCell ref="AF7:AF9"/>
+    <mergeCell ref="AG7:AG9"/>
+    <mergeCell ref="AH7:AH9"/>
+    <mergeCell ref="AI7:AI9"/>
+    <mergeCell ref="AD7:AD9"/>
+    <mergeCell ref="AE7:AE9"/>
+    <mergeCell ref="T7:T9"/>
+    <mergeCell ref="U7:U9"/>
+    <mergeCell ref="AE5:AM5"/>
+    <mergeCell ref="BO5:BW5"/>
+    <mergeCell ref="CY5:DG5"/>
+    <mergeCell ref="EI5:EQ5"/>
+    <mergeCell ref="FS5:GA5"/>
+    <mergeCell ref="HC5:HK5"/>
+    <mergeCell ref="MK4:NH4"/>
+    <mergeCell ref="NI4:NI9"/>
+    <mergeCell ref="NJ4:NJ9"/>
+    <mergeCell ref="MK5:MK9"/>
+    <mergeCell ref="ML5:ML9"/>
+    <mergeCell ref="MM5:MP7"/>
+    <mergeCell ref="MQ5:NH5"/>
+    <mergeCell ref="KF4:KK5"/>
+    <mergeCell ref="KL4:KN6"/>
+    <mergeCell ref="KO4:LF4"/>
+    <mergeCell ref="LG4:LX4"/>
+    <mergeCell ref="LY4:MD5"/>
+    <mergeCell ref="ME4:MJ5"/>
+    <mergeCell ref="KO5:KO9"/>
+    <mergeCell ref="KP5:KP9"/>
+    <mergeCell ref="KQ5:KT7"/>
+    <mergeCell ref="KU5:LF5"/>
+    <mergeCell ref="JB4:JD6"/>
+    <mergeCell ref="IG4:II6"/>
+    <mergeCell ref="IJ4:IL6"/>
+    <mergeCell ref="IM4:IU4"/>
+    <mergeCell ref="IV4:JA5"/>
+    <mergeCell ref="IM5:IU5"/>
+    <mergeCell ref="IP6:IR6"/>
+    <mergeCell ref="IS6:IU6"/>
+    <mergeCell ref="IV6:IX6"/>
+    <mergeCell ref="GQ4:GV5"/>
+    <mergeCell ref="GW4:GY6"/>
+    <mergeCell ref="GZ4:HB6"/>
+    <mergeCell ref="HC4:HK4"/>
+    <mergeCell ref="HL4:HQ5"/>
+    <mergeCell ref="HR4:HT6"/>
+    <mergeCell ref="GQ6:GS6"/>
+    <mergeCell ref="GT6:GV6"/>
+    <mergeCell ref="HC6:HE6"/>
+    <mergeCell ref="HF6:HH6"/>
+    <mergeCell ref="GH4:GJ6"/>
+    <mergeCell ref="GK4:GP5"/>
+    <mergeCell ref="GE6:GG6"/>
+    <mergeCell ref="GK6:GM6"/>
+    <mergeCell ref="GN6:GP6"/>
+    <mergeCell ref="EF4:EH6"/>
+    <mergeCell ref="EI4:EQ4"/>
+    <mergeCell ref="ER4:EW5"/>
+    <mergeCell ref="EX4:EZ6"/>
+    <mergeCell ref="FA4:FF5"/>
+    <mergeCell ref="FG4:FL5"/>
+    <mergeCell ref="ER6:ET6"/>
+    <mergeCell ref="EU6:EW6"/>
+    <mergeCell ref="FA6:FC6"/>
+    <mergeCell ref="FD6:FF6"/>
+    <mergeCell ref="FG6:FI6"/>
+    <mergeCell ref="FJ6:FL6"/>
+    <mergeCell ref="FS6:FU6"/>
+    <mergeCell ref="FV6:FX6"/>
+    <mergeCell ref="FY6:GA6"/>
+    <mergeCell ref="GB6:GD6"/>
+    <mergeCell ref="EI6:EK6"/>
+    <mergeCell ref="EL6:EN6"/>
+    <mergeCell ref="EO6:EQ6"/>
+    <mergeCell ref="DH4:DM5"/>
+    <mergeCell ref="DN4:DP6"/>
+    <mergeCell ref="DQ4:DV5"/>
+    <mergeCell ref="DW4:EB5"/>
+    <mergeCell ref="EC4:EE6"/>
+    <mergeCell ref="DE6:DG6"/>
+    <mergeCell ref="DH6:DJ6"/>
+    <mergeCell ref="DK6:DM6"/>
+    <mergeCell ref="DQ6:DS6"/>
+    <mergeCell ref="DT6:DV6"/>
+    <mergeCell ref="DW6:DY6"/>
+    <mergeCell ref="DZ6:EB6"/>
+    <mergeCell ref="KO3:MJ3"/>
+    <mergeCell ref="MK3:NH3"/>
+    <mergeCell ref="NI3:NZ3"/>
+    <mergeCell ref="OA3:OF6"/>
+    <mergeCell ref="M4:R5"/>
+    <mergeCell ref="S4:X5"/>
+    <mergeCell ref="Y4:AA6"/>
+    <mergeCell ref="AB4:AD6"/>
+    <mergeCell ref="AE4:AM4"/>
+    <mergeCell ref="AN4:AS5"/>
+    <mergeCell ref="CG3:DP3"/>
+    <mergeCell ref="DQ3:EZ3"/>
+    <mergeCell ref="FA3:GJ3"/>
+    <mergeCell ref="GK3:HT3"/>
+    <mergeCell ref="HU3:JD3"/>
+    <mergeCell ref="JE3:KN3"/>
+    <mergeCell ref="HI6:HK6"/>
+    <mergeCell ref="HL6:HN6"/>
+    <mergeCell ref="CS4:CU6"/>
+    <mergeCell ref="CV4:CX6"/>
+    <mergeCell ref="AT4:AV6"/>
+    <mergeCell ref="AW4:BB5"/>
+    <mergeCell ref="BC4:BH5"/>
+    <mergeCell ref="BI4:BK6"/>
+    <mergeCell ref="A3:A9"/>
+    <mergeCell ref="B3:B9"/>
+    <mergeCell ref="C3:C9"/>
+    <mergeCell ref="D3:D9"/>
+    <mergeCell ref="F3:F9"/>
+    <mergeCell ref="H3:L5"/>
+    <mergeCell ref="M3:AR3"/>
+    <mergeCell ref="AW3:CF3"/>
+    <mergeCell ref="LY8:LY9"/>
+    <mergeCell ref="LG5:LG9"/>
+    <mergeCell ref="LH5:LH9"/>
+    <mergeCell ref="LI5:LL7"/>
+    <mergeCell ref="LM5:LX5"/>
+    <mergeCell ref="KJ7:KJ9"/>
+    <mergeCell ref="KK7:KK9"/>
+    <mergeCell ref="KH7:KH9"/>
+    <mergeCell ref="KI7:KI9"/>
+    <mergeCell ref="JX7:JX9"/>
+    <mergeCell ref="JY7:JY9"/>
+    <mergeCell ref="JZ7:JZ9"/>
+    <mergeCell ref="KA7:KA9"/>
+    <mergeCell ref="JR7:JR9"/>
+    <mergeCell ref="JS7:JS9"/>
+    <mergeCell ref="JT7:JT9"/>
+    <mergeCell ref="HP7:HP9"/>
+    <mergeCell ref="HQ7:HQ9"/>
+    <mergeCell ref="HR7:HR9"/>
+    <mergeCell ref="HS7:HS9"/>
+    <mergeCell ref="HN7:HN9"/>
+    <mergeCell ref="HO7:HO9"/>
+    <mergeCell ref="HD7:HD9"/>
+    <mergeCell ref="HE7:HE9"/>
+    <mergeCell ref="HF7:HF9"/>
+    <mergeCell ref="HG7:HG9"/>
+    <mergeCell ref="HT7:HT9"/>
+    <mergeCell ref="HU7:HU9"/>
+    <mergeCell ref="HV7:HV9"/>
+    <mergeCell ref="HW7:HW9"/>
+    <mergeCell ref="HX7:HX9"/>
+    <mergeCell ref="HY7:HY9"/>
+    <mergeCell ref="IH7:IH9"/>
+    <mergeCell ref="II7:II9"/>
+    <mergeCell ref="IJ7:IJ9"/>
+    <mergeCell ref="IB7:IB9"/>
+    <mergeCell ref="IC7:IC9"/>
+    <mergeCell ref="ID7:ID9"/>
+    <mergeCell ref="IE7:IE9"/>
+    <mergeCell ref="HZ7:HZ9"/>
+    <mergeCell ref="IA7:IA9"/>
+    <mergeCell ref="GG7:GG9"/>
+    <mergeCell ref="GH7:GH9"/>
+    <mergeCell ref="GI7:GI9"/>
+    <mergeCell ref="GD7:GD9"/>
+    <mergeCell ref="GE7:GE9"/>
+    <mergeCell ref="FT7:FT9"/>
+    <mergeCell ref="FU7:FU9"/>
+    <mergeCell ref="FV7:FV9"/>
+    <mergeCell ref="FW7:FW9"/>
+    <mergeCell ref="FY7:FY9"/>
+    <mergeCell ref="FZ7:FZ9"/>
+    <mergeCell ref="GA7:GA9"/>
+    <mergeCell ref="GB7:GB9"/>
+    <mergeCell ref="GC7:GC9"/>
+    <mergeCell ref="EV7:EV9"/>
+    <mergeCell ref="EW7:EW9"/>
+    <mergeCell ref="EX7:EX9"/>
+    <mergeCell ref="EY7:EY9"/>
+    <mergeCell ref="ET7:ET9"/>
+    <mergeCell ref="EU7:EU9"/>
+    <mergeCell ref="EJ7:EJ9"/>
+    <mergeCell ref="EK7:EK9"/>
+    <mergeCell ref="EL7:EL9"/>
+    <mergeCell ref="EM7:EM9"/>
+    <mergeCell ref="EN7:EN9"/>
+    <mergeCell ref="EO7:EO9"/>
+    <mergeCell ref="EP7:EP9"/>
+    <mergeCell ref="EQ7:EQ9"/>
+    <mergeCell ref="ER7:ER9"/>
+    <mergeCell ref="ES7:ES9"/>
+    <mergeCell ref="DX7:DX9"/>
+    <mergeCell ref="DY7:DY9"/>
+    <mergeCell ref="DZ7:DZ9"/>
+    <mergeCell ref="EA7:EA9"/>
+    <mergeCell ref="DR7:DR9"/>
+    <mergeCell ref="DS7:DS9"/>
+    <mergeCell ref="DT7:DT9"/>
+    <mergeCell ref="DU7:DU9"/>
+    <mergeCell ref="DL7:DL9"/>
+    <mergeCell ref="DM7:DM9"/>
+    <mergeCell ref="DN7:DN9"/>
+    <mergeCell ref="DO7:DO9"/>
+    <mergeCell ref="DV7:DV9"/>
+    <mergeCell ref="DW7:DW9"/>
+    <mergeCell ref="DJ7:DJ9"/>
+    <mergeCell ref="DK7:DK9"/>
+    <mergeCell ref="CZ7:CZ9"/>
+    <mergeCell ref="DA7:DA9"/>
+    <mergeCell ref="DB7:DB9"/>
+    <mergeCell ref="DC7:DC9"/>
+    <mergeCell ref="CX7:CX9"/>
+    <mergeCell ref="CY7:CY9"/>
+    <mergeCell ref="CN7:CN9"/>
+    <mergeCell ref="CO7:CO9"/>
+    <mergeCell ref="CP7:CP9"/>
+    <mergeCell ref="CQ7:CQ9"/>
+    <mergeCell ref="DD7:DD9"/>
+    <mergeCell ref="DE7:DE9"/>
+    <mergeCell ref="DF7:DF9"/>
+    <mergeCell ref="DG7:DG9"/>
+    <mergeCell ref="DH7:DH9"/>
+    <mergeCell ref="DI7:DI9"/>
+    <mergeCell ref="CR7:CR9"/>
+    <mergeCell ref="CS7:CS9"/>
+    <mergeCell ref="CT7:CT9"/>
+    <mergeCell ref="CU7:CU9"/>
+    <mergeCell ref="CV7:CV9"/>
+    <mergeCell ref="CW7:CW9"/>
+    <mergeCell ref="CL7:CL9"/>
+    <mergeCell ref="CM7:CM9"/>
+    <mergeCell ref="CB7:CB9"/>
+    <mergeCell ref="CC7:CC9"/>
+    <mergeCell ref="CD7:CD9"/>
+    <mergeCell ref="CE7:CE9"/>
+    <mergeCell ref="BV7:BV9"/>
+    <mergeCell ref="BW7:BW9"/>
+    <mergeCell ref="BX7:BX9"/>
+    <mergeCell ref="BY7:BY9"/>
+    <mergeCell ref="BZ7:BZ9"/>
+    <mergeCell ref="CA7:CA9"/>
+    <mergeCell ref="BG7:BG9"/>
+    <mergeCell ref="BB7:BB9"/>
+    <mergeCell ref="BC7:BC9"/>
+    <mergeCell ref="AR7:AR9"/>
+    <mergeCell ref="AS7:AS9"/>
+    <mergeCell ref="AT7:AT9"/>
+    <mergeCell ref="AU7:AU9"/>
+    <mergeCell ref="AV7:AV9"/>
+    <mergeCell ref="AW7:AW9"/>
+    <mergeCell ref="AX7:AX9"/>
+    <mergeCell ref="AY7:AY9"/>
+    <mergeCell ref="AZ7:AZ9"/>
+    <mergeCell ref="BA7:BA9"/>
     <mergeCell ref="V7:V9"/>
     <mergeCell ref="W7:W9"/>
     <mergeCell ref="KL7:KL9"/>
@@ -10412,543 +10949,6 @@
     <mergeCell ref="FS7:FS9"/>
     <mergeCell ref="DP7:DP9"/>
     <mergeCell ref="DQ7:DQ9"/>
-    <mergeCell ref="BG7:BG9"/>
-    <mergeCell ref="BB7:BB9"/>
-    <mergeCell ref="BC7:BC9"/>
-    <mergeCell ref="AR7:AR9"/>
-    <mergeCell ref="AS7:AS9"/>
-    <mergeCell ref="AT7:AT9"/>
-    <mergeCell ref="AU7:AU9"/>
-    <mergeCell ref="AV7:AV9"/>
-    <mergeCell ref="AW7:AW9"/>
-    <mergeCell ref="AX7:AX9"/>
-    <mergeCell ref="AY7:AY9"/>
-    <mergeCell ref="AZ7:AZ9"/>
-    <mergeCell ref="BA7:BA9"/>
-    <mergeCell ref="CL7:CL9"/>
-    <mergeCell ref="CM7:CM9"/>
-    <mergeCell ref="CB7:CB9"/>
-    <mergeCell ref="CC7:CC9"/>
-    <mergeCell ref="CD7:CD9"/>
-    <mergeCell ref="CE7:CE9"/>
-    <mergeCell ref="BV7:BV9"/>
-    <mergeCell ref="BW7:BW9"/>
-    <mergeCell ref="BX7:BX9"/>
-    <mergeCell ref="BY7:BY9"/>
-    <mergeCell ref="BZ7:BZ9"/>
-    <mergeCell ref="CA7:CA9"/>
-    <mergeCell ref="DJ7:DJ9"/>
-    <mergeCell ref="DK7:DK9"/>
-    <mergeCell ref="CZ7:CZ9"/>
-    <mergeCell ref="DA7:DA9"/>
-    <mergeCell ref="DB7:DB9"/>
-    <mergeCell ref="DC7:DC9"/>
-    <mergeCell ref="CX7:CX9"/>
-    <mergeCell ref="CY7:CY9"/>
-    <mergeCell ref="CN7:CN9"/>
-    <mergeCell ref="CO7:CO9"/>
-    <mergeCell ref="CP7:CP9"/>
-    <mergeCell ref="CQ7:CQ9"/>
-    <mergeCell ref="DD7:DD9"/>
-    <mergeCell ref="DE7:DE9"/>
-    <mergeCell ref="DF7:DF9"/>
-    <mergeCell ref="DG7:DG9"/>
-    <mergeCell ref="DH7:DH9"/>
-    <mergeCell ref="DI7:DI9"/>
-    <mergeCell ref="CR7:CR9"/>
-    <mergeCell ref="CS7:CS9"/>
-    <mergeCell ref="CT7:CT9"/>
-    <mergeCell ref="CU7:CU9"/>
-    <mergeCell ref="CV7:CV9"/>
-    <mergeCell ref="CW7:CW9"/>
-    <mergeCell ref="DX7:DX9"/>
-    <mergeCell ref="DY7:DY9"/>
-    <mergeCell ref="DZ7:DZ9"/>
-    <mergeCell ref="EA7:EA9"/>
-    <mergeCell ref="DR7:DR9"/>
-    <mergeCell ref="DS7:DS9"/>
-    <mergeCell ref="DT7:DT9"/>
-    <mergeCell ref="DU7:DU9"/>
-    <mergeCell ref="DL7:DL9"/>
-    <mergeCell ref="DM7:DM9"/>
-    <mergeCell ref="DN7:DN9"/>
-    <mergeCell ref="DO7:DO9"/>
-    <mergeCell ref="DV7:DV9"/>
-    <mergeCell ref="DW7:DW9"/>
-    <mergeCell ref="EV7:EV9"/>
-    <mergeCell ref="EW7:EW9"/>
-    <mergeCell ref="EX7:EX9"/>
-    <mergeCell ref="EY7:EY9"/>
-    <mergeCell ref="ET7:ET9"/>
-    <mergeCell ref="EU7:EU9"/>
-    <mergeCell ref="EJ7:EJ9"/>
-    <mergeCell ref="EK7:EK9"/>
-    <mergeCell ref="EL7:EL9"/>
-    <mergeCell ref="EM7:EM9"/>
-    <mergeCell ref="EN7:EN9"/>
-    <mergeCell ref="EO7:EO9"/>
-    <mergeCell ref="EP7:EP9"/>
-    <mergeCell ref="EQ7:EQ9"/>
-    <mergeCell ref="ER7:ER9"/>
-    <mergeCell ref="ES7:ES9"/>
-    <mergeCell ref="GG7:GG9"/>
-    <mergeCell ref="GH7:GH9"/>
-    <mergeCell ref="GI7:GI9"/>
-    <mergeCell ref="GD7:GD9"/>
-    <mergeCell ref="GE7:GE9"/>
-    <mergeCell ref="FT7:FT9"/>
-    <mergeCell ref="FU7:FU9"/>
-    <mergeCell ref="FV7:FV9"/>
-    <mergeCell ref="FW7:FW9"/>
-    <mergeCell ref="FY7:FY9"/>
-    <mergeCell ref="FZ7:FZ9"/>
-    <mergeCell ref="GA7:GA9"/>
-    <mergeCell ref="GB7:GB9"/>
-    <mergeCell ref="GC7:GC9"/>
-    <mergeCell ref="HT7:HT9"/>
-    <mergeCell ref="HU7:HU9"/>
-    <mergeCell ref="HV7:HV9"/>
-    <mergeCell ref="HW7:HW9"/>
-    <mergeCell ref="HX7:HX9"/>
-    <mergeCell ref="HY7:HY9"/>
-    <mergeCell ref="IH7:IH9"/>
-    <mergeCell ref="II7:II9"/>
-    <mergeCell ref="IJ7:IJ9"/>
-    <mergeCell ref="IB7:IB9"/>
-    <mergeCell ref="IC7:IC9"/>
-    <mergeCell ref="ID7:ID9"/>
-    <mergeCell ref="IE7:IE9"/>
-    <mergeCell ref="HZ7:HZ9"/>
-    <mergeCell ref="IA7:IA9"/>
-    <mergeCell ref="HP7:HP9"/>
-    <mergeCell ref="HQ7:HQ9"/>
-    <mergeCell ref="HR7:HR9"/>
-    <mergeCell ref="HS7:HS9"/>
-    <mergeCell ref="HN7:HN9"/>
-    <mergeCell ref="HO7:HO9"/>
-    <mergeCell ref="HD7:HD9"/>
-    <mergeCell ref="HE7:HE9"/>
-    <mergeCell ref="HF7:HF9"/>
-    <mergeCell ref="HG7:HG9"/>
-    <mergeCell ref="A3:A9"/>
-    <mergeCell ref="B3:B9"/>
-    <mergeCell ref="C3:C9"/>
-    <mergeCell ref="D3:D9"/>
-    <mergeCell ref="F3:F9"/>
-    <mergeCell ref="H3:L5"/>
-    <mergeCell ref="M3:AR3"/>
-    <mergeCell ref="AW3:CF3"/>
-    <mergeCell ref="LY8:LY9"/>
-    <mergeCell ref="LG5:LG9"/>
-    <mergeCell ref="LH5:LH9"/>
-    <mergeCell ref="LI5:LL7"/>
-    <mergeCell ref="LM5:LX5"/>
-    <mergeCell ref="KJ7:KJ9"/>
-    <mergeCell ref="KK7:KK9"/>
-    <mergeCell ref="KH7:KH9"/>
-    <mergeCell ref="KI7:KI9"/>
-    <mergeCell ref="JX7:JX9"/>
-    <mergeCell ref="JY7:JY9"/>
-    <mergeCell ref="JZ7:JZ9"/>
-    <mergeCell ref="KA7:KA9"/>
-    <mergeCell ref="JR7:JR9"/>
-    <mergeCell ref="JS7:JS9"/>
-    <mergeCell ref="JT7:JT9"/>
-    <mergeCell ref="KO3:MJ3"/>
-    <mergeCell ref="MK3:NH3"/>
-    <mergeCell ref="NI3:NZ3"/>
-    <mergeCell ref="OA3:OF6"/>
-    <mergeCell ref="M4:R5"/>
-    <mergeCell ref="S4:X5"/>
-    <mergeCell ref="Y4:AA6"/>
-    <mergeCell ref="AB4:AD6"/>
-    <mergeCell ref="AE4:AM4"/>
-    <mergeCell ref="AN4:AS5"/>
-    <mergeCell ref="CG3:DP3"/>
-    <mergeCell ref="DQ3:EZ3"/>
-    <mergeCell ref="FA3:GJ3"/>
-    <mergeCell ref="GK3:HT3"/>
-    <mergeCell ref="HU3:JD3"/>
-    <mergeCell ref="JE3:KN3"/>
-    <mergeCell ref="HI6:HK6"/>
-    <mergeCell ref="HL6:HN6"/>
-    <mergeCell ref="CS4:CU6"/>
-    <mergeCell ref="CV4:CX6"/>
-    <mergeCell ref="AT4:AV6"/>
-    <mergeCell ref="AW4:BB5"/>
-    <mergeCell ref="BC4:BH5"/>
-    <mergeCell ref="BI4:BK6"/>
-    <mergeCell ref="DH4:DM5"/>
-    <mergeCell ref="DN4:DP6"/>
-    <mergeCell ref="DQ4:DV5"/>
-    <mergeCell ref="DW4:EB5"/>
-    <mergeCell ref="EC4:EE6"/>
-    <mergeCell ref="DE6:DG6"/>
-    <mergeCell ref="DH6:DJ6"/>
-    <mergeCell ref="DK6:DM6"/>
-    <mergeCell ref="DQ6:DS6"/>
-    <mergeCell ref="DT6:DV6"/>
-    <mergeCell ref="DW6:DY6"/>
-    <mergeCell ref="DZ6:EB6"/>
-    <mergeCell ref="GH4:GJ6"/>
-    <mergeCell ref="GK4:GP5"/>
-    <mergeCell ref="GE6:GG6"/>
-    <mergeCell ref="GK6:GM6"/>
-    <mergeCell ref="GN6:GP6"/>
-    <mergeCell ref="EF4:EH6"/>
-    <mergeCell ref="EI4:EQ4"/>
-    <mergeCell ref="ER4:EW5"/>
-    <mergeCell ref="EX4:EZ6"/>
-    <mergeCell ref="FA4:FF5"/>
-    <mergeCell ref="FG4:FL5"/>
-    <mergeCell ref="ER6:ET6"/>
-    <mergeCell ref="EU6:EW6"/>
-    <mergeCell ref="FA6:FC6"/>
-    <mergeCell ref="FD6:FF6"/>
-    <mergeCell ref="FG6:FI6"/>
-    <mergeCell ref="FJ6:FL6"/>
-    <mergeCell ref="FS6:FU6"/>
-    <mergeCell ref="FV6:FX6"/>
-    <mergeCell ref="FY6:GA6"/>
-    <mergeCell ref="GB6:GD6"/>
-    <mergeCell ref="EI6:EK6"/>
-    <mergeCell ref="EL6:EN6"/>
-    <mergeCell ref="EO6:EQ6"/>
-    <mergeCell ref="IG4:II6"/>
-    <mergeCell ref="IJ4:IL6"/>
-    <mergeCell ref="IM4:IU4"/>
-    <mergeCell ref="IV4:JA5"/>
-    <mergeCell ref="IM5:IU5"/>
-    <mergeCell ref="IP6:IR6"/>
-    <mergeCell ref="IS6:IU6"/>
-    <mergeCell ref="IV6:IX6"/>
-    <mergeCell ref="GQ4:GV5"/>
-    <mergeCell ref="GW4:GY6"/>
-    <mergeCell ref="GZ4:HB6"/>
-    <mergeCell ref="HC4:HK4"/>
-    <mergeCell ref="HL4:HQ5"/>
-    <mergeCell ref="HR4:HT6"/>
-    <mergeCell ref="GQ6:GS6"/>
-    <mergeCell ref="GT6:GV6"/>
-    <mergeCell ref="HC6:HE6"/>
-    <mergeCell ref="HF6:HH6"/>
-    <mergeCell ref="AE5:AM5"/>
-    <mergeCell ref="BO5:BW5"/>
-    <mergeCell ref="CY5:DG5"/>
-    <mergeCell ref="EI5:EQ5"/>
-    <mergeCell ref="FS5:GA5"/>
-    <mergeCell ref="HC5:HK5"/>
-    <mergeCell ref="MK4:NH4"/>
-    <mergeCell ref="NI4:NI9"/>
-    <mergeCell ref="NJ4:NJ9"/>
-    <mergeCell ref="MK5:MK9"/>
-    <mergeCell ref="ML5:ML9"/>
-    <mergeCell ref="MM5:MP7"/>
-    <mergeCell ref="MQ5:NH5"/>
-    <mergeCell ref="KF4:KK5"/>
-    <mergeCell ref="KL4:KN6"/>
-    <mergeCell ref="KO4:LF4"/>
-    <mergeCell ref="LG4:LX4"/>
-    <mergeCell ref="LY4:MD5"/>
-    <mergeCell ref="ME4:MJ5"/>
-    <mergeCell ref="KO5:KO9"/>
-    <mergeCell ref="KP5:KP9"/>
-    <mergeCell ref="KQ5:KT7"/>
-    <mergeCell ref="KU5:LF5"/>
-    <mergeCell ref="JB4:JD6"/>
-    <mergeCell ref="S6:U6"/>
-    <mergeCell ref="V6:X6"/>
-    <mergeCell ref="AE6:AG6"/>
-    <mergeCell ref="AH6:AJ6"/>
-    <mergeCell ref="AK6:AM6"/>
-    <mergeCell ref="AN6:AP6"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="G6:G7"/>
-    <mergeCell ref="H6:H9"/>
-    <mergeCell ref="I6:L6"/>
-    <mergeCell ref="M6:O6"/>
-    <mergeCell ref="P6:R6"/>
-    <mergeCell ref="AL7:AL9"/>
-    <mergeCell ref="AM7:AM9"/>
-    <mergeCell ref="AN7:AN9"/>
-    <mergeCell ref="AO7:AO9"/>
-    <mergeCell ref="AF7:AF9"/>
-    <mergeCell ref="AG7:AG9"/>
-    <mergeCell ref="AH7:AH9"/>
-    <mergeCell ref="AI7:AI9"/>
-    <mergeCell ref="AD7:AD9"/>
-    <mergeCell ref="AE7:AE9"/>
-    <mergeCell ref="T7:T9"/>
-    <mergeCell ref="U7:U9"/>
-    <mergeCell ref="CG6:CI6"/>
-    <mergeCell ref="CJ6:CL6"/>
-    <mergeCell ref="CM6:CO6"/>
-    <mergeCell ref="CP6:CR6"/>
-    <mergeCell ref="CY6:DA6"/>
-    <mergeCell ref="DB6:DD6"/>
-    <mergeCell ref="AQ6:AS6"/>
-    <mergeCell ref="AW6:AY6"/>
-    <mergeCell ref="AZ6:BB6"/>
-    <mergeCell ref="BC6:BE6"/>
-    <mergeCell ref="BF6:BH6"/>
-    <mergeCell ref="BO6:BQ6"/>
-    <mergeCell ref="BL4:BN6"/>
-    <mergeCell ref="BO4:BW4"/>
-    <mergeCell ref="BX4:CC5"/>
-    <mergeCell ref="CD4:CF6"/>
-    <mergeCell ref="CG4:CL5"/>
-    <mergeCell ref="CM4:CR5"/>
-    <mergeCell ref="BR6:BT6"/>
-    <mergeCell ref="BU6:BW6"/>
-    <mergeCell ref="BX6:BZ6"/>
-    <mergeCell ref="CA6:CC6"/>
-    <mergeCell ref="CY4:DG4"/>
-    <mergeCell ref="FM4:FO6"/>
-    <mergeCell ref="FP4:FR6"/>
-    <mergeCell ref="FS4:GA4"/>
-    <mergeCell ref="GB4:GG5"/>
-    <mergeCell ref="JH6:JJ6"/>
-    <mergeCell ref="JK6:JM6"/>
-    <mergeCell ref="JN6:JP6"/>
-    <mergeCell ref="JW6:JY6"/>
-    <mergeCell ref="HO6:HQ6"/>
-    <mergeCell ref="HU6:HW6"/>
-    <mergeCell ref="HX6:HZ6"/>
-    <mergeCell ref="IA6:IC6"/>
-    <mergeCell ref="ID6:IF6"/>
-    <mergeCell ref="IM6:IO6"/>
-    <mergeCell ref="JE4:JJ5"/>
-    <mergeCell ref="JK4:JP5"/>
-    <mergeCell ref="JQ4:JS6"/>
-    <mergeCell ref="JT4:JV6"/>
-    <mergeCell ref="JW4:KE4"/>
-    <mergeCell ref="JW5:KE5"/>
-    <mergeCell ref="JZ6:KB6"/>
-    <mergeCell ref="KC6:KE6"/>
-    <mergeCell ref="HU4:HZ5"/>
-    <mergeCell ref="IA4:IF5"/>
-    <mergeCell ref="NC6:NH6"/>
-    <mergeCell ref="I7:I9"/>
-    <mergeCell ref="J7:L7"/>
-    <mergeCell ref="M7:M9"/>
-    <mergeCell ref="N7:N9"/>
-    <mergeCell ref="O7:O9"/>
-    <mergeCell ref="P7:P9"/>
-    <mergeCell ref="Q7:Q9"/>
-    <mergeCell ref="R7:R9"/>
-    <mergeCell ref="S7:S9"/>
-    <mergeCell ref="LY6:LZ7"/>
-    <mergeCell ref="MA6:MD7"/>
-    <mergeCell ref="ME6:MF7"/>
-    <mergeCell ref="MG6:MJ7"/>
-    <mergeCell ref="MQ6:MV6"/>
-    <mergeCell ref="MW6:NB6"/>
-    <mergeCell ref="KF6:KH6"/>
-    <mergeCell ref="KI6:KK6"/>
-    <mergeCell ref="KU6:KZ6"/>
-    <mergeCell ref="LA6:LF6"/>
-    <mergeCell ref="LM6:LR6"/>
-    <mergeCell ref="LS6:LX6"/>
-    <mergeCell ref="IY6:JA6"/>
-    <mergeCell ref="JE6:JG6"/>
-    <mergeCell ref="X7:X9"/>
-    <mergeCell ref="Y7:Y9"/>
-    <mergeCell ref="Z7:Z9"/>
-    <mergeCell ref="AA7:AA9"/>
-    <mergeCell ref="AB7:AB9"/>
-    <mergeCell ref="AC7:AC9"/>
-    <mergeCell ref="AJ7:AJ9"/>
-    <mergeCell ref="AK7:AK9"/>
-    <mergeCell ref="AP7:AP9"/>
-    <mergeCell ref="AQ7:AQ9"/>
-    <mergeCell ref="CF7:CF9"/>
-    <mergeCell ref="CG7:CG9"/>
-    <mergeCell ref="CH7:CH9"/>
-    <mergeCell ref="CI7:CI9"/>
-    <mergeCell ref="CJ7:CJ9"/>
-    <mergeCell ref="CK7:CK9"/>
-    <mergeCell ref="BH7:BH9"/>
-    <mergeCell ref="BI7:BI9"/>
-    <mergeCell ref="BJ7:BJ9"/>
-    <mergeCell ref="BK7:BK9"/>
-    <mergeCell ref="BL7:BL9"/>
-    <mergeCell ref="BM7:BM9"/>
-    <mergeCell ref="BP7:BP9"/>
-    <mergeCell ref="BQ7:BQ9"/>
-    <mergeCell ref="BR7:BR9"/>
-    <mergeCell ref="BS7:BS9"/>
-    <mergeCell ref="BN7:BN9"/>
-    <mergeCell ref="BO7:BO9"/>
-    <mergeCell ref="BT7:BT9"/>
-    <mergeCell ref="BU7:BU9"/>
-    <mergeCell ref="BD7:BD9"/>
-    <mergeCell ref="BE7:BE9"/>
-    <mergeCell ref="BF7:BF9"/>
-    <mergeCell ref="EB7:EB9"/>
-    <mergeCell ref="EC7:EC9"/>
-    <mergeCell ref="ED7:ED9"/>
-    <mergeCell ref="EE7:EE9"/>
-    <mergeCell ref="EF7:EF9"/>
-    <mergeCell ref="EG7:EG9"/>
-    <mergeCell ref="EH7:EH9"/>
-    <mergeCell ref="EI7:EI9"/>
-    <mergeCell ref="FX7:FX9"/>
-    <mergeCell ref="EZ7:EZ9"/>
-    <mergeCell ref="FA7:FA9"/>
-    <mergeCell ref="FB7:FB9"/>
-    <mergeCell ref="FC7:FC9"/>
-    <mergeCell ref="FD7:FD9"/>
-    <mergeCell ref="FE7:FE9"/>
-    <mergeCell ref="FN7:FN9"/>
-    <mergeCell ref="FO7:FO9"/>
-    <mergeCell ref="FP7:FP9"/>
-    <mergeCell ref="FQ7:FQ9"/>
-    <mergeCell ref="FH7:FH9"/>
-    <mergeCell ref="FI7:FI9"/>
-    <mergeCell ref="FJ7:FJ9"/>
-    <mergeCell ref="FK7:FK9"/>
-    <mergeCell ref="FF7:FF9"/>
-    <mergeCell ref="FG7:FG9"/>
-    <mergeCell ref="HH7:HH9"/>
-    <mergeCell ref="HI7:HI9"/>
-    <mergeCell ref="HJ7:HJ9"/>
-    <mergeCell ref="HK7:HK9"/>
-    <mergeCell ref="HL7:HL9"/>
-    <mergeCell ref="HM7:HM9"/>
-    <mergeCell ref="GJ7:GJ9"/>
-    <mergeCell ref="GK7:GK9"/>
-    <mergeCell ref="GL7:GL9"/>
-    <mergeCell ref="GM7:GM9"/>
-    <mergeCell ref="GN7:GN9"/>
-    <mergeCell ref="GO7:GO9"/>
-    <mergeCell ref="GX7:GX9"/>
-    <mergeCell ref="GY7:GY9"/>
-    <mergeCell ref="GZ7:GZ9"/>
-    <mergeCell ref="HA7:HA9"/>
-    <mergeCell ref="GR7:GR9"/>
-    <mergeCell ref="GS7:GS9"/>
-    <mergeCell ref="GT7:GT9"/>
-    <mergeCell ref="GU7:GU9"/>
-    <mergeCell ref="GP7:GP9"/>
-    <mergeCell ref="GQ7:GQ9"/>
-    <mergeCell ref="GF7:GF9"/>
-    <mergeCell ref="IX7:IX9"/>
-    <mergeCell ref="IY7:IY9"/>
-    <mergeCell ref="IN7:IN9"/>
-    <mergeCell ref="IO7:IO9"/>
-    <mergeCell ref="IP7:IP9"/>
-    <mergeCell ref="IQ7:IQ9"/>
-    <mergeCell ref="IR7:IR9"/>
-    <mergeCell ref="IS7:IS9"/>
-    <mergeCell ref="IT7:IT9"/>
-    <mergeCell ref="IU7:IU9"/>
-    <mergeCell ref="IV7:IV9"/>
-    <mergeCell ref="IW7:IW9"/>
-    <mergeCell ref="IK7:IK9"/>
-    <mergeCell ref="KD7:KD9"/>
-    <mergeCell ref="KE7:KE9"/>
-    <mergeCell ref="KF7:KF9"/>
-    <mergeCell ref="KG7:KG9"/>
-    <mergeCell ref="JD7:JD9"/>
-    <mergeCell ref="JE7:JE9"/>
-    <mergeCell ref="JF7:JF9"/>
-    <mergeCell ref="JG7:JG9"/>
-    <mergeCell ref="JH7:JH9"/>
-    <mergeCell ref="JI7:JI9"/>
-    <mergeCell ref="JU7:JU9"/>
-    <mergeCell ref="JL7:JL9"/>
-    <mergeCell ref="JM7:JM9"/>
-    <mergeCell ref="JN7:JN9"/>
-    <mergeCell ref="JO7:JO9"/>
-    <mergeCell ref="JJ7:JJ9"/>
-    <mergeCell ref="JK7:JK9"/>
-    <mergeCell ref="KB7:KB9"/>
-    <mergeCell ref="KC7:KC9"/>
-    <mergeCell ref="IZ7:IZ9"/>
-    <mergeCell ref="JA7:JA9"/>
-    <mergeCell ref="JB7:JB9"/>
-    <mergeCell ref="JC7:JC9"/>
-    <mergeCell ref="OE7:OE8"/>
-    <mergeCell ref="OF7:OF8"/>
-    <mergeCell ref="J8:J9"/>
-    <mergeCell ref="K8:K9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="KQ8:KQ9"/>
-    <mergeCell ref="KR8:KT8"/>
-    <mergeCell ref="NE7:NH7"/>
-    <mergeCell ref="NO7:NP7"/>
-    <mergeCell ref="NQ7:NT7"/>
-    <mergeCell ref="NU7:NV7"/>
-    <mergeCell ref="NW7:NZ7"/>
-    <mergeCell ref="OA7:OA8"/>
-    <mergeCell ref="NK8:NK9"/>
-    <mergeCell ref="NL8:NN8"/>
-    <mergeCell ref="NO8:NO9"/>
-    <mergeCell ref="NP8:NP9"/>
-    <mergeCell ref="LU7:LX7"/>
-    <mergeCell ref="MQ7:MR7"/>
-    <mergeCell ref="MS7:MV7"/>
-    <mergeCell ref="MW7:MX7"/>
-    <mergeCell ref="MY7:NB7"/>
-    <mergeCell ref="NC7:ND7"/>
-    <mergeCell ref="KW7:KZ7"/>
-    <mergeCell ref="KU8:KU9"/>
-    <mergeCell ref="KV8:KV9"/>
-    <mergeCell ref="KW8:KW9"/>
-    <mergeCell ref="KX8:KZ8"/>
-    <mergeCell ref="LA8:LA9"/>
-    <mergeCell ref="LB8:LB9"/>
-    <mergeCell ref="OB7:OB8"/>
-    <mergeCell ref="OC7:OC8"/>
-    <mergeCell ref="OD7:OD8"/>
-    <mergeCell ref="LA7:LB7"/>
-    <mergeCell ref="LC7:LF7"/>
-    <mergeCell ref="LM7:LN7"/>
-    <mergeCell ref="LO7:LR7"/>
-    <mergeCell ref="LS7:LT7"/>
-    <mergeCell ref="NK4:NN7"/>
-    <mergeCell ref="NO4:NT6"/>
-    <mergeCell ref="NU4:NZ6"/>
-    <mergeCell ref="LZ8:LZ9"/>
-    <mergeCell ref="MA8:MA9"/>
-    <mergeCell ref="MB8:MD8"/>
-    <mergeCell ref="LO8:LO9"/>
-    <mergeCell ref="LP8:LR8"/>
-    <mergeCell ref="LS8:LS9"/>
-    <mergeCell ref="LT8:LT9"/>
-    <mergeCell ref="LU8:LU9"/>
-    <mergeCell ref="LV8:LX8"/>
-    <mergeCell ref="LC8:LC9"/>
-    <mergeCell ref="LD8:LF8"/>
-    <mergeCell ref="LI8:LI9"/>
-    <mergeCell ref="LJ8:LL8"/>
-    <mergeCell ref="LM8:LM9"/>
-    <mergeCell ref="LN8:LN9"/>
-    <mergeCell ref="MQ8:MQ9"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="NQ8:NQ9"/>
-    <mergeCell ref="NR8:NT8"/>
-    <mergeCell ref="NU8:NU9"/>
-    <mergeCell ref="NV8:NV9"/>
-    <mergeCell ref="NW8:NW9"/>
-    <mergeCell ref="NX8:NZ8"/>
-    <mergeCell ref="MY8:MY9"/>
-    <mergeCell ref="MZ8:NB8"/>
-    <mergeCell ref="NC8:NC9"/>
-    <mergeCell ref="ND8:ND9"/>
-    <mergeCell ref="NE8:NE9"/>
-    <mergeCell ref="NF8:NH8"/>
-    <mergeCell ref="MR8:MR9"/>
-    <mergeCell ref="MS8:MS9"/>
-    <mergeCell ref="MT8:MV8"/>
-    <mergeCell ref="MW8:MW9"/>
-    <mergeCell ref="MX8:MX9"/>
-    <mergeCell ref="ME8:ME9"/>
-    <mergeCell ref="MF8:MF9"/>
-    <mergeCell ref="MG8:MG9"/>
-    <mergeCell ref="MH8:MJ8"/>
-    <mergeCell ref="MM8:MM9"/>
-    <mergeCell ref="MN8:MP8"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
